--- a/docs/excel/Base de Datos Valpo Verde.xlsx
+++ b/docs/excel/Base de Datos Valpo Verde.xlsx
@@ -24,6 +24,8 @@
     <sheet name="DICCIONARIO_CAMPOS" sheetId="14" r:id="rId9"/>
     <sheet name="MATRICES_CALCULO" sheetId="15" r:id="rId10"/>
     <sheet name="INDICES" sheetId="17" r:id="rId11"/>
+    <sheet name="REGLAS_INDICADORES" sheetId="18" r:id="rId15"/>
+    <sheet name="VERSION" sheetId="19" r:id="rId16"/>
   </sheets>
   <definedNames>
     <definedName name="Descompactación">LISTAS!$I$2:$I$3</definedName>
@@ -4394,6 +4396,281 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:U1"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="22" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
+    <col min="6" max="6" width="8" customWidth="1"/>
+    <col min="7" max="7" width="60" customWidth="1"/>
+    <col min="8" max="8" width="30" customWidth="1"/>
+    <col min="9" max="9" width="22" customWidth="1"/>
+    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="11" max="11" width="14" customWidth="1"/>
+    <col min="12" max="12" width="12" customWidth="1"/>
+    <col min="13" max="13" width="9" customWidth="1"/>
+    <col min="14" max="14" width="13" customWidth="1"/>
+    <col min="15" max="15" width="12" customWidth="1"/>
+    <col min="16" max="16" width="12" customWidth="1"/>
+    <col min="17" max="17" width="14" customWidth="1"/>
+    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="19" max="19" width="30" customWidth="1"/>
+    <col min="20" max="20" width="24" customWidth="1"/>
+    <col min="21" max="21" width="40" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">id_regla</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">componente</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">codigo_indicador</t>
+        </is>
+      </c>
+      <c r="D1" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">indicador</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tipo_regla</t>
+        </is>
+      </c>
+      <c r="F1" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">orden</t>
+        </is>
+      </c>
+      <c r="G1" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">condicion</t>
+        </is>
+      </c>
+      <c r="H1" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">campos_utilizados</t>
+        </is>
+      </c>
+      <c r="I1" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">resultado</t>
+        </is>
+      </c>
+      <c r="J1" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">puntaje</t>
+        </is>
+      </c>
+      <c r="K1" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">regla_agregadora</t>
+        </is>
+      </c>
+      <c r="L1" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">max_indicador</t>
+        </is>
+      </c>
+      <c r="M1" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">residual</t>
+        </is>
+      </c>
+      <c r="N1" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estado_regla</t>
+        </is>
+      </c>
+      <c r="O1" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">version_desde</t>
+        </is>
+      </c>
+      <c r="P1" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">version_hasta</t>
+        </is>
+      </c>
+      <c r="Q1" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reemplazada_por</t>
+        </is>
+      </c>
+      <c r="R1" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cc</t>
+        </is>
+      </c>
+      <c r="S1" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fundamento_fuente</t>
+        </is>
+      </c>
+      <c r="T1" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">diagrama_ref</t>
+        </is>
+      </c>
+      <c r="U1" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">observaciones</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="9">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B2:B5000">
+      <formula1>"Raíces y cuello,Tronco,Copa y ramas,Infraestructura"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E2:E5000">
+      <formula1>"clasificación,ajuste,aplicabilidad"</formula1>
+    </dataValidation>
+    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" sqref="F2:F5000">
+      <formula1>1</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I2:I5000">
+      <formula1>"Despreciable,Sin afectación,Leve,Moderada,Severa,No determinado,No aplica,Mantener clasificación,Mínimo Moderada"</formula1>
+    </dataValidation>
+    <dataValidation type="whole" allowBlank="1" showErrorMessage="1" sqref="J2:J5000">
+      <formula1>0</formula1>
+      <formula2>3</formula2>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="K2:K5000">
+      <formula1>"R01,R02,R03,M04,ninguna"</formula1>
+    </dataValidation>
+    <dataValidation type="whole" allowBlank="1" showErrorMessage="1" sqref="L2:L5000">
+      <formula1>0</formula1>
+      <formula2>3</formula2>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="M2:M5000">
+      <formula1>"Sí,No"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="N2:N5000">
+      <formula1>"vigente,pendiente,reemplazada,descartada"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:J2"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="2" max="2" width="13" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="17" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="6" max="6" width="15" customWidth="1"/>
+    <col min="7" max="7" width="17" customWidth="1"/>
+    <col min="8" max="8" width="24" customWidth="1"/>
+    <col min="9" max="9" width="16" customWidth="1"/>
+    <col min="10" max="10" width="80" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">version_paquete</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rule_version</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estado</t>
+        </is>
+      </c>
+      <c r="D1" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fecha_publicacion</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cc_incluidos</t>
+        </is>
+      </c>
+      <c r="F1" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">aprobado_por</t>
+        </is>
+      </c>
+      <c r="G1" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fecha_aprobacion</t>
+        </is>
+      </c>
+      <c r="H1" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tag_git</t>
+        </is>
+      </c>
+      <c r="I1" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">version_anterior</t>
+        </is>
+      </c>
+      <c r="J1" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">observaciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">previa a 2.0.0</t>
+        </is>
+      </c>
+      <c r="C2" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sin versión formal</t>
+        </is>
+      </c>
+      <c r="E2" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CC-002</t>
+        </is>
+      </c>
+      <c r="J2" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Excel maestro sin versión formal (contenido subido el 2026-10-04, commit 24e8cae). NO constituye el paquete metodológico 2.0.0 ni una versión publicada y no define rule_version. Contiene inconsistencias internas detectadas en la auditoría de diagramas (p. ej. rangos de R02 y R03 distintos entre MATRICES_CALCULO y DICCIONARIO_CAMPOS). Las hojas REGLAS_INDICADORES y VERSION fueron agregadas por CC-002, sin reglas cargadas.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C2:C1000">
+      <formula1>"en preparación,publicada,reemplazada,sin versión formal"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F2:F1000">
+      <formula1>"marybaxmann,Valen-j211"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:DX1"/>

--- a/docs/excel/Base de Datos Valpo Verde.xlsx
+++ b/docs/excel/Base de Datos Valpo Verde.xlsx
@@ -4569,7 +4569,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -4655,6 +4655,33 @@
       <c r="J2" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">Excel maestro sin versión formal (contenido subido el 2026-10-04, commit 24e8cae). NO constituye el paquete metodológico 2.0.0 ni una versión publicada y no define rule_version. Contiene inconsistencias internas detectadas en la auditoría de diagramas (p. ej. rangos de R02 y R03 distintos entre MATRICES_CALCULO y DICCIONARIO_CAMPOS). Las hojas REGLAS_INDICADORES y VERSION fueron agregadas por CC-002, sin reglas cargadas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.0.0</t>
+        </is>
+      </c>
+      <c r="C3" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">en preparación</t>
+        </is>
+      </c>
+      <c r="E3" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CC-004</t>
+        </is>
+      </c>
+      <c r="I3" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">previa a 2.0.0</t>
+        </is>
+      </c>
+      <c r="J3" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Paquete metodológico en construcción. NO publicado; no define rule_version. Acumula los CC aprobados que se incorporen al paquete 2.0.0. CC-004 no publica la metodología 2.0.0.</t>
         </is>
       </c>
     </row>
@@ -5772,14 +5799,21 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:X71"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="8.88671875" customWidth="1"/>
+    <col min="16" max="16" width="34" customWidth="1"/>
+    <col min="17" max="17" width="32" customWidth="1"/>
+    <col min="18" max="18" width="40" customWidth="1"/>
+    <col min="19" max="19" width="8" customWidth="1"/>
+    <col min="20" max="21" width="22" customWidth="1"/>
+    <col min="22" max="23" width="12" customWidth="1"/>
+    <col min="24" max="24" width="80" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>171</v>
       </c>
@@ -5822,8 +5856,53 @@
       <c r="N1" t="s">
         <v>209</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="P1" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">id_catalogo</t>
+        </is>
+      </c>
+      <c r="Q1" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">codigo</t>
+        </is>
+      </c>
+      <c r="R1" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">etiqueta</t>
+        </is>
+      </c>
+      <c r="S1" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">orden</t>
+        </is>
+      </c>
+      <c r="T1" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">catalogo_padre</t>
+        </is>
+      </c>
+      <c r="U1" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">codigo_padre</t>
+        </is>
+      </c>
+      <c r="V1" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estado_valor</t>
+        </is>
+      </c>
+      <c r="W1" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cc</t>
+        </is>
+      </c>
+      <c r="X1" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">observaciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>133</v>
       </c>
@@ -5860,8 +5939,33 @@
       <c r="N2" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="P2" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tipo_ot</t>
+        </is>
+      </c>
+      <c r="Q2" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inspeccion</t>
+        </is>
+      </c>
+      <c r="R2" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Inspección</t>
+        </is>
+      </c>
+      <c r="V2" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vigente</t>
+        </is>
+      </c>
+      <c r="W2" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CC-004</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>200</v>
       </c>
@@ -5898,8 +6002,33 @@
       <c r="N3" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="P3" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tipo_ot</t>
+        </is>
+      </c>
+      <c r="Q3" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mantenimiento</t>
+        </is>
+      </c>
+      <c r="R3" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mantenimiento</t>
+        </is>
+      </c>
+      <c r="V3" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vigente</t>
+        </is>
+      </c>
+      <c r="W3" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CC-004</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>178</v>
       </c>
@@ -5924,8 +6053,43 @@
       <c r="N4" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="P4" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">accion</t>
+        </is>
+      </c>
+      <c r="Q4" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">evaluacion_inicial</t>
+        </is>
+      </c>
+      <c r="R4" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Evaluación inicial</t>
+        </is>
+      </c>
+      <c r="T4" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tipo_ot</t>
+        </is>
+      </c>
+      <c r="U4" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inspeccion</t>
+        </is>
+      </c>
+      <c r="V4" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vigente</t>
+        </is>
+      </c>
+      <c r="W4" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CC-004</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>202</v>
       </c>
@@ -5941,8 +6105,43 @@
       <c r="N5" t="s">
         <v>235</v>
       </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="P5" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">accion</t>
+        </is>
+      </c>
+      <c r="Q5" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reevaluacion</t>
+        </is>
+      </c>
+      <c r="R5" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reevaluación</t>
+        </is>
+      </c>
+      <c r="T5" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tipo_ot</t>
+        </is>
+      </c>
+      <c r="U5" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inspeccion</t>
+        </is>
+      </c>
+      <c r="V5" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vigente</t>
+        </is>
+      </c>
+      <c r="W5" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CC-004</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>206</v>
       </c>
@@ -5952,29 +6151,2384 @@
       <c r="N6" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="P6" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">accion</t>
+        </is>
+      </c>
+      <c r="Q6" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">evaluacion_instrumental</t>
+        </is>
+      </c>
+      <c r="R6" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Evaluación instrumental</t>
+        </is>
+      </c>
+      <c r="T6" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tipo_ot</t>
+        </is>
+      </c>
+      <c r="U6" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inspeccion</t>
+        </is>
+      </c>
+      <c r="V6" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vigente</t>
+        </is>
+      </c>
+      <c r="W6" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CC-004</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>238</v>
       </c>
       <c r="M7" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="P7" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">accion</t>
+        </is>
+      </c>
+      <c r="Q7" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">monitoreo</t>
+        </is>
+      </c>
+      <c r="R7" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Monitoreo</t>
+        </is>
+      </c>
+      <c r="T7" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tipo_ot</t>
+        </is>
+      </c>
+      <c r="U7" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inspeccion</t>
+        </is>
+      </c>
+      <c r="V7" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vigente</t>
+        </is>
+      </c>
+      <c r="W7" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CC-004</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>240</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="P8" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">accion</t>
+        </is>
+      </c>
+      <c r="Q8" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">poda</t>
+        </is>
+      </c>
+      <c r="R8" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Poda</t>
+        </is>
+      </c>
+      <c r="T8" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tipo_ot</t>
+        </is>
+      </c>
+      <c r="U8" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mantenimiento</t>
+        </is>
+      </c>
+      <c r="V8" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vigente</t>
+        </is>
+      </c>
+      <c r="W8" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CC-004</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>207</v>
+      </c>
+      <c r="P9" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">accion</t>
+        </is>
+      </c>
+      <c r="Q9" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">riego</t>
+        </is>
+      </c>
+      <c r="R9" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Riego</t>
+        </is>
+      </c>
+      <c r="T9" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tipo_ot</t>
+        </is>
+      </c>
+      <c r="U9" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mantenimiento</t>
+        </is>
+      </c>
+      <c r="V9" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vigente</t>
+        </is>
+      </c>
+      <c r="W9" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CC-004</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="P10" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">accion</t>
+        </is>
+      </c>
+      <c r="Q10" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">descompactacion</t>
+        </is>
+      </c>
+      <c r="R10" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Descompactación</t>
+        </is>
+      </c>
+      <c r="T10" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tipo_ot</t>
+        </is>
+      </c>
+      <c r="U10" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mantenimiento</t>
+        </is>
+      </c>
+      <c r="V10" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vigente</t>
+        </is>
+      </c>
+      <c r="W10" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CC-004</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BLOQUE TÉCNICO A1:N9 — derivado para los menús actuales del Excel. No editar. No es fuente de valores. La fuente es la tabla P:X. Será regenerado y retirado por CC-012.</t>
+        </is>
+      </c>
+      <c r="P11" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">accion</t>
+        </is>
+      </c>
+      <c r="Q11" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">manejo_fitosanitario</t>
+        </is>
+      </c>
+      <c r="R11" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manejo fitosanitario</t>
+        </is>
+      </c>
+      <c r="T11" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tipo_ot</t>
+        </is>
+      </c>
+      <c r="U11" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mantenimiento</t>
+        </is>
+      </c>
+      <c r="V11" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vigente</t>
+        </is>
+      </c>
+      <c r="W11" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CC-004</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="P12" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">accion</t>
+        </is>
+      </c>
+      <c r="Q12" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tala_retiro</t>
+        </is>
+      </c>
+      <c r="R12" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tala / retiro</t>
+        </is>
+      </c>
+      <c r="T12" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tipo_ot</t>
+        </is>
+      </c>
+      <c r="U12" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mantenimiento</t>
+        </is>
+      </c>
+      <c r="V12" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vigente</t>
+        </is>
+      </c>
+      <c r="W12" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CC-004</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="P13" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">accion</t>
+        </is>
+      </c>
+      <c r="Q13" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reparacion_alcorque</t>
+        </is>
+      </c>
+      <c r="R13" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reparación de alcorque</t>
+        </is>
+      </c>
+      <c r="T13" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tipo_ot</t>
+        </is>
+      </c>
+      <c r="U13" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mantenimiento</t>
+        </is>
+      </c>
+      <c r="V13" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vigente</t>
+        </is>
+      </c>
+      <c r="W13" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CC-004</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="P14" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">accion</t>
+        </is>
+      </c>
+      <c r="Q14" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">soporte_tutorado</t>
+        </is>
+      </c>
+      <c r="R14" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Soporte / tutorado</t>
+        </is>
+      </c>
+      <c r="T14" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tipo_ot</t>
+        </is>
+      </c>
+      <c r="U14" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mantenimiento</t>
+        </is>
+      </c>
+      <c r="V14" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vigente</t>
+        </is>
+      </c>
+      <c r="W14" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CC-004</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="P15" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">accion</t>
+        </is>
+      </c>
+      <c r="Q15" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">otra_intervencion</t>
+        </is>
+      </c>
+      <c r="R15" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Otra intervención</t>
+        </is>
+      </c>
+      <c r="T15" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tipo_ot</t>
+        </is>
+      </c>
+      <c r="U15" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mantenimiento</t>
+        </is>
+      </c>
+      <c r="V15" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vigente</t>
+        </is>
+      </c>
+      <c r="W15" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CC-004</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="P16" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">subtipo_accion</t>
+        </is>
+      </c>
+      <c r="Q16" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">seguimiento</t>
+        </is>
+      </c>
+      <c r="R16" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Seguimiento</t>
+        </is>
+      </c>
+      <c r="T16" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">accion</t>
+        </is>
+      </c>
+      <c r="U16" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reevaluacion</t>
+        </is>
+      </c>
+      <c r="V16" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vigente</t>
+        </is>
+      </c>
+      <c r="W16" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CC-004</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="P17" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">subtipo_accion</t>
+        </is>
+      </c>
+      <c r="Q17" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">post_intervencion</t>
+        </is>
+      </c>
+      <c r="R17" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Post intervención</t>
+        </is>
+      </c>
+      <c r="T17" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">accion</t>
+        </is>
+      </c>
+      <c r="U17" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reevaluacion</t>
+        </is>
+      </c>
+      <c r="V17" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vigente</t>
+        </is>
+      </c>
+      <c r="W17" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CC-004</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="P18" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">subtipo_accion</t>
+        </is>
+      </c>
+      <c r="Q18" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tomografia_sonica</t>
+        </is>
+      </c>
+      <c r="R18" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tomografía sónica</t>
+        </is>
+      </c>
+      <c r="T18" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">accion</t>
+        </is>
+      </c>
+      <c r="U18" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">evaluacion_instrumental</t>
+        </is>
+      </c>
+      <c r="V18" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vigente</t>
+        </is>
+      </c>
+      <c r="W18" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CC-004</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="P19" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">subtipo_accion</t>
+        </is>
+      </c>
+      <c r="Q19" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">resistografia</t>
+        </is>
+      </c>
+      <c r="R19" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Resistografía</t>
+        </is>
+      </c>
+      <c r="T19" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">accion</t>
+        </is>
+      </c>
+      <c r="U19" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">evaluacion_instrumental</t>
+        </is>
+      </c>
+      <c r="V19" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vigente</t>
+        </is>
+      </c>
+      <c r="W19" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CC-004</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="P20" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">subtipo_accion</t>
+        </is>
+      </c>
+      <c r="Q20" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">otra</t>
+        </is>
+      </c>
+      <c r="R20" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Otra</t>
+        </is>
+      </c>
+      <c r="T20" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">accion</t>
+        </is>
+      </c>
+      <c r="U20" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">evaluacion_instrumental</t>
+        </is>
+      </c>
+      <c r="V20" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vigente</t>
+        </is>
+      </c>
+      <c r="W20" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CC-004</t>
+        </is>
+      </c>
+      <c r="X20" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Requiere especificar en observaciones (obligatorio).</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="P21" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">subtipo_accion</t>
+        </is>
+      </c>
+      <c r="Q21" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fitosanitario</t>
+        </is>
+      </c>
+      <c r="R21" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fitosanitario</t>
+        </is>
+      </c>
+      <c r="T21" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">accion</t>
+        </is>
+      </c>
+      <c r="U21" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">monitoreo</t>
+        </is>
+      </c>
+      <c r="V21" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vigente</t>
+        </is>
+      </c>
+      <c r="W21" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CC-004</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="P22" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">subtipo_accion</t>
+        </is>
+      </c>
+      <c r="Q22" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estructural</t>
+        </is>
+      </c>
+      <c r="R22" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Estructural</t>
+        </is>
+      </c>
+      <c r="T22" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">accion</t>
+        </is>
+      </c>
+      <c r="U22" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">monitoreo</t>
+        </is>
+      </c>
+      <c r="V22" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vigente</t>
+        </is>
+      </c>
+      <c r="W22" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CC-004</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="P23" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">subtipo_accion</t>
+        </is>
+      </c>
+      <c r="Q23" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vitalidad</t>
+        </is>
+      </c>
+      <c r="R23" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vitalidad</t>
+        </is>
+      </c>
+      <c r="T23" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">accion</t>
+        </is>
+      </c>
+      <c r="U23" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">monitoreo</t>
+        </is>
+      </c>
+      <c r="V23" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vigente</t>
+        </is>
+      </c>
+      <c r="W23" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CC-004</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="P24" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">subtipo_accion</t>
+        </is>
+      </c>
+      <c r="Q24" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sanitaria</t>
+        </is>
+      </c>
+      <c r="R24" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sanitaria</t>
+        </is>
+      </c>
+      <c r="T24" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">accion</t>
+        </is>
+      </c>
+      <c r="U24" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">poda</t>
+        </is>
+      </c>
+      <c r="V24" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vigente</t>
+        </is>
+      </c>
+      <c r="W24" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CC-004</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="P25" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">subtipo_accion</t>
+        </is>
+      </c>
+      <c r="Q25" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">formacion</t>
+        </is>
+      </c>
+      <c r="R25" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Formación</t>
+        </is>
+      </c>
+      <c r="T25" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">accion</t>
+        </is>
+      </c>
+      <c r="U25" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">poda</t>
+        </is>
+      </c>
+      <c r="V25" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vigente</t>
+        </is>
+      </c>
+      <c r="W25" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CC-004</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="P26" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">subtipo_accion</t>
+        </is>
+      </c>
+      <c r="Q26" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">despeje</t>
+        </is>
+      </c>
+      <c r="R26" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Despeje</t>
+        </is>
+      </c>
+      <c r="T26" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">accion</t>
+        </is>
+      </c>
+      <c r="U26" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">poda</t>
+        </is>
+      </c>
+      <c r="V26" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vigente</t>
+        </is>
+      </c>
+      <c r="W26" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CC-004</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="P27" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">subtipo_accion</t>
+        </is>
+      </c>
+      <c r="Q27" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reduccion</t>
+        </is>
+      </c>
+      <c r="R27" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reducción</t>
+        </is>
+      </c>
+      <c r="T27" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">accion</t>
+        </is>
+      </c>
+      <c r="U27" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">poda</t>
+        </is>
+      </c>
+      <c r="V27" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vigente</t>
+        </is>
+      </c>
+      <c r="W27" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CC-004</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="P28" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">subtipo_accion</t>
+        </is>
+      </c>
+      <c r="Q28" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">programado</t>
+        </is>
+      </c>
+      <c r="R28" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Programado</t>
+        </is>
+      </c>
+      <c r="T28" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">accion</t>
+        </is>
+      </c>
+      <c r="U28" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">riego</t>
+        </is>
+      </c>
+      <c r="V28" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vigente</t>
+        </is>
+      </c>
+      <c r="W28" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CC-004</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="P29" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">subtipo_accion</t>
+        </is>
+      </c>
+      <c r="Q29" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">emergencia</t>
+        </is>
+      </c>
+      <c r="R29" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Emergencia</t>
+        </is>
+      </c>
+      <c r="T29" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">accion</t>
+        </is>
+      </c>
+      <c r="U29" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">riego</t>
+        </is>
+      </c>
+      <c r="V29" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vigente</t>
+        </is>
+      </c>
+      <c r="W29" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CC-004</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="P30" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">subtipo_accion</t>
+        </is>
+      </c>
+      <c r="Q30" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">manual</t>
+        </is>
+      </c>
+      <c r="R30" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="T30" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">accion</t>
+        </is>
+      </c>
+      <c r="U30" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">descompactacion</t>
+        </is>
+      </c>
+      <c r="V30" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vigente</t>
+        </is>
+      </c>
+      <c r="W30" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CC-004</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="P31" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">subtipo_accion</t>
+        </is>
+      </c>
+      <c r="Q31" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mecanica</t>
+        </is>
+      </c>
+      <c r="R31" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mecánica</t>
+        </is>
+      </c>
+      <c r="T31" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">accion</t>
+        </is>
+      </c>
+      <c r="U31" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">descompactacion</t>
+        </is>
+      </c>
+      <c r="V31" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vigente</t>
+        </is>
+      </c>
+      <c r="W31" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CC-004</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="P32" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">subtipo_accion</t>
+        </is>
+      </c>
+      <c r="Q32" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">preventivo</t>
+        </is>
+      </c>
+      <c r="R32" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventivo</t>
+        </is>
+      </c>
+      <c r="T32" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">accion</t>
+        </is>
+      </c>
+      <c r="U32" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">manejo_fitosanitario</t>
+        </is>
+      </c>
+      <c r="V32" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vigente</t>
+        </is>
+      </c>
+      <c r="W32" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CC-004</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="P33" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">subtipo_accion</t>
+        </is>
+      </c>
+      <c r="Q33" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">correctivo</t>
+        </is>
+      </c>
+      <c r="R33" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Correctivo</t>
+        </is>
+      </c>
+      <c r="T33" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">accion</t>
+        </is>
+      </c>
+      <c r="U33" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">manejo_fitosanitario</t>
+        </is>
+      </c>
+      <c r="V33" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vigente</t>
+        </is>
+      </c>
+      <c r="W33" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CC-004</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="P34" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">subtipo_accion</t>
+        </is>
+      </c>
+      <c r="Q34" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tala</t>
+        </is>
+      </c>
+      <c r="R34" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tala</t>
+        </is>
+      </c>
+      <c r="T34" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">accion</t>
+        </is>
+      </c>
+      <c r="U34" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tala_retiro</t>
+        </is>
+      </c>
+      <c r="V34" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vigente</t>
+        </is>
+      </c>
+      <c r="W34" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CC-004</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="P35" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">subtipo_accion</t>
+        </is>
+      </c>
+      <c r="Q35" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">retiro_tocon</t>
+        </is>
+      </c>
+      <c r="R35" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Retiro de tocón</t>
+        </is>
+      </c>
+      <c r="T35" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">accion</t>
+        </is>
+      </c>
+      <c r="U35" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tala_retiro</t>
+        </is>
+      </c>
+      <c r="V35" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vigente</t>
+        </is>
+      </c>
+      <c r="W35" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CC-004</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="P36" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">subtipo_accion</t>
+        </is>
+      </c>
+      <c r="Q36" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">retiro_residuos</t>
+        </is>
+      </c>
+      <c r="R36" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Retiro de residuos</t>
+        </is>
+      </c>
+      <c r="T36" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">accion</t>
+        </is>
+      </c>
+      <c r="U36" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tala_retiro</t>
+        </is>
+      </c>
+      <c r="V36" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vigente</t>
+        </is>
+      </c>
+      <c r="W36" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CC-004</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="P37" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">confirmacion_cavidad_interna</t>
+        </is>
+      </c>
+      <c r="Q37" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">si</t>
+        </is>
+      </c>
+      <c r="R37" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sí</t>
+        </is>
+      </c>
+      <c r="V37" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vigente</t>
+        </is>
+      </c>
+      <c r="W37" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CC-004</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="P38" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">confirmacion_cavidad_interna</t>
+        </is>
+      </c>
+      <c r="Q38" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">no</t>
+        </is>
+      </c>
+      <c r="R38" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="V38" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vigente</t>
+        </is>
+      </c>
+      <c r="W38" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CC-004</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="P39" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">confirmacion_cavidad_interna</t>
+        </is>
+      </c>
+      <c r="Q39" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">requiere_evaluacion_instrumental</t>
+        </is>
+      </c>
+      <c r="R39" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Requiere evaluación instrumental</t>
+        </is>
+      </c>
+      <c r="V39" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vigente</t>
+        </is>
+      </c>
+      <c r="W39" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CC-004</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="P40" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">escala_probabilidad_falla</t>
+        </is>
+      </c>
+      <c r="Q40" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">improbable</t>
+        </is>
+      </c>
+      <c r="R40" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Improbable</t>
+        </is>
+      </c>
+      <c r="S40" s="13">
+        <v>1</v>
+      </c>
+      <c r="V40" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vigente</t>
+        </is>
+      </c>
+      <c r="W40" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CC-004</t>
+        </is>
+      </c>
+      <c r="X40" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Representación. Autoridad: R01–R03 (resultado); M02 (entrada). LISTAS no define la lógica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="P41" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">escala_probabilidad_falla</t>
+        </is>
+      </c>
+      <c r="Q41" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">posible</t>
+        </is>
+      </c>
+      <c r="R41" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Posible</t>
+        </is>
+      </c>
+      <c r="S41" s="13">
+        <v>2</v>
+      </c>
+      <c r="V41" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vigente</t>
+        </is>
+      </c>
+      <c r="W41" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CC-004</t>
+        </is>
+      </c>
+      <c r="X41" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Representación. Autoridad: R01–R03 (resultado); M02 (entrada). LISTAS no define la lógica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="P42" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">escala_probabilidad_falla</t>
+        </is>
+      </c>
+      <c r="Q42" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">probable</t>
+        </is>
+      </c>
+      <c r="R42" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Probable</t>
+        </is>
+      </c>
+      <c r="S42" s="13">
+        <v>3</v>
+      </c>
+      <c r="V42" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vigente</t>
+        </is>
+      </c>
+      <c r="W42" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CC-004</t>
+        </is>
+      </c>
+      <c r="X42" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Representación. Autoridad: R01–R03 (resultado); M02 (entrada). LISTAS no define la lógica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="P43" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">escala_probabilidad_falla</t>
+        </is>
+      </c>
+      <c r="Q43" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inminente</t>
+        </is>
+      </c>
+      <c r="R43" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Inminente</t>
+        </is>
+      </c>
+      <c r="S43" s="13">
+        <v>4</v>
+      </c>
+      <c r="V43" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vigente</t>
+        </is>
+      </c>
+      <c r="W43" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CC-004</t>
+        </is>
+      </c>
+      <c r="X43" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Representación. Autoridad: R01–R03 (resultado); M02 (entrada). LISTAS no define la lógica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="P44" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">escala_nivel_riesgo</t>
+        </is>
+      </c>
+      <c r="Q44" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bajo</t>
+        </is>
+      </c>
+      <c r="R44" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bajo</t>
+        </is>
+      </c>
+      <c r="S44" s="13">
+        <v>1</v>
+      </c>
+      <c r="V44" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vigente</t>
+        </is>
+      </c>
+      <c r="W44" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CC-004</t>
+        </is>
+      </c>
+      <c r="X44" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Representación. Autoridad: M03 (resultado); R04; M05 (entrada). LISTAS no define la lógica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="P45" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">escala_nivel_riesgo</t>
+        </is>
+      </c>
+      <c r="Q45" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">moderado</t>
+        </is>
+      </c>
+      <c r="R45" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Moderado</t>
+        </is>
+      </c>
+      <c r="S45" s="13">
+        <v>2</v>
+      </c>
+      <c r="V45" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vigente</t>
+        </is>
+      </c>
+      <c r="W45" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CC-004</t>
+        </is>
+      </c>
+      <c r="X45" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Representación. Autoridad: M03 (resultado); R04; M05 (entrada). LISTAS no define la lógica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="P46" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">escala_nivel_riesgo</t>
+        </is>
+      </c>
+      <c r="Q46" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">alto</t>
+        </is>
+      </c>
+      <c r="R46" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alto</t>
+        </is>
+      </c>
+      <c r="S46" s="13">
+        <v>3</v>
+      </c>
+      <c r="V46" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vigente</t>
+        </is>
+      </c>
+      <c r="W46" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CC-004</t>
+        </is>
+      </c>
+      <c r="X46" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Representación. Autoridad: M03 (resultado); R04; M05 (entrada). LISTAS no define la lógica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="P47" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">escala_nivel_riesgo</t>
+        </is>
+      </c>
+      <c r="Q47" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">extremo</t>
+        </is>
+      </c>
+      <c r="R47" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Extremo</t>
+        </is>
+      </c>
+      <c r="S47" s="13">
+        <v>4</v>
+      </c>
+      <c r="V47" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vigente</t>
+        </is>
+      </c>
+      <c r="W47" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CC-004</t>
+        </is>
+      </c>
+      <c r="X47" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Representación. Autoridad: M03 (resultado); R04; M05 (entrada). LISTAS no define la lógica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="P48" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">escala_consecuencia</t>
+        </is>
+      </c>
+      <c r="Q48" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">despreciable</t>
+        </is>
+      </c>
+      <c r="R48" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Despreciable</t>
+        </is>
+      </c>
+      <c r="S48" s="13">
+        <v>1</v>
+      </c>
+      <c r="V48" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vigente</t>
+        </is>
+      </c>
+      <c r="W48" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CC-004</t>
+        </is>
+      </c>
+      <c r="X48" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Representación. Autoridad: M03 (entrada). LISTAS no define la lógica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="P49" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">escala_consecuencia</t>
+        </is>
+      </c>
+      <c r="Q49" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">menor</t>
+        </is>
+      </c>
+      <c r="R49" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Menor</t>
+        </is>
+      </c>
+      <c r="S49" s="13">
+        <v>2</v>
+      </c>
+      <c r="V49" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vigente</t>
+        </is>
+      </c>
+      <c r="W49" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CC-004</t>
+        </is>
+      </c>
+      <c r="X49" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Representación. Autoridad: M03 (entrada). LISTAS no define la lógica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="P50" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">escala_consecuencia</t>
+        </is>
+      </c>
+      <c r="Q50" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">significativa</t>
+        </is>
+      </c>
+      <c r="R50" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Significativa</t>
+        </is>
+      </c>
+      <c r="S50" s="13">
+        <v>3</v>
+      </c>
+      <c r="V50" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vigente</t>
+        </is>
+      </c>
+      <c r="W50" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CC-004</t>
+        </is>
+      </c>
+      <c r="X50" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Representación. Autoridad: M03 (entrada). LISTAS no define la lógica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="P51" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">escala_consecuencia</t>
+        </is>
+      </c>
+      <c r="Q51" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">severa</t>
+        </is>
+      </c>
+      <c r="R51" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Severa</t>
+        </is>
+      </c>
+      <c r="S51" s="13">
+        <v>4</v>
+      </c>
+      <c r="V51" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vigente</t>
+        </is>
+      </c>
+      <c r="W51" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CC-004</t>
+        </is>
+      </c>
+      <c r="X51" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Representación. Autoridad: M03 (entrada). LISTAS no define la lógica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="P52" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">escala_probabilidad_impacto</t>
+        </is>
+      </c>
+      <c r="Q52" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">muy_baja</t>
+        </is>
+      </c>
+      <c r="R52" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Muy baja</t>
+        </is>
+      </c>
+      <c r="S52" s="13">
+        <v>1</v>
+      </c>
+      <c r="V52" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vigente</t>
+        </is>
+      </c>
+      <c r="W52" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CC-004</t>
+        </is>
+      </c>
+      <c r="X52" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Representación. Autoridad: M01 (resultado); M02 (entrada). LISTAS no define la lógica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="P53" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">escala_probabilidad_impacto</t>
+        </is>
+      </c>
+      <c r="Q53" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">baja</t>
+        </is>
+      </c>
+      <c r="R53" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Baja</t>
+        </is>
+      </c>
+      <c r="S53" s="13">
+        <v>2</v>
+      </c>
+      <c r="V53" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vigente</t>
+        </is>
+      </c>
+      <c r="W53" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CC-004</t>
+        </is>
+      </c>
+      <c r="X53" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Representación. Autoridad: M01 (resultado); M02 (entrada). LISTAS no define la lógica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="P54" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">escala_probabilidad_impacto</t>
+        </is>
+      </c>
+      <c r="Q54" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">media</t>
+        </is>
+      </c>
+      <c r="R54" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Media</t>
+        </is>
+      </c>
+      <c r="S54" s="13">
+        <v>3</v>
+      </c>
+      <c r="V54" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vigente</t>
+        </is>
+      </c>
+      <c r="W54" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CC-004</t>
+        </is>
+      </c>
+      <c r="X54" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Representación. Autoridad: M01 (resultado); M02 (entrada). LISTAS no define la lógica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="P55" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">escala_probabilidad_impacto</t>
+        </is>
+      </c>
+      <c r="Q55" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">alta</t>
+        </is>
+      </c>
+      <c r="R55" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alta</t>
+        </is>
+      </c>
+      <c r="S55" s="13">
+        <v>4</v>
+      </c>
+      <c r="V55" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vigente</t>
+        </is>
+      </c>
+      <c r="W55" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CC-004</t>
+        </is>
+      </c>
+      <c r="X55" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Representación. Autoridad: M01 (resultado); M02 (entrada). LISTAS no define la lógica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="P56" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">escala_zona_objetivo</t>
+        </is>
+      </c>
+      <c r="Q56" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bajo_copa</t>
+        </is>
+      </c>
+      <c r="R56" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bajo la copa</t>
+        </is>
+      </c>
+      <c r="S56" s="13">
+        <v>1</v>
+      </c>
+      <c r="V56" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vigente</t>
+        </is>
+      </c>
+      <c r="W56" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CC-004</t>
+        </is>
+      </c>
+      <c r="X56" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Representación. Autoridad: M01 (entrada). LISTAS no define la lógica. Las filas de M01 usan la forma corta de la etiqueta. Se alinearán en la sincronización del paquete 2.0.0. MATRICES_CALCULO no se modifica en CC-004.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="P57" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">escala_zona_objetivo</t>
+        </is>
+      </c>
+      <c r="Q57" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">limite_copa_1x_altura</t>
+        </is>
+      </c>
+      <c r="R57" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Entre el límite de la copa y 1× la altura del árbol</t>
+        </is>
+      </c>
+      <c r="S57" s="13">
+        <v>2</v>
+      </c>
+      <c r="V57" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vigente</t>
+        </is>
+      </c>
+      <c r="W57" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CC-004</t>
+        </is>
+      </c>
+      <c r="X57" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Representación. Autoridad: M01 (entrada). LISTAS no define la lógica. Las filas de M01 usan la forma corta de la etiqueta. Se alinearán en la sincronización del paquete 2.0.0. MATRICES_CALCULO no se modifica en CC-004.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="P58" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">escala_zona_objetivo</t>
+        </is>
+      </c>
+      <c r="Q58" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">entre_1x_1_5x_altura</t>
+        </is>
+      </c>
+      <c r="R58" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Entre 1× y 1,5× la altura del árbol</t>
+        </is>
+      </c>
+      <c r="S58" s="13">
+        <v>3</v>
+      </c>
+      <c r="V58" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vigente</t>
+        </is>
+      </c>
+      <c r="W58" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CC-004</t>
+        </is>
+      </c>
+      <c r="X58" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Representación. Autoridad: M01 (entrada). LISTAS no define la lógica. Las filas de M01 usan la forma corta de la etiqueta. Se alinearán en la sincronización del paquete 2.0.0. MATRICES_CALCULO no se modifica en CC-004.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="P59" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">escala_zona_objetivo</t>
+        </is>
+      </c>
+      <c r="Q59" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mas_alla_1_5x_altura</t>
+        </is>
+      </c>
+      <c r="R59" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Más allá de 1,5× la altura del árbol</t>
+        </is>
+      </c>
+      <c r="S59" s="13">
+        <v>4</v>
+      </c>
+      <c r="V59" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vigente</t>
+        </is>
+      </c>
+      <c r="W59" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CC-004</t>
+        </is>
+      </c>
+      <c r="X59" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Representación. Autoridad: M01 (entrada). LISTAS no define la lógica. Las filas de M01 usan la forma corta de la etiqueta. Se alinearán en la sincronización del paquete 2.0.0. MATRICES_CALCULO no se modifica en CC-004.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="P60" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">escala_tasa_ocupacion</t>
+        </is>
+      </c>
+      <c r="Q60" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rara</t>
+        </is>
+      </c>
+      <c r="R60" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rara</t>
+        </is>
+      </c>
+      <c r="S60" s="13">
+        <v>1</v>
+      </c>
+      <c r="V60" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vigente</t>
+        </is>
+      </c>
+      <c r="W60" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CC-004</t>
+        </is>
+      </c>
+      <c r="X60" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Representación. Autoridad: M01 (entrada). LISTAS no define la lógica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="P61" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">escala_tasa_ocupacion</t>
+        </is>
+      </c>
+      <c r="Q61" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ocasional</t>
+        </is>
+      </c>
+      <c r="R61" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ocasional</t>
+        </is>
+      </c>
+      <c r="S61" s="13">
+        <v>2</v>
+      </c>
+      <c r="V61" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vigente</t>
+        </is>
+      </c>
+      <c r="W61" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CC-004</t>
+        </is>
+      </c>
+      <c r="X61" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Representación. Autoridad: M01 (entrada). LISTAS no define la lógica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="P62" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">escala_tasa_ocupacion</t>
+        </is>
+      </c>
+      <c r="Q62" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">frecuente</t>
+        </is>
+      </c>
+      <c r="R62" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frecuente</t>
+        </is>
+      </c>
+      <c r="S62" s="13">
+        <v>3</v>
+      </c>
+      <c r="V62" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vigente</t>
+        </is>
+      </c>
+      <c r="W62" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CC-004</t>
+        </is>
+      </c>
+      <c r="X62" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Representación. Autoridad: M01 (entrada). LISTAS no define la lógica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="P63" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">escala_tasa_ocupacion</t>
+        </is>
+      </c>
+      <c r="Q63" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">constante</t>
+        </is>
+      </c>
+      <c r="R63" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Constante</t>
+        </is>
+      </c>
+      <c r="S63" s="13">
+        <v>4</v>
+      </c>
+      <c r="V63" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vigente</t>
+        </is>
+      </c>
+      <c r="W63" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CC-004</t>
+        </is>
+      </c>
+      <c r="X63" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Representación. Autoridad: M01 (entrada). LISTAS no define la lógica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="P64" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">escala_clasificacion_infraestructura</t>
+        </is>
+      </c>
+      <c r="Q64" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bajo</t>
+        </is>
+      </c>
+      <c r="R64" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bajo</t>
+        </is>
+      </c>
+      <c r="S64" s="13">
+        <v>1</v>
+      </c>
+      <c r="V64" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vigente</t>
+        </is>
+      </c>
+      <c r="W64" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CC-004</t>
+        </is>
+      </c>
+      <c r="X64" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Representación. Autoridad: M04 (resultado); M05 (entrada). LISTAS no define la lógica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="P65" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">escala_clasificacion_infraestructura</t>
+        </is>
+      </c>
+      <c r="Q65" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">moderado</t>
+        </is>
+      </c>
+      <c r="R65" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Moderado</t>
+        </is>
+      </c>
+      <c r="S65" s="13">
+        <v>2</v>
+      </c>
+      <c r="V65" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vigente</t>
+        </is>
+      </c>
+      <c r="W65" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CC-004</t>
+        </is>
+      </c>
+      <c r="X65" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Representación. Autoridad: M04 (resultado); M05 (entrada). LISTAS no define la lógica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="P66" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">escala_clasificacion_infraestructura</t>
+        </is>
+      </c>
+      <c r="Q66" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">alto</t>
+        </is>
+      </c>
+      <c r="R66" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alto</t>
+        </is>
+      </c>
+      <c r="S66" s="13">
+        <v>3</v>
+      </c>
+      <c r="V66" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vigente</t>
+        </is>
+      </c>
+      <c r="W66" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CC-004</t>
+        </is>
+      </c>
+      <c r="X66" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Representación. Autoridad: M04 (resultado); M05 (entrada). LISTAS no define la lógica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="P67" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">escala_clasificacion_infraestructura</t>
+        </is>
+      </c>
+      <c r="Q67" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">critico</t>
+        </is>
+      </c>
+      <c r="R67" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Crítico</t>
+        </is>
+      </c>
+      <c r="S67" s="13">
+        <v>4</v>
+      </c>
+      <c r="V67" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vigente</t>
+        </is>
+      </c>
+      <c r="W67" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CC-004</t>
+        </is>
+      </c>
+      <c r="X67" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Representación. Autoridad: M04 (resultado); M05 (entrada). LISTAS no define la lógica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="P68" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">escala_prioridad</t>
+        </is>
+      </c>
+      <c r="Q68" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">baja</t>
+        </is>
+      </c>
+      <c r="R68" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Baja</t>
+        </is>
+      </c>
+      <c r="S68" s="13">
+        <v>1</v>
+      </c>
+      <c r="V68" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vigente</t>
+        </is>
+      </c>
+      <c r="W68" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CC-004</t>
+        </is>
+      </c>
+      <c r="X68" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Representación. Autoridad: M05 (resultado). LISTAS no define la lógica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="P69" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">escala_prioridad</t>
+        </is>
+      </c>
+      <c r="Q69" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">media</t>
+        </is>
+      </c>
+      <c r="R69" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Media</t>
+        </is>
+      </c>
+      <c r="S69" s="13">
+        <v>2</v>
+      </c>
+      <c r="V69" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vigente</t>
+        </is>
+      </c>
+      <c r="W69" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CC-004</t>
+        </is>
+      </c>
+      <c r="X69" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Representación. Autoridad: M05 (resultado). LISTAS no define la lógica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="P70" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">escala_prioridad</t>
+        </is>
+      </c>
+      <c r="Q70" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">alta</t>
+        </is>
+      </c>
+      <c r="R70" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alta</t>
+        </is>
+      </c>
+      <c r="S70" s="13">
+        <v>3</v>
+      </c>
+      <c r="V70" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vigente</t>
+        </is>
+      </c>
+      <c r="W70" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CC-004</t>
+        </is>
+      </c>
+      <c r="X70" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Representación. Autoridad: M05 (resultado). LISTAS no define la lógica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="P71" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">escala_prioridad</t>
+        </is>
+      </c>
+      <c r="Q71" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">critica</t>
+        </is>
+      </c>
+      <c r="R71" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Crítica</t>
+        </is>
+      </c>
+      <c r="S71" s="13">
+        <v>4</v>
+      </c>
+      <c r="V71" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vigente</t>
+        </is>
+      </c>
+      <c r="W71" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CC-004</t>
+        </is>
+      </c>
+      <c r="X71" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Representación. Autoridad: M05 (resultado). LISTAS no define la lógica.</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:B8">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="V2:V5000">
+      <formula1>"vigente,reemplazado,descartado"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -7087,8 +9641,10 @@
       <c r="G32" s="9" t="s">
         <v>282</v>
       </c>
-      <c r="H32" s="9" t="s">
-        <v>379</v>
+      <c r="H32" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LISTAS:confirmacion_cavidad_interna</t>
+        </is>
       </c>
       <c r="I32" s="9" t="s">
         <v>335</v>
@@ -7521,8 +10077,10 @@
       <c r="G44" s="10" t="s">
         <v>282</v>
       </c>
-      <c r="H44" s="10" t="s">
-        <v>379</v>
+      <c r="H44" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LISTAS:confirmacion_cavidad_interna</t>
+        </is>
       </c>
       <c r="I44" s="10" t="s">
         <v>335</v>
@@ -10684,8 +13242,10 @@
       <c r="G133" s="9" t="s">
         <v>282</v>
       </c>
-      <c r="H133" s="10" t="s">
-        <v>664</v>
+      <c r="H133" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LISTAS:escala_zona_objetivo</t>
+        </is>
       </c>
       <c r="I133" s="10" t="s">
         <v>334</v>
@@ -10718,8 +13278,10 @@
       <c r="G134" s="10" t="s">
         <v>282</v>
       </c>
-      <c r="H134" s="10" t="s">
-        <v>666</v>
+      <c r="H134" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LISTAS:escala_tasa_ocupacion</t>
+        </is>
       </c>
       <c r="I134" s="10" t="s">
         <v>334</v>
@@ -10752,8 +13314,10 @@
       <c r="G135" s="37" t="s">
         <v>282</v>
       </c>
-      <c r="H135" s="37" t="s">
-        <v>310</v>
+      <c r="H135" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LISTAS:escala_probabilidad_impacto</t>
+        </is>
       </c>
       <c r="I135" s="37" t="s">
         <v>334</v>
@@ -10762,8 +13326,10 @@
         <v>682</v>
       </c>
       <c r="K135" s="37"/>
-      <c r="L135" s="37" t="s">
-        <v>683</v>
+      <c r="L135" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Resultado automático según M01. Valores permitidos: LISTAS:escala_probabilidad_impacto. No editable manualmente.</t>
+        </is>
       </c>
     </row>
     <row r="136" spans="1:12" s="20" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -10788,8 +13354,10 @@
       <c r="G136" s="19" t="s">
         <v>282</v>
       </c>
-      <c r="H136" s="19" t="s">
-        <v>684</v>
+      <c r="H136" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LISTAS:escala_consecuencia</t>
+        </is>
       </c>
       <c r="I136" s="19" t="s">
         <v>334</v>
@@ -10822,8 +13390,10 @@
       <c r="G137" s="19" t="s">
         <v>282</v>
       </c>
-      <c r="H137" s="19" t="s">
-        <v>684</v>
+      <c r="H137" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LISTAS:escala_consecuencia</t>
+        </is>
       </c>
       <c r="I137" s="19" t="s">
         <v>334</v>
@@ -10856,8 +13426,10 @@
       <c r="G138" s="19" t="s">
         <v>282</v>
       </c>
-      <c r="H138" s="19" t="s">
-        <v>684</v>
+      <c r="H138" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LISTAS:escala_consecuencia</t>
+        </is>
       </c>
       <c r="I138" s="19" t="s">
         <v>334</v>
@@ -10890,8 +13462,10 @@
       <c r="G139" s="41" t="s">
         <v>282</v>
       </c>
-      <c r="H139" s="41" t="s">
-        <v>309</v>
+      <c r="H139" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LISTAS:escala_probabilidad_falla</t>
+        </is>
       </c>
       <c r="I139" s="41" t="s">
         <v>334</v>
@@ -10900,8 +13474,10 @@
         <v>708</v>
       </c>
       <c r="K139" s="41"/>
-      <c r="L139" s="41" t="s">
-        <v>709</v>
+      <c r="L139" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Resultado automático no editable. Puntaje total válido 0–9. Resultado permitido: LISTAS:escala_probabilidad_falla.</t>
+        </is>
       </c>
     </row>
     <row r="140" spans="1:12" s="42" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -10926,8 +13502,10 @@
       <c r="G140" s="41" t="s">
         <v>282</v>
       </c>
-      <c r="H140" s="41" t="s">
-        <v>309</v>
+      <c r="H140" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LISTAS:escala_probabilidad_falla</t>
+        </is>
       </c>
       <c r="I140" s="41" t="s">
         <v>334</v>
@@ -10936,8 +13514,10 @@
         <v>719</v>
       </c>
       <c r="K140" s="41"/>
-      <c r="L140" s="41" t="s">
-        <v>709</v>
+      <c r="L140" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Resultado automático no editable. Puntaje total válido 0–9. Resultado permitido: LISTAS:escala_probabilidad_falla.</t>
+        </is>
       </c>
     </row>
     <row r="141" spans="1:12" s="42" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -10962,8 +13542,10 @@
       <c r="G141" s="41" t="s">
         <v>282</v>
       </c>
-      <c r="H141" s="41" t="s">
-        <v>309</v>
+      <c r="H141" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LISTAS:escala_probabilidad_falla</t>
+        </is>
       </c>
       <c r="I141" s="41" t="s">
         <v>334</v>
@@ -10972,8 +13554,10 @@
         <v>728</v>
       </c>
       <c r="K141" s="41"/>
-      <c r="L141" s="41" t="s">
-        <v>709</v>
+      <c r="L141" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Resultado automático no editable. Puntaje total válido 0–9. Resultado permitido: LISTAS:escala_probabilidad_falla.</t>
+        </is>
       </c>
     </row>
     <row r="142" spans="1:12" s="38" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -10998,8 +13582,10 @@
       <c r="G142" s="37" t="s">
         <v>282</v>
       </c>
-      <c r="H142" s="37" t="s">
-        <v>312</v>
+      <c r="H142" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LISTAS:escala_nivel_riesgo</t>
+        </is>
       </c>
       <c r="I142" s="41" t="s">
         <v>334</v>
@@ -11008,8 +13594,10 @@
         <v>746</v>
       </c>
       <c r="K142" s="37"/>
-      <c r="L142" s="37" t="s">
-        <v>752</v>
+      <c r="L142" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Valor calculado automáticamente y no editable. Valores permitidos: LISTAS:escala_nivel_riesgo. Requiere valores válidos en probabilidad_falla_raices_cuello, probabilidad_impacto y consecuencia_raices_cuello</t>
+        </is>
       </c>
     </row>
     <row r="143" spans="1:12" s="38" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -11034,8 +13622,10 @@
       <c r="G143" s="37" t="s">
         <v>282</v>
       </c>
-      <c r="H143" s="37" t="s">
-        <v>312</v>
+      <c r="H143" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LISTAS:escala_nivel_riesgo</t>
+        </is>
       </c>
       <c r="I143" s="41" t="s">
         <v>334</v>
@@ -11044,8 +13634,10 @@
         <v>747</v>
       </c>
       <c r="K143" s="37"/>
-      <c r="L143" s="37" t="s">
-        <v>753</v>
+      <c r="L143" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Valor calculado automáticamente y no editable. Valores permitidos: LISTAS:escala_nivel_riesgo. Requiere valores válidos en probabilidad_falla_tronco, probabilidad_impacto y consecuencia_tronco</t>
+        </is>
       </c>
     </row>
     <row r="144" spans="1:12" s="38" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -11070,8 +13662,10 @@
       <c r="G144" s="37" t="s">
         <v>282</v>
       </c>
-      <c r="H144" s="37" t="s">
-        <v>312</v>
+      <c r="H144" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LISTAS:escala_nivel_riesgo</t>
+        </is>
       </c>
       <c r="I144" s="41" t="s">
         <v>334</v>
@@ -11080,8 +13674,10 @@
         <v>748</v>
       </c>
       <c r="K144" s="37"/>
-      <c r="L144" s="37" t="s">
-        <v>754</v>
+      <c r="L144" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Valor calculado automáticamente y no editable. Valores permitidos: LISTAS:escala_nivel_riesgo. Requiere valores válidos en probabilidad_falla_copa_ramas, probabilidad_impacto y consecuencia_copa_ramas</t>
+        </is>
       </c>
     </row>
     <row r="145" spans="1:12" s="20" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -11138,8 +13734,10 @@
       <c r="G146" s="37" t="s">
         <v>282</v>
       </c>
-      <c r="H146" s="37" t="s">
-        <v>771</v>
+      <c r="H146" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LISTAS:escala_clasificacion_infraestructura</t>
+        </is>
       </c>
       <c r="I146" s="41" t="s">
         <v>334</v>
@@ -11148,8 +13746,10 @@
         <v>770</v>
       </c>
       <c r="K146" s="37"/>
-      <c r="L146" s="37" t="s">
-        <v>773</v>
+      <c r="L146" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Valor calculado automáticamente y no editable. Valores permitidos: LISTAS:escala_clasificacion_infraestructura.</t>
+        </is>
       </c>
     </row>
     <row r="147" spans="1:12" s="38" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -11174,8 +13774,10 @@
       <c r="G147" s="37" t="s">
         <v>282</v>
       </c>
-      <c r="H147" s="37" t="s">
-        <v>312</v>
+      <c r="H147" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LISTAS:escala_nivel_riesgo</t>
+        </is>
       </c>
       <c r="I147" s="41" t="s">
         <v>334</v>
@@ -11184,8 +13786,10 @@
         <v>781</v>
       </c>
       <c r="K147" s="37"/>
-      <c r="L147" s="37" t="s">
-        <v>782</v>
+      <c r="L147" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Valor calculado automáticamente y no editable. Valores permitidos: LISTAS:escala_nivel_riesgo. Requiere clasificaciones válidas de los componentes evaluados.</t>
+        </is>
       </c>
     </row>
     <row r="148" spans="1:12" s="23" customFormat="1" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -11210,8 +13814,10 @@
       <c r="G148" s="22" t="s">
         <v>282</v>
       </c>
-      <c r="H148" s="22" t="s">
-        <v>791</v>
+      <c r="H148" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LISTAS:escala_prioridad</t>
+        </is>
       </c>
       <c r="I148" s="41" t="s">
         <v>334</v>
@@ -11220,8 +13826,10 @@
         <v>792</v>
       </c>
       <c r="K148" s="22"/>
-      <c r="L148" s="22" t="s">
-        <v>793</v>
+      <c r="L148" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Valor calculado automáticamente y no editable. Valores permitidos: LISTAS:escala_prioridad. Requiere valores válidos en clasificacion_riesgo y clasificacion_infraestructura.</t>
+        </is>
       </c>
     </row>
     <row r="149" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -11246,8 +13854,10 @@
       <c r="G149" s="8" t="s">
         <v>870</v>
       </c>
-      <c r="H149" s="8" t="s">
-        <v>871</v>
+      <c r="H149" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LISTAS:accion (filtrado por tipo_ot)</t>
+        </is>
       </c>
       <c r="I149" s="8" t="s">
         <v>334</v>
@@ -11281,8 +13891,10 @@
       <c r="G150" s="8" t="s">
         <v>870</v>
       </c>
-      <c r="H150" s="8" t="s">
-        <v>876</v>
+      <c r="H150" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LISTAS:subtipo_accion (filtrado por accion; vacío si la acción no tiene subtipos)</t>
+        </is>
       </c>
       <c r="I150" s="8" t="s">
         <v>335</v>

--- a/docs/excel/Base de Datos Valpo Verde.xlsx
+++ b/docs/excel/Base de Datos Valpo Verde.xlsx
@@ -10,10 +10,11 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA388B56-B06A-4110-851F-684CDD3218CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="4" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ARBOLES" sheetId="11" r:id="rId1"/>
+    <sheet name="MEDICIONES_DENDROMETRICAS" sheetId="20" r:id="rId17"/>
     <sheet name="REGISTRO_EVALUACION" sheetId="12" r:id="rId2"/>
     <sheet name="INCIDENCIA" sheetId="10" r:id="rId3"/>
     <sheet name="INSPECCIONES" sheetId="9" r:id="rId4"/>
@@ -3263,14 +3264,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S1"/>
+  <dimension ref="A1:L1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="13.6640625" customWidth="1"/>
     <col min="3" max="3" width="13.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3289,52 +3290,28 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ubicacion_wgs84</t>
+        </is>
+      </c>
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
-        <v>336</v>
-      </c>
-      <c r="M1" t="s">
-        <v>331</v>
-      </c>
-      <c r="N1" t="s">
-        <v>341</v>
-      </c>
-      <c r="O1" t="s">
-        <v>11</v>
-      </c>
-      <c r="P1" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>13</v>
-      </c>
-      <c r="R1" t="s">
-        <v>14</v>
-      </c>
-      <c r="S1" t="s">
-        <v>350</v>
-      </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O1048576" xr:uid="{00000000-0002-0000-0000-000000000000}">
-      <formula1>"Joven,Semimaduro,Maduro,Sobremaduro"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -4671,7 +4648,7 @@
       </c>
       <c r="E3" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">CC-004</t>
+          <t xml:space="preserve">CC-004, CC-008, CC-009, CC-020</t>
         </is>
       </c>
       <c r="I3" s="13" t="inlineStr">
@@ -4681,7 +4658,7 @@
       </c>
       <c r="J3" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Paquete metodológico en construcción. NO publicado; no define rule_version. Acumula los CC aprobados que se incorporen al paquete 2.0.0. CC-004 no publica la metodología 2.0.0.</t>
+          <t xml:space="preserve">Paquete metodológico en construcción. NO publicado; no define rule_version. Acumula los CC aprobados que se incorporen al paquete 2.0.0. CC-004 no publica la metodología 2.0.0. CC-008 (columna ambito de DICCIONARIO_CAMPOS), CC-009 y CC-020 (separación ÁRBOL / MEDICIONES_DENDROMETRICAS) se incorporan en preparación y tampoco publican la metodología 2.0.0.</t>
         </is>
       </c>
     </row>
@@ -4694,6 +4671,103 @@
       <formula1>"marybaxmann,Valen-j211"</formula1>
     </dataValidation>
   </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Q1"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">id_medicion</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">id_arbol</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fecha_medicion</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fecha_registro</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">registrado_por</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">configuracion_fustes</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">numero_fustes</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dap_fustes_cm</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dap_cm</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">altura_total_m</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">diametro_copa_m</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">altura_primera_rama_m</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clase_edad</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estado_medicion</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">motivo_anulacion</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">anulado_por</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fecha_anulacion</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -8535,7 +8609,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:M150"/>
+  <dimension ref="A1:N160"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="24" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.77734375" style="14" customWidth="1"/>
@@ -8553,7 +8627,7 @@
     <col min="13" max="16384" width="11.5546875" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>241</v>
       </c>
@@ -8590,8 +8664,13 @@
       <c r="L1" s="7" t="s">
         <v>248</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N1" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ambito</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
         <v>249</v>
       </c>
@@ -8624,8 +8703,13 @@
       <c r="L2" s="9" t="s">
         <v>319</v>
       </c>
-    </row>
-    <row r="3" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N2" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">operativo</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="s">
         <v>249</v>
       </c>
@@ -8658,8 +8742,13 @@
       <c r="L3" s="10" t="s">
         <v>320</v>
       </c>
-    </row>
-    <row r="4" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N3" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">operativo</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="12" t="s">
         <v>249</v>
       </c>
@@ -8675,8 +8764,10 @@
       <c r="E4" s="12" t="s">
         <v>260</v>
       </c>
-      <c r="F4" s="9" t="s">
-        <v>321</v>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fecha de incorporación del árbol al inventario (alta). No es la fecha de ninguna medición dendrométrica (ver MEDICIONES_DENDROMETRICAS.fecha_medicion).</t>
+        </is>
       </c>
       <c r="G4" s="9" t="s">
         <v>261</v>
@@ -8692,8 +8783,13 @@
       <c r="L4" s="9" t="s">
         <v>322</v>
       </c>
-    </row>
-    <row r="5" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N4" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">operativo</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="13" t="s">
         <v>249</v>
       </c>
@@ -8726,8 +8822,13 @@
       <c r="L5" s="10" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="6" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N5" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">operativo</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="12" t="s">
         <v>249</v>
       </c>
@@ -8760,8 +8861,13 @@
       <c r="L6" s="9" t="s">
         <v>267</v>
       </c>
-    </row>
-    <row r="7" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N6" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">operativo</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="13" t="s">
         <v>249</v>
       </c>
@@ -8792,49 +8898,79 @@
       <c r="L7" s="10" t="s">
         <v>267</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="12" t="s">
+      <c r="N7" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">operativo</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARBOLES</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ubicacion_wgs84</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Inspector / Usuario Municipal</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Punto seleccionado en el mapa o ubicación del dispositivo, capturado directamente en WGS84. La captura en otro CRS (p. ej. UTM) y su transformación siguen pendientes (ADR-010 v2.0).</t>
+        </is>
+      </c>
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ubicación canónica del árbol: punto geográfico en WGS84 (EPSG:4326). Es la ubicación oficial del ejemplar (ADR-010 v2.0).</t>
+        </is>
+      </c>
+      <c r="G8" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Punto geográfico</t>
+        </is>
+      </c>
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WGS84 / EPSG:4326 (grados decimales)</t>
+        </is>
+      </c>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Obligatorio</t>
+        </is>
+      </c>
+      <c r="J8" s="10"/>
+      <c r="K8" s="10"/>
+      <c r="L8" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Obligatorio para completar el alta del árbol (CC-020). Pertenece al ÁRBOL, no a la medición. No existen campos de latitud/longitud como segunda ubicación editable (ADR-010 v2.0).</t>
+        </is>
+      </c>
+      <c r="N8" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">operativo</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="12" t="s">
         <v>249</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="B9" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="9" t="s">
-        <v>215</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>325</v>
-      </c>
-      <c r="E8" s="12" t="s">
-        <v>315</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>269</v>
-      </c>
-      <c r="G8" s="9" t="s">
-        <v>270</v>
-      </c>
-      <c r="H8" s="9" t="s">
-        <v>271</v>
-      </c>
-      <c r="I8" s="9" t="s">
-        <v>334</v>
-      </c>
-      <c r="J8" s="9"/>
-      <c r="K8" s="9"/>
-      <c r="L8" s="9" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="13" t="s">
-        <v>249</v>
-      </c>
-      <c r="B9" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="9" t="s">
         <v>215</v>
       </c>
       <c r="D9" s="9" t="s">
@@ -8843,98 +8979,127 @@
       <c r="E9" s="12" t="s">
         <v>315</v>
       </c>
-      <c r="F9" s="10" t="s">
+      <c r="F9" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>271</v>
+      </c>
+      <c r="I9" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pendiente</t>
+        </is>
+      </c>
+      <c r="J9" s="9"/>
+      <c r="K9" s="9"/>
+      <c r="L9" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Este, Norte, huso, hemisferio y datum deben ser coherentes. No fijar SRID sin verificar configuración del proyecto. PENDIENTE (CC-020): captura en UTM, datum, huso y conservación de la coordenada original de levantamiento siguen abiertos (ADR-010 v2.0); obligatoriedad anterior: Obligatorio. La ubicación canónica del árbol es ubicacion_wgs84.</t>
+        </is>
+      </c>
+      <c r="N9" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">operativo</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="13" t="s">
+        <v>249</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>325</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>315</v>
+      </c>
+      <c r="F10" s="10" t="s">
         <v>273</v>
       </c>
-      <c r="G9" s="10" t="s">
+      <c r="G10" s="10" t="s">
         <v>270</v>
       </c>
-      <c r="H9" s="10" t="s">
+      <c r="H10" s="10" t="s">
         <v>271</v>
       </c>
-      <c r="I9" s="10" t="s">
-        <v>334</v>
-      </c>
-      <c r="J9" s="10"/>
-      <c r="K9" s="10"/>
-      <c r="L9" s="10" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" s="20" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="18" t="s">
+      <c r="I10" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pendiente</t>
+        </is>
+      </c>
+      <c r="J10" s="10"/>
+      <c r="K10" s="10"/>
+      <c r="L10" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Este, Norte, huso, hemisferio y datum deben ser coherentes. No fijar SRID sin verificar configuración del proyecto. PENDIENTE (CC-020): captura en UTM, datum, huso y conservación de la coordenada original de levantamiento siguen abiertos (ADR-010 v2.0); obligatoriedad anterior: Obligatorio. La ubicación canónica del árbol es ubicacion_wgs84.</t>
+        </is>
+      </c>
+      <c r="N10" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">operativo</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" spans="1:14" s="20" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="18" t="s">
         <v>249</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="B11" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="19" t="s">
+      <c r="C11" s="19" t="s">
         <v>251</v>
       </c>
-      <c r="D10" s="19" t="s">
+      <c r="D11" s="19" t="s">
         <v>251</v>
       </c>
-      <c r="E10" s="18" t="s">
+      <c r="E11" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="F10" s="19" t="s">
+      <c r="F11" s="19" t="s">
         <v>317</v>
       </c>
-      <c r="G10" s="19" t="s">
+      <c r="G11" s="19" t="s">
         <v>266</v>
       </c>
-      <c r="H10" s="19" t="s">
+      <c r="H11" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="I10" s="19" t="s">
-        <v>334</v>
-      </c>
-      <c r="J10" s="19"/>
-      <c r="K10" s="19"/>
-      <c r="L10" s="19" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="13" t="s">
+      <c r="I11" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pendiente</t>
+        </is>
+      </c>
+      <c r="J11" s="19"/>
+      <c r="K11" s="19"/>
+      <c r="L11" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Este, Norte, huso, hemisferio y datum deben ser coherentes. No fijar SRID sin verificar configuración del proyecto. PENDIENTE (CC-020): huso y datum siguen abiertos (ADR-010 v2.0); el valor fijo 19S no se aplica como regla, porque la plataforma no asume una única zona UTM. Obligatoriedad anterior: Obligatorio.</t>
+        </is>
+      </c>
+      <c r="N11" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">operativo</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="13" t="s">
         <v>249</v>
       </c>
-      <c r="B11" s="13" t="s">
+      <c r="B12" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="10" t="s">
-        <v>215</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>325</v>
-      </c>
-      <c r="E11" s="13" t="s">
-        <v>313</v>
-      </c>
-      <c r="F11" s="10" t="s">
-        <v>316</v>
-      </c>
-      <c r="G11" s="10" t="s">
-        <v>266</v>
-      </c>
-      <c r="H11" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="I11" s="10" t="s">
-        <v>334</v>
-      </c>
-      <c r="J11" s="10"/>
-      <c r="K11" s="10"/>
-      <c r="L11" s="10"/>
-    </row>
-    <row r="12" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="12" t="s">
-        <v>249</v>
-      </c>
-      <c r="B12" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12" s="9" t="s">
+      <c r="C12" s="10" t="s">
         <v>215</v>
       </c>
       <c r="D12" s="9" t="s">
@@ -8943,28 +9108,37 @@
       <c r="E12" s="13" t="s">
         <v>313</v>
       </c>
-      <c r="F12" s="9" t="s">
-        <v>274</v>
-      </c>
-      <c r="G12" s="9" t="s">
+      <c r="F12" s="10" t="s">
+        <v>316</v>
+      </c>
+      <c r="G12" s="10" t="s">
         <v>266</v>
       </c>
-      <c r="H12" s="9" t="s">
+      <c r="H12" s="10" t="s">
         <v>99</v>
       </c>
-      <c r="I12" s="9" t="s">
+      <c r="I12" s="10" t="s">
         <v>334</v>
       </c>
-      <c r="J12" s="9"/>
-      <c r="K12" s="9"/>
-      <c r="L12" s="9"/>
-    </row>
-    <row r="13" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J12" s="10"/>
+      <c r="K12" s="10"/>
+      <c r="L12" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pertenece al ÁRBOL. Una modificación posterior de la identificación taxonómica es una corrección o refinamiento de identificación, no una nueva medición dendrométrica. PENDIENTE (CC-020): política de especie no determinada, fuente y administración del catálogo de especies por definir.</t>
+        </is>
+      </c>
+      <c r="N12" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">operativo</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="12" t="s">
         <v>249</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>336</v>
+        <v>10</v>
       </c>
       <c r="C13" s="9" t="s">
         <v>215</v>
@@ -8976,205 +9150,335 @@
         <v>313</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>337</v>
-      </c>
-      <c r="G13" s="10" t="s">
-        <v>282</v>
+        <v>274</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>266</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>328</v>
+        <v>99</v>
       </c>
       <c r="I13" s="9" t="s">
         <v>334</v>
       </c>
       <c r="J13" s="9"/>
       <c r="K13" s="9"/>
-      <c r="L13" s="9" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="12" t="s">
-        <v>249</v>
-      </c>
-      <c r="B14" s="12" t="s">
-        <v>331</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>215</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>325</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>313</v>
-      </c>
-      <c r="F14" s="9" t="s">
-        <v>329</v>
-      </c>
-      <c r="G14" s="10" t="s">
-        <v>330</v>
-      </c>
-      <c r="H14" s="9" t="s">
-        <v>289</v>
-      </c>
-      <c r="I14" s="9" t="s">
-        <v>335</v>
+      <c r="L13" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDIENTE (CC-020): política de nombres comunes por definir (una especie puede tener más de un nombre común o local). Según PR-006, el nombre común se resuelve desde el catálogo de especies y no se duplica por árbol.</t>
+        </is>
+      </c>
+      <c r="N13" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">operativo</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MEDICIONES_DENDROMETRICAS</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">id_medicion</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Generado por plataforma</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sistema</t>
+        </is>
+      </c>
+      <c r="E14" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Asignación automática al registrar la medición.</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Identificador único y estable de la medición dendrométrica.</t>
+        </is>
+      </c>
+      <c r="G14" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Identificador (texto)</t>
+        </is>
+      </c>
+      <c r="H14" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No aplica</t>
+        </is>
+      </c>
+      <c r="I14" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Obligatorio</t>
+        </is>
       </c>
       <c r="J14" s="9"/>
-      <c r="K14" s="9" t="s">
-        <v>339</v>
-      </c>
-      <c r="L14" s="10" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="12" t="s">
-        <v>249</v>
-      </c>
-      <c r="B15" s="12" t="s">
-        <v>341</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>215</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>325</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>313</v>
-      </c>
-      <c r="F15" s="9" t="s">
-        <v>342</v>
-      </c>
-      <c r="G15" s="10" t="s">
-        <v>366</v>
-      </c>
-      <c r="H15" s="9" t="s">
-        <v>275</v>
-      </c>
-      <c r="I15" s="9" t="s">
-        <v>335</v>
+      <c r="K14" s="9"/>
+      <c r="L14" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Obligatorio, único y estable.</t>
+        </is>
+      </c>
+      <c r="N14" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">operativo</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MEDICIONES_DENDROMETRICAS</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">id_arbol</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vinculado por plataforma</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sistema</t>
+        </is>
+      </c>
+      <c r="E15" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vinculación al árbol medido.</t>
+        </is>
+      </c>
+      <c r="F15" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Árbol al que corresponde la medición. Relación conceptual: ARBOLES 1:N MEDICIONES_DENDROMETRICAS.</t>
+        </is>
+      </c>
+      <c r="G15" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Identificador (texto)</t>
+        </is>
+      </c>
+      <c r="H15" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No aplica</t>
+        </is>
+      </c>
+      <c r="I15" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Obligatorio</t>
+        </is>
       </c>
       <c r="J15" s="9"/>
-      <c r="K15" s="9" t="s">
-        <v>339</v>
-      </c>
-      <c r="L15" s="10" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" s="27" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="25" t="s">
-        <v>249</v>
-      </c>
-      <c r="B16" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="C16" s="26" t="s">
-        <v>344</v>
-      </c>
-      <c r="D16" s="26" t="s">
-        <v>324</v>
-      </c>
-      <c r="E16" s="25" t="s">
-        <v>315</v>
-      </c>
-      <c r="F16" s="26" t="s">
-        <v>346</v>
-      </c>
-      <c r="G16" s="26" t="s">
-        <v>270</v>
-      </c>
-      <c r="H16" s="26" t="s">
-        <v>275</v>
-      </c>
-      <c r="I16" s="26" t="s">
-        <v>334</v>
-      </c>
-      <c r="J16" s="26" t="s">
-        <v>347</v>
-      </c>
-      <c r="K16" s="26"/>
-      <c r="L16" s="26" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="12" t="s">
-        <v>249</v>
-      </c>
-      <c r="B17" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>215</v>
-      </c>
-      <c r="D17" s="9" t="s">
-        <v>325</v>
-      </c>
-      <c r="E17" s="12" t="s">
-        <v>315</v>
-      </c>
-      <c r="F17" s="9" t="s">
-        <v>277</v>
-      </c>
-      <c r="G17" s="9" t="s">
-        <v>270</v>
-      </c>
-      <c r="H17" s="9" t="s">
-        <v>271</v>
-      </c>
-      <c r="I17" s="9" t="s">
-        <v>334</v>
+      <c r="K15" s="9"/>
+      <c r="L15" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Referencia válida a ARBOLES.id_arbol. Un árbol puede tener varias mediciones; cada medición pertenece a un solo árbol.</t>
+        </is>
+      </c>
+      <c r="N15" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">operativo</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MEDICIONES_DENDROMETRICAS</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fecha_medicion</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Inspector / Usuario Municipal</t>
+        </is>
+      </c>
+      <c r="E16" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fecha en que se realizó la medición en terreno.</t>
+        </is>
+      </c>
+      <c r="F16" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fecha en que se realizó la medición dendrométrica. Determina el orden temporal de las mediciones y cuál es la última medición válida.</t>
+        </is>
+      </c>
+      <c r="G16" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fecha</t>
+        </is>
+      </c>
+      <c r="H16" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dd/mm/aaaa</t>
+        </is>
+      </c>
+      <c r="I16" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Obligatorio</t>
+        </is>
+      </c>
+      <c r="J16" s="9"/>
+      <c r="K16" s="9"/>
+      <c r="L16" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fecha válida. La última medición válida es la medición con estado Válida y la fecha_medicion más reciente (CC-020).</t>
+        </is>
+      </c>
+      <c r="N16" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">operativo</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MEDICIONES_DENDROMETRICAS</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fecha_registro</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sistema</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sistema</t>
+        </is>
+      </c>
+      <c r="E17" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fecha en que la medición fue ingresada al sistema.</t>
+        </is>
+      </c>
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fecha de ingreso de la medición al sistema. Tiene función de trazabilidad administrativa.</t>
+        </is>
+      </c>
+      <c r="G17" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fecha</t>
+        </is>
+      </c>
+      <c r="H17" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dd/mm/aaaa</t>
+        </is>
+      </c>
+      <c r="I17" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Obligatorio</t>
+        </is>
       </c>
       <c r="J17" s="9"/>
       <c r="K17" s="9"/>
-      <c r="L17" s="10" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="13" t="s">
-        <v>249</v>
-      </c>
-      <c r="B18" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="C18" s="10" t="s">
-        <v>215</v>
-      </c>
-      <c r="D18" s="9" t="s">
-        <v>325</v>
-      </c>
-      <c r="E18" s="12" t="s">
-        <v>315</v>
-      </c>
-      <c r="F18" s="10" t="s">
-        <v>318</v>
-      </c>
-      <c r="G18" s="10" t="s">
-        <v>270</v>
-      </c>
-      <c r="H18" s="10" t="s">
-        <v>271</v>
-      </c>
-      <c r="I18" s="10" t="s">
-        <v>334</v>
-      </c>
-      <c r="J18" s="10"/>
-      <c r="K18" s="10"/>
-      <c r="L18" s="10" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="12" t="s">
-        <v>249</v>
-      </c>
-      <c r="B19" s="12" t="s">
-        <v>14</v>
+      <c r="L17" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Asignada por el sistema. NO determina cuál medición es la vigente (CC-020).</t>
+        </is>
+      </c>
+      <c r="N17" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">operativo</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MEDICIONES_DENDROMETRICAS</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">registrado_por</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vinculado por plataforma</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sistema</t>
+        </is>
+      </c>
+      <c r="E18" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Usuario autenticado que ingresa la medición.</t>
+        </is>
+      </c>
+      <c r="F18" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Usuario que ingresa la medición al sistema.</t>
+        </is>
+      </c>
+      <c r="G18" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Identificador (texto)</t>
+        </is>
+      </c>
+      <c r="H18" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No aplica</t>
+        </is>
+      </c>
+      <c r="I18" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Obligatorio</t>
+        </is>
+      </c>
+      <c r="J18" s="9"/>
+      <c r="K18" s="9"/>
+      <c r="L18" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Referencia válida al usuario. Conservar autoría histórica. Los permisos se rigen por PR-003, PR-004 y PR-006.</t>
+        </is>
+      </c>
+      <c r="N18" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">operativo</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MEDICIONES_DENDROMETRICAS</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">configuracion_fustes</t>
+        </is>
       </c>
       <c r="C19" s="9" t="s">
         <v>215</v>
@@ -9182,523 +9486,736 @@
       <c r="D19" s="9" t="s">
         <v>325</v>
       </c>
-      <c r="E19" s="12" t="s">
-        <v>315</v>
-      </c>
-      <c r="F19" s="9" t="s">
-        <v>278</v>
-      </c>
-      <c r="G19" s="9" t="s">
-        <v>270</v>
-      </c>
-      <c r="H19" s="9" t="s">
-        <v>271</v>
+      <c r="E19" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="F19" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Configuración de los fustes del ejemplar a 1,30 m sobre el terreno. Se registra en cada medición porque condiciona la medición del DAP en esa fecha.</t>
+        </is>
+      </c>
+      <c r="G19" s="10" t="s">
+        <v>282</v>
+      </c>
+      <c r="H19" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDIENTE (CC-020): categorías definitivas por definir. El dominio anterior Sí / No (campo multifustal) no se adopta como dominio cerrado.</t>
+        </is>
       </c>
       <c r="I19" s="9" t="s">
         <v>334</v>
       </c>
       <c r="J19" s="9"/>
       <c r="K19" s="9"/>
-      <c r="L19" s="9" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" s="23" customFormat="1" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="21" t="s">
-        <v>249</v>
-      </c>
-      <c r="B20" s="21" t="s">
-        <v>350</v>
-      </c>
-      <c r="C20" s="22" t="s">
+      <c r="L19" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Obligatorio en la medición inicial (CC-020). PENDIENTE (CC-020): categorías en estudio (monofuste, bifurcado, multifuste) y su relación con numero_fustes y con el cálculo del DAP; no implementar un dominio cerrado hasta su aprobación. Obligatoriedad en mediciones posteriores: pendiente.</t>
+        </is>
+      </c>
+      <c r="N19" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">operativo</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MEDICIONES_DENDROMETRICAS</t>
+        </is>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>331</v>
+      </c>
+      <c r="C20" s="9" t="s">
         <v>215</v>
       </c>
-      <c r="D20" s="19" t="s">
+      <c r="D20" s="9" t="s">
         <v>325</v>
       </c>
-      <c r="E20" s="21" t="s">
+      <c r="E20" s="13" t="s">
         <v>313</v>
       </c>
-      <c r="F20" s="22" t="s">
-        <v>351</v>
+      <c r="F20" s="9" t="s">
+        <v>329</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>282</v>
-      </c>
-      <c r="H20" s="22" t="s">
-        <v>352</v>
-      </c>
-      <c r="I20" s="22" t="s">
-        <v>334</v>
-      </c>
-      <c r="J20" s="22"/>
-      <c r="K20" s="22"/>
-      <c r="L20" s="22" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="12" t="s">
-        <v>279</v>
+        <v>330</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>289</v>
+      </c>
+      <c r="I20" s="9" t="s">
+        <v>335</v>
+      </c>
+      <c r="J20" s="9"/>
+      <c r="K20" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Se activa cuando configuracion_fustes corresponde a más de un fuste (categorías pendientes, CC-020).</t>
+        </is>
+      </c>
+      <c r="L20" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Válido cuando se registra un número entero ≥ 2. PENDIENTE (CC-020): relación con las categorías de configuración de fustes por definir.</t>
+        </is>
+      </c>
+      <c r="N20" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">operativo</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MEDICIONES_DENDROMETRICAS</t>
+        </is>
       </c>
       <c r="B21" s="12" t="s">
-        <v>21</v>
+        <v>341</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>250</v>
+        <v>215</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>251</v>
-      </c>
-      <c r="E21" s="12" t="s">
-        <v>252</v>
-      </c>
-      <c r="F21" s="9" t="s">
-        <v>280</v>
-      </c>
-      <c r="G21" s="9" t="s">
-        <v>254</v>
+        <v>325</v>
+      </c>
+      <c r="E21" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="F21" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Diámetros individuales a 1,30 m de cada fuste medido. Son los datos primarios de un ejemplar con más de un fuste y se conservan aunque el DAP equivalente no esté calculado.</t>
+        </is>
+      </c>
+      <c r="G21" s="10" t="s">
+        <v>366</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>99</v>
+        <v>275</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="J21" s="9"/>
-      <c r="K21" s="9"/>
-      <c r="L21" s="9" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="13" t="s">
-        <v>279</v>
-      </c>
-      <c r="B22" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="C22" s="10" t="s">
-        <v>255</v>
-      </c>
-      <c r="D22" s="10" t="s">
-        <v>256</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>257</v>
-      </c>
-      <c r="F22" s="10" t="s">
-        <v>281</v>
-      </c>
-      <c r="G22" s="10" t="s">
-        <v>254</v>
-      </c>
-      <c r="H22" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="I22" s="10" t="s">
-        <v>334</v>
-      </c>
-      <c r="J22" s="10"/>
-      <c r="K22" s="10"/>
-      <c r="L22" s="10" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="12" t="s">
-        <v>279</v>
-      </c>
-      <c r="B23" s="12" t="s">
-        <v>0</v>
+      <c r="K21" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Se activa cuando configuracion_fustes corresponde a más de un fuste (categorías pendientes, CC-020).</t>
+        </is>
+      </c>
+      <c r="L21" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Obligatorio en la medición inicial cuando el ejemplar tiene más de un fuste (CC-020). La cantidad de diámetros registrados debe coincidir con numero_fustes; cada valor debe ser &gt; 0.</t>
+        </is>
+      </c>
+      <c r="N21" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">operativo</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" spans="1:14" s="27" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MEDICIONES_DENDROMETRICAS</t>
+        </is>
+      </c>
+      <c r="B22" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="26" t="s">
+        <v>344</v>
+      </c>
+      <c r="D22" s="26" t="s">
+        <v>324</v>
+      </c>
+      <c r="E22" s="25" t="s">
+        <v>315</v>
+      </c>
+      <c r="F22" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Diámetro del tronco a 1,30 m sobre el terreno, en centímetros. En un ejemplar de un solo fuste se mide directamente. En un ejemplar con más de un fuste corresponde al DAP equivalente, que se calcula desde dap_fustes_cm únicamente cuando exista una regla metodológica aprobada aplicable.</t>
+        </is>
+      </c>
+      <c r="G22" s="26" t="s">
+        <v>270</v>
+      </c>
+      <c r="H22" s="26" t="s">
+        <v>275</v>
+      </c>
+      <c r="I22" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Condicional</t>
+        </is>
+      </c>
+      <c r="J22" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDIENTE (CC-020): regla de DAP equivalente para ejemplares con más de un fuste por aprobar. La fórmula registrada antes de CC-020 se conserva solo como antecedente en la ficha CC-020 (docs/registro-cambios.md); no es vigente ni implementable.</t>
+        </is>
+      </c>
+      <c r="K22" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ejemplar de un solo fuste: ingreso manual. Ejemplar con más de un fuste: resultado calculado, pendiente mientras no exista regla aprobada.</t>
+        </is>
+      </c>
+      <c r="L22" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Valor numérico &gt; 0. Ejemplar de un solo fuste: ingreso manual obligatorio en la medición inicial. Ejemplar con más de un fuste: el DAP equivalente puede quedar pendiente de cálculo; su ausencia no impide completar la medición si se registraron los diámetros por fuste (CC-020). El resultado calculado no se edita manualmente (PR-008). Obligatoriedad en mediciones posteriores: pendiente.</t>
+        </is>
+      </c>
+      <c r="N22" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">operativo</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MEDICIONES_DENDROMETRICAS</t>
+        </is>
+      </c>
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">altura_total_m</t>
+        </is>
       </c>
       <c r="C23" s="9" t="s">
-        <v>255</v>
+        <v>215</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>257</v>
+        <v>315</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>253</v>
+        <v>277</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>254</v>
+        <v>270</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>99</v>
+        <v>271</v>
       </c>
       <c r="I23" s="9" t="s">
         <v>334</v>
       </c>
       <c r="J23" s="9"/>
       <c r="K23" s="9"/>
-      <c r="L23" s="9" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="12" t="s">
-        <v>279</v>
-      </c>
-      <c r="B24" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="C24" s="9" t="s">
+      <c r="L23" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Valor numérico ≥ 0; no admite texto. Obligatorio en la medición inicial (CC-020). Nombre metodológico canónico (antes altura_m). Referenciado por zona_objetivo (REGISTRO_EVALUACION). Obligatoriedad en mediciones posteriores: pendiente.</t>
+        </is>
+      </c>
+      <c r="N23" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">operativo</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MEDICIONES_DENDROMETRICAS</t>
+        </is>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="C24" s="10" t="s">
         <v>215</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>362</v>
+        <v>325</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>445</v>
-      </c>
-      <c r="F24" s="9" t="s">
-        <v>354</v>
-      </c>
-      <c r="G24" s="9" t="s">
+        <v>315</v>
+      </c>
+      <c r="F24" s="10" t="s">
+        <v>318</v>
+      </c>
+      <c r="G24" s="10" t="s">
+        <v>270</v>
+      </c>
+      <c r="H24" s="10" t="s">
+        <v>271</v>
+      </c>
+      <c r="I24" s="10" t="s">
+        <v>334</v>
+      </c>
+      <c r="J24" s="10"/>
+      <c r="K24" s="10"/>
+      <c r="L24" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Valor numérico ≥ 0; no admite texto. Obligatorio en la medición inicial (CC-020). Obligatoriedad en mediciones posteriores: pendiente.</t>
+        </is>
+      </c>
+      <c r="N24" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">operativo</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MEDICIONES_DENDROMETRICAS</t>
+        </is>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="D25" s="9" t="s">
+        <v>325</v>
+      </c>
+      <c r="E25" s="12" t="s">
+        <v>315</v>
+      </c>
+      <c r="F25" s="9" t="s">
+        <v>278</v>
+      </c>
+      <c r="G25" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="H25" s="9" t="s">
+        <v>271</v>
+      </c>
+      <c r="I25" s="9" t="s">
+        <v>334</v>
+      </c>
+      <c r="J25" s="9"/>
+      <c r="K25" s="9"/>
+      <c r="L25" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Valor numérico ≥ 0; no admite texto. Obligatorio en la medición inicial (CC-020). Obligatoriedad en mediciones posteriores: pendiente.</t>
+        </is>
+      </c>
+      <c r="N25" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">operativo</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" spans="1:14" s="23" customFormat="1" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MEDICIONES_DENDROMETRICAS</t>
+        </is>
+      </c>
+      <c r="B26" s="21" t="s">
+        <v>350</v>
+      </c>
+      <c r="C26" s="22" t="s">
+        <v>215</v>
+      </c>
+      <c r="D26" s="19" t="s">
+        <v>325</v>
+      </c>
+      <c r="E26" s="21" t="s">
+        <v>313</v>
+      </c>
+      <c r="F26" s="22" t="s">
+        <v>351</v>
+      </c>
+      <c r="G26" s="10" t="s">
         <v>282</v>
       </c>
-      <c r="H24" s="9" t="s">
-        <v>328</v>
-      </c>
-      <c r="I24" s="9" t="s">
-        <v>334</v>
-      </c>
-      <c r="J24" s="9"/>
-      <c r="K24" s="9"/>
-      <c r="L24" s="9" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="13" t="s">
-        <v>279</v>
-      </c>
-      <c r="B25" s="13" t="s">
-        <v>356</v>
-      </c>
-      <c r="C25" s="10" t="s">
-        <v>215</v>
-      </c>
-      <c r="D25" s="10" t="s">
-        <v>362</v>
-      </c>
-      <c r="E25" s="13" t="s">
-        <v>445</v>
-      </c>
-      <c r="F25" s="10" t="s">
-        <v>357</v>
-      </c>
-      <c r="G25" s="10" t="s">
-        <v>282</v>
-      </c>
-      <c r="H25" s="10" t="s">
-        <v>328</v>
-      </c>
-      <c r="I25" s="10" t="s">
-        <v>335</v>
-      </c>
-      <c r="J25" s="10"/>
-      <c r="K25" s="10" t="s">
-        <v>358</v>
-      </c>
-      <c r="L25" s="10" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="12" t="s">
-        <v>279</v>
-      </c>
-      <c r="B26" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="C26" s="9" t="s">
-        <v>215</v>
-      </c>
-      <c r="D26" s="9" t="s">
-        <v>362</v>
-      </c>
-      <c r="E26" s="12" t="s">
-        <v>445</v>
-      </c>
-      <c r="F26" s="9" t="s">
-        <v>360</v>
-      </c>
-      <c r="G26" s="9" t="s">
-        <v>282</v>
-      </c>
-      <c r="H26" s="9" t="s">
-        <v>328</v>
-      </c>
-      <c r="I26" s="9" t="s">
-        <v>335</v>
-      </c>
-      <c r="J26" s="9"/>
-      <c r="K26" s="9" t="s">
-        <v>358</v>
-      </c>
-      <c r="L26" s="9" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="12" t="s">
-        <v>279</v>
-      </c>
-      <c r="B27" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C27" s="9" t="s">
-        <v>215</v>
-      </c>
-      <c r="D27" s="9" t="s">
-        <v>362</v>
-      </c>
-      <c r="E27" s="12" t="s">
-        <v>445</v>
-      </c>
-      <c r="F27" s="9" t="s">
-        <v>363</v>
-      </c>
-      <c r="G27" s="9" t="s">
-        <v>282</v>
-      </c>
-      <c r="H27" s="9" t="s">
-        <v>328</v>
-      </c>
-      <c r="I27" s="9" t="s">
-        <v>334</v>
+      <c r="H26" s="22" t="s">
+        <v>352</v>
+      </c>
+      <c r="I26" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Opcional</t>
+        </is>
+      </c>
+      <c r="J26" s="22"/>
+      <c r="K26" s="22"/>
+      <c r="L26" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">La clasificación debe realizarse considerando la especie, las dimensiones alcanzadas, el patrón de crecimiento y el desarrollo de la copa, en relación con las características esperables para la especie. Estimación opcional: no es obligatoria para completar la medición inicial (CC-020). PENDIENTE (CC-020): tratamiento metodológico por consolidar.</t>
+        </is>
+      </c>
+      <c r="N26" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">operativo</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MEDICIONES_DENDROMETRICAS</t>
+        </is>
+      </c>
+      <c r="B27" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estado_medicion</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sistema</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sistema</t>
+        </is>
+      </c>
+      <c r="E27" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Válida al registrarse; pasa a Anulada solo mediante anulación lógica.</t>
+        </is>
+      </c>
+      <c r="F27" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Condición de validez de la medición. Una medición anulada permanece en el historial, pero no participa en la determinación del valor dendrométrico actual.</t>
+        </is>
+      </c>
+      <c r="G27" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Categoría</t>
+        </is>
+      </c>
+      <c r="H27" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Válida / Anulada</t>
+        </is>
+      </c>
+      <c r="I27" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Obligatorio</t>
+        </is>
       </c>
       <c r="J27" s="9"/>
       <c r="K27" s="9"/>
-      <c r="L27" s="9" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="13" t="s">
-        <v>279</v>
-      </c>
-      <c r="B28" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="C28" s="10" t="s">
-        <v>215</v>
-      </c>
-      <c r="D28" s="10" t="s">
-        <v>362</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>314</v>
-      </c>
-      <c r="F28" s="10" t="s">
-        <v>365</v>
-      </c>
-      <c r="G28" s="10" t="s">
-        <v>270</v>
-      </c>
-      <c r="H28" s="10" t="s">
-        <v>283</v>
-      </c>
-      <c r="I28" s="10" t="s">
-        <v>334</v>
-      </c>
-      <c r="J28" s="10"/>
-      <c r="K28" s="10"/>
-      <c r="L28" s="10" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="12" t="s">
-        <v>279</v>
-      </c>
-      <c r="B29" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="C29" s="9" t="s">
-        <v>215</v>
-      </c>
-      <c r="D29" s="9" t="s">
-        <v>362</v>
-      </c>
-      <c r="E29" s="12" t="s">
-        <v>313</v>
-      </c>
-      <c r="F29" s="9" t="s">
-        <v>368</v>
-      </c>
-      <c r="G29" s="9" t="s">
-        <v>266</v>
-      </c>
-      <c r="H29" s="9" t="s">
-        <v>370</v>
-      </c>
-      <c r="I29" s="9" t="s">
-        <v>335</v>
+      <c r="L27" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">La anulación no elimina la medición. Una corrección de un dato erróneo no cambia este estado: se realiza sobre la misma medición conservando auditoría (CC-020).</t>
+        </is>
+      </c>
+      <c r="N27" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">operativo</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MEDICIONES_DENDROMETRICAS</t>
+        </is>
+      </c>
+      <c r="B28" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">motivo_anulacion</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Usuario autorizado (permisos pendientes, PR-006)</t>
+        </is>
+      </c>
+      <c r="E28" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Registro del motivo al anular la medición.</t>
+        </is>
+      </c>
+      <c r="F28" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Motivo por el cual la medición completa deja de considerarse válida.</t>
+        </is>
+      </c>
+      <c r="G28" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Texto</t>
+        </is>
+      </c>
+      <c r="H28" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No aplica</t>
+        </is>
+      </c>
+      <c r="I28" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Condicional</t>
+        </is>
+      </c>
+      <c r="J28" s="9"/>
+      <c r="K28" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Se activa cuando estado_medicion = Anulada.</t>
+        </is>
+      </c>
+      <c r="L28" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Obligatorio al anular.</t>
+        </is>
+      </c>
+      <c r="N28" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">operativo</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MEDICIONES_DENDROMETRICAS</t>
+        </is>
+      </c>
+      <c r="B29" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">anulado_por</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vinculado por plataforma</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sistema</t>
+        </is>
+      </c>
+      <c r="E29" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Usuario autenticado que realiza la anulación.</t>
+        </is>
+      </c>
+      <c r="F29" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Usuario que anula la medición.</t>
+        </is>
+      </c>
+      <c r="G29" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Identificador (texto)</t>
+        </is>
+      </c>
+      <c r="H29" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No aplica</t>
+        </is>
+      </c>
+      <c r="I29" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Condicional</t>
+        </is>
       </c>
       <c r="J29" s="9"/>
-      <c r="K29" s="19" t="s">
-        <v>369</v>
-      </c>
-      <c r="L29" s="9" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="13" t="s">
-        <v>279</v>
-      </c>
-      <c r="B30" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="C30" s="10" t="s">
-        <v>215</v>
-      </c>
-      <c r="D30" s="10" t="s">
-        <v>362</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>445</v>
-      </c>
-      <c r="F30" s="24" t="s">
-        <v>372</v>
-      </c>
-      <c r="G30" s="10" t="s">
-        <v>282</v>
-      </c>
-      <c r="H30" s="10" t="s">
-        <v>328</v>
-      </c>
-      <c r="I30" s="10" t="s">
-        <v>334</v>
-      </c>
-      <c r="J30" s="10"/>
-      <c r="K30" s="10"/>
-      <c r="L30" s="10" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K29" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Se activa cuando estado_medicion = Anulada.</t>
+        </is>
+      </c>
+      <c r="L29" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Referencia válida al usuario. Conservar autoría histórica.</t>
+        </is>
+      </c>
+      <c r="N29" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">operativo</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MEDICIONES_DENDROMETRICAS</t>
+        </is>
+      </c>
+      <c r="B30" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fecha_anulacion</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sistema</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sistema</t>
+        </is>
+      </c>
+      <c r="E30" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fecha en que se registra la anulación.</t>
+        </is>
+      </c>
+      <c r="F30" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fecha de la anulación lógica de la medición.</t>
+        </is>
+      </c>
+      <c r="G30" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fecha</t>
+        </is>
+      </c>
+      <c r="H30" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dd/mm/aaaa</t>
+        </is>
+      </c>
+      <c r="I30" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Condicional</t>
+        </is>
+      </c>
+      <c r="J30" s="9"/>
+      <c r="K30" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Se activa cuando estado_medicion = Anulada.</t>
+        </is>
+      </c>
+      <c r="L30" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Asignada por el sistema al anular.</t>
+        </is>
+      </c>
+      <c r="N30" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">operativo</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="12" t="s">
         <v>279</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>215</v>
+        <v>250</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>362</v>
+        <v>251</v>
       </c>
       <c r="E31" s="12" t="s">
-        <v>445</v>
+        <v>252</v>
       </c>
       <c r="F31" s="9" t="s">
-        <v>373</v>
+        <v>280</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>282</v>
+        <v>254</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>328</v>
+        <v>99</v>
       </c>
       <c r="I31" s="9" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="J31" s="9"/>
-      <c r="K31" s="9" t="s">
-        <v>374</v>
-      </c>
+      <c r="K31" s="9"/>
       <c r="L31" s="9" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="12" t="s">
+        <v>319</v>
+      </c>
+      <c r="N31" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="13" t="s">
         <v>279</v>
       </c>
-      <c r="B32" s="12" t="s">
-        <v>375</v>
-      </c>
-      <c r="C32" s="9" t="s">
-        <v>215</v>
-      </c>
-      <c r="D32" s="9" t="s">
-        <v>362</v>
-      </c>
-      <c r="E32" s="12" t="s">
-        <v>445</v>
-      </c>
-      <c r="F32" s="9" t="s">
-        <v>376</v>
-      </c>
-      <c r="G32" s="9" t="s">
-        <v>282</v>
-      </c>
-      <c r="H32" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LISTAS:confirmacion_cavidad_interna</t>
-        </is>
-      </c>
-      <c r="I32" s="9" t="s">
-        <v>335</v>
-      </c>
-      <c r="J32" s="9"/>
-      <c r="K32" s="9" t="s">
-        <v>374</v>
-      </c>
-      <c r="L32" s="9" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="13" t="s">
+      <c r="B32" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C32" s="10" t="s">
+        <v>255</v>
+      </c>
+      <c r="D32" s="10" t="s">
+        <v>256</v>
+      </c>
+      <c r="E32" s="13" t="s">
+        <v>257</v>
+      </c>
+      <c r="F32" s="10" t="s">
+        <v>281</v>
+      </c>
+      <c r="G32" s="10" t="s">
+        <v>254</v>
+      </c>
+      <c r="H32" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="I32" s="10" t="s">
+        <v>334</v>
+      </c>
+      <c r="J32" s="10"/>
+      <c r="K32" s="10"/>
+      <c r="L32" s="10" t="s">
+        <v>258</v>
+      </c>
+      <c r="N32" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="12" t="s">
         <v>279</v>
       </c>
-      <c r="B33" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="C33" s="10" t="s">
-        <v>215</v>
-      </c>
-      <c r="D33" s="10" t="s">
-        <v>362</v>
+      <c r="B33" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>256</v>
       </c>
       <c r="E33" s="12" t="s">
-        <v>315</v>
-      </c>
-      <c r="F33" s="10" t="s">
-        <v>381</v>
-      </c>
-      <c r="G33" s="10" t="s">
-        <v>270</v>
-      </c>
-      <c r="H33" s="10" t="s">
-        <v>275</v>
-      </c>
-      <c r="I33" s="10" t="s">
-        <v>335</v>
-      </c>
-      <c r="J33" s="10"/>
-      <c r="K33" s="10" t="s">
-        <v>374</v>
-      </c>
-      <c r="L33" s="10" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>257</v>
+      </c>
+      <c r="F33" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="G33" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="H33" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="I33" s="9" t="s">
+        <v>334</v>
+      </c>
+      <c r="J33" s="9"/>
+      <c r="K33" s="9"/>
+      <c r="L33" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="N33" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="12" t="s">
         <v>279</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="C34" s="9" t="s">
         <v>215</v>
@@ -9707,34 +10224,37 @@
         <v>362</v>
       </c>
       <c r="E34" s="12" t="s">
-        <v>315</v>
+        <v>445</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>384</v>
+        <v>354</v>
       </c>
       <c r="G34" s="9" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="H34" s="9" t="s">
-        <v>275</v>
+        <v>328</v>
       </c>
       <c r="I34" s="9" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="J34" s="9"/>
-      <c r="K34" s="10" t="s">
-        <v>383</v>
-      </c>
+      <c r="K34" s="9"/>
       <c r="L34" s="9" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>355</v>
+      </c>
+      <c r="N34" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="13" t="s">
         <v>279</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>32</v>
+        <v>356</v>
       </c>
       <c r="C35" s="10" t="s">
         <v>215</v>
@@ -9743,34 +10263,39 @@
         <v>362</v>
       </c>
       <c r="E35" s="13" t="s">
-        <v>315</v>
+        <v>445</v>
       </c>
       <c r="F35" s="10" t="s">
-        <v>386</v>
+        <v>357</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>275</v>
+        <v>328</v>
       </c>
       <c r="I35" s="10" t="s">
         <v>335</v>
       </c>
       <c r="J35" s="10"/>
       <c r="K35" s="10" t="s">
-        <v>383</v>
+        <v>358</v>
       </c>
       <c r="L35" s="10" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>359</v>
+      </c>
+      <c r="N35" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="12" t="s">
         <v>279</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="C36" s="9" t="s">
         <v>215</v>
@@ -9779,218 +10304,238 @@
         <v>362</v>
       </c>
       <c r="E36" s="12" t="s">
-        <v>315</v>
+        <v>445</v>
       </c>
       <c r="F36" s="9" t="s">
-        <v>388</v>
+        <v>360</v>
       </c>
       <c r="G36" s="9" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="H36" s="9" t="s">
-        <v>275</v>
+        <v>328</v>
       </c>
       <c r="I36" s="9" t="s">
         <v>335</v>
       </c>
       <c r="J36" s="9"/>
       <c r="K36" s="9" t="s">
-        <v>383</v>
+        <v>358</v>
       </c>
       <c r="L36" s="9" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" s="27" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="25" t="s">
+        <v>361</v>
+      </c>
+      <c r="N36" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="12" t="s">
         <v>279</v>
       </c>
-      <c r="B37" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="C37" s="26" t="s">
-        <v>286</v>
-      </c>
-      <c r="D37" s="26" t="s">
-        <v>251</v>
-      </c>
-      <c r="E37" s="25" t="s">
-        <v>394</v>
-      </c>
-      <c r="F37" s="26" t="s">
-        <v>390</v>
-      </c>
-      <c r="G37" s="26" t="s">
+      <c r="B37" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C37" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="D37" s="9" t="s">
+        <v>362</v>
+      </c>
+      <c r="E37" s="12" t="s">
+        <v>445</v>
+      </c>
+      <c r="F37" s="9" t="s">
+        <v>363</v>
+      </c>
+      <c r="G37" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="H37" s="9" t="s">
+        <v>328</v>
+      </c>
+      <c r="I37" s="9" t="s">
+        <v>334</v>
+      </c>
+      <c r="J37" s="9"/>
+      <c r="K37" s="9"/>
+      <c r="L37" s="9" t="s">
+        <v>364</v>
+      </c>
+      <c r="N37" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="13" t="s">
+        <v>279</v>
+      </c>
+      <c r="B38" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C38" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="D38" s="10" t="s">
+        <v>362</v>
+      </c>
+      <c r="E38" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="F38" s="10" t="s">
+        <v>365</v>
+      </c>
+      <c r="G38" s="10" t="s">
         <v>270</v>
       </c>
-      <c r="H37" s="26" t="s">
-        <v>391</v>
-      </c>
-      <c r="I37" s="26" t="s">
-        <v>392</v>
-      </c>
-      <c r="J37" s="26" t="s">
-        <v>403</v>
-      </c>
-      <c r="K37" s="26" t="s">
-        <v>383</v>
-      </c>
-      <c r="L37" s="26" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="12" t="s">
+      <c r="H38" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="I38" s="10" t="s">
+        <v>334</v>
+      </c>
+      <c r="J38" s="10"/>
+      <c r="K38" s="10"/>
+      <c r="L38" s="10" t="s">
+        <v>367</v>
+      </c>
+      <c r="N38" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="12" t="s">
         <v>279</v>
       </c>
-      <c r="B38" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="C38" s="9" t="s">
+      <c r="B39" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C39" s="9" t="s">
         <v>215</v>
       </c>
-      <c r="D38" s="9" t="s">
+      <c r="D39" s="9" t="s">
         <v>362</v>
       </c>
-      <c r="E38" s="12" t="s">
-        <v>315</v>
-      </c>
-      <c r="F38" s="9" t="s">
-        <v>396</v>
-      </c>
-      <c r="G38" s="9" t="s">
-        <v>270</v>
-      </c>
-      <c r="H38" s="9" t="s">
-        <v>275</v>
-      </c>
-      <c r="I38" s="9" t="s">
+      <c r="E39" s="12" t="s">
+        <v>313</v>
+      </c>
+      <c r="F39" s="9" t="s">
+        <v>368</v>
+      </c>
+      <c r="G39" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="H39" s="9" t="s">
+        <v>370</v>
+      </c>
+      <c r="I39" s="9" t="s">
         <v>335</v>
       </c>
-      <c r="J38" s="9"/>
-      <c r="K38" s="9" t="s">
-        <v>395</v>
-      </c>
-      <c r="L38" s="9" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" s="27" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="25" t="s">
+      <c r="J39" s="9"/>
+      <c r="K39" s="19" t="s">
+        <v>369</v>
+      </c>
+      <c r="L39" s="9" t="s">
+        <v>371</v>
+      </c>
+      <c r="N39" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="13" t="s">
         <v>279</v>
       </c>
-      <c r="B39" s="25" t="s">
-        <v>36</v>
-      </c>
-      <c r="C39" s="26" t="s">
-        <v>286</v>
-      </c>
-      <c r="D39" s="26" t="s">
-        <v>398</v>
-      </c>
-      <c r="E39" s="25" t="s">
-        <v>394</v>
-      </c>
-      <c r="F39" s="25" t="s">
-        <v>400</v>
-      </c>
-      <c r="G39" s="26" t="s">
-        <v>270</v>
-      </c>
-      <c r="H39" s="26" t="s">
-        <v>275</v>
-      </c>
-      <c r="I39" s="26" t="s">
-        <v>392</v>
-      </c>
-      <c r="J39" s="26" t="s">
-        <v>402</v>
-      </c>
-      <c r="K39" s="26" t="s">
-        <v>395</v>
-      </c>
-      <c r="L39" s="26" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" s="27" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="25" t="s">
+      <c r="B40" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C40" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="D40" s="10" t="s">
+        <v>362</v>
+      </c>
+      <c r="E40" s="13" t="s">
+        <v>445</v>
+      </c>
+      <c r="F40" s="24" t="s">
+        <v>372</v>
+      </c>
+      <c r="G40" s="10" t="s">
+        <v>282</v>
+      </c>
+      <c r="H40" s="10" t="s">
+        <v>328</v>
+      </c>
+      <c r="I40" s="10" t="s">
+        <v>334</v>
+      </c>
+      <c r="J40" s="10"/>
+      <c r="K40" s="10"/>
+      <c r="L40" s="10" t="s">
+        <v>377</v>
+      </c>
+      <c r="N40" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="12" t="s">
         <v>279</v>
       </c>
-      <c r="B40" s="25" t="s">
-        <v>37</v>
-      </c>
-      <c r="C40" s="26" t="s">
-        <v>286</v>
-      </c>
-      <c r="D40" s="26" t="s">
-        <v>251</v>
-      </c>
-      <c r="E40" s="25" t="s">
-        <v>288</v>
-      </c>
-      <c r="F40" s="26" t="s">
-        <v>404</v>
-      </c>
-      <c r="G40" s="26" t="s">
-        <v>270</v>
-      </c>
-      <c r="H40" s="26" t="s">
-        <v>289</v>
-      </c>
-      <c r="I40" s="26" t="s">
-        <v>392</v>
-      </c>
-      <c r="J40" s="26" t="s">
-        <v>401</v>
-      </c>
-      <c r="K40" s="26" t="s">
-        <v>395</v>
-      </c>
-      <c r="L40" s="26" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" s="16" customFormat="1" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="28" t="s">
-        <v>279</v>
-      </c>
-      <c r="B41" s="28" t="s">
-        <v>38</v>
-      </c>
-      <c r="C41" s="29" t="s">
+      <c r="B41" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C41" s="9" t="s">
         <v>215</v>
       </c>
-      <c r="D41" s="29" t="s">
+      <c r="D41" s="9" t="s">
         <v>362</v>
       </c>
-      <c r="E41" s="28" t="s">
-        <v>479</v>
-      </c>
-      <c r="F41" s="29" t="s">
-        <v>290</v>
-      </c>
-      <c r="G41" s="29" t="s">
-        <v>266</v>
-      </c>
-      <c r="H41" s="29" t="s">
-        <v>99</v>
-      </c>
-      <c r="I41" s="29" t="s">
-        <v>406</v>
-      </c>
-      <c r="J41" s="29"/>
-      <c r="K41" s="29"/>
-      <c r="L41" s="29" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E41" s="12" t="s">
+        <v>445</v>
+      </c>
+      <c r="F41" s="9" t="s">
+        <v>373</v>
+      </c>
+      <c r="G41" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="H41" s="9" t="s">
+        <v>328</v>
+      </c>
+      <c r="I41" s="9" t="s">
+        <v>335</v>
+      </c>
+      <c r="J41" s="9"/>
+      <c r="K41" s="9" t="s">
+        <v>374</v>
+      </c>
+      <c r="L41" s="9" t="s">
+        <v>378</v>
+      </c>
+      <c r="N41" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="12" t="s">
         <v>279</v>
       </c>
       <c r="B42" s="12" t="s">
-        <v>39</v>
+        <v>375</v>
       </c>
       <c r="C42" s="9" t="s">
         <v>215</v>
@@ -10002,29 +10547,38 @@
         <v>445</v>
       </c>
       <c r="F42" s="9" t="s">
-        <v>408</v>
+        <v>376</v>
       </c>
       <c r="G42" s="9" t="s">
         <v>282</v>
       </c>
-      <c r="H42" s="9" t="s">
-        <v>328</v>
+      <c r="H42" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LISTAS:confirmacion_cavidad_interna</t>
+        </is>
       </c>
       <c r="I42" s="9" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="J42" s="9"/>
-      <c r="K42" s="9"/>
+      <c r="K42" s="9" t="s">
+        <v>374</v>
+      </c>
       <c r="L42" s="9" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>380</v>
+      </c>
+      <c r="N42" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="13" t="s">
         <v>279</v>
       </c>
       <c r="B43" s="13" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C43" s="10" t="s">
         <v>215</v>
@@ -10032,401 +10586,452 @@
       <c r="D43" s="10" t="s">
         <v>362</v>
       </c>
-      <c r="E43" s="13" t="s">
-        <v>445</v>
+      <c r="E43" s="12" t="s">
+        <v>315</v>
       </c>
       <c r="F43" s="10" t="s">
-        <v>409</v>
+        <v>381</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>282</v>
+        <v>270</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>328</v>
+        <v>275</v>
       </c>
       <c r="I43" s="10" t="s">
         <v>335</v>
       </c>
       <c r="J43" s="10"/>
       <c r="K43" s="10" t="s">
-        <v>418</v>
+        <v>374</v>
       </c>
       <c r="L43" s="10" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="13" t="s">
+        <v>382</v>
+      </c>
+      <c r="N43" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="12" t="s">
         <v>279</v>
       </c>
-      <c r="B44" s="13" t="s">
-        <v>407</v>
-      </c>
-      <c r="C44" s="10" t="s">
+      <c r="B44" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="9" t="s">
         <v>215</v>
       </c>
-      <c r="D44" s="10" t="s">
+      <c r="D44" s="9" t="s">
         <v>362</v>
       </c>
-      <c r="E44" s="13" t="s">
-        <v>445</v>
-      </c>
-      <c r="F44" s="10" t="s">
-        <v>410</v>
-      </c>
-      <c r="G44" s="10" t="s">
-        <v>282</v>
-      </c>
-      <c r="H44" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LISTAS:confirmacion_cavidad_interna</t>
-        </is>
-      </c>
-      <c r="I44" s="10" t="s">
+      <c r="E44" s="12" t="s">
+        <v>315</v>
+      </c>
+      <c r="F44" s="9" t="s">
+        <v>384</v>
+      </c>
+      <c r="G44" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="H44" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="I44" s="9" t="s">
         <v>335</v>
       </c>
-      <c r="J44" s="10"/>
+      <c r="J44" s="9"/>
       <c r="K44" s="10" t="s">
-        <v>418</v>
-      </c>
-      <c r="L44" s="10" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="12" t="s">
+        <v>383</v>
+      </c>
+      <c r="L44" s="9" t="s">
+        <v>385</v>
+      </c>
+      <c r="N44" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="13" t="s">
         <v>279</v>
       </c>
-      <c r="B45" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="C45" s="9" t="s">
+      <c r="B45" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C45" s="10" t="s">
         <v>215</v>
       </c>
-      <c r="D45" s="9" t="s">
+      <c r="D45" s="10" t="s">
         <v>362</v>
       </c>
-      <c r="E45" s="12" t="s">
+      <c r="E45" s="13" t="s">
         <v>315</v>
       </c>
-      <c r="F45" s="9" t="s">
-        <v>411</v>
-      </c>
-      <c r="G45" s="9" t="s">
+      <c r="F45" s="10" t="s">
+        <v>386</v>
+      </c>
+      <c r="G45" s="10" t="s">
         <v>270</v>
       </c>
-      <c r="H45" s="9" t="s">
+      <c r="H45" s="10" t="s">
         <v>275</v>
       </c>
-      <c r="I45" s="9" t="s">
+      <c r="I45" s="10" t="s">
         <v>335</v>
       </c>
-      <c r="J45" s="9"/>
-      <c r="K45" s="9" t="s">
-        <v>418</v>
-      </c>
-      <c r="L45" s="9" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="13" t="s">
+      <c r="J45" s="10"/>
+      <c r="K45" s="10" t="s">
+        <v>383</v>
+      </c>
+      <c r="L45" s="10" t="s">
+        <v>387</v>
+      </c>
+      <c r="N45" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="12" t="s">
         <v>279</v>
       </c>
-      <c r="B46" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="C46" s="10" t="s">
+      <c r="B46" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C46" s="9" t="s">
         <v>215</v>
       </c>
-      <c r="D46" s="10" t="s">
+      <c r="D46" s="9" t="s">
         <v>362</v>
       </c>
-      <c r="E46" s="13" t="s">
+      <c r="E46" s="12" t="s">
         <v>315</v>
       </c>
-      <c r="F46" s="10" t="s">
-        <v>412</v>
-      </c>
-      <c r="G46" s="10" t="s">
+      <c r="F46" s="9" t="s">
+        <v>388</v>
+      </c>
+      <c r="G46" s="9" t="s">
         <v>270</v>
       </c>
-      <c r="H46" s="10" t="s">
+      <c r="H46" s="9" t="s">
         <v>275</v>
       </c>
-      <c r="I46" s="10" t="s">
+      <c r="I46" s="9" t="s">
         <v>335</v>
       </c>
-      <c r="J46" s="10"/>
-      <c r="K46" s="10" t="s">
-        <v>419</v>
-      </c>
-      <c r="L46" s="10" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="12" t="s">
+      <c r="J46" s="9"/>
+      <c r="K46" s="9" t="s">
+        <v>383</v>
+      </c>
+      <c r="L46" s="9" t="s">
+        <v>389</v>
+      </c>
+      <c r="N46" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" spans="1:14" s="27" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="25" t="s">
         <v>279</v>
       </c>
-      <c r="B47" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="C47" s="9" t="s">
+      <c r="B47" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="C47" s="26" t="s">
+        <v>286</v>
+      </c>
+      <c r="D47" s="26" t="s">
+        <v>251</v>
+      </c>
+      <c r="E47" s="25" t="s">
+        <v>394</v>
+      </c>
+      <c r="F47" s="26" t="s">
+        <v>390</v>
+      </c>
+      <c r="G47" s="26" t="s">
+        <v>270</v>
+      </c>
+      <c r="H47" s="26" t="s">
+        <v>391</v>
+      </c>
+      <c r="I47" s="26" t="s">
+        <v>392</v>
+      </c>
+      <c r="J47" s="26" t="s">
+        <v>403</v>
+      </c>
+      <c r="K47" s="26" t="s">
+        <v>383</v>
+      </c>
+      <c r="L47" s="26" t="s">
+        <v>393</v>
+      </c>
+      <c r="N47" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="12" t="s">
+        <v>279</v>
+      </c>
+      <c r="B48" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C48" s="9" t="s">
         <v>215</v>
       </c>
-      <c r="D47" s="9" t="s">
+      <c r="D48" s="9" t="s">
         <v>362</v>
       </c>
-      <c r="E47" s="12" t="s">
+      <c r="E48" s="12" t="s">
         <v>315</v>
       </c>
-      <c r="F47" s="9" t="s">
-        <v>284</v>
-      </c>
-      <c r="G47" s="9" t="s">
+      <c r="F48" s="9" t="s">
+        <v>396</v>
+      </c>
+      <c r="G48" s="9" t="s">
         <v>270</v>
       </c>
-      <c r="H47" s="9" t="s">
+      <c r="H48" s="9" t="s">
         <v>275</v>
       </c>
-      <c r="I47" s="9" t="s">
+      <c r="I48" s="9" t="s">
         <v>335</v>
       </c>
-      <c r="J47" s="9"/>
-      <c r="K47" s="9" t="s">
-        <v>419</v>
-      </c>
-      <c r="L47" s="9" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="48" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="13" t="s">
-        <v>279</v>
-      </c>
-      <c r="B48" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="C48" s="10" t="s">
-        <v>215</v>
-      </c>
-      <c r="D48" s="10" t="s">
-        <v>362</v>
-      </c>
-      <c r="E48" s="13" t="s">
-        <v>315</v>
-      </c>
-      <c r="F48" s="10" t="s">
-        <v>285</v>
-      </c>
-      <c r="G48" s="10" t="s">
-        <v>270</v>
-      </c>
-      <c r="H48" s="10" t="s">
-        <v>275</v>
-      </c>
-      <c r="I48" s="10" t="s">
-        <v>335</v>
-      </c>
-      <c r="J48" s="10"/>
-      <c r="K48" s="10" t="s">
-        <v>419</v>
-      </c>
-      <c r="L48" s="10" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="49" spans="1:13" s="27" customFormat="1" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J48" s="9"/>
+      <c r="K48" s="9" t="s">
+        <v>395</v>
+      </c>
+      <c r="L48" s="9" t="s">
+        <v>397</v>
+      </c>
+      <c r="N48" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" spans="1:14" s="27" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="25" t="s">
         <v>279</v>
       </c>
       <c r="B49" s="25" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="C49" s="26" t="s">
         <v>286</v>
       </c>
       <c r="D49" s="26" t="s">
-        <v>251</v>
+        <v>398</v>
       </c>
       <c r="E49" s="25" t="s">
-        <v>287</v>
-      </c>
-      <c r="F49" s="26" t="s">
-        <v>413</v>
+        <v>394</v>
+      </c>
+      <c r="F49" s="25" t="s">
+        <v>400</v>
       </c>
       <c r="G49" s="26" t="s">
         <v>270</v>
       </c>
       <c r="H49" s="26" t="s">
-        <v>391</v>
+        <v>275</v>
       </c>
       <c r="I49" s="26" t="s">
         <v>392</v>
       </c>
       <c r="J49" s="26" t="s">
-        <v>425</v>
+        <v>402</v>
       </c>
       <c r="K49" s="26" t="s">
-        <v>419</v>
+        <v>395</v>
       </c>
       <c r="L49" s="26" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="50" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="13" t="s">
+        <v>399</v>
+      </c>
+      <c r="N49" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" spans="1:14" s="27" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="25" t="s">
         <v>279</v>
       </c>
-      <c r="B50" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="C50" s="10" t="s">
+      <c r="B50" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="C50" s="26" t="s">
+        <v>286</v>
+      </c>
+      <c r="D50" s="26" t="s">
+        <v>251</v>
+      </c>
+      <c r="E50" s="25" t="s">
+        <v>288</v>
+      </c>
+      <c r="F50" s="26" t="s">
+        <v>404</v>
+      </c>
+      <c r="G50" s="26" t="s">
+        <v>270</v>
+      </c>
+      <c r="H50" s="26" t="s">
+        <v>289</v>
+      </c>
+      <c r="I50" s="26" t="s">
+        <v>392</v>
+      </c>
+      <c r="J50" s="26" t="s">
+        <v>401</v>
+      </c>
+      <c r="K50" s="26" t="s">
+        <v>395</v>
+      </c>
+      <c r="L50" s="26" t="s">
+        <v>405</v>
+      </c>
+      <c r="N50" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" spans="1:14" s="16" customFormat="1" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="28" t="s">
+        <v>279</v>
+      </c>
+      <c r="B51" s="28" t="s">
+        <v>38</v>
+      </c>
+      <c r="C51" s="29" t="s">
         <v>215</v>
       </c>
-      <c r="D50" s="10" t="s">
+      <c r="D51" s="29" t="s">
         <v>362</v>
       </c>
-      <c r="E50" s="13" t="s">
-        <v>315</v>
-      </c>
-      <c r="F50" s="10" t="s">
-        <v>414</v>
-      </c>
-      <c r="G50" s="10" t="s">
-        <v>270</v>
-      </c>
-      <c r="H50" s="10" t="s">
-        <v>275</v>
-      </c>
-      <c r="I50" s="10" t="s">
+      <c r="E51" s="28" t="s">
+        <v>479</v>
+      </c>
+      <c r="F51" s="29" t="s">
+        <v>290</v>
+      </c>
+      <c r="G51" s="29" t="s">
+        <v>266</v>
+      </c>
+      <c r="H51" s="29" t="s">
+        <v>99</v>
+      </c>
+      <c r="I51" s="29" t="s">
+        <v>406</v>
+      </c>
+      <c r="J51" s="29"/>
+      <c r="K51" s="29"/>
+      <c r="L51" s="29" t="s">
+        <v>478</v>
+      </c>
+      <c r="N51" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="12" t="s">
+        <v>279</v>
+      </c>
+      <c r="B52" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C52" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="D52" s="9" t="s">
+        <v>362</v>
+      </c>
+      <c r="E52" s="12" t="s">
+        <v>445</v>
+      </c>
+      <c r="F52" s="9" t="s">
+        <v>408</v>
+      </c>
+      <c r="G52" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="H52" s="9" t="s">
+        <v>328</v>
+      </c>
+      <c r="I52" s="9" t="s">
+        <v>334</v>
+      </c>
+      <c r="J52" s="9"/>
+      <c r="K52" s="9"/>
+      <c r="L52" s="9" t="s">
+        <v>421</v>
+      </c>
+      <c r="N52" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="13" t="s">
+        <v>279</v>
+      </c>
+      <c r="B53" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C53" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="D53" s="10" t="s">
+        <v>362</v>
+      </c>
+      <c r="E53" s="13" t="s">
+        <v>445</v>
+      </c>
+      <c r="F53" s="10" t="s">
+        <v>409</v>
+      </c>
+      <c r="G53" s="10" t="s">
+        <v>282</v>
+      </c>
+      <c r="H53" s="10" t="s">
+        <v>328</v>
+      </c>
+      <c r="I53" s="10" t="s">
         <v>335</v>
       </c>
-      <c r="J50" s="10"/>
-      <c r="K50" s="10" t="s">
-        <v>420</v>
-      </c>
-      <c r="L50" s="10" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="51" spans="1:13" s="27" customFormat="1" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="25" t="s">
-        <v>279</v>
-      </c>
-      <c r="B51" s="25" t="s">
-        <v>47</v>
-      </c>
-      <c r="C51" s="26" t="s">
-        <v>286</v>
-      </c>
-      <c r="D51" s="26" t="s">
-        <v>251</v>
-      </c>
-      <c r="E51" s="25" t="s">
-        <v>415</v>
-      </c>
-      <c r="F51" s="26" t="s">
-        <v>416</v>
-      </c>
-      <c r="G51" s="26" t="s">
-        <v>270</v>
-      </c>
-      <c r="H51" s="26" t="s">
-        <v>275</v>
-      </c>
-      <c r="I51" s="26" t="s">
-        <v>392</v>
-      </c>
-      <c r="J51" s="26" t="s">
-        <v>433</v>
-      </c>
-      <c r="K51" s="26" t="s">
-        <v>420</v>
-      </c>
-      <c r="L51" s="26" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="52" spans="1:13" s="27" customFormat="1" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="25" t="s">
-        <v>279</v>
-      </c>
-      <c r="B52" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="C52" s="26" t="s">
-        <v>286</v>
-      </c>
-      <c r="D52" s="26" t="s">
-        <v>251</v>
-      </c>
-      <c r="E52" s="25" t="s">
-        <v>288</v>
-      </c>
-      <c r="F52" s="26" t="s">
-        <v>417</v>
-      </c>
-      <c r="G52" s="26" t="s">
-        <v>270</v>
-      </c>
-      <c r="H52" s="26" t="s">
-        <v>289</v>
-      </c>
-      <c r="I52" s="26" t="s">
-        <v>392</v>
-      </c>
-      <c r="J52" s="26" t="s">
-        <v>434</v>
-      </c>
-      <c r="K52" s="26" t="s">
-        <v>420</v>
-      </c>
-      <c r="L52" s="26" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="53" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="12" t="s">
-        <v>279</v>
-      </c>
-      <c r="B53" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="C53" s="9" t="s">
-        <v>215</v>
-      </c>
-      <c r="D53" s="9" t="s">
-        <v>362</v>
-      </c>
-      <c r="E53" s="12" t="s">
-        <v>445</v>
-      </c>
-      <c r="F53" s="9" t="s">
-        <v>435</v>
-      </c>
-      <c r="G53" s="9" t="s">
-        <v>282</v>
-      </c>
-      <c r="H53" s="9" t="s">
-        <v>328</v>
-      </c>
-      <c r="I53" s="9" t="s">
-        <v>334</v>
-      </c>
-      <c r="J53" s="9"/>
-      <c r="K53" s="9"/>
-      <c r="L53" s="9" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="54" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J53" s="10"/>
+      <c r="K53" s="10" t="s">
+        <v>418</v>
+      </c>
+      <c r="L53" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="N53" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="13" t="s">
         <v>279</v>
       </c>
       <c r="B54" s="13" t="s">
-        <v>50</v>
+        <v>407</v>
       </c>
       <c r="C54" s="10" t="s">
         <v>215</v>
@@ -10435,37 +11040,41 @@
         <v>362</v>
       </c>
       <c r="E54" s="13" t="s">
-        <v>313</v>
+        <v>445</v>
       </c>
       <c r="F54" s="10" t="s">
-        <v>437</v>
+        <v>410</v>
       </c>
       <c r="G54" s="10" t="s">
         <v>282</v>
       </c>
-      <c r="H54" s="10" t="s">
-        <v>439</v>
+      <c r="H54" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LISTAS:confirmacion_cavidad_interna</t>
+        </is>
       </c>
       <c r="I54" s="10" t="s">
         <v>335</v>
       </c>
       <c r="J54" s="10"/>
       <c r="K54" s="10" t="s">
-        <v>438</v>
+        <v>418</v>
       </c>
       <c r="L54" s="10" t="s">
-        <v>440</v>
-      </c>
-      <c r="M54" s="8" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="55" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+        <v>423</v>
+      </c>
+      <c r="N54" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="12" t="s">
         <v>279</v>
       </c>
       <c r="B55" s="12" t="s">
-        <v>442</v>
+        <v>41</v>
       </c>
       <c r="C55" s="9" t="s">
         <v>215</v>
@@ -10474,32 +11083,39 @@
         <v>362</v>
       </c>
       <c r="E55" s="12" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="F55" s="9" t="s">
-        <v>443</v>
+        <v>411</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>282</v>
+        <v>270</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>328</v>
+        <v>275</v>
       </c>
       <c r="I55" s="9" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="J55" s="9"/>
-      <c r="K55" s="9"/>
+      <c r="K55" s="9" t="s">
+        <v>418</v>
+      </c>
       <c r="L55" s="9" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="56" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+        <v>424</v>
+      </c>
+      <c r="N55" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="13" t="s">
         <v>279</v>
       </c>
       <c r="B56" s="13" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="C56" s="10" t="s">
         <v>215</v>
@@ -10508,32 +11124,39 @@
         <v>362</v>
       </c>
       <c r="E56" s="13" t="s">
-        <v>445</v>
+        <v>315</v>
       </c>
       <c r="F56" s="10" t="s">
-        <v>446</v>
+        <v>412</v>
       </c>
       <c r="G56" s="10" t="s">
-        <v>282</v>
-      </c>
-      <c r="H56" s="9" t="s">
-        <v>328</v>
-      </c>
-      <c r="I56" s="9" t="s">
-        <v>334</v>
+        <v>270</v>
+      </c>
+      <c r="H56" s="10" t="s">
+        <v>275</v>
+      </c>
+      <c r="I56" s="10" t="s">
+        <v>335</v>
       </c>
       <c r="J56" s="10"/>
-      <c r="K56" s="10"/>
+      <c r="K56" s="10" t="s">
+        <v>419</v>
+      </c>
       <c r="L56" s="10" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="57" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+        <v>429</v>
+      </c>
+      <c r="N56" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="12" t="s">
         <v>279</v>
       </c>
       <c r="B57" s="12" t="s">
-        <v>448</v>
+        <v>43</v>
       </c>
       <c r="C57" s="9" t="s">
         <v>215</v>
@@ -10542,32 +11165,39 @@
         <v>362</v>
       </c>
       <c r="E57" s="12" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="F57" s="9" t="s">
-        <v>449</v>
+        <v>284</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>282</v>
+        <v>270</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>328</v>
+        <v>275</v>
       </c>
       <c r="I57" s="9" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="J57" s="9"/>
-      <c r="K57" s="9"/>
+      <c r="K57" s="9" t="s">
+        <v>419</v>
+      </c>
       <c r="L57" s="9" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="58" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.35">
+        <v>426</v>
+      </c>
+      <c r="N57" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="13" t="s">
         <v>279</v>
       </c>
-      <c r="B58" s="6" t="s">
-        <v>453</v>
+      <c r="B58" s="13" t="s">
+        <v>44</v>
       </c>
       <c r="C58" s="10" t="s">
         <v>215</v>
@@ -10576,68 +11206,82 @@
         <v>362</v>
       </c>
       <c r="E58" s="13" t="s">
-        <v>445</v>
+        <v>315</v>
       </c>
       <c r="F58" s="10" t="s">
-        <v>456</v>
+        <v>285</v>
       </c>
       <c r="G58" s="10" t="s">
-        <v>282</v>
+        <v>270</v>
       </c>
       <c r="H58" s="10" t="s">
-        <v>328</v>
-      </c>
-      <c r="I58" s="9" t="s">
-        <v>334</v>
+        <v>275</v>
+      </c>
+      <c r="I58" s="10" t="s">
+        <v>335</v>
       </c>
       <c r="J58" s="10"/>
-      <c r="K58" s="10"/>
+      <c r="K58" s="10" t="s">
+        <v>419</v>
+      </c>
       <c r="L58" s="10" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="59" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="12" t="s">
+        <v>427</v>
+      </c>
+      <c r="N58" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" spans="1:14" s="27" customFormat="1" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="25" t="s">
         <v>279</v>
       </c>
-      <c r="B59" s="12" t="s">
-        <v>454</v>
-      </c>
-      <c r="C59" s="9" t="s">
-        <v>215</v>
-      </c>
-      <c r="D59" s="9" t="s">
-        <v>362</v>
-      </c>
-      <c r="E59" s="12" t="s">
-        <v>445</v>
-      </c>
-      <c r="F59" s="9" t="s">
-        <v>459</v>
-      </c>
-      <c r="G59" s="10" t="s">
-        <v>282</v>
-      </c>
-      <c r="H59" s="9" t="s">
-        <v>458</v>
-      </c>
-      <c r="I59" s="9" t="s">
-        <v>451</v>
-      </c>
-      <c r="J59" s="9"/>
-      <c r="K59" s="9" t="s">
-        <v>460</v>
-      </c>
-      <c r="L59" s="9" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="60" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B59" s="25" t="s">
+        <v>45</v>
+      </c>
+      <c r="C59" s="26" t="s">
+        <v>286</v>
+      </c>
+      <c r="D59" s="26" t="s">
+        <v>251</v>
+      </c>
+      <c r="E59" s="25" t="s">
+        <v>287</v>
+      </c>
+      <c r="F59" s="26" t="s">
+        <v>413</v>
+      </c>
+      <c r="G59" s="26" t="s">
+        <v>270</v>
+      </c>
+      <c r="H59" s="26" t="s">
+        <v>391</v>
+      </c>
+      <c r="I59" s="26" t="s">
+        <v>392</v>
+      </c>
+      <c r="J59" s="26" t="s">
+        <v>425</v>
+      </c>
+      <c r="K59" s="26" t="s">
+        <v>419</v>
+      </c>
+      <c r="L59" s="26" t="s">
+        <v>428</v>
+      </c>
+      <c r="N59" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" spans="1:14" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="13" t="s">
         <v>279</v>
       </c>
       <c r="B60" s="13" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="C60" s="10" t="s">
         <v>215</v>
@@ -10646,106 +11290,125 @@
         <v>362</v>
       </c>
       <c r="E60" s="13" t="s">
-        <v>445</v>
+        <v>315</v>
       </c>
       <c r="F60" s="10" t="s">
-        <v>462</v>
+        <v>414</v>
       </c>
       <c r="G60" s="10" t="s">
-        <v>282</v>
+        <v>270</v>
       </c>
       <c r="H60" s="10" t="s">
-        <v>452</v>
-      </c>
-      <c r="I60" s="9" t="s">
-        <v>451</v>
+        <v>275</v>
+      </c>
+      <c r="I60" s="10" t="s">
+        <v>335</v>
       </c>
       <c r="J60" s="10"/>
-      <c r="K60" s="9" t="s">
-        <v>463</v>
+      <c r="K60" s="10" t="s">
+        <v>420</v>
       </c>
       <c r="L60" s="10" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="61" spans="1:13" s="20" customFormat="1" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="18" t="s">
+        <v>430</v>
+      </c>
+      <c r="N60" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" spans="1:14" s="27" customFormat="1" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="25" t="s">
         <v>279</v>
       </c>
-      <c r="B61" s="18" t="s">
-        <v>455</v>
-      </c>
-      <c r="C61" s="19" t="s">
-        <v>215</v>
-      </c>
-      <c r="D61" s="19" t="s">
-        <v>362</v>
-      </c>
-      <c r="E61" s="18" t="s">
-        <v>315</v>
-      </c>
-      <c r="F61" s="19" t="s">
-        <v>465</v>
-      </c>
-      <c r="G61" s="19" t="s">
+      <c r="B61" s="25" t="s">
+        <v>47</v>
+      </c>
+      <c r="C61" s="26" t="s">
+        <v>286</v>
+      </c>
+      <c r="D61" s="26" t="s">
+        <v>251</v>
+      </c>
+      <c r="E61" s="25" t="s">
+        <v>415</v>
+      </c>
+      <c r="F61" s="26" t="s">
+        <v>416</v>
+      </c>
+      <c r="G61" s="26" t="s">
         <v>270</v>
       </c>
-      <c r="H61" s="19" t="s">
+      <c r="H61" s="26" t="s">
         <v>275</v>
       </c>
-      <c r="I61" s="19" t="s">
-        <v>467</v>
-      </c>
-      <c r="J61" s="19"/>
-      <c r="K61" s="19" t="s">
-        <v>463</v>
-      </c>
-      <c r="L61" s="19" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="62" spans="1:13" s="20" customFormat="1" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="18" t="s">
+      <c r="I61" s="26" t="s">
+        <v>392</v>
+      </c>
+      <c r="J61" s="26" t="s">
+        <v>433</v>
+      </c>
+      <c r="K61" s="26" t="s">
+        <v>420</v>
+      </c>
+      <c r="L61" s="26" t="s">
+        <v>431</v>
+      </c>
+      <c r="N61" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" spans="1:14" s="27" customFormat="1" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="25" t="s">
         <v>279</v>
       </c>
-      <c r="B62" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="C62" s="19" t="s">
-        <v>215</v>
-      </c>
-      <c r="D62" s="19" t="s">
-        <v>362</v>
-      </c>
-      <c r="E62" s="18" t="s">
-        <v>315</v>
-      </c>
-      <c r="F62" s="19" t="s">
-        <v>468</v>
-      </c>
-      <c r="G62" s="19" t="s">
+      <c r="B62" s="25" t="s">
+        <v>48</v>
+      </c>
+      <c r="C62" s="26" t="s">
+        <v>286</v>
+      </c>
+      <c r="D62" s="26" t="s">
+        <v>251</v>
+      </c>
+      <c r="E62" s="25" t="s">
+        <v>288</v>
+      </c>
+      <c r="F62" s="26" t="s">
+        <v>417</v>
+      </c>
+      <c r="G62" s="26" t="s">
         <v>270</v>
       </c>
-      <c r="H62" s="19" t="s">
-        <v>275</v>
-      </c>
-      <c r="I62" s="19" t="s">
-        <v>467</v>
-      </c>
-      <c r="J62" s="19"/>
-      <c r="K62" s="19" t="s">
-        <v>463</v>
-      </c>
-      <c r="L62" s="19" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="63" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H62" s="26" t="s">
+        <v>289</v>
+      </c>
+      <c r="I62" s="26" t="s">
+        <v>392</v>
+      </c>
+      <c r="J62" s="26" t="s">
+        <v>434</v>
+      </c>
+      <c r="K62" s="26" t="s">
+        <v>420</v>
+      </c>
+      <c r="L62" s="26" t="s">
+        <v>432</v>
+      </c>
+      <c r="N62" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" spans="1:14" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="12" t="s">
         <v>279</v>
       </c>
       <c r="B63" s="12" t="s">
-        <v>470</v>
+        <v>49</v>
       </c>
       <c r="C63" s="9" t="s">
         <v>215</v>
@@ -10757,7 +11420,7 @@
         <v>445</v>
       </c>
       <c r="F63" s="9" t="s">
-        <v>471</v>
+        <v>435</v>
       </c>
       <c r="G63" s="9" t="s">
         <v>282</v>
@@ -10771,15 +11434,20 @@
       <c r="J63" s="9"/>
       <c r="K63" s="9"/>
       <c r="L63" s="9" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="64" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+        <v>436</v>
+      </c>
+      <c r="N63" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" spans="1:14" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="13" t="s">
         <v>279</v>
       </c>
       <c r="B64" s="13" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C64" s="10" t="s">
         <v>215</v>
@@ -10788,34 +11456,42 @@
         <v>362</v>
       </c>
       <c r="E64" s="13" t="s">
-        <v>445</v>
+        <v>313</v>
       </c>
       <c r="F64" s="10" t="s">
-        <v>291</v>
+        <v>437</v>
       </c>
       <c r="G64" s="10" t="s">
         <v>282</v>
       </c>
       <c r="H64" s="10" t="s">
-        <v>328</v>
+        <v>439</v>
       </c>
       <c r="I64" s="10" t="s">
-        <v>451</v>
+        <v>335</v>
       </c>
       <c r="J64" s="10"/>
       <c r="K64" s="10" t="s">
-        <v>474</v>
+        <v>438</v>
       </c>
       <c r="L64" s="10" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="65" spans="1:12" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+        <v>440</v>
+      </c>
+      <c r="M64" s="8" t="s">
+        <v>441</v>
+      </c>
+      <c r="N64" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" spans="1:14" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="12" t="s">
         <v>279</v>
       </c>
       <c r="B65" s="12" t="s">
-        <v>475</v>
+        <v>442</v>
       </c>
       <c r="C65" s="9" t="s">
         <v>215</v>
@@ -10824,10 +11500,10 @@
         <v>362</v>
       </c>
       <c r="E65" s="12" t="s">
-        <v>445</v>
+        <v>313</v>
       </c>
       <c r="F65" s="9" t="s">
-        <v>476</v>
+        <v>443</v>
       </c>
       <c r="G65" s="9" t="s">
         <v>282</v>
@@ -10836,56 +11512,64 @@
         <v>328</v>
       </c>
       <c r="I65" s="9" t="s">
-        <v>451</v>
+        <v>334</v>
       </c>
       <c r="J65" s="9"/>
-      <c r="K65" s="9" t="s">
-        <v>474</v>
-      </c>
+      <c r="K65" s="9"/>
       <c r="L65" s="9" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="66" spans="1:12" s="16" customFormat="1" ht="28.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A66" s="28" t="s">
+        <v>444</v>
+      </c>
+      <c r="N65" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" spans="1:14" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="13" t="s">
         <v>279</v>
       </c>
-      <c r="B66" s="28" t="s">
-        <v>55</v>
-      </c>
-      <c r="C66" s="29" t="s">
+      <c r="B66" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="C66" s="10" t="s">
         <v>215</v>
       </c>
-      <c r="D66" s="29" t="s">
+      <c r="D66" s="10" t="s">
         <v>362</v>
       </c>
-      <c r="E66" s="28" t="s">
-        <v>479</v>
-      </c>
-      <c r="F66" s="29" t="s">
-        <v>292</v>
-      </c>
-      <c r="G66" s="29" t="s">
-        <v>266</v>
-      </c>
-      <c r="H66" s="29" t="s">
-        <v>99</v>
-      </c>
-      <c r="I66" s="29" t="s">
-        <v>406</v>
-      </c>
-      <c r="J66" s="29"/>
-      <c r="K66" s="29"/>
-      <c r="L66" s="29" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="67" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E66" s="13" t="s">
+        <v>445</v>
+      </c>
+      <c r="F66" s="10" t="s">
+        <v>446</v>
+      </c>
+      <c r="G66" s="10" t="s">
+        <v>282</v>
+      </c>
+      <c r="H66" s="9" t="s">
+        <v>328</v>
+      </c>
+      <c r="I66" s="9" t="s">
+        <v>334</v>
+      </c>
+      <c r="J66" s="10"/>
+      <c r="K66" s="10"/>
+      <c r="L66" s="10" t="s">
+        <v>447</v>
+      </c>
+      <c r="N66" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" spans="1:14" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="12" t="s">
         <v>279</v>
       </c>
       <c r="B67" s="12" t="s">
-        <v>56</v>
+        <v>448</v>
       </c>
       <c r="C67" s="9" t="s">
         <v>215</v>
@@ -10894,10 +11578,10 @@
         <v>362</v>
       </c>
       <c r="E67" s="12" t="s">
-        <v>445</v>
+        <v>313</v>
       </c>
       <c r="F67" s="9" t="s">
-        <v>480</v>
+        <v>449</v>
       </c>
       <c r="G67" s="9" t="s">
         <v>282</v>
@@ -10911,193 +11595,223 @@
       <c r="J67" s="9"/>
       <c r="K67" s="9"/>
       <c r="L67" s="9" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="68" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="12" t="s">
+        <v>450</v>
+      </c>
+      <c r="N67" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" spans="1:14" ht="28.8" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A68" s="13" t="s">
         <v>279</v>
       </c>
-      <c r="B68" s="12" t="s">
-        <v>484</v>
-      </c>
-      <c r="C68" s="9" t="s">
+      <c r="B68" s="6" t="s">
+        <v>453</v>
+      </c>
+      <c r="C68" s="10" t="s">
         <v>215</v>
       </c>
-      <c r="D68" s="9" t="s">
+      <c r="D68" s="10" t="s">
         <v>362</v>
       </c>
       <c r="E68" s="13" t="s">
-        <v>315</v>
-      </c>
-      <c r="F68" s="9" t="s">
-        <v>488</v>
-      </c>
-      <c r="G68" s="9" t="s">
-        <v>270</v>
-      </c>
-      <c r="H68" s="9" t="s">
-        <v>490</v>
+        <v>445</v>
+      </c>
+      <c r="F68" s="10" t="s">
+        <v>456</v>
+      </c>
+      <c r="G68" s="10" t="s">
+        <v>282</v>
+      </c>
+      <c r="H68" s="10" t="s">
+        <v>328</v>
       </c>
       <c r="I68" s="9" t="s">
-        <v>451</v>
-      </c>
-      <c r="J68" s="9"/>
-      <c r="K68" s="9" t="s">
-        <v>482</v>
-      </c>
-      <c r="L68" s="9" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="69" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>334</v>
+      </c>
+      <c r="J68" s="10"/>
+      <c r="K68" s="10"/>
+      <c r="L68" s="10" t="s">
+        <v>457</v>
+      </c>
+      <c r="N68" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" spans="1:14" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="12" t="s">
         <v>279</v>
       </c>
-      <c r="B69" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="C69" s="10" t="s">
+      <c r="B69" s="12" t="s">
+        <v>454</v>
+      </c>
+      <c r="C69" s="9" t="s">
         <v>215</v>
       </c>
-      <c r="D69" s="10" t="s">
+      <c r="D69" s="9" t="s">
         <v>362</v>
       </c>
-      <c r="E69" s="13" t="s">
+      <c r="E69" s="12" t="s">
+        <v>445</v>
+      </c>
+      <c r="F69" s="9" t="s">
+        <v>459</v>
+      </c>
+      <c r="G69" s="10" t="s">
+        <v>282</v>
+      </c>
+      <c r="H69" s="9" t="s">
+        <v>458</v>
+      </c>
+      <c r="I69" s="9" t="s">
+        <v>451</v>
+      </c>
+      <c r="J69" s="9"/>
+      <c r="K69" s="9" t="s">
+        <v>460</v>
+      </c>
+      <c r="L69" s="9" t="s">
+        <v>461</v>
+      </c>
+      <c r="N69" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" spans="1:14" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="13" t="s">
+        <v>279</v>
+      </c>
+      <c r="B70" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="C70" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="D70" s="10" t="s">
+        <v>362</v>
+      </c>
+      <c r="E70" s="13" t="s">
+        <v>445</v>
+      </c>
+      <c r="F70" s="10" t="s">
+        <v>462</v>
+      </c>
+      <c r="G70" s="10" t="s">
+        <v>282</v>
+      </c>
+      <c r="H70" s="10" t="s">
+        <v>452</v>
+      </c>
+      <c r="I70" s="9" t="s">
+        <v>451</v>
+      </c>
+      <c r="J70" s="10"/>
+      <c r="K70" s="9" t="s">
+        <v>463</v>
+      </c>
+      <c r="L70" s="10" t="s">
+        <v>464</v>
+      </c>
+      <c r="N70" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" spans="1:14" s="20" customFormat="1" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="18" t="s">
+        <v>279</v>
+      </c>
+      <c r="B71" s="18" t="s">
+        <v>455</v>
+      </c>
+      <c r="C71" s="19" t="s">
+        <v>215</v>
+      </c>
+      <c r="D71" s="19" t="s">
+        <v>362</v>
+      </c>
+      <c r="E71" s="18" t="s">
         <v>315</v>
       </c>
-      <c r="F69" s="10" t="s">
-        <v>491</v>
-      </c>
-      <c r="G69" s="10" t="s">
+      <c r="F71" s="19" t="s">
+        <v>465</v>
+      </c>
+      <c r="G71" s="19" t="s">
         <v>270</v>
       </c>
-      <c r="H69" s="10" t="s">
+      <c r="H71" s="19" t="s">
         <v>275</v>
       </c>
-      <c r="I69" s="10" t="s">
-        <v>451</v>
-      </c>
-      <c r="J69" s="10"/>
-      <c r="K69" s="10" t="s">
-        <v>482</v>
-      </c>
-      <c r="L69" s="10" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="70" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="12" t="s">
+      <c r="I71" s="19" t="s">
+        <v>467</v>
+      </c>
+      <c r="J71" s="19"/>
+      <c r="K71" s="19" t="s">
+        <v>463</v>
+      </c>
+      <c r="L71" s="19" t="s">
+        <v>466</v>
+      </c>
+      <c r="N71" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" spans="1:14" s="20" customFormat="1" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="18" t="s">
         <v>279</v>
       </c>
-      <c r="B70" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="C70" s="9" t="s">
+      <c r="B72" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="C72" s="19" t="s">
         <v>215</v>
       </c>
-      <c r="D70" s="9" t="s">
+      <c r="D72" s="19" t="s">
         <v>362</v>
       </c>
-      <c r="E70" s="12" t="s">
-        <v>445</v>
-      </c>
-      <c r="F70" s="9" t="s">
-        <v>492</v>
-      </c>
-      <c r="G70" s="9" t="s">
-        <v>282</v>
-      </c>
-      <c r="H70" s="9" t="s">
-        <v>328</v>
-      </c>
-      <c r="I70" s="9" t="s">
-        <v>334</v>
-      </c>
-      <c r="J70" s="9"/>
-      <c r="K70" s="9"/>
-      <c r="L70" s="9" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="71" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="12" t="s">
-        <v>279</v>
-      </c>
-      <c r="B71" s="12" t="s">
-        <v>485</v>
-      </c>
-      <c r="C71" s="9" t="s">
-        <v>215</v>
-      </c>
-      <c r="D71" s="9" t="s">
-        <v>362</v>
-      </c>
-      <c r="E71" s="12" t="s">
+      <c r="E72" s="18" t="s">
         <v>315</v>
       </c>
-      <c r="F71" s="9" t="s">
-        <v>494</v>
-      </c>
-      <c r="G71" s="10" t="s">
+      <c r="F72" s="19" t="s">
+        <v>468</v>
+      </c>
+      <c r="G72" s="19" t="s">
         <v>270</v>
       </c>
-      <c r="H71" s="9" t="s">
-        <v>495</v>
-      </c>
-      <c r="I71" s="9" t="s">
-        <v>451</v>
-      </c>
-      <c r="J71" s="9"/>
-      <c r="K71" s="9" t="s">
-        <v>496</v>
-      </c>
-      <c r="L71" s="9" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="72" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="12" t="s">
-        <v>279</v>
-      </c>
-      <c r="B72" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="C72" s="10" t="s">
-        <v>215</v>
-      </c>
-      <c r="D72" s="10" t="s">
-        <v>362</v>
-      </c>
-      <c r="E72" s="13" t="s">
-        <v>315</v>
-      </c>
-      <c r="F72" s="10" t="s">
-        <v>498</v>
-      </c>
-      <c r="G72" s="10" t="s">
-        <v>270</v>
-      </c>
-      <c r="H72" s="10" t="s">
+      <c r="H72" s="19" t="s">
         <v>275</v>
       </c>
-      <c r="I72" s="10" t="s">
-        <v>451</v>
-      </c>
-      <c r="J72" s="10"/>
-      <c r="K72" s="10" t="s">
-        <v>496</v>
-      </c>
-      <c r="L72" s="10" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="73" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I72" s="19" t="s">
+        <v>467</v>
+      </c>
+      <c r="J72" s="19"/>
+      <c r="K72" s="19" t="s">
+        <v>463</v>
+      </c>
+      <c r="L72" s="19" t="s">
+        <v>469</v>
+      </c>
+      <c r="N72" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" spans="1:14" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="12" t="s">
         <v>279</v>
       </c>
       <c r="B73" s="12" t="s">
-        <v>60</v>
+        <v>470</v>
       </c>
       <c r="C73" s="9" t="s">
         <v>215</v>
@@ -11106,16 +11820,16 @@
         <v>362</v>
       </c>
       <c r="E73" s="12" t="s">
-        <v>315</v>
+        <v>445</v>
       </c>
       <c r="F73" s="9" t="s">
-        <v>293</v>
+        <v>471</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="H73" s="9" t="s">
-        <v>490</v>
+        <v>328</v>
       </c>
       <c r="I73" s="9" t="s">
         <v>334</v>
@@ -11123,15 +11837,20 @@
       <c r="J73" s="9"/>
       <c r="K73" s="9"/>
       <c r="L73" s="9" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="74" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="12" t="s">
+        <v>472</v>
+      </c>
+      <c r="N73" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" spans="1:14" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="13" t="s">
         <v>279</v>
       </c>
       <c r="B74" s="13" t="s">
-        <v>486</v>
+        <v>54</v>
       </c>
       <c r="C74" s="10" t="s">
         <v>215</v>
@@ -11140,134 +11859,158 @@
         <v>362</v>
       </c>
       <c r="E74" s="13" t="s">
-        <v>315</v>
+        <v>445</v>
       </c>
       <c r="F74" s="10" t="s">
-        <v>500</v>
+        <v>291</v>
       </c>
       <c r="G74" s="10" t="s">
         <v>282</v>
       </c>
       <c r="H74" s="10" t="s">
-        <v>490</v>
+        <v>328</v>
       </c>
       <c r="I74" s="10" t="s">
-        <v>334</v>
+        <v>451</v>
       </c>
       <c r="J74" s="10"/>
-      <c r="K74" s="10"/>
+      <c r="K74" s="10" t="s">
+        <v>474</v>
+      </c>
       <c r="L74" s="10" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="75" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>473</v>
+      </c>
+      <c r="N74" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" spans="1:14" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="12" t="s">
         <v>279</v>
       </c>
-      <c r="B75" s="13" t="s">
-        <v>487</v>
-      </c>
-      <c r="C75" s="10" t="s">
+      <c r="B75" s="12" t="s">
+        <v>475</v>
+      </c>
+      <c r="C75" s="9" t="s">
         <v>215</v>
       </c>
-      <c r="D75" s="10" t="s">
+      <c r="D75" s="9" t="s">
         <v>362</v>
       </c>
-      <c r="E75" s="13" t="s">
-        <v>315</v>
-      </c>
-      <c r="F75" s="10" t="s">
-        <v>502</v>
-      </c>
-      <c r="G75" s="10" t="s">
+      <c r="E75" s="12" t="s">
+        <v>445</v>
+      </c>
+      <c r="F75" s="9" t="s">
+        <v>476</v>
+      </c>
+      <c r="G75" s="9" t="s">
         <v>282</v>
       </c>
-      <c r="H75" s="10" t="s">
-        <v>490</v>
-      </c>
-      <c r="I75" s="10" t="s">
+      <c r="H75" s="9" t="s">
+        <v>328</v>
+      </c>
+      <c r="I75" s="9" t="s">
+        <v>451</v>
+      </c>
+      <c r="J75" s="9"/>
+      <c r="K75" s="9" t="s">
+        <v>474</v>
+      </c>
+      <c r="L75" s="9" t="s">
+        <v>477</v>
+      </c>
+      <c r="N75" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" spans="1:14" s="16" customFormat="1" ht="28.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A76" s="28" t="s">
+        <v>279</v>
+      </c>
+      <c r="B76" s="28" t="s">
+        <v>55</v>
+      </c>
+      <c r="C76" s="29" t="s">
+        <v>215</v>
+      </c>
+      <c r="D76" s="29" t="s">
+        <v>362</v>
+      </c>
+      <c r="E76" s="28" t="s">
+        <v>479</v>
+      </c>
+      <c r="F76" s="29" t="s">
+        <v>292</v>
+      </c>
+      <c r="G76" s="29" t="s">
+        <v>266</v>
+      </c>
+      <c r="H76" s="29" t="s">
+        <v>99</v>
+      </c>
+      <c r="I76" s="29" t="s">
+        <v>406</v>
+      </c>
+      <c r="J76" s="29"/>
+      <c r="K76" s="29"/>
+      <c r="L76" s="29" t="s">
+        <v>478</v>
+      </c>
+      <c r="N76" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="12" t="s">
+        <v>279</v>
+      </c>
+      <c r="B77" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="C77" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="D77" s="9" t="s">
+        <v>362</v>
+      </c>
+      <c r="E77" s="12" t="s">
+        <v>445</v>
+      </c>
+      <c r="F77" s="9" t="s">
+        <v>480</v>
+      </c>
+      <c r="G77" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="H77" s="9" t="s">
+        <v>328</v>
+      </c>
+      <c r="I77" s="9" t="s">
         <v>334</v>
       </c>
-      <c r="J75" s="10"/>
-      <c r="K75" s="10"/>
-      <c r="L75" s="10" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="76" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="13" t="s">
-        <v>279</v>
-      </c>
-      <c r="B76" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="C76" s="10" t="s">
-        <v>215</v>
-      </c>
-      <c r="D76" s="10" t="s">
-        <v>362</v>
-      </c>
-      <c r="E76" s="13" t="s">
-        <v>445</v>
-      </c>
-      <c r="F76" s="10" t="s">
-        <v>504</v>
-      </c>
-      <c r="G76" s="10" t="s">
-        <v>282</v>
-      </c>
-      <c r="H76" s="10" t="s">
-        <v>328</v>
-      </c>
-      <c r="I76" s="10" t="s">
-        <v>334</v>
-      </c>
-      <c r="J76" s="10"/>
-      <c r="K76" s="10"/>
-      <c r="L76" s="10" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="77" spans="1:12" s="16" customFormat="1" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="28" t="s">
-        <v>279</v>
-      </c>
-      <c r="B77" s="28" t="s">
-        <v>62</v>
-      </c>
-      <c r="C77" s="29" t="s">
-        <v>215</v>
-      </c>
-      <c r="D77" s="29" t="s">
-        <v>362</v>
-      </c>
-      <c r="E77" s="28" t="s">
-        <v>479</v>
-      </c>
-      <c r="F77" s="29" t="s">
-        <v>292</v>
-      </c>
-      <c r="G77" s="29" t="s">
-        <v>266</v>
-      </c>
-      <c r="H77" s="29" t="s">
-        <v>99</v>
-      </c>
-      <c r="I77" s="29" t="s">
-        <v>406</v>
-      </c>
-      <c r="J77" s="29"/>
-      <c r="K77" s="29"/>
-      <c r="L77" s="29" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="78" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J77" s="9"/>
+      <c r="K77" s="9"/>
+      <c r="L77" s="9" t="s">
+        <v>481</v>
+      </c>
+      <c r="N77" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="12" t="s">
         <v>279</v>
       </c>
       <c r="B78" s="12" t="s">
-        <v>63</v>
+        <v>484</v>
       </c>
       <c r="C78" s="9" t="s">
         <v>215</v>
@@ -11275,33 +12018,40 @@
       <c r="D78" s="9" t="s">
         <v>362</v>
       </c>
-      <c r="E78" s="12" t="s">
-        <v>445</v>
+      <c r="E78" s="13" t="s">
+        <v>315</v>
       </c>
       <c r="F78" s="9" t="s">
-        <v>505</v>
+        <v>488</v>
       </c>
       <c r="G78" s="9" t="s">
-        <v>282</v>
+        <v>270</v>
       </c>
       <c r="H78" s="9" t="s">
-        <v>328</v>
+        <v>490</v>
       </c>
       <c r="I78" s="9" t="s">
-        <v>334</v>
+        <v>451</v>
       </c>
       <c r="J78" s="9"/>
-      <c r="K78" s="9"/>
+      <c r="K78" s="9" t="s">
+        <v>482</v>
+      </c>
       <c r="L78" s="9" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="79" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="13" t="s">
+        <v>489</v>
+      </c>
+      <c r="N78" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="12" t="s">
         <v>279</v>
       </c>
       <c r="B79" s="13" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="C79" s="10" t="s">
         <v>215</v>
@@ -11310,34 +12060,39 @@
         <v>362</v>
       </c>
       <c r="E79" s="13" t="s">
-        <v>445</v>
+        <v>315</v>
       </c>
       <c r="F79" s="10" t="s">
-        <v>294</v>
+        <v>491</v>
       </c>
       <c r="G79" s="10" t="s">
-        <v>282</v>
-      </c>
-      <c r="H79" s="9" t="s">
-        <v>328</v>
-      </c>
-      <c r="I79" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="H79" s="10" t="s">
+        <v>275</v>
+      </c>
+      <c r="I79" s="10" t="s">
         <v>451</v>
       </c>
       <c r="J79" s="10"/>
       <c r="K79" s="10" t="s">
-        <v>549</v>
+        <v>482</v>
       </c>
       <c r="L79" s="10" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="80" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>483</v>
+      </c>
+      <c r="N79" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="12" t="s">
         <v>279</v>
       </c>
       <c r="B80" s="12" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="C80" s="9" t="s">
         <v>215</v>
@@ -11345,179 +12100,198 @@
       <c r="D80" s="9" t="s">
         <v>362</v>
       </c>
-      <c r="E80" s="13" t="s">
+      <c r="E80" s="12" t="s">
         <v>445</v>
       </c>
       <c r="F80" s="9" t="s">
-        <v>508</v>
-      </c>
-      <c r="G80" s="10" t="s">
+        <v>492</v>
+      </c>
+      <c r="G80" s="9" t="s">
         <v>282</v>
       </c>
       <c r="H80" s="9" t="s">
-        <v>295</v>
-      </c>
-      <c r="I80" s="10" t="s">
+        <v>328</v>
+      </c>
+      <c r="I80" s="9" t="s">
+        <v>334</v>
+      </c>
+      <c r="J80" s="9"/>
+      <c r="K80" s="9"/>
+      <c r="L80" s="9" t="s">
+        <v>493</v>
+      </c>
+      <c r="N80" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="12" t="s">
+        <v>279</v>
+      </c>
+      <c r="B81" s="12" t="s">
+        <v>485</v>
+      </c>
+      <c r="C81" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="D81" s="9" t="s">
+        <v>362</v>
+      </c>
+      <c r="E81" s="12" t="s">
+        <v>315</v>
+      </c>
+      <c r="F81" s="9" t="s">
+        <v>494</v>
+      </c>
+      <c r="G81" s="10" t="s">
+        <v>270</v>
+      </c>
+      <c r="H81" s="9" t="s">
+        <v>495</v>
+      </c>
+      <c r="I81" s="9" t="s">
         <v>451</v>
       </c>
-      <c r="J80" s="9"/>
-      <c r="K80" s="9" t="s">
-        <v>509</v>
-      </c>
-      <c r="L80" s="9" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="81" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="13" t="s">
-        <v>279</v>
-      </c>
-      <c r="B81" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="C81" s="10" t="s">
-        <v>215</v>
-      </c>
-      <c r="D81" s="10" t="s">
-        <v>362</v>
-      </c>
-      <c r="E81" s="13" t="s">
-        <v>445</v>
-      </c>
-      <c r="F81" s="10" t="s">
-        <v>511</v>
-      </c>
-      <c r="G81" s="10" t="s">
-        <v>282</v>
-      </c>
-      <c r="H81" s="10" t="s">
-        <v>328</v>
-      </c>
-      <c r="I81" s="10" t="s">
-        <v>451</v>
-      </c>
-      <c r="J81" s="10"/>
-      <c r="K81" s="10" t="s">
-        <v>509</v>
-      </c>
-      <c r="L81" s="10" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="82" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J81" s="9"/>
+      <c r="K81" s="9" t="s">
+        <v>496</v>
+      </c>
+      <c r="L81" s="9" t="s">
+        <v>497</v>
+      </c>
+      <c r="N81" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="12" t="s">
         <v>279</v>
       </c>
-      <c r="B82" s="12" t="s">
-        <v>513</v>
-      </c>
-      <c r="C82" s="9" t="s">
+      <c r="B82" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="C82" s="10" t="s">
         <v>215</v>
       </c>
-      <c r="D82" s="9" t="s">
+      <c r="D82" s="10" t="s">
         <v>362</v>
       </c>
-      <c r="E82" s="12" t="s">
-        <v>445</v>
-      </c>
-      <c r="F82" s="9" t="s">
-        <v>514</v>
-      </c>
-      <c r="G82" s="9" t="s">
-        <v>282</v>
-      </c>
-      <c r="H82" s="9" t="s">
-        <v>328</v>
-      </c>
-      <c r="I82" s="9" t="s">
+      <c r="E82" s="13" t="s">
+        <v>315</v>
+      </c>
+      <c r="F82" s="10" t="s">
+        <v>498</v>
+      </c>
+      <c r="G82" s="10" t="s">
+        <v>270</v>
+      </c>
+      <c r="H82" s="10" t="s">
+        <v>275</v>
+      </c>
+      <c r="I82" s="10" t="s">
         <v>451</v>
       </c>
-      <c r="J82" s="9"/>
-      <c r="K82" s="9" t="s">
-        <v>515</v>
-      </c>
-      <c r="L82" s="9" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="83" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="13" t="s">
+      <c r="J82" s="10"/>
+      <c r="K82" s="10" t="s">
+        <v>496</v>
+      </c>
+      <c r="L82" s="10" t="s">
+        <v>483</v>
+      </c>
+      <c r="N82" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="12" t="s">
         <v>279</v>
       </c>
-      <c r="B83" s="13" t="s">
-        <v>517</v>
-      </c>
-      <c r="C83" s="10" t="s">
+      <c r="B83" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="C83" s="9" t="s">
         <v>215</v>
       </c>
-      <c r="D83" s="10" t="s">
+      <c r="D83" s="9" t="s">
         <v>362</v>
       </c>
-      <c r="E83" s="13" t="s">
-        <v>445</v>
-      </c>
-      <c r="F83" s="10" t="s">
-        <v>519</v>
-      </c>
-      <c r="G83" s="10" t="s">
-        <v>282</v>
+      <c r="E83" s="12" t="s">
+        <v>315</v>
+      </c>
+      <c r="F83" s="9" t="s">
+        <v>293</v>
+      </c>
+      <c r="G83" s="9" t="s">
+        <v>270</v>
       </c>
       <c r="H83" s="9" t="s">
-        <v>328</v>
+        <v>490</v>
       </c>
       <c r="I83" s="9" t="s">
-        <v>451</v>
+        <v>334</v>
       </c>
       <c r="J83" s="9"/>
-      <c r="K83" s="9" t="s">
-        <v>515</v>
-      </c>
-      <c r="L83" s="10" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="84" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K83" s="9"/>
+      <c r="L83" s="9" t="s">
+        <v>499</v>
+      </c>
+      <c r="N83" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="12" t="s">
         <v>279</v>
       </c>
-      <c r="B84" s="12" t="s">
-        <v>520</v>
-      </c>
-      <c r="C84" s="9" t="s">
+      <c r="B84" s="13" t="s">
+        <v>486</v>
+      </c>
+      <c r="C84" s="10" t="s">
         <v>215</v>
       </c>
-      <c r="D84" s="9" t="s">
+      <c r="D84" s="10" t="s">
         <v>362</v>
       </c>
-      <c r="E84" s="12" t="s">
-        <v>445</v>
-      </c>
-      <c r="F84" s="9" t="s">
-        <v>521</v>
-      </c>
-      <c r="G84" s="9" t="s">
+      <c r="E84" s="13" t="s">
+        <v>315</v>
+      </c>
+      <c r="F84" s="10" t="s">
+        <v>500</v>
+      </c>
+      <c r="G84" s="10" t="s">
         <v>282</v>
       </c>
-      <c r="H84" s="9" t="s">
-        <v>328</v>
-      </c>
-      <c r="I84" s="9" t="s">
-        <v>451</v>
-      </c>
-      <c r="J84" s="9"/>
-      <c r="K84" s="9" t="s">
-        <v>515</v>
-      </c>
-      <c r="L84" s="9" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="85" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="13" t="s">
+      <c r="H84" s="10" t="s">
+        <v>490</v>
+      </c>
+      <c r="I84" s="10" t="s">
+        <v>334</v>
+      </c>
+      <c r="J84" s="10"/>
+      <c r="K84" s="10"/>
+      <c r="L84" s="10" t="s">
+        <v>501</v>
+      </c>
+      <c r="N84" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="12" t="s">
         <v>279</v>
       </c>
       <c r="B85" s="13" t="s">
-        <v>523</v>
+        <v>487</v>
       </c>
       <c r="C85" s="10" t="s">
         <v>215</v>
@@ -11526,106 +12300,115 @@
         <v>362</v>
       </c>
       <c r="E85" s="13" t="s">
-        <v>445</v>
+        <v>315</v>
       </c>
       <c r="F85" s="10" t="s">
-        <v>524</v>
+        <v>502</v>
       </c>
       <c r="G85" s="10" t="s">
         <v>282</v>
       </c>
-      <c r="H85" s="9" t="s">
+      <c r="H85" s="10" t="s">
+        <v>490</v>
+      </c>
+      <c r="I85" s="10" t="s">
+        <v>334</v>
+      </c>
+      <c r="J85" s="10"/>
+      <c r="K85" s="10"/>
+      <c r="L85" s="10" t="s">
+        <v>503</v>
+      </c>
+      <c r="N85" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="13" t="s">
+        <v>279</v>
+      </c>
+      <c r="B86" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="C86" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="D86" s="10" t="s">
+        <v>362</v>
+      </c>
+      <c r="E86" s="13" t="s">
+        <v>445</v>
+      </c>
+      <c r="F86" s="10" t="s">
+        <v>504</v>
+      </c>
+      <c r="G86" s="10" t="s">
+        <v>282</v>
+      </c>
+      <c r="H86" s="10" t="s">
         <v>328</v>
       </c>
-      <c r="I85" s="9" t="s">
-        <v>451</v>
-      </c>
-      <c r="J85" s="9"/>
-      <c r="K85" s="9" t="s">
-        <v>515</v>
-      </c>
-      <c r="L85" s="10" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="86" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="12" t="s">
+      <c r="I86" s="10" t="s">
+        <v>334</v>
+      </c>
+      <c r="J86" s="10"/>
+      <c r="K86" s="10"/>
+      <c r="L86" s="10" t="s">
+        <v>504</v>
+      </c>
+      <c r="N86" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" spans="1:14" s="16" customFormat="1" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A87" s="28" t="s">
         <v>279</v>
       </c>
-      <c r="B86" s="12" t="s">
-        <v>526</v>
-      </c>
-      <c r="C86" s="9" t="s">
+      <c r="B87" s="28" t="s">
+        <v>62</v>
+      </c>
+      <c r="C87" s="29" t="s">
         <v>215</v>
       </c>
-      <c r="D86" s="9" t="s">
+      <c r="D87" s="29" t="s">
         <v>362</v>
       </c>
-      <c r="E86" s="12" t="s">
-        <v>445</v>
-      </c>
-      <c r="F86" s="9" t="s">
-        <v>527</v>
-      </c>
-      <c r="G86" s="9" t="s">
-        <v>282</v>
-      </c>
-      <c r="H86" s="9" t="s">
-        <v>328</v>
-      </c>
-      <c r="I86" s="9" t="s">
-        <v>451</v>
-      </c>
-      <c r="J86" s="9"/>
-      <c r="K86" s="9" t="s">
-        <v>515</v>
-      </c>
-      <c r="L86" s="9" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="87" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="13" t="s">
-        <v>279</v>
-      </c>
-      <c r="B87" s="13" t="s">
-        <v>529</v>
-      </c>
-      <c r="C87" s="10" t="s">
-        <v>215</v>
-      </c>
-      <c r="D87" s="10" t="s">
-        <v>362</v>
-      </c>
-      <c r="E87" s="13" t="s">
-        <v>315</v>
-      </c>
-      <c r="F87" s="10" t="s">
-        <v>530</v>
-      </c>
-      <c r="G87" s="10" t="s">
-        <v>270</v>
-      </c>
-      <c r="H87" s="10" t="s">
-        <v>275</v>
-      </c>
-      <c r="I87" s="10" t="s">
-        <v>451</v>
-      </c>
-      <c r="J87" s="10"/>
-      <c r="K87" s="10" t="s">
-        <v>531</v>
-      </c>
-      <c r="L87" s="10" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="88" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E87" s="28" t="s">
+        <v>479</v>
+      </c>
+      <c r="F87" s="29" t="s">
+        <v>292</v>
+      </c>
+      <c r="G87" s="29" t="s">
+        <v>266</v>
+      </c>
+      <c r="H87" s="29" t="s">
+        <v>99</v>
+      </c>
+      <c r="I87" s="29" t="s">
+        <v>406</v>
+      </c>
+      <c r="J87" s="29"/>
+      <c r="K87" s="29"/>
+      <c r="L87" s="29" t="s">
+        <v>478</v>
+      </c>
+      <c r="N87" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="12" t="s">
         <v>279</v>
       </c>
       <c r="B88" s="12" t="s">
-        <v>533</v>
+        <v>63</v>
       </c>
       <c r="C88" s="9" t="s">
         <v>215</v>
@@ -11637,31 +12420,34 @@
         <v>445</v>
       </c>
       <c r="F88" s="9" t="s">
-        <v>534</v>
-      </c>
-      <c r="G88" s="15" t="s">
-        <v>296</v>
-      </c>
-      <c r="H88" s="15" t="s">
-        <v>297</v>
+        <v>505</v>
+      </c>
+      <c r="G88" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="H88" s="9" t="s">
+        <v>328</v>
       </c>
       <c r="I88" s="9" t="s">
-        <v>451</v>
+        <v>334</v>
       </c>
       <c r="J88" s="9"/>
-      <c r="K88" s="9" t="s">
-        <v>535</v>
-      </c>
+      <c r="K88" s="9"/>
       <c r="L88" s="9" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="89" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>506</v>
+      </c>
+      <c r="N88" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="13" t="s">
         <v>279</v>
       </c>
       <c r="B89" s="13" t="s">
-        <v>537</v>
+        <v>64</v>
       </c>
       <c r="C89" s="10" t="s">
         <v>215</v>
@@ -11670,34 +12456,39 @@
         <v>362</v>
       </c>
       <c r="E89" s="13" t="s">
-        <v>315</v>
+        <v>445</v>
       </c>
       <c r="F89" s="10" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="G89" s="10" t="s">
-        <v>270</v>
-      </c>
-      <c r="H89" s="10" t="s">
-        <v>275</v>
+        <v>282</v>
+      </c>
+      <c r="H89" s="9" t="s">
+        <v>328</v>
       </c>
       <c r="I89" s="9" t="s">
         <v>451</v>
       </c>
-      <c r="J89" s="9"/>
-      <c r="K89" s="9" t="s">
-        <v>535</v>
+      <c r="J89" s="10"/>
+      <c r="K89" s="10" t="s">
+        <v>549</v>
       </c>
       <c r="L89" s="10" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="90" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>507</v>
+      </c>
+      <c r="N89" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="12" t="s">
         <v>279</v>
       </c>
       <c r="B90" s="12" t="s">
-        <v>539</v>
+        <v>65</v>
       </c>
       <c r="C90" s="9" t="s">
         <v>215</v>
@@ -11705,35 +12496,40 @@
       <c r="D90" s="9" t="s">
         <v>362</v>
       </c>
-      <c r="E90" s="12" t="s">
-        <v>315</v>
+      <c r="E90" s="13" t="s">
+        <v>445</v>
       </c>
       <c r="F90" s="9" t="s">
-        <v>299</v>
-      </c>
-      <c r="G90" s="9" t="s">
-        <v>270</v>
+        <v>508</v>
+      </c>
+      <c r="G90" s="10" t="s">
+        <v>282</v>
       </c>
       <c r="H90" s="9" t="s">
-        <v>275</v>
-      </c>
-      <c r="I90" s="9" t="s">
+        <v>295</v>
+      </c>
+      <c r="I90" s="10" t="s">
         <v>451</v>
       </c>
       <c r="J90" s="9"/>
       <c r="K90" s="9" t="s">
-        <v>535</v>
+        <v>509</v>
       </c>
       <c r="L90" s="9" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="91" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>510</v>
+      </c>
+      <c r="N90" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="13" t="s">
         <v>279</v>
       </c>
       <c r="B91" s="13" t="s">
-        <v>541</v>
+        <v>66</v>
       </c>
       <c r="C91" s="10" t="s">
         <v>215</v>
@@ -11742,34 +12538,39 @@
         <v>362</v>
       </c>
       <c r="E91" s="13" t="s">
-        <v>315</v>
+        <v>445</v>
       </c>
       <c r="F91" s="10" t="s">
-        <v>542</v>
+        <v>511</v>
       </c>
       <c r="G91" s="10" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="H91" s="10" t="s">
-        <v>300</v>
+        <v>328</v>
       </c>
       <c r="I91" s="10" t="s">
         <v>451</v>
       </c>
       <c r="J91" s="10"/>
       <c r="K91" s="10" t="s">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="L91" s="10" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="92" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>512</v>
+      </c>
+      <c r="N91" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="12" t="s">
         <v>279</v>
       </c>
       <c r="B92" s="12" t="s">
-        <v>67</v>
+        <v>513</v>
       </c>
       <c r="C92" s="9" t="s">
         <v>215</v>
@@ -11781,7 +12582,7 @@
         <v>445</v>
       </c>
       <c r="F92" s="9" t="s">
-        <v>301</v>
+        <v>514</v>
       </c>
       <c r="G92" s="9" t="s">
         <v>282</v>
@@ -11797,15 +12598,20 @@
         <v>515</v>
       </c>
       <c r="L92" s="9" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="93" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>516</v>
+      </c>
+      <c r="N92" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="13" t="s">
         <v>279</v>
       </c>
       <c r="B93" s="13" t="s">
-        <v>68</v>
+        <v>517</v>
       </c>
       <c r="C93" s="10" t="s">
         <v>215</v>
@@ -11814,322 +12620,367 @@
         <v>362</v>
       </c>
       <c r="E93" s="13" t="s">
+        <v>445</v>
+      </c>
+      <c r="F93" s="10" t="s">
+        <v>519</v>
+      </c>
+      <c r="G93" s="10" t="s">
+        <v>282</v>
+      </c>
+      <c r="H93" s="9" t="s">
+        <v>328</v>
+      </c>
+      <c r="I93" s="9" t="s">
+        <v>451</v>
+      </c>
+      <c r="J93" s="9"/>
+      <c r="K93" s="9" t="s">
+        <v>515</v>
+      </c>
+      <c r="L93" s="10" t="s">
+        <v>518</v>
+      </c>
+      <c r="N93" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A94" s="12" t="s">
+        <v>279</v>
+      </c>
+      <c r="B94" s="12" t="s">
+        <v>520</v>
+      </c>
+      <c r="C94" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="D94" s="9" t="s">
+        <v>362</v>
+      </c>
+      <c r="E94" s="12" t="s">
+        <v>445</v>
+      </c>
+      <c r="F94" s="9" t="s">
+        <v>521</v>
+      </c>
+      <c r="G94" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="H94" s="9" t="s">
+        <v>328</v>
+      </c>
+      <c r="I94" s="9" t="s">
+        <v>451</v>
+      </c>
+      <c r="J94" s="9"/>
+      <c r="K94" s="9" t="s">
+        <v>515</v>
+      </c>
+      <c r="L94" s="9" t="s">
+        <v>522</v>
+      </c>
+      <c r="N94" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A95" s="13" t="s">
+        <v>279</v>
+      </c>
+      <c r="B95" s="13" t="s">
+        <v>523</v>
+      </c>
+      <c r="C95" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="D95" s="10" t="s">
+        <v>362</v>
+      </c>
+      <c r="E95" s="13" t="s">
+        <v>445</v>
+      </c>
+      <c r="F95" s="10" t="s">
+        <v>524</v>
+      </c>
+      <c r="G95" s="10" t="s">
+        <v>282</v>
+      </c>
+      <c r="H95" s="9" t="s">
+        <v>328</v>
+      </c>
+      <c r="I95" s="9" t="s">
+        <v>451</v>
+      </c>
+      <c r="J95" s="9"/>
+      <c r="K95" s="9" t="s">
+        <v>515</v>
+      </c>
+      <c r="L95" s="10" t="s">
+        <v>525</v>
+      </c>
+      <c r="N95" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A96" s="12" t="s">
+        <v>279</v>
+      </c>
+      <c r="B96" s="12" t="s">
+        <v>526</v>
+      </c>
+      <c r="C96" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="D96" s="9" t="s">
+        <v>362</v>
+      </c>
+      <c r="E96" s="12" t="s">
+        <v>445</v>
+      </c>
+      <c r="F96" s="9" t="s">
+        <v>527</v>
+      </c>
+      <c r="G96" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="H96" s="9" t="s">
+        <v>328</v>
+      </c>
+      <c r="I96" s="9" t="s">
+        <v>451</v>
+      </c>
+      <c r="J96" s="9"/>
+      <c r="K96" s="9" t="s">
+        <v>515</v>
+      </c>
+      <c r="L96" s="9" t="s">
+        <v>528</v>
+      </c>
+      <c r="N96" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A97" s="13" t="s">
+        <v>279</v>
+      </c>
+      <c r="B97" s="13" t="s">
+        <v>529</v>
+      </c>
+      <c r="C97" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="D97" s="10" t="s">
+        <v>362</v>
+      </c>
+      <c r="E97" s="13" t="s">
         <v>315</v>
       </c>
-      <c r="F93" s="10" t="s">
-        <v>545</v>
-      </c>
-      <c r="G93" s="10" t="s">
+      <c r="F97" s="10" t="s">
+        <v>530</v>
+      </c>
+      <c r="G97" s="10" t="s">
         <v>270</v>
       </c>
-      <c r="H93" s="10" t="s">
-        <v>271</v>
-      </c>
-      <c r="I93" s="10" t="s">
+      <c r="H97" s="10" t="s">
+        <v>275</v>
+      </c>
+      <c r="I97" s="10" t="s">
         <v>451</v>
       </c>
-      <c r="J93" s="10"/>
-      <c r="K93" s="10" t="s">
-        <v>515</v>
-      </c>
-      <c r="L93" s="10" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="94" spans="1:12" s="32" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="30" t="s">
+      <c r="J97" s="10"/>
+      <c r="K97" s="10" t="s">
+        <v>531</v>
+      </c>
+      <c r="L97" s="10" t="s">
+        <v>532</v>
+      </c>
+      <c r="N97" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A98" s="12" t="s">
         <v>279</v>
       </c>
-      <c r="B94" s="30" t="s">
-        <v>69</v>
-      </c>
-      <c r="C94" s="31" t="s">
+      <c r="B98" s="12" t="s">
+        <v>533</v>
+      </c>
+      <c r="C98" s="9" t="s">
         <v>215</v>
       </c>
-      <c r="D94" s="31" t="s">
+      <c r="D98" s="9" t="s">
         <v>362</v>
       </c>
-      <c r="E94" s="30" t="s">
+      <c r="E98" s="12" t="s">
         <v>445</v>
       </c>
-      <c r="F94" s="31" t="s">
-        <v>546</v>
-      </c>
-      <c r="G94" s="31" t="s">
-        <v>282</v>
-      </c>
-      <c r="H94" s="31" t="s">
-        <v>328</v>
-      </c>
-      <c r="I94" s="31" t="s">
+      <c r="F98" s="9" t="s">
+        <v>534</v>
+      </c>
+      <c r="G98" s="15" t="s">
+        <v>296</v>
+      </c>
+      <c r="H98" s="15" t="s">
+        <v>297</v>
+      </c>
+      <c r="I98" s="9" t="s">
         <v>451</v>
       </c>
-      <c r="J94" s="31"/>
-      <c r="K94" s="31" t="s">
-        <v>515</v>
-      </c>
-      <c r="L94" s="31" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="95" spans="1:12" s="35" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="33" t="s">
+      <c r="J98" s="9"/>
+      <c r="K98" s="9" t="s">
+        <v>535</v>
+      </c>
+      <c r="L98" s="9" t="s">
+        <v>536</v>
+      </c>
+      <c r="N98" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A99" s="13" t="s">
         <v>279</v>
       </c>
-      <c r="B95" s="33" t="s">
-        <v>70</v>
-      </c>
-      <c r="C95" s="34" t="s">
+      <c r="B99" s="13" t="s">
+        <v>537</v>
+      </c>
+      <c r="C99" s="10" t="s">
         <v>215</v>
       </c>
-      <c r="D95" s="34" t="s">
+      <c r="D99" s="10" t="s">
         <v>362</v>
       </c>
-      <c r="E95" s="33" t="s">
-        <v>445</v>
-      </c>
-      <c r="F95" s="34" t="s">
-        <v>548</v>
-      </c>
-      <c r="G95" s="34" t="s">
-        <v>282</v>
-      </c>
-      <c r="H95" s="34" t="s">
-        <v>328</v>
-      </c>
-      <c r="I95" s="34" t="s">
-        <v>451</v>
-      </c>
-      <c r="J95" s="34"/>
-      <c r="K95" s="34" t="s">
-        <v>549</v>
-      </c>
-      <c r="L95" s="34" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="96" spans="1:12" s="35" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="33" t="s">
-        <v>279</v>
-      </c>
-      <c r="B96" s="33" t="s">
-        <v>553</v>
-      </c>
-      <c r="C96" s="34" t="s">
-        <v>215</v>
-      </c>
-      <c r="D96" s="34" t="s">
-        <v>362</v>
-      </c>
-      <c r="E96" s="33" t="s">
-        <v>445</v>
-      </c>
-      <c r="F96" s="34" t="s">
-        <v>554</v>
-      </c>
-      <c r="G96" s="34" t="s">
-        <v>282</v>
-      </c>
-      <c r="H96" s="34" t="s">
-        <v>555</v>
-      </c>
-      <c r="I96" s="34" t="s">
-        <v>451</v>
-      </c>
-      <c r="J96" s="34"/>
-      <c r="K96" s="34" t="s">
-        <v>551</v>
-      </c>
-      <c r="L96" s="34" t="s">
-        <v>556</v>
-      </c>
-    </row>
-    <row r="97" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="12" t="s">
-        <v>279</v>
-      </c>
-      <c r="B97" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="C97" s="9" t="s">
-        <v>215</v>
-      </c>
-      <c r="D97" s="9" t="s">
-        <v>362</v>
-      </c>
-      <c r="E97" s="12" t="s">
-        <v>445</v>
-      </c>
-      <c r="F97" s="9" t="s">
-        <v>302</v>
-      </c>
-      <c r="G97" s="9" t="s">
-        <v>282</v>
-      </c>
-      <c r="H97" s="9" t="s">
-        <v>328</v>
-      </c>
-      <c r="I97" s="9" t="s">
-        <v>451</v>
-      </c>
-      <c r="J97" s="9"/>
-      <c r="K97" s="9" t="s">
-        <v>551</v>
-      </c>
-      <c r="L97" s="9" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="98" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="13" t="s">
-        <v>279</v>
-      </c>
-      <c r="B98" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="C98" s="10" t="s">
-        <v>215</v>
-      </c>
-      <c r="D98" s="10" t="s">
-        <v>362</v>
-      </c>
-      <c r="E98" s="13" t="s">
-        <v>445</v>
-      </c>
-      <c r="F98" s="10" t="s">
-        <v>559</v>
-      </c>
-      <c r="G98" s="10" t="s">
-        <v>282</v>
-      </c>
-      <c r="H98" s="10" t="s">
-        <v>328</v>
-      </c>
-      <c r="I98" s="10" t="s">
-        <v>451</v>
-      </c>
-      <c r="J98" s="10"/>
-      <c r="K98" s="9" t="s">
-        <v>557</v>
-      </c>
-      <c r="L98" s="10" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="99" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="12" t="s">
-        <v>279</v>
-      </c>
-      <c r="B99" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="C99" s="9" t="s">
-        <v>215</v>
-      </c>
-      <c r="D99" s="9" t="s">
-        <v>362</v>
-      </c>
-      <c r="E99" s="12" t="s">
-        <v>445</v>
-      </c>
-      <c r="F99" s="9" t="s">
-        <v>558</v>
-      </c>
-      <c r="G99" s="9" t="s">
-        <v>282</v>
-      </c>
-      <c r="H99" s="9" t="s">
-        <v>328</v>
+      <c r="E99" s="13" t="s">
+        <v>315</v>
+      </c>
+      <c r="F99" s="10" t="s">
+        <v>298</v>
+      </c>
+      <c r="G99" s="10" t="s">
+        <v>270</v>
+      </c>
+      <c r="H99" s="10" t="s">
+        <v>275</v>
       </c>
       <c r="I99" s="9" t="s">
         <v>451</v>
       </c>
       <c r="J99" s="9"/>
       <c r="K99" s="9" t="s">
-        <v>557</v>
-      </c>
-      <c r="L99" s="9" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="100" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="13" t="s">
+        <v>535</v>
+      </c>
+      <c r="L99" s="10" t="s">
+        <v>538</v>
+      </c>
+      <c r="N99" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A100" s="12" t="s">
         <v>279</v>
       </c>
-      <c r="B100" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="C100" s="10" t="s">
+      <c r="B100" s="12" t="s">
+        <v>539</v>
+      </c>
+      <c r="C100" s="9" t="s">
         <v>215</v>
       </c>
-      <c r="D100" s="10" t="s">
+      <c r="D100" s="9" t="s">
         <v>362</v>
       </c>
-      <c r="E100" s="13" t="s">
-        <v>445</v>
-      </c>
-      <c r="F100" s="10" t="s">
-        <v>561</v>
-      </c>
-      <c r="G100" s="10" t="s">
-        <v>282</v>
-      </c>
-      <c r="H100" s="10" t="s">
-        <v>328</v>
-      </c>
-      <c r="I100" s="10" t="s">
+      <c r="E100" s="12" t="s">
+        <v>315</v>
+      </c>
+      <c r="F100" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="G100" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="H100" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="I100" s="9" t="s">
         <v>451</v>
       </c>
-      <c r="J100" s="10"/>
+      <c r="J100" s="9"/>
       <c r="K100" s="9" t="s">
-        <v>557</v>
-      </c>
-      <c r="L100" s="10" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="101" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="12" t="s">
+        <v>535</v>
+      </c>
+      <c r="L100" s="9" t="s">
+        <v>540</v>
+      </c>
+      <c r="N100" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A101" s="13" t="s">
         <v>279</v>
       </c>
-      <c r="B101" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C101" s="9" t="s">
+      <c r="B101" s="13" t="s">
+        <v>541</v>
+      </c>
+      <c r="C101" s="10" t="s">
         <v>215</v>
       </c>
-      <c r="D101" s="9" t="s">
+      <c r="D101" s="10" t="s">
         <v>362</v>
       </c>
-      <c r="E101" s="12" t="s">
-        <v>445</v>
-      </c>
-      <c r="F101" s="9" t="s">
-        <v>562</v>
-      </c>
-      <c r="G101" s="9" t="s">
-        <v>282</v>
-      </c>
-      <c r="H101" s="9" t="s">
-        <v>328</v>
-      </c>
-      <c r="I101" s="9" t="s">
+      <c r="E101" s="13" t="s">
+        <v>315</v>
+      </c>
+      <c r="F101" s="10" t="s">
+        <v>542</v>
+      </c>
+      <c r="G101" s="10" t="s">
+        <v>270</v>
+      </c>
+      <c r="H101" s="10" t="s">
+        <v>300</v>
+      </c>
+      <c r="I101" s="10" t="s">
         <v>451</v>
       </c>
-      <c r="J101" s="9"/>
-      <c r="K101" s="9" t="s">
-        <v>557</v>
-      </c>
-      <c r="L101" s="9" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="102" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J101" s="10"/>
+      <c r="K101" s="10" t="s">
+        <v>515</v>
+      </c>
+      <c r="L101" s="10" t="s">
+        <v>276</v>
+      </c>
+      <c r="N101" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="12" t="s">
         <v>279</v>
       </c>
       <c r="B102" s="12" t="s">
-        <v>563</v>
+        <v>67</v>
       </c>
       <c r="C102" s="9" t="s">
         <v>215</v>
@@ -12138,176 +12989,203 @@
         <v>362</v>
       </c>
       <c r="E102" s="12" t="s">
-        <v>315</v>
+        <v>445</v>
       </c>
       <c r="F102" s="9" t="s">
-        <v>564</v>
+        <v>301</v>
       </c>
       <c r="G102" s="9" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="H102" s="9" t="s">
-        <v>275</v>
+        <v>328</v>
       </c>
       <c r="I102" s="9" t="s">
         <v>451</v>
       </c>
       <c r="J102" s="9"/>
       <c r="K102" s="9" t="s">
-        <v>565</v>
+        <v>515</v>
       </c>
       <c r="L102" s="9" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="103" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="12" t="s">
+        <v>543</v>
+      </c>
+      <c r="N102" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A103" s="13" t="s">
         <v>279</v>
       </c>
-      <c r="B103" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="C103" s="9" t="s">
+      <c r="B103" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="C103" s="10" t="s">
         <v>215</v>
       </c>
-      <c r="D103" s="9" t="s">
+      <c r="D103" s="10" t="s">
         <v>362</v>
       </c>
-      <c r="E103" s="12" t="s">
+      <c r="E103" s="13" t="s">
         <v>315</v>
       </c>
-      <c r="F103" s="9" t="s">
-        <v>303</v>
-      </c>
-      <c r="G103" s="9" t="s">
+      <c r="F103" s="10" t="s">
+        <v>545</v>
+      </c>
+      <c r="G103" s="10" t="s">
         <v>270</v>
       </c>
-      <c r="H103" s="9" t="s">
-        <v>300</v>
-      </c>
-      <c r="I103" s="9" t="s">
+      <c r="H103" s="10" t="s">
+        <v>271</v>
+      </c>
+      <c r="I103" s="10" t="s">
         <v>451</v>
       </c>
-      <c r="J103" s="9"/>
-      <c r="K103" s="9" t="s">
-        <v>557</v>
-      </c>
-      <c r="L103" s="9" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="104" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="13" t="s">
+      <c r="J103" s="10"/>
+      <c r="K103" s="10" t="s">
+        <v>515</v>
+      </c>
+      <c r="L103" s="10" t="s">
+        <v>544</v>
+      </c>
+      <c r="N103" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" spans="1:14" s="32" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A104" s="30" t="s">
         <v>279</v>
       </c>
-      <c r="B104" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="C104" s="10" t="s">
+      <c r="B104" s="30" t="s">
+        <v>69</v>
+      </c>
+      <c r="C104" s="31" t="s">
         <v>215</v>
       </c>
-      <c r="D104" s="10" t="s">
+      <c r="D104" s="31" t="s">
         <v>362</v>
       </c>
-      <c r="E104" s="13" t="s">
+      <c r="E104" s="30" t="s">
         <v>445</v>
       </c>
-      <c r="F104" s="10" t="s">
-        <v>304</v>
-      </c>
-      <c r="G104" s="10" t="s">
+      <c r="F104" s="31" t="s">
+        <v>546</v>
+      </c>
+      <c r="G104" s="31" t="s">
         <v>282</v>
       </c>
-      <c r="H104" s="10" t="s">
+      <c r="H104" s="31" t="s">
         <v>328</v>
       </c>
-      <c r="I104" s="10" t="s">
+      <c r="I104" s="31" t="s">
         <v>451</v>
       </c>
-      <c r="J104" s="10"/>
-      <c r="K104" s="10" t="s">
-        <v>557</v>
-      </c>
-      <c r="L104" s="10" t="s">
-        <v>567</v>
-      </c>
-    </row>
-    <row r="105" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A105" s="12" t="s">
+      <c r="J104" s="31"/>
+      <c r="K104" s="31" t="s">
+        <v>515</v>
+      </c>
+      <c r="L104" s="31" t="s">
+        <v>547</v>
+      </c>
+      <c r="N104" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" spans="1:14" s="35" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A105" s="33" t="s">
         <v>279</v>
       </c>
-      <c r="B105" s="12" t="s">
-        <v>568</v>
-      </c>
-      <c r="C105" s="9" t="s">
+      <c r="B105" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="C105" s="34" t="s">
         <v>215</v>
       </c>
-      <c r="D105" s="9" t="s">
+      <c r="D105" s="34" t="s">
         <v>362</v>
       </c>
-      <c r="E105" s="12" t="s">
-        <v>315</v>
-      </c>
-      <c r="F105" s="9" t="s">
-        <v>569</v>
-      </c>
-      <c r="G105" s="9" t="s">
-        <v>270</v>
-      </c>
-      <c r="H105" s="9" t="s">
-        <v>275</v>
-      </c>
-      <c r="I105" s="9" t="s">
+      <c r="E105" s="33" t="s">
+        <v>445</v>
+      </c>
+      <c r="F105" s="34" t="s">
+        <v>548</v>
+      </c>
+      <c r="G105" s="34" t="s">
+        <v>282</v>
+      </c>
+      <c r="H105" s="34" t="s">
+        <v>328</v>
+      </c>
+      <c r="I105" s="34" t="s">
         <v>451</v>
       </c>
-      <c r="J105" s="9"/>
-      <c r="K105" s="9" t="s">
+      <c r="J105" s="34"/>
+      <c r="K105" s="34" t="s">
+        <v>549</v>
+      </c>
+      <c r="L105" s="34" t="s">
+        <v>550</v>
+      </c>
+      <c r="N105" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" spans="1:14" s="35" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A106" s="33" t="s">
+        <v>279</v>
+      </c>
+      <c r="B106" s="33" t="s">
+        <v>553</v>
+      </c>
+      <c r="C106" s="34" t="s">
+        <v>215</v>
+      </c>
+      <c r="D106" s="34" t="s">
+        <v>362</v>
+      </c>
+      <c r="E106" s="33" t="s">
+        <v>445</v>
+      </c>
+      <c r="F106" s="34" t="s">
+        <v>554</v>
+      </c>
+      <c r="G106" s="34" t="s">
+        <v>282</v>
+      </c>
+      <c r="H106" s="34" t="s">
+        <v>555</v>
+      </c>
+      <c r="I106" s="34" t="s">
+        <v>451</v>
+      </c>
+      <c r="J106" s="34"/>
+      <c r="K106" s="34" t="s">
         <v>551</v>
       </c>
-      <c r="L105" s="9" t="s">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="106" spans="1:12" s="20" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="18" t="s">
+      <c r="L106" s="34" t="s">
+        <v>556</v>
+      </c>
+      <c r="N106" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A107" s="12" t="s">
         <v>279</v>
       </c>
-      <c r="B106" s="18" t="s">
-        <v>571</v>
-      </c>
-      <c r="C106" s="19" t="s">
-        <v>215</v>
-      </c>
-      <c r="D106" s="19" t="s">
-        <v>362</v>
-      </c>
-      <c r="E106" s="18" t="s">
-        <v>445</v>
-      </c>
-      <c r="F106" s="19" t="s">
-        <v>573</v>
-      </c>
-      <c r="G106" s="19" t="s">
-        <v>282</v>
-      </c>
-      <c r="H106" s="19" t="s">
-        <v>328</v>
-      </c>
-      <c r="I106" s="19" t="s">
-        <v>334</v>
-      </c>
-      <c r="J106" s="19"/>
-      <c r="K106" s="19"/>
-      <c r="L106" s="19" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="107" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A107" s="18" t="s">
-        <v>279</v>
-      </c>
       <c r="B107" s="12" t="s">
-        <v>572</v>
+        <v>71</v>
       </c>
       <c r="C107" s="9" t="s">
         <v>215</v>
@@ -12319,7 +13197,7 @@
         <v>445</v>
       </c>
       <c r="F107" s="9" t="s">
-        <v>576</v>
+        <v>302</v>
       </c>
       <c r="G107" s="9" t="s">
         <v>282</v>
@@ -12328,128 +13206,150 @@
         <v>328</v>
       </c>
       <c r="I107" s="9" t="s">
-        <v>334</v>
+        <v>451</v>
       </c>
       <c r="J107" s="9"/>
-      <c r="K107" s="9"/>
+      <c r="K107" s="9" t="s">
+        <v>551</v>
+      </c>
       <c r="L107" s="9" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="108" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="18" t="s">
+        <v>552</v>
+      </c>
+      <c r="N107" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A108" s="13" t="s">
         <v>279</v>
       </c>
-      <c r="B108" s="12" t="s">
-        <v>581</v>
-      </c>
-      <c r="C108" s="9" t="s">
+      <c r="B108" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="C108" s="10" t="s">
         <v>215</v>
       </c>
-      <c r="D108" s="9" t="s">
+      <c r="D108" s="10" t="s">
         <v>362</v>
       </c>
-      <c r="E108" s="12" t="s">
+      <c r="E108" s="13" t="s">
         <v>445</v>
       </c>
-      <c r="F108" s="9" t="s">
-        <v>583</v>
-      </c>
-      <c r="G108" s="9" t="s">
+      <c r="F108" s="10" t="s">
+        <v>559</v>
+      </c>
+      <c r="G108" s="10" t="s">
         <v>282</v>
       </c>
-      <c r="H108" s="9" t="s">
-        <v>582</v>
-      </c>
-      <c r="I108" s="9" t="s">
+      <c r="H108" s="10" t="s">
+        <v>328</v>
+      </c>
+      <c r="I108" s="10" t="s">
         <v>451</v>
       </c>
-      <c r="J108" s="9"/>
+      <c r="J108" s="10"/>
       <c r="K108" s="9" t="s">
-        <v>578</v>
-      </c>
-      <c r="L108" s="9" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="109" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A109" s="18" t="s">
+        <v>557</v>
+      </c>
+      <c r="L108" s="10" t="s">
+        <v>516</v>
+      </c>
+      <c r="N108" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A109" s="12" t="s">
         <v>279</v>
       </c>
-      <c r="B109" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="C109" s="10" t="s">
+      <c r="B109" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="C109" s="9" t="s">
         <v>215</v>
       </c>
-      <c r="D109" s="10" t="s">
+      <c r="D109" s="9" t="s">
         <v>362</v>
       </c>
-      <c r="E109" s="13" t="s">
-        <v>315</v>
-      </c>
-      <c r="F109" s="10" t="s">
-        <v>577</v>
-      </c>
-      <c r="G109" s="10" t="s">
-        <v>270</v>
-      </c>
-      <c r="H109" s="10" t="s">
-        <v>271</v>
-      </c>
-      <c r="I109" s="10" t="s">
+      <c r="E109" s="12" t="s">
+        <v>445</v>
+      </c>
+      <c r="F109" s="9" t="s">
+        <v>558</v>
+      </c>
+      <c r="G109" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="H109" s="9" t="s">
+        <v>328</v>
+      </c>
+      <c r="I109" s="9" t="s">
         <v>451</v>
       </c>
-      <c r="J109" s="10"/>
-      <c r="K109" s="10" t="s">
-        <v>585</v>
-      </c>
-      <c r="L109" s="10" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="110" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="18" t="s">
+      <c r="J109" s="9"/>
+      <c r="K109" s="9" t="s">
+        <v>557</v>
+      </c>
+      <c r="L109" s="9" t="s">
+        <v>560</v>
+      </c>
+      <c r="N109" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A110" s="13" t="s">
         <v>279</v>
       </c>
-      <c r="B110" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="C110" s="9" t="s">
+      <c r="B110" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="C110" s="10" t="s">
         <v>215</v>
       </c>
-      <c r="D110" s="9" t="s">
+      <c r="D110" s="10" t="s">
         <v>362</v>
       </c>
-      <c r="E110" s="12" t="s">
-        <v>315</v>
-      </c>
-      <c r="F110" s="9" t="s">
-        <v>580</v>
-      </c>
-      <c r="G110" s="9" t="s">
-        <v>270</v>
-      </c>
-      <c r="H110" s="9" t="s">
-        <v>271</v>
-      </c>
-      <c r="I110" s="9" t="s">
+      <c r="E110" s="13" t="s">
+        <v>445</v>
+      </c>
+      <c r="F110" s="10" t="s">
+        <v>561</v>
+      </c>
+      <c r="G110" s="10" t="s">
+        <v>282</v>
+      </c>
+      <c r="H110" s="10" t="s">
+        <v>328</v>
+      </c>
+      <c r="I110" s="10" t="s">
         <v>451</v>
       </c>
-      <c r="J110" s="9"/>
+      <c r="J110" s="10"/>
       <c r="K110" s="9" t="s">
-        <v>585</v>
-      </c>
-      <c r="L110" s="9" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="111" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A111" s="18" t="s">
+        <v>557</v>
+      </c>
+      <c r="L110" s="10" t="s">
+        <v>528</v>
+      </c>
+      <c r="N110" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A111" s="12" t="s">
         <v>279</v>
       </c>
       <c r="B111" s="12" t="s">
-        <v>586</v>
+        <v>75</v>
       </c>
       <c r="C111" s="9" t="s">
         <v>215</v>
@@ -12458,108 +13358,121 @@
         <v>362</v>
       </c>
       <c r="E111" s="12" t="s">
-        <v>315</v>
+        <v>445</v>
       </c>
       <c r="F111" s="9" t="s">
-        <v>589</v>
+        <v>562</v>
       </c>
       <c r="G111" s="9" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="H111" s="9" t="s">
-        <v>271</v>
+        <v>328</v>
       </c>
       <c r="I111" s="9" t="s">
         <v>451</v>
       </c>
       <c r="J111" s="9"/>
       <c r="K111" s="9" t="s">
-        <v>587</v>
+        <v>557</v>
       </c>
       <c r="L111" s="9" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="112" spans="1:12" s="27" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A112" s="18" t="s">
+        <v>525</v>
+      </c>
+      <c r="N111" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A112" s="12" t="s">
         <v>279</v>
       </c>
-      <c r="B112" s="25" t="s">
-        <v>590</v>
-      </c>
-      <c r="C112" s="26" t="s">
-        <v>286</v>
-      </c>
-      <c r="D112" s="26" t="s">
-        <v>251</v>
-      </c>
-      <c r="E112" s="25" t="s">
-        <v>633</v>
-      </c>
-      <c r="F112" s="26" t="s">
-        <v>591</v>
-      </c>
-      <c r="G112" s="26" t="s">
+      <c r="B112" s="12" t="s">
+        <v>563</v>
+      </c>
+      <c r="C112" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="D112" s="9" t="s">
+        <v>362</v>
+      </c>
+      <c r="E112" s="12" t="s">
+        <v>315</v>
+      </c>
+      <c r="F112" s="9" t="s">
+        <v>564</v>
+      </c>
+      <c r="G112" s="9" t="s">
         <v>270</v>
       </c>
-      <c r="H112" s="26" t="s">
+      <c r="H112" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="I112" s="9" t="s">
+        <v>451</v>
+      </c>
+      <c r="J112" s="9"/>
+      <c r="K112" s="9" t="s">
+        <v>565</v>
+      </c>
+      <c r="L112" s="9" t="s">
+        <v>532</v>
+      </c>
+      <c r="N112" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A113" s="12" t="s">
+        <v>279</v>
+      </c>
+      <c r="B113" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="C113" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="D113" s="9" t="s">
+        <v>362</v>
+      </c>
+      <c r="E113" s="12" t="s">
+        <v>315</v>
+      </c>
+      <c r="F113" s="9" t="s">
+        <v>303</v>
+      </c>
+      <c r="G113" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="H113" s="9" t="s">
         <v>300</v>
       </c>
-      <c r="I112" s="26" t="s">
-        <v>392</v>
-      </c>
-      <c r="J112" s="26" t="s">
-        <v>593</v>
-      </c>
-      <c r="K112" s="26" t="s">
-        <v>578</v>
-      </c>
-      <c r="L112" s="26" t="s">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="113" spans="1:12" s="45" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="18" t="s">
+      <c r="I113" s="9" t="s">
+        <v>451</v>
+      </c>
+      <c r="J113" s="9"/>
+      <c r="K113" s="9" t="s">
+        <v>557</v>
+      </c>
+      <c r="L113" s="9" t="s">
+        <v>566</v>
+      </c>
+      <c r="N113" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A114" s="13" t="s">
         <v>279</v>
       </c>
-      <c r="B113" s="43" t="s">
-        <v>594</v>
-      </c>
-      <c r="C113" s="44" t="s">
-        <v>215</v>
-      </c>
-      <c r="D113" s="44" t="s">
-        <v>362</v>
-      </c>
-      <c r="E113" s="43" t="s">
-        <v>445</v>
-      </c>
-      <c r="F113" s="44" t="s">
-        <v>596</v>
-      </c>
-      <c r="G113" s="44" t="s">
-        <v>282</v>
-      </c>
-      <c r="H113" s="44" t="s">
-        <v>328</v>
-      </c>
-      <c r="I113" s="44" t="s">
-        <v>451</v>
-      </c>
-      <c r="J113" s="44"/>
-      <c r="K113" s="44" t="s">
-        <v>578</v>
-      </c>
-      <c r="L113" s="44" t="s">
-        <v>595</v>
-      </c>
-    </row>
-    <row r="114" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A114" s="18" t="s">
-        <v>279</v>
-      </c>
       <c r="B114" s="13" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C114" s="10" t="s">
         <v>215</v>
@@ -12571,7 +13484,7 @@
         <v>445</v>
       </c>
       <c r="F114" s="10" t="s">
-        <v>597</v>
+        <v>304</v>
       </c>
       <c r="G114" s="10" t="s">
         <v>282</v>
@@ -12584,18 +13497,23 @@
       </c>
       <c r="J114" s="10"/>
       <c r="K114" s="10" t="s">
-        <v>578</v>
+        <v>557</v>
       </c>
       <c r="L114" s="10" t="s">
-        <v>598</v>
-      </c>
-    </row>
-    <row r="115" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A115" s="18" t="s">
+        <v>567</v>
+      </c>
+      <c r="N114" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A115" s="12" t="s">
         <v>279</v>
       </c>
       <c r="B115" s="12" t="s">
-        <v>81</v>
+        <v>568</v>
       </c>
       <c r="C115" s="9" t="s">
         <v>215</v>
@@ -12604,70 +13522,78 @@
         <v>362</v>
       </c>
       <c r="E115" s="12" t="s">
-        <v>445</v>
+        <v>315</v>
       </c>
       <c r="F115" s="9" t="s">
-        <v>599</v>
+        <v>569</v>
       </c>
       <c r="G115" s="9" t="s">
-        <v>282</v>
+        <v>270</v>
       </c>
       <c r="H115" s="9" t="s">
-        <v>328</v>
+        <v>275</v>
       </c>
       <c r="I115" s="9" t="s">
         <v>451</v>
       </c>
       <c r="J115" s="9"/>
       <c r="K115" s="9" t="s">
-        <v>578</v>
+        <v>551</v>
       </c>
       <c r="L115" s="9" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="116" spans="1:12" s="45" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>570</v>
+      </c>
+      <c r="N115" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" spans="1:14" s="20" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="18" t="s">
         <v>279</v>
       </c>
-      <c r="B116" s="46" t="s">
-        <v>601</v>
-      </c>
-      <c r="C116" s="47" t="s">
+      <c r="B116" s="18" t="s">
+        <v>571</v>
+      </c>
+      <c r="C116" s="19" t="s">
         <v>215</v>
       </c>
-      <c r="D116" s="47" t="s">
+      <c r="D116" s="19" t="s">
         <v>362</v>
       </c>
-      <c r="E116" s="46" t="s">
+      <c r="E116" s="18" t="s">
         <v>445</v>
       </c>
-      <c r="F116" s="47" t="s">
-        <v>603</v>
-      </c>
-      <c r="G116" s="47" t="s">
+      <c r="F116" s="19" t="s">
+        <v>573</v>
+      </c>
+      <c r="G116" s="19" t="s">
         <v>282</v>
       </c>
-      <c r="H116" s="47" t="s">
-        <v>602</v>
-      </c>
-      <c r="I116" s="9" t="s">
-        <v>451</v>
-      </c>
-      <c r="J116" s="47"/>
-      <c r="K116" s="47" t="s">
-        <v>578</v>
-      </c>
-      <c r="L116" s="47" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="117" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H116" s="19" t="s">
+        <v>328</v>
+      </c>
+      <c r="I116" s="19" t="s">
+        <v>334</v>
+      </c>
+      <c r="J116" s="19"/>
+      <c r="K116" s="19"/>
+      <c r="L116" s="19" t="s">
+        <v>574</v>
+      </c>
+      <c r="N116" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="18" t="s">
         <v>279</v>
       </c>
       <c r="B117" s="12" t="s">
-        <v>83</v>
+        <v>572</v>
       </c>
       <c r="C117" s="9" t="s">
         <v>215</v>
@@ -12679,7 +13605,7 @@
         <v>445</v>
       </c>
       <c r="F117" s="9" t="s">
-        <v>607</v>
+        <v>576</v>
       </c>
       <c r="G117" s="9" t="s">
         <v>282</v>
@@ -12688,58 +13614,66 @@
         <v>328</v>
       </c>
       <c r="I117" s="9" t="s">
-        <v>451</v>
+        <v>334</v>
       </c>
       <c r="J117" s="9"/>
-      <c r="K117" s="9" t="s">
-        <v>549</v>
-      </c>
+      <c r="K117" s="9"/>
       <c r="L117" s="9" t="s">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="118" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>575</v>
+      </c>
+      <c r="N117" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="18" t="s">
         <v>279</v>
       </c>
-      <c r="B118" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="C118" s="10" t="s">
+      <c r="B118" s="12" t="s">
+        <v>581</v>
+      </c>
+      <c r="C118" s="9" t="s">
         <v>215</v>
       </c>
-      <c r="D118" s="10" t="s">
+      <c r="D118" s="9" t="s">
         <v>362</v>
       </c>
-      <c r="E118" s="13" t="s">
+      <c r="E118" s="12" t="s">
         <v>445</v>
       </c>
-      <c r="F118" s="10" t="s">
-        <v>609</v>
-      </c>
-      <c r="G118" s="10" t="s">
+      <c r="F118" s="9" t="s">
+        <v>583</v>
+      </c>
+      <c r="G118" s="9" t="s">
         <v>282</v>
       </c>
-      <c r="H118" s="10" t="s">
-        <v>610</v>
-      </c>
-      <c r="I118" s="10" t="s">
+      <c r="H118" s="9" t="s">
+        <v>582</v>
+      </c>
+      <c r="I118" s="9" t="s">
         <v>451</v>
       </c>
-      <c r="J118" s="10"/>
-      <c r="K118" s="10" t="s">
-        <v>611</v>
-      </c>
-      <c r="L118" s="10" t="s">
-        <v>612</v>
-      </c>
-    </row>
-    <row r="119" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J118" s="9"/>
+      <c r="K118" s="9" t="s">
+        <v>578</v>
+      </c>
+      <c r="L118" s="9" t="s">
+        <v>584</v>
+      </c>
+      <c r="N118" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="18" t="s">
         <v>279</v>
       </c>
       <c r="B119" s="13" t="s">
-        <v>614</v>
+        <v>78</v>
       </c>
       <c r="C119" s="10" t="s">
         <v>215</v>
@@ -12748,178 +13682,205 @@
         <v>362</v>
       </c>
       <c r="E119" s="13" t="s">
-        <v>445</v>
+        <v>315</v>
       </c>
       <c r="F119" s="10" t="s">
-        <v>615</v>
+        <v>577</v>
       </c>
       <c r="G119" s="10" t="s">
-        <v>616</v>
+        <v>270</v>
       </c>
       <c r="H119" s="10" t="s">
-        <v>99</v>
+        <v>271</v>
       </c>
       <c r="I119" s="10" t="s">
         <v>451</v>
       </c>
       <c r="J119" s="10"/>
       <c r="K119" s="10" t="s">
-        <v>613</v>
+        <v>585</v>
       </c>
       <c r="L119" s="10" t="s">
-        <v>617</v>
-      </c>
-    </row>
-    <row r="120" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="13" t="s">
+        <v>579</v>
+      </c>
+      <c r="N119" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A120" s="18" t="s">
         <v>279</v>
       </c>
-      <c r="B120" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="C120" s="10" t="s">
+      <c r="B120" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="C120" s="9" t="s">
         <v>215</v>
       </c>
-      <c r="D120" s="10" t="s">
+      <c r="D120" s="9" t="s">
         <v>362</v>
       </c>
-      <c r="E120" s="13" t="s">
+      <c r="E120" s="12" t="s">
+        <v>315</v>
+      </c>
+      <c r="F120" s="9" t="s">
+        <v>580</v>
+      </c>
+      <c r="G120" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="H120" s="9" t="s">
+        <v>271</v>
+      </c>
+      <c r="I120" s="9" t="s">
+        <v>451</v>
+      </c>
+      <c r="J120" s="9"/>
+      <c r="K120" s="9" t="s">
+        <v>585</v>
+      </c>
+      <c r="L120" s="9" t="s">
+        <v>579</v>
+      </c>
+      <c r="N120" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A121" s="18" t="s">
+        <v>279</v>
+      </c>
+      <c r="B121" s="12" t="s">
+        <v>586</v>
+      </c>
+      <c r="C121" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="D121" s="9" t="s">
+        <v>362</v>
+      </c>
+      <c r="E121" s="12" t="s">
+        <v>315</v>
+      </c>
+      <c r="F121" s="9" t="s">
+        <v>589</v>
+      </c>
+      <c r="G121" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="H121" s="9" t="s">
+        <v>271</v>
+      </c>
+      <c r="I121" s="9" t="s">
+        <v>451</v>
+      </c>
+      <c r="J121" s="9"/>
+      <c r="K121" s="9" t="s">
+        <v>587</v>
+      </c>
+      <c r="L121" s="9" t="s">
+        <v>588</v>
+      </c>
+      <c r="N121" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" spans="1:14" s="27" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A122" s="18" t="s">
+        <v>279</v>
+      </c>
+      <c r="B122" s="25" t="s">
+        <v>590</v>
+      </c>
+      <c r="C122" s="26" t="s">
+        <v>286</v>
+      </c>
+      <c r="D122" s="26" t="s">
+        <v>251</v>
+      </c>
+      <c r="E122" s="25" t="s">
+        <v>633</v>
+      </c>
+      <c r="F122" s="26" t="s">
+        <v>591</v>
+      </c>
+      <c r="G122" s="26" t="s">
+        <v>270</v>
+      </c>
+      <c r="H122" s="26" t="s">
+        <v>300</v>
+      </c>
+      <c r="I122" s="26" t="s">
+        <v>392</v>
+      </c>
+      <c r="J122" s="26" t="s">
+        <v>593</v>
+      </c>
+      <c r="K122" s="26" t="s">
+        <v>578</v>
+      </c>
+      <c r="L122" s="26" t="s">
+        <v>592</v>
+      </c>
+      <c r="N122" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" spans="1:14" s="45" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A123" s="18" t="s">
+        <v>279</v>
+      </c>
+      <c r="B123" s="43" t="s">
+        <v>594</v>
+      </c>
+      <c r="C123" s="44" t="s">
+        <v>215</v>
+      </c>
+      <c r="D123" s="44" t="s">
+        <v>362</v>
+      </c>
+      <c r="E123" s="43" t="s">
         <v>445</v>
       </c>
-      <c r="F120" s="10" t="s">
-        <v>618</v>
-      </c>
-      <c r="G120" s="10" t="s">
+      <c r="F123" s="44" t="s">
+        <v>596</v>
+      </c>
+      <c r="G123" s="44" t="s">
         <v>282</v>
       </c>
-      <c r="H120" s="10" t="s">
+      <c r="H123" s="44" t="s">
         <v>328</v>
       </c>
-      <c r="I120" s="10" t="s">
+      <c r="I123" s="44" t="s">
         <v>451</v>
       </c>
-      <c r="J120" s="10"/>
-      <c r="K120" s="10" t="s">
-        <v>611</v>
-      </c>
-      <c r="L120" s="10" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="121" spans="1:12" s="50" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A121" s="48" t="s">
+      <c r="J123" s="44"/>
+      <c r="K123" s="44" t="s">
+        <v>578</v>
+      </c>
+      <c r="L123" s="44" t="s">
+        <v>595</v>
+      </c>
+      <c r="N123" s="44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A124" s="18" t="s">
         <v>279</v>
       </c>
-      <c r="B121" s="48" t="s">
-        <v>605</v>
-      </c>
-      <c r="C121" s="49" t="s">
-        <v>215</v>
-      </c>
-      <c r="D121" s="49" t="s">
-        <v>362</v>
-      </c>
-      <c r="E121" s="48" t="s">
-        <v>445</v>
-      </c>
-      <c r="F121" s="49" t="s">
-        <v>620</v>
-      </c>
-      <c r="G121" s="49" t="s">
-        <v>282</v>
-      </c>
-      <c r="H121" s="49" t="s">
-        <v>328</v>
-      </c>
-      <c r="I121" s="49" t="s">
-        <v>451</v>
-      </c>
-      <c r="J121" s="49"/>
-      <c r="K121" s="49" t="s">
-        <v>606</v>
-      </c>
-      <c r="L121" s="49" t="s">
-        <v>621</v>
-      </c>
-    </row>
-    <row r="122" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A122" s="13" t="s">
-        <v>279</v>
-      </c>
-      <c r="B122" s="13" t="s">
-        <v>85</v>
-      </c>
-      <c r="C122" s="10" t="s">
-        <v>215</v>
-      </c>
-      <c r="D122" s="10" t="s">
-        <v>362</v>
-      </c>
-      <c r="E122" s="13" t="s">
-        <v>445</v>
-      </c>
-      <c r="F122" s="10" t="s">
-        <v>622</v>
-      </c>
-      <c r="G122" s="10" t="s">
-        <v>282</v>
-      </c>
-      <c r="H122" s="10" t="s">
-        <v>328</v>
-      </c>
-      <c r="I122" s="10" t="s">
-        <v>451</v>
-      </c>
-      <c r="J122" s="10"/>
-      <c r="K122" s="10" t="s">
-        <v>549</v>
-      </c>
-      <c r="L122" s="10" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="123" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A123" s="13" t="s">
-        <v>279</v>
-      </c>
-      <c r="B123" s="13" t="s">
-        <v>644</v>
-      </c>
-      <c r="C123" s="10" t="s">
-        <v>215</v>
-      </c>
-      <c r="D123" s="10" t="s">
-        <v>362</v>
-      </c>
-      <c r="E123" s="13" t="s">
-        <v>445</v>
-      </c>
-      <c r="F123" s="10" t="s">
-        <v>646</v>
-      </c>
-      <c r="G123" s="10" t="s">
-        <v>282</v>
-      </c>
-      <c r="H123" s="10" t="s">
-        <v>328</v>
-      </c>
-      <c r="I123" s="10" t="s">
-        <v>451</v>
-      </c>
-      <c r="J123" s="10"/>
-      <c r="K123" s="10" t="s">
-        <v>624</v>
-      </c>
-      <c r="L123" s="10" t="s">
-        <v>647</v>
-      </c>
-    </row>
-    <row r="124" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A124" s="13" t="s">
-        <v>279</v>
-      </c>
       <c r="B124" s="13" t="s">
-        <v>645</v>
+        <v>80</v>
       </c>
       <c r="C124" s="10" t="s">
         <v>215</v>
@@ -12931,141 +13892,159 @@
         <v>445</v>
       </c>
       <c r="F124" s="10" t="s">
-        <v>651</v>
+        <v>597</v>
       </c>
       <c r="G124" s="10" t="s">
         <v>282</v>
       </c>
       <c r="H124" s="10" t="s">
-        <v>649</v>
+        <v>328</v>
       </c>
       <c r="I124" s="10" t="s">
         <v>451</v>
       </c>
       <c r="J124" s="10"/>
       <c r="K124" s="10" t="s">
-        <v>624</v>
+        <v>578</v>
       </c>
       <c r="L124" s="10" t="s">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="125" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A125" s="13" t="s">
+        <v>598</v>
+      </c>
+      <c r="N124" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A125" s="18" t="s">
         <v>279</v>
       </c>
       <c r="B125" s="12" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C125" s="9" t="s">
         <v>215</v>
       </c>
-      <c r="D125" s="10" t="s">
+      <c r="D125" s="9" t="s">
         <v>362</v>
       </c>
       <c r="E125" s="12" t="s">
         <v>445</v>
       </c>
       <c r="F125" s="9" t="s">
-        <v>626</v>
+        <v>599</v>
       </c>
       <c r="G125" s="9" t="s">
         <v>282</v>
       </c>
       <c r="H125" s="9" t="s">
-        <v>625</v>
+        <v>328</v>
       </c>
       <c r="I125" s="9" t="s">
         <v>451</v>
       </c>
       <c r="J125" s="9"/>
       <c r="K125" s="9" t="s">
-        <v>648</v>
+        <v>578</v>
       </c>
       <c r="L125" s="9" t="s">
-        <v>627</v>
-      </c>
-    </row>
-    <row r="126" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A126" s="13" t="s">
+        <v>600</v>
+      </c>
+      <c r="N125" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" spans="1:14" s="45" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A126" s="18" t="s">
         <v>279</v>
       </c>
-      <c r="B126" s="13" t="s">
-        <v>628</v>
-      </c>
-      <c r="C126" s="10" t="s">
+      <c r="B126" s="46" t="s">
+        <v>601</v>
+      </c>
+      <c r="C126" s="47" t="s">
         <v>215</v>
       </c>
-      <c r="D126" s="10" t="s">
+      <c r="D126" s="47" t="s">
         <v>362</v>
       </c>
-      <c r="E126" s="13" t="s">
-        <v>315</v>
-      </c>
-      <c r="F126" s="10" t="s">
-        <v>629</v>
-      </c>
-      <c r="G126" s="10" t="s">
-        <v>270</v>
-      </c>
-      <c r="H126" s="10" t="s">
-        <v>271</v>
-      </c>
-      <c r="I126" s="10" t="s">
+      <c r="E126" s="46" t="s">
+        <v>445</v>
+      </c>
+      <c r="F126" s="47" t="s">
+        <v>603</v>
+      </c>
+      <c r="G126" s="47" t="s">
+        <v>282</v>
+      </c>
+      <c r="H126" s="47" t="s">
+        <v>602</v>
+      </c>
+      <c r="I126" s="9" t="s">
         <v>451</v>
       </c>
-      <c r="J126" s="10"/>
-      <c r="K126" s="9" t="s">
-        <v>648</v>
-      </c>
-      <c r="L126" s="10" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="127" spans="1:12" s="27" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A127" s="13" t="s">
+      <c r="J126" s="47"/>
+      <c r="K126" s="47" t="s">
+        <v>578</v>
+      </c>
+      <c r="L126" s="47" t="s">
+        <v>604</v>
+      </c>
+      <c r="N126" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A127" s="18" t="s">
         <v>279</v>
       </c>
-      <c r="B127" s="25" t="s">
-        <v>632</v>
-      </c>
-      <c r="C127" s="26" t="s">
-        <v>286</v>
-      </c>
-      <c r="D127" s="26" t="s">
-        <v>251</v>
-      </c>
-      <c r="E127" s="25" t="s">
-        <v>394</v>
-      </c>
-      <c r="F127" s="26" t="s">
-        <v>635</v>
-      </c>
-      <c r="G127" s="26" t="s">
+      <c r="B127" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="C127" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="D127" s="9" t="s">
+        <v>362</v>
+      </c>
+      <c r="E127" s="12" t="s">
+        <v>445</v>
+      </c>
+      <c r="F127" s="9" t="s">
+        <v>607</v>
+      </c>
+      <c r="G127" s="9" t="s">
         <v>282</v>
       </c>
-      <c r="H127" s="26" t="s">
-        <v>636</v>
-      </c>
-      <c r="I127" s="26" t="s">
-        <v>392</v>
-      </c>
-      <c r="J127" s="26" t="s">
-        <v>634</v>
-      </c>
-      <c r="K127" s="26" t="s">
-        <v>631</v>
-      </c>
-      <c r="L127" s="26" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="128" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A128" s="13" t="s">
+      <c r="H127" s="9" t="s">
+        <v>328</v>
+      </c>
+      <c r="I127" s="9" t="s">
+        <v>451</v>
+      </c>
+      <c r="J127" s="9"/>
+      <c r="K127" s="9" t="s">
+        <v>549</v>
+      </c>
+      <c r="L127" s="9" t="s">
+        <v>608</v>
+      </c>
+      <c r="N127" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A128" s="18" t="s">
         <v>279</v>
       </c>
       <c r="B128" s="13" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="C128" s="10" t="s">
         <v>215</v>
@@ -13077,31 +14056,36 @@
         <v>445</v>
       </c>
       <c r="F128" s="10" t="s">
-        <v>640</v>
+        <v>609</v>
       </c>
       <c r="G128" s="10" t="s">
         <v>282</v>
       </c>
       <c r="H128" s="10" t="s">
-        <v>638</v>
+        <v>610</v>
       </c>
       <c r="I128" s="10" t="s">
         <v>451</v>
       </c>
       <c r="J128" s="10"/>
       <c r="K128" s="10" t="s">
-        <v>652</v>
+        <v>611</v>
       </c>
       <c r="L128" s="10" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="129" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A129" s="13" t="s">
+        <v>612</v>
+      </c>
+      <c r="N128" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A129" s="18" t="s">
         <v>279</v>
       </c>
       <c r="B129" s="13" t="s">
-        <v>641</v>
+        <v>614</v>
       </c>
       <c r="C129" s="10" t="s">
         <v>215</v>
@@ -13110,88 +14094,121 @@
         <v>362</v>
       </c>
       <c r="E129" s="13" t="s">
-        <v>315</v>
+        <v>445</v>
       </c>
       <c r="F129" s="10" t="s">
-        <v>642</v>
+        <v>615</v>
       </c>
       <c r="G129" s="10" t="s">
-        <v>270</v>
+        <v>616</v>
       </c>
       <c r="H129" s="10" t="s">
-        <v>271</v>
+        <v>99</v>
       </c>
       <c r="I129" s="10" t="s">
         <v>451</v>
       </c>
       <c r="J129" s="10"/>
       <c r="K129" s="10" t="s">
-        <v>652</v>
+        <v>613</v>
       </c>
       <c r="L129" s="10" t="s">
-        <v>643</v>
-      </c>
-    </row>
-    <row r="130" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>617</v>
+      </c>
+      <c r="N129" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="13" t="s">
         <v>279</v>
       </c>
-      <c r="B130" s="12" t="s">
-        <v>653</v>
-      </c>
-      <c r="C130" s="9" t="s">
+      <c r="B130" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="C130" s="10" t="s">
         <v>215</v>
       </c>
       <c r="D130" s="10" t="s">
         <v>362</v>
       </c>
-      <c r="E130" s="12" t="s">
+      <c r="E130" s="13" t="s">
         <v>445</v>
       </c>
-      <c r="F130" s="9" t="s">
-        <v>654</v>
-      </c>
-      <c r="G130" s="9" t="s">
+      <c r="F130" s="10" t="s">
+        <v>618</v>
+      </c>
+      <c r="G130" s="10" t="s">
         <v>282</v>
       </c>
-      <c r="H130" s="9" t="s">
+      <c r="H130" s="10" t="s">
         <v>328</v>
       </c>
-      <c r="I130" s="9" t="s">
+      <c r="I130" s="10" t="s">
         <v>451</v>
       </c>
-      <c r="J130" s="9"/>
-      <c r="K130" s="9" t="s">
-        <v>652</v>
-      </c>
-      <c r="L130" s="9" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="131" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A131" s="13" t="s">
+      <c r="J130" s="10"/>
+      <c r="K130" s="10" t="s">
+        <v>611</v>
+      </c>
+      <c r="L130" s="10" t="s">
+        <v>619</v>
+      </c>
+      <c r="N130" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" spans="1:14" s="50" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A131" s="48" t="s">
         <v>279</v>
       </c>
-      <c r="B131" s="12" t="s">
-        <v>755</v>
-      </c>
-      <c r="C131" s="9"/>
-      <c r="D131" s="10"/>
-      <c r="E131" s="12"/>
-      <c r="F131" s="9"/>
-      <c r="G131" s="9"/>
-      <c r="H131" s="9"/>
-      <c r="I131" s="9"/>
-      <c r="J131" s="9"/>
-      <c r="K131" s="9"/>
-      <c r="L131" s="9"/>
-    </row>
-    <row r="132" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B131" s="48" t="s">
+        <v>605</v>
+      </c>
+      <c r="C131" s="49" t="s">
+        <v>215</v>
+      </c>
+      <c r="D131" s="49" t="s">
+        <v>362</v>
+      </c>
+      <c r="E131" s="48" t="s">
+        <v>445</v>
+      </c>
+      <c r="F131" s="49" t="s">
+        <v>620</v>
+      </c>
+      <c r="G131" s="49" t="s">
+        <v>282</v>
+      </c>
+      <c r="H131" s="49" t="s">
+        <v>328</v>
+      </c>
+      <c r="I131" s="49" t="s">
+        <v>451</v>
+      </c>
+      <c r="J131" s="49"/>
+      <c r="K131" s="49" t="s">
+        <v>606</v>
+      </c>
+      <c r="L131" s="49" t="s">
+        <v>621</v>
+      </c>
+      <c r="N131" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="13" t="s">
         <v>279</v>
       </c>
       <c r="B132" s="13" t="s">
-        <v>656</v>
+        <v>85</v>
       </c>
       <c r="C132" s="10" t="s">
         <v>215</v>
@@ -13200,709 +14217,1190 @@
         <v>362</v>
       </c>
       <c r="E132" s="13" t="s">
-        <v>479</v>
+        <v>445</v>
       </c>
       <c r="F132" s="10" t="s">
-        <v>657</v>
+        <v>622</v>
       </c>
       <c r="G132" s="10" t="s">
-        <v>266</v>
+        <v>282</v>
       </c>
       <c r="H132" s="10" t="s">
-        <v>99</v>
+        <v>328</v>
       </c>
       <c r="I132" s="10" t="s">
-        <v>659</v>
+        <v>451</v>
       </c>
       <c r="J132" s="10"/>
-      <c r="K132" s="10"/>
+      <c r="K132" s="10" t="s">
+        <v>549</v>
+      </c>
       <c r="L132" s="10" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="133" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>623</v>
+      </c>
+      <c r="N132" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="13" t="s">
         <v>279</v>
       </c>
       <c r="B133" s="13" t="s">
-        <v>660</v>
-      </c>
-      <c r="C133" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="C133" s="10" t="s">
         <v>215</v>
       </c>
       <c r="D133" s="10" t="s">
         <v>362</v>
       </c>
-      <c r="E133" s="12" t="s">
+      <c r="E133" s="13" t="s">
         <v>445</v>
       </c>
       <c r="F133" s="10" t="s">
-        <v>662</v>
-      </c>
-      <c r="G133" s="9" t="s">
+        <v>646</v>
+      </c>
+      <c r="G133" s="10" t="s">
         <v>282</v>
       </c>
-      <c r="H133" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LISTAS:escala_zona_objetivo</t>
-        </is>
+      <c r="H133" s="10" t="s">
+        <v>328</v>
       </c>
       <c r="I133" s="10" t="s">
-        <v>334</v>
+        <v>451</v>
       </c>
       <c r="J133" s="10"/>
-      <c r="K133" s="10"/>
+      <c r="K133" s="10" t="s">
+        <v>624</v>
+      </c>
       <c r="L133" s="10" t="s">
-        <v>663</v>
-      </c>
-    </row>
-    <row r="134" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>647</v>
+      </c>
+      <c r="N133" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="13" t="s">
         <v>279</v>
       </c>
       <c r="B134" s="13" t="s">
-        <v>661</v>
-      </c>
-      <c r="C134" s="9" t="s">
+        <v>645</v>
+      </c>
+      <c r="C134" s="10" t="s">
         <v>215</v>
       </c>
       <c r="D134" s="10" t="s">
         <v>362</v>
       </c>
-      <c r="E134" s="12" t="s">
+      <c r="E134" s="13" t="s">
         <v>445</v>
       </c>
       <c r="F134" s="10" t="s">
-        <v>665</v>
+        <v>651</v>
       </c>
       <c r="G134" s="10" t="s">
         <v>282</v>
       </c>
-      <c r="H134" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LISTAS:escala_tasa_ocupacion</t>
-        </is>
+      <c r="H134" s="10" t="s">
+        <v>649</v>
       </c>
       <c r="I134" s="10" t="s">
-        <v>334</v>
+        <v>451</v>
       </c>
       <c r="J134" s="10"/>
-      <c r="K134" s="10"/>
+      <c r="K134" s="10" t="s">
+        <v>624</v>
+      </c>
       <c r="L134" s="10" t="s">
-        <v>667</v>
-      </c>
-    </row>
-    <row r="135" spans="1:12" s="38" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>650</v>
+      </c>
+      <c r="N134" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="13" t="s">
         <v>279</v>
       </c>
-      <c r="B135" s="36" t="s">
-        <v>93</v>
-      </c>
-      <c r="C135" s="37" t="s">
-        <v>286</v>
-      </c>
-      <c r="D135" s="37" t="s">
-        <v>251</v>
-      </c>
-      <c r="E135" s="36" t="s">
-        <v>305</v>
-      </c>
-      <c r="F135" s="37" t="s">
-        <v>668</v>
-      </c>
-      <c r="G135" s="37" t="s">
+      <c r="B135" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="C135" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="D135" s="10" t="s">
+        <v>362</v>
+      </c>
+      <c r="E135" s="12" t="s">
+        <v>445</v>
+      </c>
+      <c r="F135" s="9" t="s">
+        <v>626</v>
+      </c>
+      <c r="G135" s="9" t="s">
         <v>282</v>
       </c>
-      <c r="H135" s="37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LISTAS:escala_probabilidad_impacto</t>
-        </is>
-      </c>
-      <c r="I135" s="37" t="s">
-        <v>334</v>
-      </c>
-      <c r="J135" s="37" t="s">
-        <v>682</v>
-      </c>
-      <c r="K135" s="37"/>
-      <c r="L135" s="37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Resultado automático según M01. Valores permitidos: LISTAS:escala_probabilidad_impacto. No editable manualmente.</t>
-        </is>
-      </c>
-    </row>
-    <row r="136" spans="1:12" s="20" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H135" s="9" t="s">
+        <v>625</v>
+      </c>
+      <c r="I135" s="9" t="s">
+        <v>451</v>
+      </c>
+      <c r="J135" s="9"/>
+      <c r="K135" s="9" t="s">
+        <v>648</v>
+      </c>
+      <c r="L135" s="9" t="s">
+        <v>627</v>
+      </c>
+      <c r="N135" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="13" t="s">
         <v>279</v>
       </c>
-      <c r="B136" s="18" t="s">
-        <v>687</v>
-      </c>
-      <c r="C136" s="19" t="s">
+      <c r="B136" s="13" t="s">
+        <v>628</v>
+      </c>
+      <c r="C136" s="10" t="s">
         <v>215</v>
       </c>
-      <c r="D136" s="19" t="s">
+      <c r="D136" s="10" t="s">
         <v>362</v>
       </c>
-      <c r="E136" s="18" t="s">
-        <v>445</v>
-      </c>
-      <c r="F136" s="19" t="s">
-        <v>685</v>
-      </c>
-      <c r="G136" s="19" t="s">
-        <v>282</v>
-      </c>
-      <c r="H136" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LISTAS:escala_consecuencia</t>
-        </is>
-      </c>
-      <c r="I136" s="19" t="s">
-        <v>334</v>
-      </c>
-      <c r="J136" s="19"/>
-      <c r="K136" s="19"/>
-      <c r="L136" s="19" t="s">
-        <v>686</v>
-      </c>
-    </row>
-    <row r="137" spans="1:12" s="20" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E136" s="13" t="s">
+        <v>315</v>
+      </c>
+      <c r="F136" s="10" t="s">
+        <v>629</v>
+      </c>
+      <c r="G136" s="10" t="s">
+        <v>270</v>
+      </c>
+      <c r="H136" s="10" t="s">
+        <v>271</v>
+      </c>
+      <c r="I136" s="10" t="s">
+        <v>451</v>
+      </c>
+      <c r="J136" s="10"/>
+      <c r="K136" s="9" t="s">
+        <v>648</v>
+      </c>
+      <c r="L136" s="10" t="s">
+        <v>630</v>
+      </c>
+      <c r="N136" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" spans="1:14" s="27" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" s="13" t="s">
         <v>279</v>
       </c>
-      <c r="B137" s="18" t="s">
-        <v>688</v>
-      </c>
-      <c r="C137" s="19" t="s">
-        <v>215</v>
-      </c>
-      <c r="D137" s="19" t="s">
-        <v>362</v>
-      </c>
-      <c r="E137" s="18" t="s">
-        <v>445</v>
-      </c>
-      <c r="F137" s="19" t="s">
-        <v>685</v>
-      </c>
-      <c r="G137" s="19" t="s">
+      <c r="B137" s="25" t="s">
+        <v>632</v>
+      </c>
+      <c r="C137" s="26" t="s">
+        <v>286</v>
+      </c>
+      <c r="D137" s="26" t="s">
+        <v>251</v>
+      </c>
+      <c r="E137" s="25" t="s">
+        <v>394</v>
+      </c>
+      <c r="F137" s="26" t="s">
+        <v>635</v>
+      </c>
+      <c r="G137" s="26" t="s">
         <v>282</v>
       </c>
-      <c r="H137" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LISTAS:escala_consecuencia</t>
-        </is>
-      </c>
-      <c r="I137" s="19" t="s">
-        <v>334</v>
-      </c>
-      <c r="J137" s="19"/>
-      <c r="K137" s="19"/>
-      <c r="L137" s="19" t="s">
-        <v>686</v>
-      </c>
-    </row>
-    <row r="138" spans="1:12" s="20" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H137" s="26" t="s">
+        <v>636</v>
+      </c>
+      <c r="I137" s="26" t="s">
+        <v>392</v>
+      </c>
+      <c r="J137" s="26" t="s">
+        <v>634</v>
+      </c>
+      <c r="K137" s="26" t="s">
+        <v>631</v>
+      </c>
+      <c r="L137" s="26" t="s">
+        <v>637</v>
+      </c>
+      <c r="N137" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="13" t="s">
         <v>279</v>
       </c>
-      <c r="B138" s="18" t="s">
+      <c r="B138" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="C138" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="D138" s="10" t="s">
+        <v>362</v>
+      </c>
+      <c r="E138" s="13" t="s">
+        <v>445</v>
+      </c>
+      <c r="F138" s="10" t="s">
+        <v>640</v>
+      </c>
+      <c r="G138" s="10" t="s">
+        <v>282</v>
+      </c>
+      <c r="H138" s="10" t="s">
+        <v>638</v>
+      </c>
+      <c r="I138" s="10" t="s">
+        <v>451</v>
+      </c>
+      <c r="J138" s="10"/>
+      <c r="K138" s="10" t="s">
+        <v>652</v>
+      </c>
+      <c r="L138" s="10" t="s">
+        <v>639</v>
+      </c>
+      <c r="N138" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A139" s="13" t="s">
+        <v>279</v>
+      </c>
+      <c r="B139" s="13" t="s">
+        <v>641</v>
+      </c>
+      <c r="C139" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="D139" s="10" t="s">
+        <v>362</v>
+      </c>
+      <c r="E139" s="13" t="s">
+        <v>315</v>
+      </c>
+      <c r="F139" s="10" t="s">
+        <v>642</v>
+      </c>
+      <c r="G139" s="10" t="s">
+        <v>270</v>
+      </c>
+      <c r="H139" s="10" t="s">
+        <v>271</v>
+      </c>
+      <c r="I139" s="10" t="s">
+        <v>451</v>
+      </c>
+      <c r="J139" s="10"/>
+      <c r="K139" s="10" t="s">
+        <v>652</v>
+      </c>
+      <c r="L139" s="10" t="s">
+        <v>643</v>
+      </c>
+      <c r="N139" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A140" s="13" t="s">
+        <v>279</v>
+      </c>
+      <c r="B140" s="12" t="s">
+        <v>653</v>
+      </c>
+      <c r="C140" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="D140" s="10" t="s">
+        <v>362</v>
+      </c>
+      <c r="E140" s="12" t="s">
+        <v>445</v>
+      </c>
+      <c r="F140" s="9" t="s">
+        <v>654</v>
+      </c>
+      <c r="G140" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="H140" s="9" t="s">
+        <v>328</v>
+      </c>
+      <c r="I140" s="9" t="s">
+        <v>451</v>
+      </c>
+      <c r="J140" s="9"/>
+      <c r="K140" s="9" t="s">
+        <v>652</v>
+      </c>
+      <c r="L140" s="9" t="s">
+        <v>655</v>
+      </c>
+      <c r="N140" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A141" s="13" t="s">
+        <v>279</v>
+      </c>
+      <c r="B141" s="12" t="s">
+        <v>755</v>
+      </c>
+      <c r="C141" s="9"/>
+      <c r="D141" s="10"/>
+      <c r="E141" s="12"/>
+      <c r="F141" s="9"/>
+      <c r="G141" s="9"/>
+      <c r="H141" s="9"/>
+      <c r="I141" s="9"/>
+      <c r="J141" s="9"/>
+      <c r="K141" s="9"/>
+      <c r="L141" s="9"/>
+      <c r="N141" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A142" s="13" t="s">
+        <v>279</v>
+      </c>
+      <c r="B142" s="13" t="s">
+        <v>656</v>
+      </c>
+      <c r="C142" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="D142" s="10" t="s">
+        <v>362</v>
+      </c>
+      <c r="E142" s="13" t="s">
+        <v>479</v>
+      </c>
+      <c r="F142" s="10" t="s">
+        <v>657</v>
+      </c>
+      <c r="G142" s="10" t="s">
+        <v>266</v>
+      </c>
+      <c r="H142" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="I142" s="10" t="s">
+        <v>659</v>
+      </c>
+      <c r="J142" s="10"/>
+      <c r="K142" s="10"/>
+      <c r="L142" s="10" t="s">
+        <v>658</v>
+      </c>
+      <c r="N142" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A143" s="13" t="s">
+        <v>279</v>
+      </c>
+      <c r="B143" s="13" t="s">
+        <v>660</v>
+      </c>
+      <c r="C143" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="D143" s="10" t="s">
+        <v>362</v>
+      </c>
+      <c r="E143" s="12" t="s">
+        <v>445</v>
+      </c>
+      <c r="F143" s="10" t="s">
+        <v>662</v>
+      </c>
+      <c r="G143" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="H143" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LISTAS:escala_zona_objetivo</t>
+        </is>
+      </c>
+      <c r="I143" s="10" t="s">
+        <v>334</v>
+      </c>
+      <c r="J143" s="10"/>
+      <c r="K143" s="10"/>
+      <c r="L143" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Seleccionar una única categoría según la ubicación del objetivo. La altura de referencia corresponde a la altura total del árbol (altura_total_m, MEDICIONES_DENDROMETRICAS). Qué medición se utiliza en cada inspección queda pendiente (relación MEDICIÓN ↔ INSPECCIÓN, CC-020).</t>
+        </is>
+      </c>
+      <c r="N143" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A144" s="13" t="s">
+        <v>279</v>
+      </c>
+      <c r="B144" s="13" t="s">
+        <v>661</v>
+      </c>
+      <c r="C144" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="D144" s="10" t="s">
+        <v>362</v>
+      </c>
+      <c r="E144" s="12" t="s">
+        <v>445</v>
+      </c>
+      <c r="F144" s="10" t="s">
+        <v>665</v>
+      </c>
+      <c r="G144" s="10" t="s">
+        <v>282</v>
+      </c>
+      <c r="H144" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LISTAS:escala_tasa_ocupacion</t>
+        </is>
+      </c>
+      <c r="I144" s="10" t="s">
+        <v>334</v>
+      </c>
+      <c r="J144" s="10"/>
+      <c r="K144" s="10"/>
+      <c r="L144" s="10" t="s">
+        <v>667</v>
+      </c>
+      <c r="N144" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" spans="1:14" s="38" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A145" s="13" t="s">
+        <v>279</v>
+      </c>
+      <c r="B145" s="36" t="s">
+        <v>93</v>
+      </c>
+      <c r="C145" s="37" t="s">
+        <v>286</v>
+      </c>
+      <c r="D145" s="37" t="s">
+        <v>251</v>
+      </c>
+      <c r="E145" s="36" t="s">
+        <v>305</v>
+      </c>
+      <c r="F145" s="37" t="s">
+        <v>668</v>
+      </c>
+      <c r="G145" s="37" t="s">
+        <v>282</v>
+      </c>
+      <c r="H145" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LISTAS:escala_probabilidad_impacto</t>
+        </is>
+      </c>
+      <c r="I145" s="37" t="s">
+        <v>334</v>
+      </c>
+      <c r="J145" s="37" t="s">
+        <v>682</v>
+      </c>
+      <c r="K145" s="37"/>
+      <c r="L145" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Resultado automático según M01. Valores permitidos: LISTAS:escala_probabilidad_impacto. No editable manualmente.</t>
+        </is>
+      </c>
+      <c r="N145" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" spans="1:14" s="20" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A146" s="13" t="s">
+        <v>279</v>
+      </c>
+      <c r="B146" s="18" t="s">
+        <v>687</v>
+      </c>
+      <c r="C146" s="19" t="s">
+        <v>215</v>
+      </c>
+      <c r="D146" s="19" t="s">
+        <v>362</v>
+      </c>
+      <c r="E146" s="18" t="s">
+        <v>445</v>
+      </c>
+      <c r="F146" s="19" t="s">
+        <v>685</v>
+      </c>
+      <c r="G146" s="19" t="s">
+        <v>282</v>
+      </c>
+      <c r="H146" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LISTAS:escala_consecuencia</t>
+        </is>
+      </c>
+      <c r="I146" s="19" t="s">
+        <v>334</v>
+      </c>
+      <c r="J146" s="19"/>
+      <c r="K146" s="19"/>
+      <c r="L146" s="19" t="s">
+        <v>686</v>
+      </c>
+      <c r="N146" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" spans="1:14" s="20" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A147" s="13" t="s">
+        <v>279</v>
+      </c>
+      <c r="B147" s="18" t="s">
+        <v>688</v>
+      </c>
+      <c r="C147" s="19" t="s">
+        <v>215</v>
+      </c>
+      <c r="D147" s="19" t="s">
+        <v>362</v>
+      </c>
+      <c r="E147" s="18" t="s">
+        <v>445</v>
+      </c>
+      <c r="F147" s="19" t="s">
+        <v>685</v>
+      </c>
+      <c r="G147" s="19" t="s">
+        <v>282</v>
+      </c>
+      <c r="H147" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LISTAS:escala_consecuencia</t>
+        </is>
+      </c>
+      <c r="I147" s="19" t="s">
+        <v>334</v>
+      </c>
+      <c r="J147" s="19"/>
+      <c r="K147" s="19"/>
+      <c r="L147" s="19" t="s">
+        <v>686</v>
+      </c>
+      <c r="N147" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" spans="1:14" s="20" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A148" s="13" t="s">
+        <v>279</v>
+      </c>
+      <c r="B148" s="18" t="s">
         <v>689</v>
       </c>
-      <c r="C138" s="19" t="s">
+      <c r="C148" s="19" t="s">
         <v>215</v>
       </c>
-      <c r="D138" s="19" t="s">
+      <c r="D148" s="19" t="s">
         <v>362</v>
       </c>
-      <c r="E138" s="18" t="s">
+      <c r="E148" s="18" t="s">
         <v>445</v>
       </c>
-      <c r="F138" s="19" t="s">
+      <c r="F148" s="19" t="s">
         <v>685</v>
       </c>
-      <c r="G138" s="19" t="s">
+      <c r="G148" s="19" t="s">
         <v>282</v>
       </c>
-      <c r="H138" s="19" t="inlineStr">
+      <c r="H148" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">LISTAS:escala_consecuencia</t>
         </is>
       </c>
-      <c r="I138" s="19" t="s">
+      <c r="I148" s="19" t="s">
         <v>334</v>
       </c>
-      <c r="J138" s="19"/>
-      <c r="K138" s="19"/>
-      <c r="L138" s="19" t="s">
+      <c r="J148" s="19"/>
+      <c r="K148" s="19"/>
+      <c r="L148" s="19" t="s">
         <v>686</v>
       </c>
-    </row>
-    <row r="139" spans="1:12" s="42" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A139" s="40" t="s">
+      <c r="N148" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" spans="1:14" s="42" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A149" s="40" t="s">
         <v>279</v>
       </c>
-      <c r="B139" s="40" t="s">
+      <c r="B149" s="40" t="s">
         <v>690</v>
       </c>
-      <c r="C139" s="41" t="s">
+      <c r="C149" s="41" t="s">
         <v>286</v>
       </c>
-      <c r="D139" s="41" t="s">
+      <c r="D149" s="41" t="s">
         <v>251</v>
       </c>
-      <c r="E139" s="40" t="s">
+      <c r="E149" s="40" t="s">
         <v>305</v>
       </c>
-      <c r="F139" s="41" t="s">
+      <c r="F149" s="41" t="s">
         <v>693</v>
       </c>
-      <c r="G139" s="41" t="s">
+      <c r="G149" s="41" t="s">
         <v>282</v>
       </c>
-      <c r="H139" s="41" t="inlineStr">
+      <c r="H149" s="41" t="inlineStr">
         <is>
           <t xml:space="preserve">LISTAS:escala_probabilidad_falla</t>
         </is>
       </c>
-      <c r="I139" s="41" t="s">
+      <c r="I149" s="41" t="s">
         <v>334</v>
       </c>
-      <c r="J139" s="41" t="s">
+      <c r="J149" s="41" t="s">
         <v>708</v>
       </c>
-      <c r="K139" s="41"/>
-      <c r="L139" s="41" t="inlineStr">
+      <c r="K149" s="41"/>
+      <c r="L149" s="41" t="inlineStr">
         <is>
           <t xml:space="preserve">Resultado automático no editable. Puntaje total válido 0–9. Resultado permitido: LISTAS:escala_probabilidad_falla.</t>
         </is>
       </c>
-    </row>
-    <row r="140" spans="1:12" s="42" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A140" s="40" t="s">
+      <c r="N149" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" spans="1:14" s="42" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A150" s="40" t="s">
         <v>279</v>
       </c>
-      <c r="B140" s="40" t="s">
+      <c r="B150" s="40" t="s">
         <v>691</v>
       </c>
-      <c r="C140" s="41" t="s">
+      <c r="C150" s="41" t="s">
         <v>286</v>
       </c>
-      <c r="D140" s="41" t="s">
+      <c r="D150" s="41" t="s">
         <v>251</v>
       </c>
-      <c r="E140" s="40" t="s">
+      <c r="E150" s="40" t="s">
         <v>305</v>
       </c>
-      <c r="F140" s="41" t="s">
+      <c r="F150" s="41" t="s">
         <v>694</v>
       </c>
-      <c r="G140" s="41" t="s">
+      <c r="G150" s="41" t="s">
         <v>282</v>
       </c>
-      <c r="H140" s="41" t="inlineStr">
+      <c r="H150" s="41" t="inlineStr">
         <is>
           <t xml:space="preserve">LISTAS:escala_probabilidad_falla</t>
         </is>
       </c>
-      <c r="I140" s="41" t="s">
+      <c r="I150" s="41" t="s">
         <v>334</v>
       </c>
-      <c r="J140" s="41" t="s">
+      <c r="J150" s="41" t="s">
         <v>719</v>
       </c>
-      <c r="K140" s="41"/>
-      <c r="L140" s="41" t="inlineStr">
+      <c r="K150" s="41"/>
+      <c r="L150" s="41" t="inlineStr">
         <is>
           <t xml:space="preserve">Resultado automático no editable. Puntaje total válido 0–9. Resultado permitido: LISTAS:escala_probabilidad_falla.</t>
         </is>
       </c>
-    </row>
-    <row r="141" spans="1:12" s="42" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A141" s="40" t="s">
+      <c r="N150" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" spans="1:14" s="42" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A151" s="40" t="s">
         <v>279</v>
       </c>
-      <c r="B141" s="40" t="s">
+      <c r="B151" s="40" t="s">
         <v>692</v>
       </c>
-      <c r="C141" s="41" t="s">
+      <c r="C151" s="41" t="s">
         <v>286</v>
       </c>
-      <c r="D141" s="41" t="s">
+      <c r="D151" s="41" t="s">
         <v>251</v>
       </c>
-      <c r="E141" s="40" t="s">
+      <c r="E151" s="40" t="s">
         <v>305</v>
       </c>
-      <c r="F141" s="41" t="s">
+      <c r="F151" s="41" t="s">
         <v>695</v>
       </c>
-      <c r="G141" s="41" t="s">
+      <c r="G151" s="41" t="s">
         <v>282</v>
       </c>
-      <c r="H141" s="41" t="inlineStr">
+      <c r="H151" s="41" t="inlineStr">
         <is>
           <t xml:space="preserve">LISTAS:escala_probabilidad_falla</t>
         </is>
       </c>
-      <c r="I141" s="41" t="s">
+      <c r="I151" s="41" t="s">
         <v>334</v>
       </c>
-      <c r="J141" s="41" t="s">
+      <c r="J151" s="41" t="s">
         <v>728</v>
       </c>
-      <c r="K141" s="41"/>
-      <c r="L141" s="41" t="inlineStr">
+      <c r="K151" s="41"/>
+      <c r="L151" s="41" t="inlineStr">
         <is>
           <t xml:space="preserve">Resultado automático no editable. Puntaje total válido 0–9. Resultado permitido: LISTAS:escala_probabilidad_falla.</t>
         </is>
       </c>
-    </row>
-    <row r="142" spans="1:12" s="38" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A142" s="36" t="s">
+      <c r="N151" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" spans="1:14" s="38" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A152" s="36" t="s">
         <v>279</v>
       </c>
-      <c r="B142" s="36" t="s">
+      <c r="B152" s="36" t="s">
         <v>88</v>
       </c>
-      <c r="C142" s="37" t="s">
+      <c r="C152" s="37" t="s">
         <v>286</v>
       </c>
-      <c r="D142" s="37" t="s">
+      <c r="D152" s="37" t="s">
         <v>251</v>
       </c>
-      <c r="E142" s="36" t="s">
+      <c r="E152" s="36" t="s">
         <v>305</v>
       </c>
-      <c r="F142" s="37" t="s">
+      <c r="F152" s="37" t="s">
         <v>751</v>
       </c>
-      <c r="G142" s="37" t="s">
+      <c r="G152" s="37" t="s">
         <v>282</v>
       </c>
-      <c r="H142" s="37" t="inlineStr">
+      <c r="H152" s="37" t="inlineStr">
         <is>
           <t xml:space="preserve">LISTAS:escala_nivel_riesgo</t>
         </is>
       </c>
-      <c r="I142" s="41" t="s">
+      <c r="I152" s="41" t="s">
         <v>334</v>
       </c>
-      <c r="J142" s="37" t="s">
+      <c r="J152" s="37" t="s">
         <v>746</v>
       </c>
-      <c r="K142" s="37"/>
-      <c r="L142" s="37" t="inlineStr">
+      <c r="K152" s="37"/>
+      <c r="L152" s="37" t="inlineStr">
         <is>
           <t xml:space="preserve">Valor calculado automáticamente y no editable. Valores permitidos: LISTAS:escala_nivel_riesgo. Requiere valores válidos en probabilidad_falla_raices_cuello, probabilidad_impacto y consecuencia_raices_cuello</t>
         </is>
       </c>
-    </row>
-    <row r="143" spans="1:12" s="38" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A143" s="36" t="s">
+      <c r="N152" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" spans="1:14" s="38" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A153" s="36" t="s">
         <v>279</v>
       </c>
-      <c r="B143" s="36" t="s">
+      <c r="B153" s="36" t="s">
         <v>89</v>
       </c>
-      <c r="C143" s="37" t="s">
+      <c r="C153" s="37" t="s">
         <v>286</v>
       </c>
-      <c r="D143" s="37" t="s">
+      <c r="D153" s="37" t="s">
         <v>251</v>
       </c>
-      <c r="E143" s="36" t="s">
+      <c r="E153" s="36" t="s">
         <v>305</v>
       </c>
-      <c r="F143" s="37" t="s">
+      <c r="F153" s="37" t="s">
         <v>749</v>
       </c>
-      <c r="G143" s="37" t="s">
+      <c r="G153" s="37" t="s">
         <v>282</v>
       </c>
-      <c r="H143" s="37" t="inlineStr">
+      <c r="H153" s="37" t="inlineStr">
         <is>
           <t xml:space="preserve">LISTAS:escala_nivel_riesgo</t>
         </is>
       </c>
-      <c r="I143" s="41" t="s">
+      <c r="I153" s="41" t="s">
         <v>334</v>
       </c>
-      <c r="J143" s="37" t="s">
+      <c r="J153" s="37" t="s">
         <v>747</v>
       </c>
-      <c r="K143" s="37"/>
-      <c r="L143" s="37" t="inlineStr">
+      <c r="K153" s="37"/>
+      <c r="L153" s="37" t="inlineStr">
         <is>
           <t xml:space="preserve">Valor calculado automáticamente y no editable. Valores permitidos: LISTAS:escala_nivel_riesgo. Requiere valores válidos en probabilidad_falla_tronco, probabilidad_impacto y consecuencia_tronco</t>
         </is>
       </c>
-    </row>
-    <row r="144" spans="1:12" s="38" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A144" s="36" t="s">
+      <c r="N153" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" spans="1:14" s="38" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A154" s="36" t="s">
         <v>279</v>
       </c>
-      <c r="B144" s="36" t="s">
+      <c r="B154" s="36" t="s">
         <v>90</v>
       </c>
-      <c r="C144" s="37" t="s">
+      <c r="C154" s="37" t="s">
         <v>286</v>
       </c>
-      <c r="D144" s="37" t="s">
+      <c r="D154" s="37" t="s">
         <v>251</v>
       </c>
-      <c r="E144" s="36" t="s">
+      <c r="E154" s="36" t="s">
         <v>305</v>
       </c>
-      <c r="F144" s="37" t="s">
+      <c r="F154" s="37" t="s">
         <v>750</v>
       </c>
-      <c r="G144" s="37" t="s">
+      <c r="G154" s="37" t="s">
         <v>282</v>
       </c>
-      <c r="H144" s="37" t="inlineStr">
+      <c r="H154" s="37" t="inlineStr">
         <is>
           <t xml:space="preserve">LISTAS:escala_nivel_riesgo</t>
         </is>
       </c>
-      <c r="I144" s="41" t="s">
+      <c r="I154" s="41" t="s">
         <v>334</v>
       </c>
-      <c r="J144" s="37" t="s">
+      <c r="J154" s="37" t="s">
         <v>748</v>
       </c>
-      <c r="K144" s="37"/>
-      <c r="L144" s="37" t="inlineStr">
+      <c r="K154" s="37"/>
+      <c r="L154" s="37" t="inlineStr">
         <is>
           <t xml:space="preserve">Valor calculado automáticamente y no editable. Valores permitidos: LISTAS:escala_nivel_riesgo. Requiere valores válidos en probabilidad_falla_copa_ramas, probabilidad_impacto y consecuencia_copa_ramas</t>
         </is>
       </c>
-    </row>
-    <row r="145" spans="1:12" s="20" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A145" s="18" t="s">
+      <c r="N154" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" spans="1:14" s="20" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A155" s="18" t="s">
         <v>279</v>
       </c>
-      <c r="B145" s="18" t="s">
+      <c r="B155" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="C145" s="19" t="s">
+      <c r="C155" s="19" t="s">
         <v>286</v>
       </c>
-      <c r="D145" s="19" t="s">
+      <c r="D155" s="19" t="s">
         <v>251</v>
       </c>
-      <c r="E145" s="18" t="s">
+      <c r="E155" s="18" t="s">
         <v>305</v>
       </c>
-      <c r="F145" s="19" t="s">
+      <c r="F155" s="19" t="s">
         <v>308</v>
       </c>
-      <c r="G145" s="19" t="s">
+      <c r="G155" s="19" t="s">
         <v>282</v>
       </c>
-      <c r="H145" s="19" t="s">
+      <c r="H155" s="19" t="s">
         <v>306</v>
       </c>
-      <c r="I145" s="19"/>
-      <c r="J145" s="19"/>
-      <c r="K145" s="19"/>
-      <c r="L145" s="19" t="s">
+      <c r="I155" s="19"/>
+      <c r="J155" s="19"/>
+      <c r="K155" s="19"/>
+      <c r="L155" s="19" t="s">
         <v>307</v>
       </c>
-    </row>
-    <row r="146" spans="1:12" s="38" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A146" s="36" t="s">
+      <c r="N155" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" spans="1:14" s="38" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A156" s="36" t="s">
         <v>279</v>
       </c>
-      <c r="B146" s="36" t="s">
+      <c r="B156" s="36" t="s">
         <v>92</v>
       </c>
-      <c r="C146" s="37" t="s">
+      <c r="C156" s="37" t="s">
         <v>286</v>
       </c>
-      <c r="D146" s="37" t="s">
+      <c r="D156" s="37" t="s">
         <v>251</v>
       </c>
-      <c r="E146" s="36" t="s">
+      <c r="E156" s="36" t="s">
         <v>305</v>
       </c>
-      <c r="F146" s="37" t="s">
+      <c r="F156" s="37" t="s">
         <v>772</v>
       </c>
-      <c r="G146" s="37" t="s">
+      <c r="G156" s="37" t="s">
         <v>282</v>
       </c>
-      <c r="H146" s="37" t="inlineStr">
+      <c r="H156" s="37" t="inlineStr">
         <is>
           <t xml:space="preserve">LISTAS:escala_clasificacion_infraestructura</t>
         </is>
       </c>
-      <c r="I146" s="41" t="s">
+      <c r="I156" s="41" t="s">
         <v>334</v>
       </c>
-      <c r="J146" s="37" t="s">
+      <c r="J156" s="37" t="s">
         <v>770</v>
       </c>
-      <c r="K146" s="37"/>
-      <c r="L146" s="37" t="inlineStr">
+      <c r="K156" s="37"/>
+      <c r="L156" s="37" t="inlineStr">
         <is>
           <t xml:space="preserve">Valor calculado automáticamente y no editable. Valores permitidos: LISTAS:escala_clasificacion_infraestructura.</t>
         </is>
       </c>
-    </row>
-    <row r="147" spans="1:12" s="38" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A147" s="36" t="s">
+      <c r="N156" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" spans="1:14" s="38" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A157" s="36" t="s">
         <v>279</v>
       </c>
-      <c r="B147" s="36" t="s">
+      <c r="B157" s="36" t="s">
         <v>94</v>
       </c>
-      <c r="C147" s="37" t="s">
+      <c r="C157" s="37" t="s">
         <v>286</v>
       </c>
-      <c r="D147" s="37" t="s">
+      <c r="D157" s="37" t="s">
         <v>251</v>
       </c>
-      <c r="E147" s="36" t="s">
+      <c r="E157" s="36" t="s">
         <v>311</v>
       </c>
-      <c r="F147" s="37" t="s">
+      <c r="F157" s="37" t="s">
         <v>780</v>
       </c>
-      <c r="G147" s="37" t="s">
+      <c r="G157" s="37" t="s">
         <v>282</v>
       </c>
-      <c r="H147" s="37" t="inlineStr">
+      <c r="H157" s="37" t="inlineStr">
         <is>
           <t xml:space="preserve">LISTAS:escala_nivel_riesgo</t>
         </is>
       </c>
-      <c r="I147" s="41" t="s">
+      <c r="I157" s="41" t="s">
         <v>334</v>
       </c>
-      <c r="J147" s="37" t="s">
+      <c r="J157" s="37" t="s">
         <v>781</v>
       </c>
-      <c r="K147" s="37"/>
-      <c r="L147" s="37" t="inlineStr">
+      <c r="K157" s="37"/>
+      <c r="L157" s="37" t="inlineStr">
         <is>
           <t xml:space="preserve">Valor calculado automáticamente y no editable. Valores permitidos: LISTAS:escala_nivel_riesgo. Requiere clasificaciones válidas de los componentes evaluados.</t>
         </is>
       </c>
-    </row>
-    <row r="148" spans="1:12" s="23" customFormat="1" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A148" s="21" t="s">
+      <c r="N157" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" spans="1:14" s="23" customFormat="1" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A158" s="21" t="s">
         <v>279</v>
       </c>
-      <c r="B148" s="21" t="s">
+      <c r="B158" s="21" t="s">
         <v>95</v>
       </c>
-      <c r="C148" s="22" t="s">
+      <c r="C158" s="22" t="s">
         <v>286</v>
       </c>
-      <c r="D148" s="22" t="s">
+      <c r="D158" s="22" t="s">
         <v>251</v>
       </c>
-      <c r="E148" s="21" t="s">
+      <c r="E158" s="21" t="s">
         <v>305</v>
       </c>
-      <c r="F148" s="22" t="s">
+      <c r="F158" s="22" t="s">
         <v>790</v>
       </c>
-      <c r="G148" s="22" t="s">
+      <c r="G158" s="22" t="s">
         <v>282</v>
       </c>
-      <c r="H148" s="22" t="inlineStr">
+      <c r="H158" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">LISTAS:escala_prioridad</t>
         </is>
       </c>
-      <c r="I148" s="41" t="s">
+      <c r="I158" s="41" t="s">
         <v>334</v>
       </c>
-      <c r="J148" s="22" t="s">
+      <c r="J158" s="22" t="s">
         <v>792</v>
       </c>
-      <c r="K148" s="22"/>
-      <c r="L148" s="22" t="inlineStr">
+      <c r="K158" s="22"/>
+      <c r="L158" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">Valor calculado automáticamente y no editable. Valores permitidos: LISTAS:escala_prioridad. Requiere valores válidos en clasificacion_riesgo y clasificacion_infraestructura.</t>
         </is>
       </c>
-    </row>
-    <row r="149" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A149" s="14" t="s">
+      <c r="N158" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologico</t>
+        </is>
+      </c>
+    </row>
+    <row r="159" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A159" s="14" t="s">
         <v>866</v>
       </c>
-      <c r="B149" s="14" t="s">
+      <c r="B159" s="14" t="s">
         <v>162</v>
       </c>
-      <c r="C149" s="8" t="s">
+      <c r="C159" s="8" t="s">
         <v>867</v>
       </c>
-      <c r="D149" s="8" t="s">
+      <c r="D159" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="E149" s="14" t="s">
+      <c r="E159" s="14" t="s">
         <v>868</v>
       </c>
-      <c r="F149" s="8" t="s">
+      <c r="F159" s="8" t="s">
         <v>869</v>
       </c>
-      <c r="G149" s="8" t="s">
+      <c r="G159" s="8" t="s">
         <v>870</v>
       </c>
-      <c r="H149" s="8" t="inlineStr">
+      <c r="H159" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">LISTAS:accion (filtrado por tipo_ot)</t>
         </is>
       </c>
-      <c r="I149" s="8" t="s">
+      <c r="I159" s="8" t="s">
         <v>334</v>
       </c>
-      <c r="K149" s="52" t="s">
+      <c r="K159" s="52" t="s">
         <v>872</v>
       </c>
-      <c r="L149" s="52" t="s">
+      <c r="L159" s="52" t="s">
         <v>873</v>
       </c>
     </row>
-    <row r="150" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A150" s="14" t="s">
+    <row r="160" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A160" s="14" t="s">
         <v>866</v>
       </c>
-      <c r="B150" s="14" t="s">
+      <c r="B160" s="14" t="s">
         <v>163</v>
       </c>
-      <c r="C150" s="8" t="s">
+      <c r="C160" s="8" t="s">
         <v>867</v>
       </c>
-      <c r="D150" s="8" t="s">
+      <c r="D160" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="E150" s="14" t="s">
+      <c r="E160" s="14" t="s">
         <v>874</v>
       </c>
-      <c r="F150" s="8" t="s">
+      <c r="F160" s="8" t="s">
         <v>875</v>
       </c>
-      <c r="G150" s="8" t="s">
+      <c r="G160" s="8" t="s">
         <v>870</v>
       </c>
-      <c r="H150" s="8" t="inlineStr">
+      <c r="H160" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">LISTAS:subtipo_accion (filtrado por accion; vacío si la acción no tiene subtipos)</t>
         </is>
       </c>
-      <c r="I150" s="8" t="s">
+      <c r="I160" s="8" t="s">
         <v>335</v>
       </c>
-      <c r="K150" s="52" t="s">
+      <c r="K160" s="52" t="s">
         <v>877</v>
       </c>
-      <c r="L150" s="52" t="s">
+      <c r="L160" s="52" t="s">
         <v>878</v>
       </c>
     </row>

--- a/docs/excel/Base de Datos Valpo Verde.xlsx
+++ b/docs/excel/Base de Datos Valpo Verde.xlsx
@@ -9062,11 +9062,15 @@
       <c r="D11" s="19" t="s">
         <v>251</v>
       </c>
-      <c r="E11" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="F11" s="19" t="s">
-        <v>317</v>
+      <c r="E11" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Según el CRS de captura configurado para el proyecto; mecanismo pendiente (ADR-010 v2.0).</t>
+        </is>
+      </c>
+      <c r="F11" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zona UTM y hemisferio asociados a la coordenada UTM registrada. No se asume una zona única para la plataforma.</t>
+        </is>
       </c>
       <c r="G11" s="19" t="s">
         <v>266</v>
@@ -9083,7 +9087,7 @@
       <c r="K11" s="19"/>
       <c r="L11" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Este, Norte, huso, hemisferio y datum deben ser coherentes. No fijar SRID sin verificar configuración del proyecto. PENDIENTE (CC-020): huso y datum siguen abiertos (ADR-010 v2.0); el valor fijo 19S no se aplica como regla, porque la plataforma no asume una única zona UTM. Obligatoriedad anterior: Obligatorio.</t>
+          <t xml:space="preserve">Este, Norte, huso, hemisferio y datum deben ser coherentes. No fijar SRID sin verificar configuración del proyecto. PENDIENTE (CC-020 / ADR-010 v2.0): obligatoriedad de la captura UTM, datum, huso y conservación de la coordenada original de levantamiento por definir. Obligatoriedad anterior: Obligatorio. La ubicación canónica obligatoria del árbol es ubicacion_wgs84.</t>
         </is>
       </c>
       <c r="N11" s="19" t="inlineStr">
@@ -9491,7 +9495,7 @@
       </c>
       <c r="F19" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Configuración de los fustes del ejemplar a 1,30 m sobre el terreno. Se registra en cada medición porque condiciona la medición del DAP en esa fecha.</t>
+          <t xml:space="preserve">Configuración de los fustes del ejemplar. Se registra en cada medición porque condiciona la medición del DAP en esa fecha.</t>
         </is>
       </c>
       <c r="G19" s="10" t="s">
@@ -9509,7 +9513,7 @@
       <c r="K19" s="9"/>
       <c r="L19" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Obligatorio en la medición inicial (CC-020). PENDIENTE (CC-020): categorías en estudio (monofuste, bifurcado, multifuste) y su relación con numero_fustes y con el cálculo del DAP; no implementar un dominio cerrado hasta su aprobación. Obligatoriedad en mediciones posteriores: pendiente.</t>
+          <t xml:space="preserve">Obligatorio en la medición inicial (CC-020). PENDIENTE (CC-020): categorías definitivas, criterio/altura de referencia y relación con numero_fustes y cálculo del DAP por definir. No implementar un dominio cerrado hasta su aprobación. Obligatoriedad en mediciones posteriores: pendiente.</t>
         </is>
       </c>
       <c r="N19" s="9" t="inlineStr">
@@ -9536,8 +9540,10 @@
       <c r="E20" s="13" t="s">
         <v>313</v>
       </c>
-      <c r="F20" s="9" t="s">
-        <v>329</v>
+      <c r="F20" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Número de fustes del ejemplar considerados en la medición.</t>
+        </is>
       </c>
       <c r="G20" s="10" t="s">
         <v>330</v>
@@ -9556,7 +9562,7 @@
       </c>
       <c r="L20" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Válido cuando se registra un número entero ≥ 2. PENDIENTE (CC-020): relación con las categorías de configuración de fustes por definir.</t>
+          <t xml:space="preserve">Válido cuando se registra un número entero ≥ 2. PENDIENTE (CC-020): criterio/altura de referencia para determinar el número de fustes aplicables. Relación con las categorías de configuración de fustes por definir.</t>
         </is>
       </c>
       <c r="N20" s="10" t="inlineStr">
@@ -9585,7 +9591,7 @@
       </c>
       <c r="F21" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Diámetros individuales a 1,30 m de cada fuste medido. Son los datos primarios de un ejemplar con más de un fuste y se conservan aunque el DAP equivalente no esté calculado.</t>
+          <t xml:space="preserve">Diámetros individuales de los fustes considerados en la medición. Son los datos primarios de un ejemplar con más de un fuste y se conservan aunque el DAP equivalente no esté calculado.</t>
         </is>
       </c>
       <c r="G21" s="10" t="s">
@@ -9605,7 +9611,7 @@
       </c>
       <c r="L21" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Obligatorio en la medición inicial cuando el ejemplar tiene más de un fuste (CC-020). La cantidad de diámetros registrados debe coincidir con numero_fustes; cada valor debe ser &gt; 0.</t>
+          <t xml:space="preserve">Obligatorio en la medición inicial cuando el ejemplar tiene más de un fuste (CC-020). La cantidad de diámetros registrados debe coincidir con numero_fustes; cada valor debe ser &gt; 0. PENDIENTE (CC-020): criterio/altura de referencia que determina los fustes aplicables.</t>
         </is>
       </c>
       <c r="N21" s="10" t="inlineStr">

--- a/docs/excel/Base de Datos Valpo Verde.xlsx
+++ b/docs/excel/Base de Datos Valpo Verde.xlsx
@@ -6561,8 +6561,10 @@
       <c r="AV5" t="s">
         <v>937</v>
       </c>
-      <c r="AW5" t="s">
-        <v>940</v>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cruzar clasificacion_riesgo × clasificacion_infraestructura y devolver la categoría correspondiente de M05. Si clasificacion_infraestructura = No aplica, usar la columna Bajo. Todo riesgo Extremo entrega prioridad Crítica. Si clasificacion_riesgo = No determinado, clasificacion_prioridad = No determinado.</t>
+        </is>
       </c>
     </row>
     <row r="6" spans="1:52" x14ac:dyDescent="0.3">
@@ -11537,7 +11539,7 @@
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">CC-024, CC-026, CC-027, CC-028</t>
+          <t xml:space="preserve">CC-024, CC-026, CC-027, CC-028, CC-029</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
@@ -19686,19 +19688,23 @@
       <c r="G172" s="15" t="s">
         <v>357</v>
       </c>
-      <c r="H172" s="15" t="s">
-        <v>709</v>
+      <c r="H172" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Baja / Media / Alta / Crítica / No determinado</t>
+        </is>
       </c>
       <c r="I172" s="25" t="s">
         <v>324</v>
       </c>
-      <c r="J172" s="15" t="s">
-        <v>710</v>
+      <c r="J172" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M05: cruzar clasificacion_riesgo (Bajo/Moderado/Alto/Extremo) × clasificacion_infraestructura (Bajo/Moderado/Alto/Crítico). Si clasificacion_infraestructura = No aplica, usar la columna Bajo. Todo riesgo Extremo → Crítica. Si clasificacion_riesgo = No determinado, clasificacion_prioridad = No determinado. Orientación: Baja = seguimiento rutinario; Media = intervención programada; Alta = intervención prioritaria en el corto plazo; Crítica = atención urgente.</t>
+        </is>
       </c>
       <c r="K172" s="15"/>
       <c r="L172" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valor calculado automáticamente. El Inspector puede ajustarlo registrando justificacion_ajuste_clasificacion; la plataforma conserva el valor calculado, el valor ajustado, el Inspector y la fecha del ajuste. Valores permitidos: Baja / Media / Alta / Crítica. Requiere valores válidos en clasificacion_riesgo y clasificacion_infraestructura. Si se ajusta clasificacion_riesgo o clasificacion_infraestructura, calcular con el valor ajustado.</t>
+          <t xml:space="preserve">Valor calculado automáticamente. El Inspector puede ajustarlo registrando justificacion_ajuste_clasificacion; la plataforma conserva el valor calculado, el valor ajustado, el Inspector y la fecha del ajuste. Valores permitidos: Baja / Media / Alta / Crítica / No determinado. Requiere valores válidos en clasificacion_riesgo y clasificacion_infraestructura. Si se ajusta clasificacion_riesgo o clasificacion_infraestructura, calcular con el valor ajustado.</t>
         </is>
       </c>
     </row>

--- a/docs/excel/Base de Datos Valpo Verde.xlsx
+++ b/docs/excel/Base de Datos Valpo Verde.xlsx
@@ -5261,62 +5261,62 @@
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t xml:space="preserve">origen_biogeografico</t>
+          <t xml:space="preserve">multifustal</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t xml:space="preserve">multifustal</t>
+          <t xml:space="preserve">numero_fustes</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t xml:space="preserve">numero_fustes</t>
+          <t xml:space="preserve">dap_fustes_cm</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dap_fustes_cm</t>
+          <t xml:space="preserve">dap_cm</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dap_cm</t>
+          <t xml:space="preserve">altura_total_m</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t xml:space="preserve">altura_total_m</t>
+          <t xml:space="preserve">diametro_copa_ns_m</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t xml:space="preserve">diametro_copa_ns_m</t>
+          <t xml:space="preserve">diametro_copa_eo_m</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t xml:space="preserve">diametro_copa_eo_m</t>
+          <t xml:space="preserve">diametro_copa_m</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t xml:space="preserve">diametro_copa_m</t>
+          <t xml:space="preserve">altura_primera_rama_m</t>
         </is>
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t xml:space="preserve">altura_primera_rama_m</t>
+          <t xml:space="preserve">altura_base_copa_viva_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t xml:space="preserve">altura_base_copa_viva_m</t>
+          <t xml:space="preserve">clase_edad</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t xml:space="preserve">clase_edad</t>
+          <t xml:space="preserve">rango_edad_estimada_anios</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
@@ -5327,7 +5327,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y2:Y1048576" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X2:X1048576" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Joven,Semimaduro,Tempranamente maduro,Maduro,Sobremaduro"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5584,14 +5584,16 @@
       </c>
       <c r="D9" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARBOLES.id_arbol; ARBOLES.id_proyecto; ARBOLES.id_sector; ARBOLES.sector; ARBOLES.origen_biogeografico; estado_presencia derivado.</t>
+          <t xml:space="preserve">ARBOLES.id_arbol; ARBOLES.id_proyecto; ARBOLES.id_sector; ARBOLES.sector; ARBOLES.especie_cientifica; CATALOGO_ESPECIES.origen_biogeografico (vinculado mediante especie_cientifica); estado_presencia derivado.</t>
         </is>
       </c>
       <c r="E9" s="30" t="s">
         <v>1253</v>
       </c>
-      <c r="F9" s="30" t="s">
-        <v>1255</v>
+      <c r="F9" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PN = (N_nativos / N_presentes) × 100. N_nativos = número de árboles presentes cuya especie tiene CATALOGO_ESPECIES.origen_biogeografico = Nativa o Endémica; N_presentes = Número total de Árboles presentes en el ámbito seleccionado. Contar individuos únicos. Fuente: inventario de SIVU.</t>
+        </is>
       </c>
       <c r="G9" s="30" t="s">
         <v>1254</v>
@@ -5616,14 +5618,16 @@
       </c>
       <c r="D10" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARBOLES.id_arbol; ARBOLES.id_proyecto; ARBOLES.id_sector; ARBOLES.sector; ARBOLES.origen_biogeografico; estado_presencia derivado.</t>
+          <t xml:space="preserve">ARBOLES.id_arbol; ARBOLES.id_proyecto; ARBOLES.id_sector; ARBOLES.sector; ARBOLES.especie_cientifica; CATALOGO_ESPECIES.origen_biogeografico (vinculado mediante especie_cientifica); estado_presencia derivado.</t>
         </is>
       </c>
       <c r="E10" s="30" t="s">
         <v>1253</v>
       </c>
-      <c r="F10" s="30" t="s">
-        <v>1260</v>
+      <c r="F10" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PI = (N_introducidos / N_presentes) × 100. N_introducidos = número de árboles presentes cuya especie tiene CATALOGO_ESPECIES.origen_biogeografico = Introducida; N_presentes = Número total de Árboles presentes en el ámbito seleccionado. Contar individuos únicos, independientemente de sus fustes o inspecciones. Fuente: inventario de SIVU.</t>
+        </is>
       </c>
       <c r="G10" s="30" t="s">
         <v>1254</v>
@@ -6243,18 +6247,39 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0724DCB-01ED-4E1E-B9D5-08D0DCF7F3F6}">
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:3" ht="15" x14ac:dyDescent="0.35">
-      <c r="A1" s="61" t="s">
-        <v>10</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1208</v>
-      </c>
-      <c r="C1" s="61" t="s">
-        <v>1209</v>
+    <row r="1" spans="1:6" ht="15" x14ac:dyDescent="0.35">
+      <c r="A1" s="61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">especie_cientifica</t>
+        </is>
+      </c>
+      <c r="B1" s="61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">genero</t>
+        </is>
+      </c>
+      <c r="C1" s="61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">familia</t>
+        </is>
+      </c>
+      <c r="D1" s="61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">origen_biogeografico</t>
+        </is>
+      </c>
+      <c r="E1" s="61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">persistencia_follaje</t>
+        </is>
+      </c>
+      <c r="F1" s="61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tipo_hoja</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -7457,12 +7482,12 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">El Usuario municipal solo ingresa en el alta el nombre común o científico, la ubicación y, opcionalmente, el origen biogeográfico. Crea las OT y define requiere_revision_inspector en las OT de Mantenimiento.</t>
+          <t xml:space="preserve">El Usuario municipal solo ingresa en el alta el nombre común o científico y la ubicación. Crea las OT y define requiere_revision_inspector en las OT de Mantenimiento.</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">especie_cientifica; nombre_comun; origen_biogeografico; sector; ubicacion_descriptiva; utm_este; utm_norte; requiere_revision_inspector</t>
+          <t xml:space="preserve">especie_cientifica; nombre_comun; sector; ubicacion_descriptiva; utm_este; utm_norte; requiere_revision_inspector</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
@@ -11539,7 +11564,7 @@
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">CC-024, CC-026, CC-027, CC-028, CC-029</t>
+          <t xml:space="preserve">CC-024, CC-026, CC-027, CC-028, CC-029, CC-039</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
@@ -13028,7 +13053,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M260"/>
+  <dimension ref="A1:M263"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="24" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7" style="41" customWidth="1"/>
@@ -13561,44 +13586,40 @@
         <v>1420</v>
       </c>
     </row>
-    <row r="15" spans="1:12" s="46" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="44" t="s">
+    <row r="15" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="10" t="s">
         <v>317</v>
       </c>
-      <c r="B15" s="48" t="s">
-        <v>12</v>
-      </c>
-      <c r="C15" s="45" t="s">
+      <c r="B15" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C15" s="7" t="s">
         <v>276</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Inspector / Usuario municipal</t>
-        </is>
-      </c>
-      <c r="E15" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Asignación por el Inspector según la distribución natural de la especie identificada.</t>
-        </is>
-      </c>
-      <c r="F15" s="45" t="s">
-        <v>1068</v>
+          <t xml:space="preserve">Inspector</t>
+        </is>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>342</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>356</v>
       </c>
       <c r="G15" s="8" t="s">
         <v>357</v>
       </c>
-      <c r="H15" s="45" t="s">
-        <v>355</v>
-      </c>
-      <c r="I15" s="45" t="s">
+      <c r="H15" s="7" t="s">
+        <v>358</v>
+      </c>
+      <c r="I15" s="7" t="s">
         <v>324</v>
       </c>
-      <c r="J15" s="45"/>
-      <c r="K15" s="45"/>
-      <c r="L15" s="45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Debe ser coherente con especie_cientifica. La clasificación debe considerar la distribución natural de la especie respecto de Chile, no el lugar de plantación ni el origen del ejemplar. En el alta municipal es opcional; el Inspector lo confirma o corrige mediante OT.</t>
-        </is>
+      <c r="J15" s="7"/>
+      <c r="K15" s="7"/>
+      <c r="L15" s="7" t="s">
+        <v>359</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -13606,7 +13627,7 @@
         <v>317</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C16" s="7" t="s">
         <v>276</v>
@@ -13620,21 +13641,23 @@
         <v>342</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>324</v>
+        <v>363</v>
       </c>
       <c r="J16" s="7"/>
-      <c r="K16" s="7"/>
-      <c r="L16" s="7" t="s">
-        <v>359</v>
+      <c r="K16" s="7" t="s">
+        <v>364</v>
+      </c>
+      <c r="L16" s="8" t="s">
+        <v>365</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -13642,7 +13665,7 @@
         <v>317</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C17" s="7" t="s">
         <v>276</v>
@@ -13656,13 +13679,13 @@
         <v>342</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="I17" s="7" t="s">
         <v>363</v>
@@ -13672,107 +13695,105 @@
         <v>364</v>
       </c>
       <c r="L17" s="8" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="10" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" s="35" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="17" t="s">
         <v>317</v>
       </c>
-      <c r="B18" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="C18" s="7" t="s">
+      <c r="B18" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" s="18" t="s">
+        <v>370</v>
+      </c>
+      <c r="D18" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sistema / Inspector</t>
+        </is>
+      </c>
+      <c r="E18" s="17" t="s">
+        <v>345</v>
+      </c>
+      <c r="F18" s="18" t="s">
+        <v>371</v>
+      </c>
+      <c r="G18" s="18" t="s">
+        <v>347</v>
+      </c>
+      <c r="H18" s="18" t="s">
+        <v>368</v>
+      </c>
+      <c r="I18" s="18" t="s">
+        <v>324</v>
+      </c>
+      <c r="J18" s="18" t="s">
+        <v>372</v>
+      </c>
+      <c r="K18" s="18"/>
+      <c r="L18" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Valor numérico &gt; 0. No admite texto. Si no puede medirse, mantener la evaluación preguardada; no registrar 0. Si multifustal = No, el valor debe ser ingresado manualmente; si multifustal = Sí, debe ser calculado automáticamente por la plataforma.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="10" t="s">
+        <v>317</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>1386</v>
+      </c>
+      <c r="C19" s="7" t="s">
         <v>276</v>
       </c>
-      <c r="D18" s="7" t="inlineStr">
+      <c r="D19" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Inspector</t>
         </is>
       </c>
-      <c r="E18" s="11" t="s">
-        <v>342</v>
-      </c>
-      <c r="F18" s="7" t="s">
-        <v>366</v>
-      </c>
-      <c r="G18" s="8" t="s">
-        <v>367</v>
-      </c>
-      <c r="H18" s="7" t="s">
-        <v>368</v>
-      </c>
-      <c r="I18" s="7" t="s">
-        <v>363</v>
-      </c>
-      <c r="J18" s="7"/>
-      <c r="K18" s="7" t="s">
-        <v>364</v>
-      </c>
-      <c r="L18" s="8" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" s="35" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="17" t="s">
-        <v>317</v>
-      </c>
-      <c r="B19" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="C19" s="18" t="s">
-        <v>370</v>
-      </c>
-      <c r="D19" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sistema / Inspector</t>
-        </is>
-      </c>
-      <c r="E19" s="17" t="s">
+      <c r="E19" s="10" t="s">
         <v>345</v>
       </c>
-      <c r="F19" s="18" t="s">
-        <v>371</v>
-      </c>
-      <c r="G19" s="18" t="s">
+      <c r="F19" s="7" t="s">
+        <v>374</v>
+      </c>
+      <c r="G19" s="7" t="s">
         <v>347</v>
       </c>
-      <c r="H19" s="18" t="s">
-        <v>368</v>
-      </c>
-      <c r="I19" s="18" t="s">
+      <c r="H19" s="7" t="s">
+        <v>348</v>
+      </c>
+      <c r="I19" s="7" t="s">
         <v>324</v>
       </c>
-      <c r="J19" s="18" t="s">
-        <v>372</v>
-      </c>
-      <c r="K19" s="18"/>
-      <c r="L19" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Valor numérico &gt; 0. No admite texto. Si no puede medirse, mantener la evaluación preguardada; no registrar 0. Si multifustal = No, el valor debe ser ingresado manualmente; si multifustal = Sí, debe ser calculado automáticamente por la plataforma.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J19" s="7"/>
+      <c r="K19" s="7"/>
+      <c r="L19" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Valor numérico &gt; 0. No admite texto. Si no puede medirse, mantener la evaluación preguardada; no registrar 0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="10" t="s">
         <v>317</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>1386</v>
+        <v>1388</v>
       </c>
       <c r="C20" s="7" t="s">
         <v>276</v>
       </c>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Inspector</t>
-        </is>
+      <c r="D20" s="7" t="s">
+        <v>259</v>
       </c>
       <c r="E20" s="10" t="s">
         <v>345</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>374</v>
+        <v>1421</v>
       </c>
       <c r="G20" s="7" t="s">
         <v>347</v>
@@ -13781,14 +13802,16 @@
         <v>348</v>
       </c>
       <c r="I20" s="7" t="s">
-        <v>324</v>
-      </c>
-      <c r="J20" s="7"/>
-      <c r="K20" s="7"/>
-      <c r="L20" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Valor numérico &gt; 0. No admite texto. Si no puede medirse, mantener la evaluación preguardada; no registrar 0.</t>
-        </is>
+        <v>1422</v>
+      </c>
+      <c r="J20" s="7" t="s">
+        <v>1151</v>
+      </c>
+      <c r="K20" s="7" t="s">
+        <v>1423</v>
+      </c>
+      <c r="L20" s="8" t="s">
+        <v>1424</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -13796,7 +13819,7 @@
         <v>317</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>1388</v>
+        <v>1389</v>
       </c>
       <c r="C21" s="7" t="s">
         <v>276</v>
@@ -13808,7 +13831,7 @@
         <v>345</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>1421</v>
+        <v>1425</v>
       </c>
       <c r="G21" s="7" t="s">
         <v>347</v>
@@ -13834,19 +13857,19 @@
         <v>317</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>1389</v>
+        <v>17</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>276</v>
+        <v>419</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>259</v>
+        <v>319</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>345</v>
+        <v>1426</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>1425</v>
+        <v>1427</v>
       </c>
       <c r="G22" s="7" t="s">
         <v>347</v>
@@ -13855,54 +13878,54 @@
         <v>348</v>
       </c>
       <c r="I22" s="7" t="s">
-        <v>1422</v>
+        <v>363</v>
       </c>
       <c r="J22" s="7" t="s">
+        <v>1428</v>
+      </c>
+      <c r="K22" s="7" t="s">
+        <v>1429</v>
+      </c>
+      <c r="L22" s="8" t="s">
+        <v>1430</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>317</v>
+      </c>
+      <c r="B23" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" s="65" t="s">
+        <v>276</v>
+      </c>
+      <c r="D23" t="s">
+        <v>259</v>
+      </c>
+      <c r="E23" t="s">
+        <v>345</v>
+      </c>
+      <c r="F23" t="s">
+        <v>1390</v>
+      </c>
+      <c r="G23" t="s">
+        <v>347</v>
+      </c>
+      <c r="H23" t="s">
+        <v>348</v>
+      </c>
+      <c r="I23" t="s">
+        <v>1431</v>
+      </c>
+      <c r="J23" t="s">
         <v>1151</v>
       </c>
-      <c r="K22" s="7" t="s">
-        <v>1423</v>
-      </c>
-      <c r="L22" s="8" t="s">
-        <v>1424</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="10" t="s">
-        <v>317</v>
-      </c>
-      <c r="B23" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>419</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>319</v>
-      </c>
-      <c r="E23" s="10" t="s">
-        <v>1426</v>
-      </c>
-      <c r="F23" s="7" t="s">
-        <v>1427</v>
-      </c>
-      <c r="G23" s="7" t="s">
-        <v>347</v>
-      </c>
-      <c r="H23" s="7" t="s">
-        <v>348</v>
-      </c>
-      <c r="I23" s="7" t="s">
-        <v>363</v>
-      </c>
-      <c r="J23" s="7" t="s">
-        <v>1428</v>
-      </c>
-      <c r="K23" s="7" t="s">
-        <v>1429</v>
-      </c>
-      <c r="L23" s="8" t="s">
-        <v>1430</v>
+      <c r="K23" t="s">
+        <v>1391</v>
+      </c>
+      <c r="L23" t="s">
+        <v>1432</v>
       </c>
     </row>
     <row r="24" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
@@ -13910,7 +13933,7 @@
         <v>317</v>
       </c>
       <c r="B24" t="s">
-        <v>18</v>
+        <v>1387</v>
       </c>
       <c r="C24" s="65" t="s">
         <v>276</v>
@@ -13922,7 +13945,7 @@
         <v>345</v>
       </c>
       <c r="F24" t="s">
-        <v>1390</v>
+        <v>1392</v>
       </c>
       <c r="G24" t="s">
         <v>347</v>
@@ -13937,84 +13960,108 @@
         <v>1151</v>
       </c>
       <c r="K24" t="s">
-        <v>1391</v>
+        <v>1433</v>
       </c>
       <c r="L24" t="s">
-        <v>1432</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" s="51" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="49" t="s">
         <v>317</v>
       </c>
-      <c r="B25" t="s">
-        <v>1387</v>
-      </c>
-      <c r="C25" s="65" t="s">
+      <c r="B25" s="49" t="s">
+        <v>19</v>
+      </c>
+      <c r="C25" s="50" t="s">
         <v>276</v>
       </c>
-      <c r="D25" t="s">
-        <v>259</v>
-      </c>
-      <c r="E25" t="s">
-        <v>345</v>
-      </c>
-      <c r="F25" t="s">
-        <v>1392</v>
-      </c>
-      <c r="G25" t="s">
-        <v>347</v>
-      </c>
-      <c r="H25" t="s">
-        <v>348</v>
-      </c>
-      <c r="I25" t="s">
-        <v>1431</v>
-      </c>
-      <c r="J25" t="s">
-        <v>1151</v>
-      </c>
-      <c r="K25" t="s">
-        <v>1433</v>
-      </c>
-      <c r="L25" t="s">
-        <v>1434</v>
+      <c r="D25" s="50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Inspector</t>
+        </is>
+      </c>
+      <c r="E25" s="49" t="s">
+        <v>342</v>
+      </c>
+      <c r="F25" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="G25" s="50" t="s">
+        <v>357</v>
+      </c>
+      <c r="H25" s="50" t="s">
+        <v>377</v>
+      </c>
+      <c r="I25" s="50" t="s">
+        <v>324</v>
+      </c>
+      <c r="J25" s="50"/>
+      <c r="K25" s="50"/>
+      <c r="L25" s="50" t="s">
+        <v>378</v>
       </c>
     </row>
     <row r="26" spans="1:12" s="51" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="49" t="s">
-        <v>317</v>
-      </c>
-      <c r="B26" s="49" t="s">
-        <v>19</v>
-      </c>
-      <c r="C26" s="50" t="s">
-        <v>276</v>
+      <c r="A26" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARBOLES</t>
+        </is>
+      </c>
+      <c r="B26" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rango_edad_estimada_anios</t>
+        </is>
+      </c>
+      <c r="C26" s="50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Estimado</t>
+        </is>
       </c>
       <c r="D26" s="50" t="inlineStr">
         <is>
           <t xml:space="preserve">Inspector</t>
         </is>
       </c>
-      <c r="E26" s="49" t="s">
-        <v>342</v>
-      </c>
-      <c r="F26" s="50" t="s">
-        <v>376</v>
-      </c>
-      <c r="G26" s="50" t="s">
-        <v>357</v>
-      </c>
-      <c r="H26" s="50" t="s">
-        <v>377</v>
-      </c>
-      <c r="I26" s="50" t="s">
-        <v>324</v>
-      </c>
-      <c r="J26" s="50"/>
-      <c r="K26" s="50"/>
-      <c r="L26" s="50" t="s">
-        <v>378</v>
+      <c r="E26" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Estimación a partir de especie_cientifica, dap_cm, altura_total_m, características de crecimiento de la especie, fotografías con regla topográfica y antecedentes disponibles.</t>
+        </is>
+      </c>
+      <c r="F26" s="50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Intervalo de edad cronológica estimada del ejemplar, en años, independiente de su etapa de desarrollo.</t>
+        </is>
+      </c>
+      <c r="G26" s="50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Categoría</t>
+        </is>
+      </c>
+      <c r="H26" s="50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0–5 / 6–10 / 11–15 / 16–20 / 21–25 / 26–30 / 31–35 / 36–40 / 41–45 / 46–50 / 51–55 / 56–60 / 61–65 / 66–70 / 71–75 / 76–80 / 81–85 / 86–90 / 91–95 / 96–100 / Más de 100 años</t>
+        </is>
+      </c>
+      <c r="I26" s="50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Obligatorio (pendiente de validar su factibilidad)</t>
+        </is>
+      </c>
+      <c r="J26" s="50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Estimación; no calcular a partir de clase_edad ni únicamente a partir de dap_cm.</t>
+        </is>
+      </c>
+      <c r="K26" s="50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">En la inspección de Evaluación inicial o de Levantamiento del árbol.</t>
+        </is>
+      </c>
+      <c r="L26" s="50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Seleccionar un único intervalo. No establecer equivalencias automáticas entre clase_edad y la edad cronológica. No utilizar únicamente el DAP como determinante de la edad. La estimación corresponde a la fecha_inspeccion en que se registró; conservar el historial por inspección.</t>
+        </is>
       </c>
     </row>
     <row r="27" spans="1:12" s="51" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -22978,74 +23025,74 @@
     <row r="257" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A257" s="41" t="inlineStr">
         <is>
-          <t xml:space="preserve">PROYECTOS</t>
+          <t xml:space="preserve">CATALOGO_ESPECIES</t>
         </is>
       </c>
       <c r="B257" s="41" t="inlineStr">
         <is>
-          <t xml:space="preserve">id_proyecto</t>
+          <t xml:space="preserve">origen_biogeografico</t>
         </is>
       </c>
       <c r="C257" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generado por plataforma</t>
+          <t xml:space="preserve">Manual</t>
         </is>
       </c>
       <c r="D257" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sistema</t>
+          <t xml:space="preserve">Inspector</t>
         </is>
       </c>
       <c r="E257" s="41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asignación automática al crear el proyecto.</t>
+          <t xml:space="preserve">Asignación según la distribución natural de la especie respecto de Chile, consultando el Catálogo de las plantas vasculares de Chile (Rodríguez et al., 2018) o su versión en línea vigente.</t>
         </is>
       </c>
       <c r="F257" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Identificador único y estable del proyecto, que separa inventarios, delimitación territorial y acceso de usuarios.</t>
+          <t xml:space="preserve">Clasificación de la especie según su procedencia biogeográfica respecto del territorio chileno. Endémica: especie nativa cuya distribución natural está restringida a Chile. Nativa: especie nativa de Chile cuya distribución natural no se restringe al país. Introducida: especie exótica presente en Chile fuera de su distribución natural.</t>
         </is>
       </c>
       <c r="G257" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Identificador (texto)</t>
+          <t xml:space="preserve">Categoría</t>
         </is>
       </c>
       <c r="H257" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">No aplica</t>
+          <t xml:space="preserve">Nativa / Endémica / Introducida</t>
         </is>
       </c>
       <c r="I257" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Obligatorio</t>
+          <t xml:space="preserve">Obligatorio para completar la clasificación del catálogo</t>
         </is>
       </c>
       <c r="J257" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asignación automática única.</t>
+          <t xml:space="preserve">La plataforma lo vincula al árbol mediante especie_cientifica.</t>
         </is>
       </c>
       <c r="K257" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Al crear el proyecto.</t>
+          <t xml:space="preserve">Al completar o actualizar la clasificación de la especie.</t>
         </is>
       </c>
       <c r="L257" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">No editable. Solo el Administrador puede crear proyectos.</t>
+          <t xml:space="preserve">Categorías excluyentes: una especie endémica no se registra como Nativa. Considerar la distribución natural de la especie respecto de Chile, no el lugar de plantación ni el origen del ejemplar. Si aún no se conoce, dejar nulo; no inventarlo ni bloquear el registro del árbol. Se muestra en la ficha del árbol mediante especie_cientifica; no se ingresa por ejemplar ni se duplica en ARBOLES. Si el árbol no tiene especie_cientifica vigente, se informa como Origen no determinado.</t>
         </is>
       </c>
     </row>
     <row r="258" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A258" s="41" t="inlineStr">
         <is>
-          <t xml:space="preserve">PROYECTOS</t>
+          <t xml:space="preserve">CATALOGO_ESPECIES</t>
         </is>
       </c>
       <c r="B258" s="41" t="inlineStr">
         <is>
-          <t xml:space="preserve">nombre_proyecto</t>
+          <t xml:space="preserve">persistencia_follaje</t>
         </is>
       </c>
       <c r="C258" s="33" t="inlineStr">
@@ -23055,169 +23102,355 @@
       </c>
       <c r="D258" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Administrador</t>
+          <t xml:space="preserve">Inspector</t>
         </is>
       </c>
       <c r="E258" s="41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ingreso del nombre al crear o editar el proyecto.</t>
+          <t xml:space="preserve">Asignación según fuentes botánicas de referencia al incorporar o completar la especie en el catálogo.</t>
         </is>
       </c>
       <c r="F258" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nombre visible del proyecto.</t>
+          <t xml:space="preserve">Comportamiento habitual del follaje de la especie a lo largo del año. Perennifolia: conserva follaje funcional durante todo el año, con renovación gradual. Caducifolia: pierde la totalidad del follaje durante la estación desfavorable. Semicaducifolia: pierde parcialmente el follaje, o lo pierde por un período breve, según las condiciones climáticas del año.</t>
         </is>
       </c>
       <c r="G258" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Texto</t>
+          <t xml:space="preserve">Categoría</t>
         </is>
       </c>
       <c r="H258" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">No aplica</t>
+          <t xml:space="preserve">Perennifolia / Caducifolia / Semicaducifolia</t>
         </is>
       </c>
       <c r="I258" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Obligatorio</t>
+          <t xml:space="preserve">Obligatorio para completar la clasificación del catálogo</t>
         </is>
       </c>
       <c r="J258" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">No aplica.</t>
+          <t xml:space="preserve">La plataforma la vincula al árbol mediante especie_cientifica.</t>
         </is>
       </c>
       <c r="K258" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Al crear o editar el proyecto.</t>
+          <t xml:space="preserve">Al completar o actualizar la clasificación de la especie.</t>
         </is>
       </c>
       <c r="L258" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">No vacío. Su modificación no altera id_proyecto.</t>
+          <t xml:space="preserve">Corresponde al comportamiento habitual de la especie, no a la condición observada en el ejemplar. Si las fuentes describen un comportamiento variable, registrar el habitual en las condiciones climáticas de Valparaíso. Si aún no se conoce, dejar nulo; no inventarla ni bloquear el registro del árbol. No duplicar en ARBOLES. Si el árbol no tiene especie_cientifica vigente, no mostrar valor.</t>
         </is>
       </c>
     </row>
     <row r="259" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A259" s="41" t="inlineStr">
         <is>
-          <t xml:space="preserve">MIEMBROS_PROYECTO</t>
+          <t xml:space="preserve">CATALOGO_ESPECIES</t>
         </is>
       </c>
       <c r="B259" s="41" t="inlineStr">
         <is>
-          <t xml:space="preserve">id_proyecto</t>
+          <t xml:space="preserve">tipo_hoja</t>
         </is>
       </c>
       <c r="C259" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vinculado por plataforma</t>
+          <t xml:space="preserve">Manual</t>
         </is>
       </c>
       <c r="D259" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Administrador</t>
+          <t xml:space="preserve">Inspector</t>
         </is>
       </c>
       <c r="E259" s="41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Selección del proyecto al asignar un miembro.</t>
+          <t xml:space="preserve">Asignación según fuentes botánicas de referencia al incorporar o completar la especie en el catálogo.</t>
         </is>
       </c>
       <c r="F259" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Proyecto al que se asigna el usuario.</t>
+          <t xml:space="preserve">Morfología predominante de las hojas adultas de la especie. Latifoliada: lámina ancha y plana. Acicular: hoja alargada y angosta, en forma de aguja. Escuamiforme: hoja reducida a escamas adosadas a la ramilla. Palmera: hoja de palmera, palmada o pinnada.</t>
         </is>
       </c>
       <c r="G259" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Identificador (texto)</t>
+          <t xml:space="preserve">Categoría</t>
         </is>
       </c>
       <c r="H259" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">No aplica</t>
+          <t xml:space="preserve">Latifoliada / Acicular / Escuamiforme / Palmera</t>
         </is>
       </c>
       <c r="I259" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Obligatorio</t>
+          <t xml:space="preserve">Obligatorio para completar la clasificación del catálogo</t>
         </is>
       </c>
       <c r="J259" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">No aplica.</t>
+          <t xml:space="preserve">La plataforma lo vincula al árbol mediante especie_cientifica.</t>
         </is>
       </c>
       <c r="K259" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Al asignar un usuario a un proyecto.</t>
+          <t xml:space="preserve">Al completar o actualizar la clasificación de la especie.</t>
         </is>
       </c>
       <c r="L259" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Referencia válida a PROYECTOS. Un usuario puede pertenecer a varios proyectos; no repetir la misma combinación id_proyecto e id_usuario.</t>
+          <t xml:space="preserve">Seleccionar una única categoría según el follaje adulto; no considerar el follaje juvenil. Si la morfología no coincide exactamente con una categoría, asignar la más cercana: las estructuras planas que cumplen función foliar, como los filodios, se clasifican como Latifoliada; las hojas reducidas a escamas sobre ramillas verdes se clasifican como Escuamiforme. Si aún no se conoce, dejar nulo; no inventarlo ni bloquear el registro del árbol. No duplicar en ARBOLES. Si el árbol no tiene especie_cientifica vigente, no mostrar valor.</t>
         </is>
       </c>
     </row>
     <row r="260" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A260" s="41" t="inlineStr">
         <is>
+          <t xml:space="preserve">PROYECTOS</t>
+        </is>
+      </c>
+      <c r="B260" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">id_proyecto</t>
+        </is>
+      </c>
+      <c r="C260" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Generado por plataforma</t>
+        </is>
+      </c>
+      <c r="D260" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sistema</t>
+        </is>
+      </c>
+      <c r="E260" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Asignación automática al crear el proyecto.</t>
+        </is>
+      </c>
+      <c r="F260" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Identificador único y estable del proyecto, que separa inventarios, delimitación territorial y acceso de usuarios.</t>
+        </is>
+      </c>
+      <c r="G260" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Identificador (texto)</t>
+        </is>
+      </c>
+      <c r="H260" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No aplica</t>
+        </is>
+      </c>
+      <c r="I260" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Obligatorio</t>
+        </is>
+      </c>
+      <c r="J260" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Asignación automática única.</t>
+        </is>
+      </c>
+      <c r="K260" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Al crear el proyecto.</t>
+        </is>
+      </c>
+      <c r="L260" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No editable. Solo el Administrador puede crear proyectos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="261" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A261" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PROYECTOS</t>
+        </is>
+      </c>
+      <c r="B261" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nombre_proyecto</t>
+        </is>
+      </c>
+      <c r="C261" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="D261" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Administrador</t>
+        </is>
+      </c>
+      <c r="E261" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ingreso del nombre al crear o editar el proyecto.</t>
+        </is>
+      </c>
+      <c r="F261" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nombre visible del proyecto.</t>
+        </is>
+      </c>
+      <c r="G261" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Texto</t>
+        </is>
+      </c>
+      <c r="H261" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No aplica</t>
+        </is>
+      </c>
+      <c r="I261" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Obligatorio</t>
+        </is>
+      </c>
+      <c r="J261" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No aplica.</t>
+        </is>
+      </c>
+      <c r="K261" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Al crear o editar el proyecto.</t>
+        </is>
+      </c>
+      <c r="L261" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No vacío. Su modificación no altera id_proyecto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="262" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A262" s="41" t="inlineStr">
+        <is>
           <t xml:space="preserve">MIEMBROS_PROYECTO</t>
         </is>
       </c>
-      <c r="B260" s="41" t="inlineStr">
+      <c r="B262" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">id_proyecto</t>
+        </is>
+      </c>
+      <c r="C262" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vinculado por plataforma</t>
+        </is>
+      </c>
+      <c r="D262" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Administrador</t>
+        </is>
+      </c>
+      <c r="E262" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Selección del proyecto al asignar un miembro.</t>
+        </is>
+      </c>
+      <c r="F262" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proyecto al que se asigna el usuario.</t>
+        </is>
+      </c>
+      <c r="G262" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Identificador (texto)</t>
+        </is>
+      </c>
+      <c r="H262" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No aplica</t>
+        </is>
+      </c>
+      <c r="I262" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Obligatorio</t>
+        </is>
+      </c>
+      <c r="J262" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No aplica.</t>
+        </is>
+      </c>
+      <c r="K262" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Al asignar un usuario a un proyecto.</t>
+        </is>
+      </c>
+      <c r="L262" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Referencia válida a PROYECTOS. Un usuario puede pertenecer a varios proyectos; no repetir la misma combinación id_proyecto e id_usuario.</t>
+        </is>
+      </c>
+    </row>
+    <row r="263" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A263" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MIEMBROS_PROYECTO</t>
+        </is>
+      </c>
+      <c r="B263" s="41" t="inlineStr">
         <is>
           <t xml:space="preserve">id_usuario</t>
         </is>
       </c>
-      <c r="C260" s="33" t="inlineStr">
+      <c r="C263" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">Vinculado por plataforma</t>
         </is>
       </c>
-      <c r="D260" s="33" t="inlineStr">
+      <c r="D263" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">Administrador</t>
         </is>
       </c>
-      <c r="E260" s="41" t="inlineStr">
+      <c r="E263" s="41" t="inlineStr">
         <is>
           <t xml:space="preserve">Selección del usuario al asignarlo al proyecto.</t>
         </is>
       </c>
-      <c r="F260" s="33" t="inlineStr">
+      <c r="F263" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">Usuario con acceso al proyecto.</t>
         </is>
       </c>
-      <c r="G260" s="33" t="inlineStr">
+      <c r="G263" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">Identificador (texto)</t>
         </is>
       </c>
-      <c r="H260" s="33" t="inlineStr">
+      <c r="H263" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">No aplica</t>
         </is>
       </c>
-      <c r="I260" s="33" t="inlineStr">
+      <c r="I263" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">Obligatorio</t>
         </is>
       </c>
-      <c r="J260" s="33" t="inlineStr">
+      <c r="J263" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">No aplica.</t>
         </is>
       </c>
-      <c r="K260" s="33" t="inlineStr">
+      <c r="K263" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">Al asignar un usuario a un proyecto.</t>
         </is>
       </c>
-      <c r="L260" s="33" t="inlineStr">
+      <c r="L263" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">Referencia válida a USUARIOS con activo = Sí. El rol del usuario se mantiene en USUARIOS.Rol.</t>
         </is>

--- a/docs/excel/Base de Datos Valpo Verde.xlsx
+++ b/docs/excel/Base de Datos Valpo Verde.xlsx
@@ -7135,7 +7135,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -7680,7 +7680,7 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">SIVU sugiere, según nivel_riesgo, el rango de la próxima inspección técnica y del próximo monitoreo: Bajo 24 meses y 12 meses; Moderado 12 meses y 3 a 6 meses; Alto 1 a 3 meses y 2 a 4 semanas; Extremo reevaluación dentro de 1 a 4 semanas y monitoreo inmediato y continuo mientras persista el peligro. Al llegar el inicio de cada rango, la fecha se envía al calendario del módulo para agendarla. El Inspector puede ajustarla registrando justificacion_ajuste_fecha.</t>
+          <t xml:space="preserve">SIVU sugiere, según nivel_riesgo, el rango de la próxima inspección técnica y del próximo monitoreo: Bajo 24 meses y 12 meses; Moderado 12 meses y 3 a 6 meses; Alto 1 a 3 meses y 2 a 4 semanas; Extremo reevaluación dentro de 1 a 4 semanas y monitoreo inmediato y continuo mientras persista el peligro. SIVU no agenda automáticamente: al llegar el inicio de cada rango, muestra un recordatorio en la lista de próximas inspecciones y monitoreos del proyecto, con el inicio y el término del rango, desde la cual el Usuario municipal crea y programa la OT. El Inspector puede ajustar la fecha registrando justificacion_ajuste_fecha.</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
@@ -7691,6 +7691,28 @@
       <c r="D25" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">INSPECCION</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Historial y vigencia</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mientras una inspección está Preguardado, el Inspector puede modificar todos sus datos. Una inspección Finalizado no se modifica: si contiene un error, el Inspector la anula registrando motivo_anulacion. La inspección anulada se conserva en el historial y deja de considerarse para la vigencia. Los datos correctos se registran en una nueva inspección: en la misma OT si todavía no está completada; si lo está, en una nueva OT. Solo el Inspector anula inspecciones.</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estado_registro; motivo_anulacion; anulado_por; fecha_anulacion</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">INSPECCION; ARBOLES; REGISTRO_EVALUACION; ORDENES DE TRABAJO</t>
         </is>
       </c>
     </row>
@@ -11435,7 +11457,7 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -11585,6 +11607,38 @@
       <c r="J4" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Contenido del Excel auditado el 2026-10-18 (incluye REGLAS_GENERALES y REGLAS_INDICADORES con 98 reglas). Por CC-028 es la única fuente metodológica del proyecto y reemplaza al Excel anterior; prevalece sobre CC-008, CC-009 y CC-020 en lo que los contradiga (conflictos P1–P9 de CC-026). NO publica la versión 2.0.0 ni define rule_version (C1 pendiente).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.0.0</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.0</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">aprobación de publicación pendiente</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CC-024, CC-026, CC-027, CC-028, CC-029, CC-030, CC-031, CC-032, CC-034, CC-035, CC-036, CC-037, CC-039</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.0.0 en preparación (fuente única desde CC-028)</t>
+        </is>
+      </c>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Incluye AM-10: textos de CC-031, CC-032, CC-036 y CC-037; rango_edad_estimada_anios opcional (CC-039) y referencia estacional de la defoliación en caducifolias (AM-11). El Excel maestro es la única fuente (CC-028) y los diagramas no forman parte del paquete (CC-030). INDICES sigue en propuesta (DM-09). Todas las reglas de REGLAS_INDICADORES son vigentes en esta versión (PR-011 v3.0). Al publicar, la autora completa fecha_publicacion, aprobado_por, fecha_aprobacion y tag_git, y cambia el estado a publicada.</t>
         </is>
       </c>
     </row>
@@ -12418,7 +12472,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:S1"/>
+  <dimension ref="A1:V1"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.6640625" customWidth="1"/>
@@ -12428,7 +12482,7 @@
     <col min="14" max="14" width="25.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:22" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">id_inspeccion</t>
@@ -12522,6 +12576,21 @@
       <c r="S1" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">estado_registro</t>
+        </is>
+      </c>
+      <c r="T1" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">motivo_anulacion</t>
+        </is>
+      </c>
+      <c r="U1" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">anulado_por</t>
+        </is>
+      </c>
+      <c r="V1" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fecha_anulacion</t>
         </is>
       </c>
     </row>
@@ -13053,7 +13122,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M263"/>
+  <dimension ref="A1:M266"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="24" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7" style="41" customWidth="1"/>
@@ -13381,7 +13450,7 @@
       </c>
       <c r="E9" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ingreso manual de la coordenada del árbol obtenida en terreno.</t>
+          <t xml:space="preserve">Ingreso manual de la coordenada del árbol obtenida en terreno. Como ayuda, al marcar el punto en el mapa del formulario la plataforma rellena utm_este y utm_norte, que siguen siendo editables.</t>
         </is>
       </c>
       <c r="F9" s="7" t="s">
@@ -13398,8 +13467,10 @@
       </c>
       <c r="J9" s="7"/>
       <c r="K9" s="7"/>
-      <c r="L9" s="7" t="s">
-        <v>349</v>
+      <c r="L9" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Coordenada UTM huso 19S, datum WGS84 (EPSG:32719). Este y Norte deben ser coherentes con el huso y el datum fijos. Si proviene del punto marcado en el mapa, la plataforma la convierte a UTM y puede editarse antes de guardar.</t>
+        </is>
       </c>
     </row>
     <row r="10" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -13417,7 +13488,7 @@
       </c>
       <c r="E10" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ingreso manual de la coordenada del árbol obtenida en terreno.</t>
+          <t xml:space="preserve">Ingreso manual de la coordenada del árbol obtenida en terreno. Como ayuda, al marcar el punto en el mapa del formulario la plataforma rellena utm_este y utm_norte, que siguen siendo editables.</t>
         </is>
       </c>
       <c r="F10" s="8" t="s">
@@ -13434,8 +13505,10 @@
       </c>
       <c r="J10" s="8"/>
       <c r="K10" s="8"/>
-      <c r="L10" s="8" t="s">
-        <v>349</v>
+      <c r="L10" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Coordenada UTM huso 19S, datum WGS84 (EPSG:32719). Norte y Este deben ser coherentes con el huso y el datum fijos. Si proviene del punto marcado en el mapa, la plataforma la convierte a UTM y puede editarse antes de guardar.</t>
+        </is>
       </c>
     </row>
     <row r="11" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -14045,7 +14118,7 @@
       </c>
       <c r="I26" s="50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Obligatorio (pendiente de validar su factibilidad)</t>
+          <t xml:space="preserve">Opcional</t>
         </is>
       </c>
       <c r="J26" s="50" t="inlineStr">
@@ -14060,7 +14133,7 @@
       </c>
       <c r="L26" s="50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seleccionar un único intervalo. No establecer equivalencias automáticas entre clase_edad y la edad cronológica. No utilizar únicamente el DAP como determinante de la edad. La estimación corresponde a la fecha_inspeccion en que se registró; conservar el historial por inspección.</t>
+          <t xml:space="preserve">Seleccionar un único intervalo. No establecer equivalencias automáticas entre clase_edad y la edad cronológica. No utilizar únicamente el DAP como determinante de la edad. La estimación corresponde a la fecha_inspeccion en que se registró; conservar el historial por inspección. Opcional mientras no se valide la factibilidad de su estimación; no se exige para finalizar la inspección.</t>
         </is>
       </c>
     </row>
@@ -16235,8 +16308,10 @@
         <v>525</v>
       </c>
       <c r="K83" s="7"/>
-      <c r="L83" s="7" t="s">
-        <v>526</v>
+      <c r="L83" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Valor numérico entre 0 y 100 %. 0 % representa ausencia de pérdida de follaje respecto del árbol de referencia. La estimación debe realizarse sobre la copa evaluable y respecto de una condición de referencia comparable. En especies con persistencia_follaje = Caducifolia o Semicaducifolia (CATALOGO_ESPECIES) evaluadas en receso vegetativo, la referencia es la copa de la misma especie en esa condición estacional: la pérdida estacional de hojas no se registra como defoliación.</t>
+        </is>
       </c>
     </row>
     <row r="84" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -19972,11 +20047,15 @@
       <c r="D178" s="33" t="s">
         <v>1071</v>
       </c>
-      <c r="E178" s="41" t="s">
-        <v>1072</v>
-      </c>
-      <c r="F178" s="33" t="s">
-        <v>1073</v>
+      <c r="E178" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mediante el ingreso del nombre de la persona que comunica la incidencia en el formulario ciudadano público, al que se accede por el código QR del árbol.</t>
+        </is>
+      </c>
+      <c r="F178" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nombre de la persona natural que informa una situación relacionada con el arbolado urbano o su interacción con la infraestructura. Es un dato personal: solo lo ve el Usuario municipal y se conserva únicamente mientras se revisa la incidencia.</t>
+        </is>
       </c>
       <c r="G178" s="33" t="s">
         <v>343</v>
@@ -19984,12 +20063,14 @@
       <c r="H178" s="33" t="s">
         <v>1074</v>
       </c>
-      <c r="I178" s="33" t="s">
-        <v>324</v>
+      <c r="I178" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Obligatorio al reportar</t>
+        </is>
       </c>
       <c r="L178" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aceptar caracteres alfabéticos, espacios y tildes. Limitar a 100 caracteres.</t>
+          <t xml:space="preserve">Aceptar caracteres alfabéticos, espacios y tildes. Limitar a 100 caracteres. Visible solo para el Usuario municipal. Se elimina junto con rut_reportante cuando resultado_revision = Validada o Descartada; con Requiere antecedentes se conserva hasta el resultado final.</t>
         </is>
       </c>
     </row>
@@ -20006,11 +20087,15 @@
       <c r="D179" s="33" t="s">
         <v>1071</v>
       </c>
-      <c r="E179" s="41" t="s">
-        <v>1076</v>
-      </c>
-      <c r="F179" s="33" t="s">
-        <v>1077</v>
+      <c r="E179" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mediante el ingreso del RUT de la persona que comunica la incidencia en el formulario ciudadano público, al que se accede por el código QR del árbol.</t>
+        </is>
+      </c>
+      <c r="F179" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Identificador tributario de la persona natural que reporta. Es un dato personal: solo lo ve el Usuario municipal y se conserva únicamente mientras se revisa la incidencia.</t>
+        </is>
       </c>
       <c r="G179" s="33" t="s">
         <v>343</v>
@@ -20018,12 +20103,14 @@
       <c r="H179" s="33" t="s">
         <v>1078</v>
       </c>
-      <c r="I179" s="33" t="s">
-        <v>324</v>
+      <c r="I179" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Obligatorio al reportar</t>
+        </is>
       </c>
       <c r="L179" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Validar estructura y dígito verificador del RUT.</t>
+          <t xml:space="preserve">Validar estructura y dígito verificador del RUT. Visible solo para el Usuario municipal. Se elimina junto con nombre_reportante cuando resultado_revision = Validada o Descartada; con Requiere antecedentes se conserva hasta el resultado final.</t>
         </is>
       </c>
     </row>
@@ -20306,8 +20393,10 @@
       <c r="E187" s="41" t="s">
         <v>1088</v>
       </c>
-      <c r="F187" s="33" t="s">
-        <v>1089</v>
+      <c r="F187" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Resultado administrativo de la verificación municipal del reporte. Validada: el reporte requiere atención. Descartada: no corresponde atenderlo. Requiere antecedentes: la información disponible no basta para decidir y es necesario que el Inspector confirme en terreno el estado del árbol; no implica pedir información al reportante.</t>
+        </is>
       </c>
       <c r="G187" s="33" t="s">
         <v>357</v>
@@ -20327,7 +20416,7 @@
       </c>
       <c r="L187" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Debe utilizar valores de un catálogo controlado.</t>
+          <t xml:space="preserve">Debe utilizar valores de un catálogo controlado. Requiere antecedentes es un resultado intermedio: el Usuario municipal crea una OT de Inspección del árbol vinculada mediante id_incidencia y, con el resultado de esa inspección, registra Validada o Descartada. Al registrar Validada o Descartada se eliminan nombre_reportante y rut_reportante.</t>
         </is>
       </c>
     </row>
@@ -20892,7 +20981,7 @@
       </c>
       <c r="L202" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Posterior a fecha_inspeccion. Mostrar el rango sugerido; al llegar la fecha de inicio, enviarla al calendario del módulo para agendarla. Si el Inspector la modifica, exigir justificacion_ajuste_fecha.</t>
+          <t xml:space="preserve">Posterior a fecha_inspeccion. Mostrar el rango sugerido. Al llegar la fecha de inicio, SIVU la muestra como recordatorio en la lista de próximas inspecciones del proyecto, desde la cual el Usuario municipal crea y programa la OT; SIVU no agenda automáticamente. Si el Inspector la modifica, exigir justificacion_ajuste_fecha.</t>
         </is>
       </c>
     </row>
@@ -20954,7 +21043,7 @@
       </c>
       <c r="L203" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Igual o posterior a fecha_inspeccion. Mostrar el rango sugerido; al llegar la fecha de inicio, enviarla al calendario del módulo para agendarla. Si el Inspector la modifica, exigir justificacion_ajuste_fecha.</t>
+          <t xml:space="preserve">Igual o posterior a fecha_inspeccion. Mostrar el rango sugerido. Al llegar la fecha de inicio, SIVU la muestra como recordatorio en la lista de próximos monitoreos del proyecto, desde la cual el Usuario municipal crea y programa la OT; SIVU no agenda automáticamente. Si el Inspector la modifica, exigir justificacion_ajuste_fecha.</t>
         </is>
       </c>
     </row>
@@ -21176,149 +21265,234 @@
       </c>
       <c r="D209" s="33" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sistema / Inspector (solo la anulación)</t>
+        </is>
+      </c>
+      <c r="E209" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Asignación automática según la completitud de los datos obligatorios aplicables de la inspección. El valor Anulado lo registra el Inspector.</t>
+        </is>
+      </c>
+      <c r="F209" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Estado del registro de la inspección. Preguardado: falta al menos un dato obligatorio aplicable. Finalizado: todos los datos obligatorios aplicables están registrados. Anulado: inspección finalizada que el Inspector anuló por contener un error; se conserva en el historial y no se considera para la vigencia.</t>
+        </is>
+      </c>
+      <c r="G209" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Categoría</t>
+        </is>
+      </c>
+      <c r="H209" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preguardado / Finalizado / Anulado</t>
+        </is>
+      </c>
+      <c r="I209" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Obligatorio</t>
+        </is>
+      </c>
+      <c r="J209" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Finalizado cuando están completos todos los campos obligatorios y los condicionales activados de la inspección, de su REGISTRO_EVALUACION y de los datos técnicos del árbol registrados en ella; en otro caso, Preguardado. Anulado solo desde Finalizado, cuando el Inspector registra motivo_anulacion.</t>
+        </is>
+      </c>
+      <c r="K209" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Al guardar la inspección.</t>
+        </is>
+      </c>
+      <c r="L209" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No editable manualmente, salvo la anulación por el Inspector. Valor inicial: Preguardado. Una inspección Preguardado o Anulado no modifica la evaluación vigente del árbol. Mientras alguna inspección vinculada esté Preguardado, la OT no puede pasar a estado_ot = Completada. Una medición pendiente no equivale a cero ni a No presenta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="210" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A210" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">INSPECCION</t>
+        </is>
+      </c>
+      <c r="B210" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">motivo_anulacion</t>
+        </is>
+      </c>
+      <c r="C210" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="D210" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Inspector</t>
+        </is>
+      </c>
+      <c r="E210" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Descripción libre del Inspector al anular la inspección.</t>
+        </is>
+      </c>
+      <c r="F210" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fundamento de la anulación de una inspección finalizada que contiene un error.</t>
+        </is>
+      </c>
+      <c r="G210" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Texto</t>
+        </is>
+      </c>
+      <c r="H210" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No aplica</t>
+        </is>
+      </c>
+      <c r="I210" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Condicional</t>
+        </is>
+      </c>
+      <c r="J210" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No aplica.</t>
+        </is>
+      </c>
+      <c r="K210" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estado_registro = Anulado</t>
+        </is>
+      </c>
+      <c r="L210" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Texto libre, no vacío. Solo el Inspector anula. No editable después de registrar la anulación.</t>
+        </is>
+      </c>
+    </row>
+    <row r="211" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A211" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">INSPECCION</t>
+        </is>
+      </c>
+      <c r="B211" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">anulado_por</t>
+        </is>
+      </c>
+      <c r="C211" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vinculado por plataforma</t>
+        </is>
+      </c>
+      <c r="D211" s="33" t="inlineStr">
+        <is>
           <t xml:space="preserve">Sistema</t>
         </is>
       </c>
-      <c r="E209" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Asignación automática según la completitud de los datos obligatorios aplicables de la inspección.</t>
-        </is>
-      </c>
-      <c r="F209" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Estado de completitud del registro de la inspección. Preguardado: falta al menos un dato obligatorio aplicable. Finalizado: todos los datos obligatorios aplicables están registrados.</t>
-        </is>
-      </c>
-      <c r="G209" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Categoría</t>
-        </is>
-      </c>
-      <c r="H209" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Preguardado / Finalizado</t>
-        </is>
-      </c>
-      <c r="I209" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Obligatorio</t>
-        </is>
-      </c>
-      <c r="J209" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Finalizado cuando están completos todos los campos obligatorios y los condicionales activados de la inspección, de su REGISTRO_EVALUACION y de los datos técnicos del árbol registrados en ella; en otro caso, Preguardado.</t>
-        </is>
-      </c>
-      <c r="K209" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Al guardar la inspección.</t>
-        </is>
-      </c>
-      <c r="L209" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">No editable manualmente. Valor inicial: Preguardado. Una inspección Preguardado no modifica la evaluación vigente del árbol. Mientras alguna inspección vinculada esté Preguardado, la OT no puede pasar a estado_ot = Completada. Una medición pendiente no equivale a cero ni a No presenta.</t>
-        </is>
-      </c>
-    </row>
-    <row r="210" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A210" s="41" t="s">
-        <v>790</v>
-      </c>
-      <c r="B210" s="41" t="s">
-        <v>198</v>
-      </c>
-      <c r="C210" s="33" t="s">
-        <v>318</v>
-      </c>
-      <c r="D210" s="33" t="s">
-        <v>319</v>
-      </c>
-      <c r="E210" s="41" t="s">
-        <v>320</v>
-      </c>
-      <c r="F210" s="33" t="s">
-        <v>791</v>
-      </c>
-      <c r="G210" s="33" t="s">
-        <v>322</v>
-      </c>
-      <c r="H210" s="33" t="s">
-        <v>792</v>
-      </c>
-      <c r="I210" s="33" t="s">
-        <v>324</v>
-      </c>
-      <c r="K210" s="8"/>
-      <c r="L210" s="8" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="211" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A211" s="41" t="s">
-        <v>790</v>
-      </c>
-      <c r="B211" s="41" t="s">
-        <v>177</v>
-      </c>
-      <c r="C211" s="33" t="s">
-        <v>326</v>
-      </c>
-      <c r="D211" s="33" t="s">
-        <v>319</v>
-      </c>
-      <c r="E211" s="41" t="s">
-        <v>328</v>
-      </c>
-      <c r="F211" s="33" t="s">
-        <v>793</v>
-      </c>
-      <c r="G211" s="33" t="s">
-        <v>322</v>
-      </c>
-      <c r="H211" s="33" t="s">
-        <v>323</v>
-      </c>
-      <c r="I211" s="33" t="s">
-        <v>324</v>
-      </c>
-      <c r="K211" s="8"/>
+      <c r="E211" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Usuario autenticado que anula la inspección.</t>
+        </is>
+      </c>
+      <c r="F211" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Inspector que anuló la inspección.</t>
+        </is>
+      </c>
+      <c r="G211" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Identificador (texto)</t>
+        </is>
+      </c>
+      <c r="H211" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No aplica</t>
+        </is>
+      </c>
+      <c r="I211" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Condicional</t>
+        </is>
+      </c>
+      <c r="J211" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No aplica.</t>
+        </is>
+      </c>
+      <c r="K211" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estado_registro = Anulado</t>
+        </is>
+      </c>
       <c r="L211" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Referencia válida a ORDENES DE TRABAJO con Tipo_ot = Mantenimiento. Una OT puede tener varios registros de MANTENIMIENTO: si una ejecución es rechazada, la corrección se registra como un nuevo registro y se conservan los anteriores.</t>
+          <t xml:space="preserve">Referencia válida a USUARIOS con rol Inspector. Conservar autoría histórica.</t>
         </is>
       </c>
     </row>
     <row r="212" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A212" s="41" t="s">
-        <v>790</v>
-      </c>
-      <c r="B212" s="41" t="s">
-        <v>0</v>
-      </c>
-      <c r="C212" s="33" t="s">
-        <v>326</v>
-      </c>
-      <c r="D212" s="33" t="s">
-        <v>319</v>
-      </c>
-      <c r="E212" s="41" t="s">
-        <v>746</v>
-      </c>
-      <c r="F212" s="33" t="s">
-        <v>795</v>
-      </c>
-      <c r="G212" s="33" t="s">
-        <v>322</v>
-      </c>
-      <c r="H212" s="33" t="s">
-        <v>323</v>
-      </c>
-      <c r="I212" s="33" t="s">
-        <v>324</v>
-      </c>
-      <c r="K212" s="8"/>
-      <c r="L212" s="8" t="s">
-        <v>748</v>
+      <c r="A212" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">INSPECCION</t>
+        </is>
+      </c>
+      <c r="B212" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fecha_anulacion</t>
+        </is>
+      </c>
+      <c r="C212" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sistema</t>
+        </is>
+      </c>
+      <c r="D212" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sistema</t>
+        </is>
+      </c>
+      <c r="E212" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fecha y hora asignadas por el sistema al registrar la anulación.</t>
+        </is>
+      </c>
+      <c r="F212" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Momento en que la inspección fue anulada.</t>
+        </is>
+      </c>
+      <c r="G212" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fecha y hora</t>
+        </is>
+      </c>
+      <c r="H212" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dd/mm/aaaa HH:mm</t>
+        </is>
+      </c>
+      <c r="I212" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Condicional</t>
+        </is>
+      </c>
+      <c r="J212" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No aplica.</t>
+        </is>
+      </c>
+      <c r="K212" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estado_registro = Anulado</t>
+        </is>
+      </c>
+      <c r="L212" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Igual o posterior a fecha_registro. No editable.</t>
+        </is>
       </c>
     </row>
     <row r="213" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -21326,32 +21500,32 @@
         <v>790</v>
       </c>
       <c r="B213" s="41" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C213" s="33" t="s">
-        <v>276</v>
+        <v>318</v>
       </c>
       <c r="D213" s="33" t="s">
-        <v>261</v>
+        <v>319</v>
       </c>
       <c r="E213" s="41" t="s">
-        <v>749</v>
+        <v>320</v>
       </c>
       <c r="F213" s="33" t="s">
-        <v>796</v>
+        <v>791</v>
       </c>
       <c r="G213" s="33" t="s">
-        <v>335</v>
+        <v>322</v>
       </c>
       <c r="H213" s="33" t="s">
-        <v>336</v>
+        <v>792</v>
       </c>
       <c r="I213" s="33" t="s">
         <v>324</v>
       </c>
       <c r="K213" s="8"/>
       <c r="L213" s="8" t="s">
-        <v>337</v>
+        <v>325</v>
       </c>
     </row>
     <row r="214" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -21359,19 +21533,19 @@
         <v>790</v>
       </c>
       <c r="B214" s="41" t="s">
-        <v>200</v>
+        <v>177</v>
       </c>
       <c r="C214" s="33" t="s">
         <v>326</v>
       </c>
       <c r="D214" s="33" t="s">
-        <v>261</v>
+        <v>319</v>
       </c>
       <c r="E214" s="41" t="s">
-        <v>797</v>
+        <v>328</v>
       </c>
       <c r="F214" s="33" t="s">
-        <v>798</v>
+        <v>793</v>
       </c>
       <c r="G214" s="33" t="s">
         <v>322</v>
@@ -21383,8 +21557,10 @@
         <v>324</v>
       </c>
       <c r="K214" s="8"/>
-      <c r="L214" s="8" t="s">
-        <v>799</v>
+      <c r="L214" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Referencia válida a ORDENES DE TRABAJO con Tipo_ot = Mantenimiento. Una OT puede tener varios registros de MANTENIMIENTO: si una ejecución es rechazada, la corrección se registra como un nuevo registro y se conservan los anteriores.</t>
+        </is>
       </c>
     </row>
     <row r="215" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -21392,32 +21568,32 @@
         <v>790</v>
       </c>
       <c r="B215" s="41" t="s">
-        <v>201</v>
+        <v>0</v>
       </c>
       <c r="C215" s="33" t="s">
-        <v>276</v>
+        <v>326</v>
       </c>
       <c r="D215" s="33" t="s">
-        <v>261</v>
+        <v>319</v>
       </c>
       <c r="E215" s="41" t="s">
-        <v>721</v>
+        <v>746</v>
       </c>
       <c r="F215" s="33" t="s">
-        <v>800</v>
+        <v>795</v>
       </c>
       <c r="G215" s="33" t="s">
-        <v>357</v>
+        <v>322</v>
       </c>
       <c r="H215" s="33" t="s">
-        <v>801</v>
+        <v>323</v>
       </c>
       <c r="I215" s="33" t="s">
         <v>324</v>
       </c>
       <c r="K215" s="8"/>
       <c r="L215" s="8" t="s">
-        <v>802</v>
+        <v>748</v>
       </c>
     </row>
     <row r="216" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -21425,7 +21601,7 @@
         <v>790</v>
       </c>
       <c r="B216" s="41" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="C216" s="33" t="s">
         <v>276</v>
@@ -21434,25 +21610,23 @@
         <v>261</v>
       </c>
       <c r="E216" s="41" t="s">
-        <v>803</v>
+        <v>749</v>
       </c>
       <c r="F216" s="33" t="s">
-        <v>804</v>
+        <v>796</v>
       </c>
       <c r="G216" s="33" t="s">
-        <v>357</v>
+        <v>335</v>
       </c>
       <c r="H216" s="33" t="s">
-        <v>805</v>
+        <v>336</v>
       </c>
       <c r="I216" s="33" t="s">
-        <v>363</v>
-      </c>
-      <c r="K216" s="8" t="s">
-        <v>806</v>
-      </c>
+        <v>324</v>
+      </c>
+      <c r="K216" s="8"/>
       <c r="L216" s="8" t="s">
-        <v>807</v>
+        <v>337</v>
       </c>
     </row>
     <row r="217" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -21460,40 +21634,32 @@
         <v>790</v>
       </c>
       <c r="B217" s="41" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="C217" s="33" t="s">
-        <v>276</v>
+        <v>326</v>
       </c>
       <c r="D217" s="33" t="s">
         <v>261</v>
       </c>
-      <c r="E217" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Selección desde lista.</t>
-        </is>
+      <c r="E217" s="41" t="s">
+        <v>797</v>
       </c>
       <c r="F217" s="33" t="s">
-        <v>809</v>
-      </c>
-      <c r="G217" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Categoría</t>
-        </is>
-      </c>
-      <c r="H217" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ejecutado completamente / Ejecutado parcialmente / No ejecutado</t>
-        </is>
+        <v>798</v>
+      </c>
+      <c r="G217" s="33" t="s">
+        <v>322</v>
+      </c>
+      <c r="H217" s="33" t="s">
+        <v>323</v>
       </c>
       <c r="I217" s="33" t="s">
         <v>324</v>
       </c>
       <c r="K217" s="8"/>
-      <c r="L217" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Seleccionar una opción de la lista. El cierre automático de la OT solo procede si resultado = Ejecutado completamente; en otro caso, la OT permanece En ejecución.</t>
-        </is>
+      <c r="L217" s="8" t="s">
+        <v>799</v>
       </c>
     </row>
     <row r="218" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -21501,7 +21667,7 @@
         <v>790</v>
       </c>
       <c r="B218" s="41" t="s">
-        <v>188</v>
+        <v>201</v>
       </c>
       <c r="C218" s="33" t="s">
         <v>276</v>
@@ -21510,23 +21676,23 @@
         <v>261</v>
       </c>
       <c r="E218" s="41" t="s">
-        <v>811</v>
+        <v>721</v>
       </c>
       <c r="F218" s="33" t="s">
-        <v>812</v>
+        <v>800</v>
       </c>
       <c r="G218" s="33" t="s">
-        <v>343</v>
+        <v>357</v>
       </c>
       <c r="H218" s="33" t="s">
-        <v>323</v>
+        <v>801</v>
       </c>
       <c r="I218" s="33" t="s">
-        <v>439</v>
+        <v>324</v>
       </c>
       <c r="K218" s="8"/>
       <c r="L218" s="8" t="s">
-        <v>730</v>
+        <v>802</v>
       </c>
     </row>
     <row r="219" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -21534,7 +21700,7 @@
         <v>790</v>
       </c>
       <c r="B219" s="41" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C219" s="33" t="s">
         <v>276</v>
@@ -21543,29 +21709,33 @@
         <v>261</v>
       </c>
       <c r="E219" s="41" t="s">
-        <v>721</v>
+        <v>803</v>
       </c>
       <c r="F219" s="33" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="G219" s="33" t="s">
         <v>357</v>
       </c>
       <c r="H219" s="33" t="s">
-        <v>358</v>
+        <v>805</v>
       </c>
       <c r="I219" s="33" t="s">
-        <v>324</v>
-      </c>
-      <c r="K219" s="8"/>
-      <c r="L219" s="8"/>
+        <v>363</v>
+      </c>
+      <c r="K219" s="8" t="s">
+        <v>806</v>
+      </c>
+      <c r="L219" s="8" t="s">
+        <v>807</v>
+      </c>
     </row>
     <row r="220" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A220" s="41" t="s">
         <v>790</v>
       </c>
       <c r="B220" s="41" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C220" s="33" t="s">
         <v>276</v>
@@ -21573,26 +21743,32 @@
       <c r="D220" s="33" t="s">
         <v>261</v>
       </c>
-      <c r="E220" s="41" t="s">
-        <v>814</v>
+      <c r="E220" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Selección desde lista.</t>
+        </is>
       </c>
       <c r="F220" s="33" t="s">
-        <v>815</v>
-      </c>
-      <c r="G220" s="33" t="s">
-        <v>335</v>
-      </c>
-      <c r="H220" s="33" t="s">
-        <v>336</v>
+        <v>809</v>
+      </c>
+      <c r="G220" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Categoría</t>
+        </is>
+      </c>
+      <c r="H220" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ejecutado completamente / Ejecutado parcialmente / No ejecutado</t>
+        </is>
       </c>
       <c r="I220" s="33" t="s">
-        <v>363</v>
-      </c>
-      <c r="K220" s="8" t="s">
-        <v>816</v>
-      </c>
-      <c r="L220" s="8" t="s">
-        <v>817</v>
+        <v>324</v>
+      </c>
+      <c r="K220" s="8"/>
+      <c r="L220" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Seleccionar una opción de la lista. El cierre automático de la OT solo procede si resultado = Ejecutado completamente; en otro caso, la OT permanece En ejecución.</t>
+        </is>
       </c>
     </row>
     <row r="221" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -21600,7 +21776,7 @@
         <v>790</v>
       </c>
       <c r="B221" s="41" t="s">
-        <v>163</v>
+        <v>188</v>
       </c>
       <c r="C221" s="33" t="s">
         <v>276</v>
@@ -21609,27 +21785,23 @@
         <v>261</v>
       </c>
       <c r="E221" s="41" t="s">
-        <v>733</v>
+        <v>811</v>
       </c>
       <c r="F221" s="33" t="s">
-        <v>818</v>
+        <v>812</v>
       </c>
       <c r="G221" s="33" t="s">
-        <v>735</v>
+        <v>343</v>
       </c>
       <c r="H221" s="33" t="s">
-        <v>736</v>
-      </c>
-      <c r="I221" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Obligatorio</t>
-        </is>
+        <v>323</v>
+      </c>
+      <c r="I221" s="33" t="s">
+        <v>439</v>
       </c>
       <c r="K221" s="8"/>
-      <c r="L221" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Obligatoria para completar la OT. Conservar las imágenes vinculadas a cada registro de ejecución.</t>
-        </is>
+      <c r="L221" s="8" t="s">
+        <v>730</v>
       </c>
     </row>
     <row r="222" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -21637,85 +21809,65 @@
         <v>790</v>
       </c>
       <c r="B222" s="41" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C222" s="33" t="s">
         <v>276</v>
       </c>
-      <c r="D222" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sistema / Inspector</t>
-        </is>
+      <c r="D222" s="33" t="s">
+        <v>261</v>
       </c>
       <c r="E222" s="41" t="s">
         <v>721</v>
       </c>
-      <c r="F222" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Estado de la revisión de la acción ejecutada, realizada por el Inspector.</t>
-        </is>
+      <c r="F222" s="33" t="s">
+        <v>813</v>
       </c>
       <c r="G222" s="33" t="s">
         <v>357</v>
       </c>
       <c r="H222" s="33" t="s">
-        <v>821</v>
-      </c>
-      <c r="I222" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Condicional</t>
-        </is>
-      </c>
-      <c r="K222" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">requiere_revision_inspector = Sí en la orden de trabajo.</t>
-        </is>
-      </c>
-      <c r="L222" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Valor inicial: Pendiente de revisión, asignado por el Sistema. Aprobado o Rechazado lo registra el Inspector. Si requiere_revision_inspector = No, desactivar y dejar vacío.</t>
-        </is>
-      </c>
+        <v>358</v>
+      </c>
+      <c r="I222" s="33" t="s">
+        <v>324</v>
+      </c>
+      <c r="K222" s="8"/>
+      <c r="L222" s="8"/>
     </row>
     <row r="223" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A223" s="41" t="s">
         <v>790</v>
       </c>
       <c r="B223" s="41" t="s">
-        <v>165</v>
+        <v>205</v>
       </c>
       <c r="C223" s="33" t="s">
-        <v>326</v>
-      </c>
-      <c r="D223" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Inspector</t>
-        </is>
+        <v>276</v>
+      </c>
+      <c r="D223" s="33" t="s">
+        <v>261</v>
       </c>
       <c r="E223" s="41" t="s">
-        <v>823</v>
-      </c>
-      <c r="F223" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Inspector que revisa la acción ejecutada.</t>
-        </is>
+        <v>814</v>
+      </c>
+      <c r="F223" s="33" t="s">
+        <v>815</v>
       </c>
       <c r="G223" s="33" t="s">
-        <v>322</v>
+        <v>335</v>
       </c>
       <c r="H223" s="33" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
       <c r="I223" s="33" t="s">
         <v>363</v>
       </c>
       <c r="K223" s="8" t="s">
-        <v>825</v>
-      </c>
-      <c r="L223" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Referencia válida a USUARIOS con rol Inspector.</t>
-        </is>
+        <v>816</v>
+      </c>
+      <c r="L223" s="8" t="s">
+        <v>817</v>
       </c>
     </row>
     <row r="224" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -21723,36 +21875,36 @@
         <v>790</v>
       </c>
       <c r="B224" s="41" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C224" s="33" t="s">
         <v>276</v>
       </c>
-      <c r="D224" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Inspector</t>
-        </is>
+      <c r="D224" s="33" t="s">
+        <v>261</v>
       </c>
       <c r="E224" s="41" t="s">
-        <v>827</v>
+        <v>733</v>
       </c>
       <c r="F224" s="33" t="s">
-        <v>828</v>
+        <v>818</v>
       </c>
       <c r="G224" s="33" t="s">
-        <v>335</v>
+        <v>735</v>
       </c>
       <c r="H224" s="33" t="s">
-        <v>336</v>
-      </c>
-      <c r="I224" s="33" t="s">
-        <v>363</v>
-      </c>
-      <c r="K224" s="8" t="s">
-        <v>825</v>
-      </c>
-      <c r="L224" s="8" t="s">
-        <v>829</v>
+        <v>736</v>
+      </c>
+      <c r="I224" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Obligatorio</t>
+        </is>
+      </c>
+      <c r="K224" s="8"/>
+      <c r="L224" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Obligatoria para completar la OT. Conservar las imágenes vinculadas a cada registro de ejecución.</t>
+        </is>
       </c>
     </row>
     <row r="225" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -21760,45 +21912,55 @@
         <v>790</v>
       </c>
       <c r="B225" s="41" t="s">
-        <v>167</v>
+        <v>206</v>
       </c>
       <c r="C225" s="33" t="s">
         <v>276</v>
       </c>
       <c r="D225" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Inspector</t>
+          <t xml:space="preserve">Sistema / Inspector</t>
         </is>
       </c>
       <c r="E225" s="41" t="s">
-        <v>830</v>
-      </c>
-      <c r="F225" s="33" t="s">
-        <v>831</v>
+        <v>721</v>
+      </c>
+      <c r="F225" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Estado de la revisión de la acción ejecutada, realizada por el Inspector.</t>
+        </is>
       </c>
       <c r="G225" s="33" t="s">
-        <v>343</v>
+        <v>357</v>
       </c>
       <c r="H225" s="33" t="s">
-        <v>323</v>
-      </c>
-      <c r="I225" s="33" t="s">
-        <v>363</v>
-      </c>
-      <c r="K225" s="8" t="s">
-        <v>832</v>
-      </c>
-      <c r="L225" s="8"/>
+        <v>821</v>
+      </c>
+      <c r="I225" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Condicional</t>
+        </is>
+      </c>
+      <c r="K225" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">requiere_revision_inspector = Sí en la orden de trabajo.</t>
+        </is>
+      </c>
+      <c r="L225" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Valor inicial: Pendiente de revisión, asignado por el Sistema. Aprobado o Rechazado lo registra el Inspector. Si requiere_revision_inspector = No, desactivar y dejar vacío.</t>
+        </is>
+      </c>
     </row>
     <row r="226" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A226" s="41" t="s">
         <v>790</v>
       </c>
       <c r="B226" s="41" t="s">
-        <v>207</v>
+        <v>165</v>
       </c>
       <c r="C226" s="33" t="s">
-        <v>276</v>
+        <v>326</v>
       </c>
       <c r="D226" s="33" t="inlineStr">
         <is>
@@ -21806,16 +21968,18 @@
         </is>
       </c>
       <c r="E226" s="41" t="s">
-        <v>721</v>
-      </c>
-      <c r="F226" s="33" t="s">
-        <v>833</v>
+        <v>823</v>
+      </c>
+      <c r="F226" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Inspector que revisa la acción ejecutada.</t>
+        </is>
       </c>
       <c r="G226" s="33" t="s">
-        <v>357</v>
+        <v>322</v>
       </c>
       <c r="H226" s="33" t="s">
-        <v>358</v>
+        <v>323</v>
       </c>
       <c r="I226" s="33" t="s">
         <v>363</v>
@@ -21823,14 +21987,18 @@
       <c r="K226" s="8" t="s">
         <v>825</v>
       </c>
-      <c r="L226" s="8"/>
+      <c r="L226" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Referencia válida a USUARIOS con rol Inspector.</t>
+        </is>
+      </c>
     </row>
     <row r="227" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A227" s="41" t="s">
         <v>790</v>
       </c>
       <c r="B227" s="41" t="s">
-        <v>208</v>
+        <v>164</v>
       </c>
       <c r="C227" s="33" t="s">
         <v>276</v>
@@ -21841,10 +22009,10 @@
         </is>
       </c>
       <c r="E227" s="41" t="s">
-        <v>834</v>
+        <v>827</v>
       </c>
       <c r="F227" s="33" t="s">
-        <v>835</v>
+        <v>828</v>
       </c>
       <c r="G227" s="33" t="s">
         <v>335</v>
@@ -21856,150 +22024,117 @@
         <v>363</v>
       </c>
       <c r="K227" s="8" t="s">
+        <v>825</v>
+      </c>
+      <c r="L227" s="8" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="228" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A228" s="41" t="s">
+        <v>790</v>
+      </c>
+      <c r="B228" s="41" t="s">
+        <v>167</v>
+      </c>
+      <c r="C228" s="33" t="s">
+        <v>276</v>
+      </c>
+      <c r="D228" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Inspector</t>
+        </is>
+      </c>
+      <c r="E228" s="41" t="s">
+        <v>830</v>
+      </c>
+      <c r="F228" s="33" t="s">
+        <v>831</v>
+      </c>
+      <c r="G228" s="33" t="s">
+        <v>343</v>
+      </c>
+      <c r="H228" s="33" t="s">
+        <v>323</v>
+      </c>
+      <c r="I228" s="33" t="s">
+        <v>363</v>
+      </c>
+      <c r="K228" s="8" t="s">
+        <v>832</v>
+      </c>
+      <c r="L228" s="8"/>
+    </row>
+    <row r="229" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A229" s="41" t="s">
+        <v>790</v>
+      </c>
+      <c r="B229" s="41" t="s">
+        <v>207</v>
+      </c>
+      <c r="C229" s="33" t="s">
+        <v>276</v>
+      </c>
+      <c r="D229" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Inspector</t>
+        </is>
+      </c>
+      <c r="E229" s="41" t="s">
+        <v>721</v>
+      </c>
+      <c r="F229" s="33" t="s">
+        <v>833</v>
+      </c>
+      <c r="G229" s="33" t="s">
+        <v>357</v>
+      </c>
+      <c r="H229" s="33" t="s">
+        <v>358</v>
+      </c>
+      <c r="I229" s="33" t="s">
+        <v>363</v>
+      </c>
+      <c r="K229" s="8" t="s">
+        <v>825</v>
+      </c>
+      <c r="L229" s="8"/>
+    </row>
+    <row r="230" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A230" s="41" t="s">
+        <v>790</v>
+      </c>
+      <c r="B230" s="41" t="s">
+        <v>208</v>
+      </c>
+      <c r="C230" s="33" t="s">
+        <v>276</v>
+      </c>
+      <c r="D230" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Inspector</t>
+        </is>
+      </c>
+      <c r="E230" s="41" t="s">
+        <v>834</v>
+      </c>
+      <c r="F230" s="33" t="s">
+        <v>835</v>
+      </c>
+      <c r="G230" s="33" t="s">
+        <v>335</v>
+      </c>
+      <c r="H230" s="33" t="s">
+        <v>336</v>
+      </c>
+      <c r="I230" s="33" t="s">
+        <v>363</v>
+      </c>
+      <c r="K230" s="8" t="s">
         <v>836</v>
       </c>
-      <c r="L227" s="8" t="s">
+      <c r="L230" s="8" t="s">
         <v>837</v>
-      </c>
-    </row>
-    <row r="228" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A228" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ORDENES DE TRABAJO</t>
-        </is>
-      </c>
-      <c r="B228" s="41" t="s">
-        <v>220</v>
-      </c>
-      <c r="C228" s="33" t="s">
-        <v>318</v>
-      </c>
-      <c r="D228" s="33" t="s">
-        <v>319</v>
-      </c>
-      <c r="E228" s="41" t="s">
-        <v>320</v>
-      </c>
-      <c r="F228" s="33" t="s">
-        <v>839</v>
-      </c>
-      <c r="G228" s="33" t="s">
-        <v>322</v>
-      </c>
-      <c r="H228" s="33" t="s">
-        <v>840</v>
-      </c>
-      <c r="I228" s="33" t="s">
-        <v>324</v>
-      </c>
-      <c r="K228" s="8"/>
-      <c r="L228" s="8" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="229" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A229" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ORDENES DE TRABAJO</t>
-        </is>
-      </c>
-      <c r="B229" s="41" t="s">
-        <v>221</v>
-      </c>
-      <c r="C229" s="33" t="s">
-        <v>326</v>
-      </c>
-      <c r="D229" s="33" t="s">
-        <v>715</v>
-      </c>
-      <c r="E229" s="41" t="s">
-        <v>328</v>
-      </c>
-      <c r="F229" s="33" t="s">
-        <v>841</v>
-      </c>
-      <c r="G229" s="33" t="s">
-        <v>322</v>
-      </c>
-      <c r="H229" s="33" t="s">
-        <v>323</v>
-      </c>
-      <c r="I229" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Condicional</t>
-        </is>
-      </c>
-      <c r="K229" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Accion_solicitada distinta de Levantamiento.</t>
-        </is>
-      </c>
-      <c r="L229" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Referencia válida a ARBOLES. En OT de Levantamiento, dejar vacío; los árboles registrados o evaluados se vinculan mediante INSPECCION.id_arbol.</t>
-        </is>
-      </c>
-    </row>
-    <row r="230" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A230" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ORDENES DE TRABAJO</t>
-        </is>
-      </c>
-      <c r="B230" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">id_incidencia</t>
-        </is>
-      </c>
-      <c r="C230" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Vinculado por plataforma</t>
-        </is>
-      </c>
-      <c r="D230" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sistema / Usuario municipal</t>
-        </is>
-      </c>
-      <c r="E230" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Vinculación a la incidencia que origina la orden de trabajo.</t>
-        </is>
-      </c>
-      <c r="F230" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Incidencia reportada que origina la orden de trabajo.</t>
-        </is>
-      </c>
-      <c r="G230" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Identificador (texto)</t>
-        </is>
-      </c>
-      <c r="H230" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">No aplica</t>
-        </is>
-      </c>
-      <c r="I230" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Condicional</t>
-        </is>
-      </c>
-      <c r="J230" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">No aplica.</t>
-        </is>
-      </c>
-      <c r="K230" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cuando la orden de trabajo se origina en una incidencia.</t>
-        </is>
-      </c>
-      <c r="L230" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Referencia válida a INCIDENCIA.</t>
-        </is>
       </c>
     </row>
     <row r="231" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -22009,32 +22144,32 @@
         </is>
       </c>
       <c r="B231" s="41" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C231" s="33" t="s">
-        <v>276</v>
+        <v>318</v>
       </c>
       <c r="D231" s="33" t="s">
-        <v>257</v>
+        <v>319</v>
       </c>
       <c r="E231" s="41" t="s">
-        <v>721</v>
+        <v>320</v>
       </c>
       <c r="F231" s="33" t="s">
-        <v>842</v>
+        <v>839</v>
       </c>
       <c r="G231" s="33" t="s">
-        <v>357</v>
+        <v>322</v>
       </c>
       <c r="H231" s="33" t="s">
-        <v>843</v>
+        <v>840</v>
       </c>
       <c r="I231" s="33" t="s">
         <v>324</v>
       </c>
       <c r="K231" s="8"/>
       <c r="L231" s="8" t="s">
-        <v>844</v>
+        <v>325</v>
       </c>
     </row>
     <row r="232" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -22044,36 +22179,40 @@
         </is>
       </c>
       <c r="B232" s="41" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C232" s="33" t="s">
-        <v>845</v>
+        <v>326</v>
       </c>
       <c r="D232" s="33" t="s">
-        <v>257</v>
+        <v>715</v>
       </c>
       <c r="E232" s="41" t="s">
-        <v>846</v>
+        <v>328</v>
       </c>
       <c r="F232" s="33" t="s">
-        <v>847</v>
+        <v>841</v>
       </c>
       <c r="G232" s="33" t="s">
-        <v>848</v>
-      </c>
-      <c r="H232" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Inspección: Evaluación inicial; Reevaluación; Evaluación instrumental; Monitoreo; Levantamiento. Mantenimiento: Poda; Riego; Descompactación; Manejo fitosanitario; Tala_retiro; Reparación_alcorque; Soporte_tutorado; Otra_Intervención.</t>
-        </is>
-      </c>
-      <c r="I232" s="33" t="s">
-        <v>324</v>
-      </c>
-      <c r="K232" s="8" t="s">
-        <v>850</v>
-      </c>
-      <c r="L232" s="8" t="s">
-        <v>851</v>
+        <v>322</v>
+      </c>
+      <c r="H232" s="33" t="s">
+        <v>323</v>
+      </c>
+      <c r="I232" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Condicional</t>
+        </is>
+      </c>
+      <c r="K232" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Accion_solicitada distinta de Levantamiento.</t>
+        </is>
+      </c>
+      <c r="L232" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Referencia válida a ARBOLES. En OT de Levantamiento, dejar vacío; los árboles registrados o evaluados se vinculan mediante INSPECCION.id_arbol.</t>
+        </is>
       </c>
     </row>
     <row r="233" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -22082,37 +22221,60 @@
           <t xml:space="preserve">ORDENES DE TRABAJO</t>
         </is>
       </c>
-      <c r="B233" s="41" t="s">
-        <v>224</v>
-      </c>
-      <c r="C233" s="33" t="s">
-        <v>845</v>
-      </c>
-      <c r="D233" s="33" t="s">
-        <v>257</v>
-      </c>
-      <c r="E233" s="41" t="s">
-        <v>852</v>
-      </c>
-      <c r="F233" s="33" t="s">
-        <v>853</v>
-      </c>
-      <c r="G233" s="33" t="s">
-        <v>848</v>
+      <c r="B233" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">id_incidencia</t>
+        </is>
+      </c>
+      <c r="C233" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vinculado por plataforma</t>
+        </is>
+      </c>
+      <c r="D233" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sistema / Usuario municipal</t>
+        </is>
+      </c>
+      <c r="E233" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vinculación a la incidencia que origina la orden de trabajo.</t>
+        </is>
+      </c>
+      <c r="F233" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Incidencia reportada que origina la orden de trabajo.</t>
+        </is>
+      </c>
+      <c r="G233" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Identificador (texto)</t>
+        </is>
       </c>
       <c r="H233" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reevaluación: Seguimiento; Post_intervención. Evaluación instrumental: Tomografía_sónica; Resistografía; Otra. Monitoreo: Fitosanitario; Estructural; Vitalidad. Poda: Sanitaria; Formación; Despeje; Reducción. Riego: Programado; Emergencia. Descompactación: Manual; Mecánica. Manejo fitosanitario: Preventivo; Correctivo; Retiro_residuos. Tala_retiro: Tala; Retiro_tocón.</t>
-        </is>
-      </c>
-      <c r="I233" s="33" t="s">
-        <v>363</v>
-      </c>
-      <c r="K233" s="8" t="s">
-        <v>855</v>
-      </c>
-      <c r="L233" s="8" t="s">
-        <v>856</v>
+          <t xml:space="preserve">No aplica</t>
+        </is>
+      </c>
+      <c r="I233" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Condicional</t>
+        </is>
+      </c>
+      <c r="J233" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No aplica.</t>
+        </is>
+      </c>
+      <c r="K233" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cuando la orden de trabajo se origina en una incidencia.</t>
+        </is>
+      </c>
+      <c r="L233" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Referencia válida a INCIDENCIA.</t>
+        </is>
       </c>
     </row>
     <row r="234" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -22122,7 +22284,7 @@
         </is>
       </c>
       <c r="B234" s="41" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="C234" s="33" t="s">
         <v>276</v>
@@ -22131,23 +22293,23 @@
         <v>257</v>
       </c>
       <c r="E234" s="41" t="s">
-        <v>857</v>
+        <v>721</v>
       </c>
       <c r="F234" s="33" t="s">
-        <v>858</v>
+        <v>842</v>
       </c>
       <c r="G234" s="33" t="s">
-        <v>343</v>
+        <v>357</v>
       </c>
       <c r="H234" s="33" t="s">
-        <v>323</v>
+        <v>843</v>
       </c>
       <c r="I234" s="33" t="s">
-        <v>439</v>
+        <v>324</v>
       </c>
       <c r="K234" s="8"/>
       <c r="L234" s="8" t="s">
-        <v>730</v>
+        <v>844</v>
       </c>
     </row>
     <row r="235" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -22157,34 +22319,36 @@
         </is>
       </c>
       <c r="B235" s="41" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C235" s="33" t="s">
-        <v>276</v>
+        <v>845</v>
       </c>
       <c r="D235" s="33" t="s">
         <v>257</v>
       </c>
       <c r="E235" s="41" t="s">
-        <v>721</v>
+        <v>846</v>
       </c>
       <c r="F235" s="33" t="s">
-        <v>859</v>
+        <v>847</v>
       </c>
       <c r="G235" s="33" t="s">
-        <v>357</v>
-      </c>
-      <c r="H235" s="33" t="s">
-        <v>770</v>
+        <v>848</v>
+      </c>
+      <c r="H235" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Inspección: Evaluación inicial; Reevaluación; Evaluación instrumental; Monitoreo; Levantamiento. Mantenimiento: Poda; Riego; Descompactación; Manejo fitosanitario; Tala_retiro; Reparación_alcorque; Soporte_tutorado; Otra_Intervención.</t>
+        </is>
       </c>
       <c r="I235" s="33" t="s">
         <v>324</v>
       </c>
-      <c r="K235" s="8"/>
-      <c r="L235" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Si el árbol tiene una evaluación vigente, proponer por defecto su clasificacion_prioridad; el Usuario municipal puede modificarla.</t>
-        </is>
+      <c r="K235" s="8" t="s">
+        <v>850</v>
+      </c>
+      <c r="L235" s="8" t="s">
+        <v>851</v>
       </c>
     </row>
     <row r="236" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -22194,36 +22358,36 @@
         </is>
       </c>
       <c r="B236" s="41" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="C236" s="33" t="s">
-        <v>276</v>
-      </c>
-      <c r="D236" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Usuario municipal / Sistema</t>
-        </is>
+        <v>845</v>
+      </c>
+      <c r="D236" s="33" t="s">
+        <v>257</v>
       </c>
       <c r="E236" s="41" t="s">
-        <v>738</v>
+        <v>852</v>
       </c>
       <c r="F236" s="33" t="s">
-        <v>861</v>
+        <v>853</v>
       </c>
       <c r="G236" s="33" t="s">
-        <v>357</v>
-      </c>
-      <c r="H236" s="33" t="s">
-        <v>862</v>
+        <v>848</v>
+      </c>
+      <c r="H236" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reevaluación: Seguimiento; Post_intervención. Evaluación instrumental: Tomografía_sónica; Resistografía; Otra. Monitoreo: Fitosanitario; Estructural; Vitalidad. Poda: Sanitaria; Formación; Despeje; Reducción. Riego: Programado; Emergencia. Descompactación: Manual; Mecánica. Manejo fitosanitario: Preventivo; Correctivo; Retiro_residuos. Tala_retiro: Tala; Retiro_tocón.</t>
+        </is>
       </c>
       <c r="I236" s="33" t="s">
-        <v>324</v>
-      </c>
-      <c r="K236" s="8"/>
-      <c r="L236" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Valor inicial: Pendiente. No permitir Completada mientras alguna inspección vinculada tenga estado_registro = Preguardado. Al pasar a Completada, registrar fecha_completada_ot. En OT de Mantenimiento, el Sistema asigna Completada: si requiere_revision_inspector = No, al registrarse la ejecución con resultado = Ejecutado completamente y la evidencia fotográfica; si requiere_revision_inspector = Sí, cuando estado_revision = Aprobado. Si estado_revision = Rechazado, la OT vuelve a En ejecución.</t>
-        </is>
+        <v>363</v>
+      </c>
+      <c r="K236" s="8" t="s">
+        <v>855</v>
+      </c>
+      <c r="L236" s="8" t="s">
+        <v>856</v>
       </c>
     </row>
     <row r="237" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -22233,32 +22397,32 @@
         </is>
       </c>
       <c r="B237" s="41" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C237" s="33" t="s">
-        <v>319</v>
+        <v>276</v>
       </c>
       <c r="D237" s="33" t="s">
-        <v>319</v>
+        <v>257</v>
       </c>
       <c r="E237" s="41" t="s">
-        <v>864</v>
+        <v>857</v>
       </c>
       <c r="F237" s="33" t="s">
-        <v>865</v>
+        <v>858</v>
       </c>
       <c r="G237" s="33" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="H237" s="33" t="s">
-        <v>336</v>
+        <v>323</v>
       </c>
       <c r="I237" s="33" t="s">
-        <v>324</v>
+        <v>439</v>
       </c>
       <c r="K237" s="8"/>
       <c r="L237" s="8" t="s">
-        <v>337</v>
+        <v>730</v>
       </c>
     </row>
     <row r="238" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -22268,7 +22432,7 @@
         </is>
       </c>
       <c r="B238" s="41" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="C238" s="33" t="s">
         <v>276</v>
@@ -22277,25 +22441,25 @@
         <v>257</v>
       </c>
       <c r="E238" s="41" t="s">
-        <v>866</v>
+        <v>721</v>
       </c>
       <c r="F238" s="33" t="s">
-        <v>867</v>
+        <v>859</v>
       </c>
       <c r="G238" s="33" t="s">
-        <v>335</v>
+        <v>357</v>
       </c>
       <c r="H238" s="33" t="s">
-        <v>336</v>
+        <v>770</v>
       </c>
       <c r="I238" s="33" t="s">
-        <v>363</v>
-      </c>
-      <c r="K238" s="8" t="s">
-        <v>868</v>
-      </c>
-      <c r="L238" s="8" t="s">
-        <v>869</v>
+        <v>324</v>
+      </c>
+      <c r="K238" s="8"/>
+      <c r="L238" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Si el árbol tiene una evaluación vigente, proponer por defecto su clasificacion_prioridad; el Usuario municipal puede modificarla.</t>
+        </is>
       </c>
     </row>
     <row r="239" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -22304,59 +22468,36 @@
           <t xml:space="preserve">ORDENES DE TRABAJO</t>
         </is>
       </c>
-      <c r="B239" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fecha_completada_ot</t>
-        </is>
-      </c>
-      <c r="C239" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sistema</t>
-        </is>
+      <c r="B239" s="41" t="s">
+        <v>227</v>
+      </c>
+      <c r="C239" s="33" t="s">
+        <v>276</v>
       </c>
       <c r="D239" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sistema</t>
-        </is>
-      </c>
-      <c r="E239" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fecha asignada por el sistema cuando estado_ot cambia a Completada.</t>
-        </is>
-      </c>
-      <c r="F239" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fecha en que se completa la orden de trabajo. Determina la evaluación vigente del árbol.</t>
-        </is>
-      </c>
-      <c r="G239" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fecha</t>
-        </is>
-      </c>
-      <c r="H239" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dd/mm/aaaa</t>
-        </is>
-      </c>
-      <c r="I239" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Condicional</t>
-        </is>
-      </c>
-      <c r="J239" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">No aplica.</t>
-        </is>
-      </c>
-      <c r="K239" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estado_ot = Completada</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Usuario municipal / Sistema</t>
+        </is>
+      </c>
+      <c r="E239" s="41" t="s">
+        <v>738</v>
+      </c>
+      <c r="F239" s="33" t="s">
+        <v>861</v>
+      </c>
+      <c r="G239" s="33" t="s">
+        <v>357</v>
+      </c>
+      <c r="H239" s="33" t="s">
+        <v>862</v>
+      </c>
+      <c r="I239" s="33" t="s">
+        <v>324</v>
+      </c>
+      <c r="K239" s="8"/>
       <c r="L239" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">No editable manualmente. Igual o posterior a fecha_creacion_OT. La evaluación vigente corresponde a la OT completada más recientemente según esta fecha, aunque su fecha_inspeccion sea anterior a la de otra inspección.</t>
+          <t xml:space="preserve">Valor inicial: Pendiente. No permitir Completada mientras alguna inspección vinculada tenga estado_registro = Preguardado. Al pasar a Completada, registrar fecha_completada_ot. En OT de Mantenimiento, el Sistema asigna Completada: si requiere_revision_inspector = No, al registrarse la ejecución con resultado = Ejecutado completamente y la evidencia fotográfica; si requiere_revision_inspector = Sí, cuando estado_revision = Aprobado. Si estado_revision = Rechazado, la OT vuelve a En ejecución.</t>
         </is>
       </c>
     </row>
@@ -22366,37 +22507,33 @@
           <t xml:space="preserve">ORDENES DE TRABAJO</t>
         </is>
       </c>
-      <c r="B240" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ot_creado_por</t>
-        </is>
+      <c r="B240" s="41" t="s">
+        <v>228</v>
       </c>
       <c r="C240" s="33" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="D240" s="33" t="s">
         <v>319</v>
       </c>
       <c r="E240" s="41" t="s">
-        <v>870</v>
+        <v>864</v>
       </c>
       <c r="F240" s="33" t="s">
-        <v>871</v>
+        <v>865</v>
       </c>
       <c r="G240" s="33" t="s">
-        <v>322</v>
+        <v>335</v>
       </c>
       <c r="H240" s="33" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
       <c r="I240" s="33" t="s">
         <v>324</v>
       </c>
       <c r="K240" s="8"/>
-      <c r="L240" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Referencia válida a USUARIOS.</t>
-        </is>
+      <c r="L240" s="8" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="241" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -22406,7 +22543,7 @@
         </is>
       </c>
       <c r="B241" s="41" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C241" s="33" t="s">
         <v>276</v>
@@ -22415,23 +22552,25 @@
         <v>257</v>
       </c>
       <c r="E241" s="41" t="s">
-        <v>873</v>
+        <v>866</v>
       </c>
       <c r="F241" s="33" t="s">
-        <v>874</v>
+        <v>867</v>
       </c>
       <c r="G241" s="33" t="s">
-        <v>322</v>
+        <v>335</v>
       </c>
       <c r="H241" s="33" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
       <c r="I241" s="33" t="s">
-        <v>324</v>
-      </c>
-      <c r="K241" s="8"/>
+        <v>363</v>
+      </c>
+      <c r="K241" s="8" t="s">
+        <v>868</v>
+      </c>
       <c r="L241" s="8" t="s">
-        <v>875</v>
+        <v>869</v>
       </c>
     </row>
     <row r="242" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -22442,37 +22581,37 @@
       </c>
       <c r="B242" s="41" t="inlineStr">
         <is>
-          <t xml:space="preserve">requiere_revision_inspector</t>
+          <t xml:space="preserve">fecha_completada_ot</t>
         </is>
       </c>
       <c r="C242" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Manual</t>
+          <t xml:space="preserve">Sistema</t>
         </is>
       </c>
       <c r="D242" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Usuario municipal</t>
+          <t xml:space="preserve">Sistema</t>
         </is>
       </c>
       <c r="E242" s="41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Selección al crear la orden de trabajo.</t>
+          <t xml:space="preserve">Fecha asignada por el sistema cuando estado_ot cambia a Completada.</t>
         </is>
       </c>
       <c r="F242" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Indica si la ejecución de la acción de mantenimiento debe ser aprobada o rechazada por el Inspector.</t>
+          <t xml:space="preserve">Fecha en que se completa la orden de trabajo. Determina la evaluación vigente del árbol.</t>
         </is>
       </c>
       <c r="G242" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Categoría</t>
+          <t xml:space="preserve">Fecha</t>
         </is>
       </c>
       <c r="H242" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sí / No</t>
+          <t xml:space="preserve">dd/mm/aaaa</t>
         </is>
       </c>
       <c r="I242" s="33" t="inlineStr">
@@ -22482,17 +22621,17 @@
       </c>
       <c r="J242" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valor inicial: No. Si subtipo_accion = Tala o Retiro_tocón, el Sistema asigna Sí y no permite modificarlo.</t>
+          <t xml:space="preserve">No aplica.</t>
         </is>
       </c>
       <c r="K242" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tipo_ot = Mantenimiento</t>
+          <t xml:space="preserve">estado_ot = Completada</t>
         </is>
       </c>
       <c r="L242" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sí: la OT se completa cuando el Inspector registra estado_revision = Aprobado. No: la OT se completa automáticamente al registrarse en MANTENIMIENTO la ejecución con resultado = Ejecutado completamente y la evidencia fotográfica. Si cambia Tipo_ot, Accion_solicitada o subtipo_accion, volver a aplicar la regla.</t>
+          <t xml:space="preserve">No editable manualmente. Igual o posterior a fecha_creacion_OT. La evaluación vigente corresponde a la OT completada más recientemente según esta fecha, aunque su fecha_inspeccion sea anterior a la de otra inspección.</t>
         </is>
       </c>
     </row>
@@ -22502,143 +22641,177 @@
           <t xml:space="preserve">ORDENES DE TRABAJO</t>
         </is>
       </c>
-      <c r="B243" s="41" t="s">
-        <v>188</v>
+      <c r="B243" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ot_creado_por</t>
+        </is>
       </c>
       <c r="C243" s="33" t="s">
-        <v>276</v>
+        <v>326</v>
       </c>
       <c r="D243" s="33" t="s">
-        <v>257</v>
+        <v>319</v>
       </c>
       <c r="E243" s="41" t="s">
-        <v>857</v>
-      </c>
-      <c r="F243" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Indicaciones complementarias para ejecutar la orden. En OT de Levantamiento, descripción del área de trabajo.</t>
-        </is>
+        <v>870</v>
+      </c>
+      <c r="F243" s="33" t="s">
+        <v>871</v>
       </c>
       <c r="G243" s="33" t="s">
-        <v>343</v>
+        <v>322</v>
       </c>
       <c r="H243" s="33" t="s">
         <v>323</v>
       </c>
       <c r="I243" s="33" t="s">
-        <v>363</v>
-      </c>
-      <c r="K243" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Accion_solicitada o subtipo_accion = Otra / Otra_Intervención, o Accion_solicitada = Levantamiento</t>
-        </is>
-      </c>
+        <v>324</v>
+      </c>
+      <c r="K243" s="8"/>
       <c r="L243" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Obligatorio para especificar acciones o subtipos «Otra» y para describir el área de trabajo de una OT de Levantamiento; opcional en los demás casos.</t>
+          <t xml:space="preserve">Referencia válida a USUARIOS.</t>
         </is>
       </c>
     </row>
     <row r="244" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A244" s="41" t="inlineStr">
         <is>
-          <t xml:space="preserve">USUARIOS</t>
+          <t xml:space="preserve">ORDENES DE TRABAJO</t>
         </is>
       </c>
       <c r="B244" s="41" t="s">
-        <v>244</v>
+        <v>231</v>
       </c>
       <c r="C244" s="33" t="s">
-        <v>318</v>
+        <v>276</v>
       </c>
       <c r="D244" s="33" t="s">
-        <v>319</v>
+        <v>257</v>
       </c>
       <c r="E244" s="41" t="s">
-        <v>1099</v>
+        <v>873</v>
       </c>
       <c r="F244" s="33" t="s">
-        <v>1100</v>
+        <v>874</v>
       </c>
       <c r="G244" s="33" t="s">
-        <v>343</v>
+        <v>322</v>
       </c>
       <c r="H244" s="33" t="s">
-        <v>1101</v>
+        <v>323</v>
       </c>
       <c r="I244" s="33" t="s">
         <v>324</v>
       </c>
-      <c r="L244" s="33" t="s">
-        <v>1102</v>
+      <c r="K244" s="8"/>
+      <c r="L244" s="8" t="s">
+        <v>875</v>
       </c>
     </row>
     <row r="245" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A245" s="41" t="inlineStr">
         <is>
-          <t xml:space="preserve">USUARIOS</t>
-        </is>
-      </c>
-      <c r="B245" s="41" t="s">
-        <v>245</v>
-      </c>
-      <c r="C245" s="33" t="s">
-        <v>276</v>
-      </c>
-      <c r="D245" s="33" t="s">
-        <v>252</v>
-      </c>
-      <c r="E245" s="41" t="s">
-        <v>1103</v>
-      </c>
-      <c r="F245" s="33" t="s">
-        <v>1104</v>
-      </c>
-      <c r="G245" s="33" t="s">
-        <v>343</v>
-      </c>
-      <c r="H245" s="33" t="s">
-        <v>1105</v>
-      </c>
-      <c r="I245" s="33" t="s">
-        <v>324</v>
-      </c>
-      <c r="L245" s="33" t="s">
-        <v>1106</v>
+          <t xml:space="preserve">ORDENES DE TRABAJO</t>
+        </is>
+      </c>
+      <c r="B245" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">requiere_revision_inspector</t>
+        </is>
+      </c>
+      <c r="C245" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="D245" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Usuario municipal</t>
+        </is>
+      </c>
+      <c r="E245" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Selección al crear la orden de trabajo.</t>
+        </is>
+      </c>
+      <c r="F245" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Indica si la ejecución de la acción de mantenimiento debe ser aprobada o rechazada por el Inspector.</t>
+        </is>
+      </c>
+      <c r="G245" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Categoría</t>
+        </is>
+      </c>
+      <c r="H245" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sí / No</t>
+        </is>
+      </c>
+      <c r="I245" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Condicional</t>
+        </is>
+      </c>
+      <c r="J245" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Valor inicial: No. Si subtipo_accion = Tala o Retiro_tocón, el Sistema asigna Sí y no permite modificarlo.</t>
+        </is>
+      </c>
+      <c r="K245" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tipo_ot = Mantenimiento</t>
+        </is>
+      </c>
+      <c r="L245" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sí: la OT se completa cuando el Inspector registra estado_revision = Aprobado. No: la OT se completa automáticamente al registrarse en MANTENIMIENTO la ejecución con resultado = Ejecutado completamente y la evidencia fotográfica. Si cambia Tipo_ot, Accion_solicitada o subtipo_accion, volver a aplicar la regla.</t>
+        </is>
       </c>
     </row>
     <row r="246" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A246" s="41" t="inlineStr">
         <is>
-          <t xml:space="preserve">USUARIOS</t>
+          <t xml:space="preserve">ORDENES DE TRABAJO</t>
         </is>
       </c>
       <c r="B246" s="41" t="s">
-        <v>246</v>
+        <v>188</v>
       </c>
       <c r="C246" s="33" t="s">
         <v>276</v>
       </c>
       <c r="D246" s="33" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="E246" s="41" t="s">
-        <v>1107</v>
-      </c>
-      <c r="F246" s="41" t="s">
-        <v>1108</v>
+        <v>857</v>
+      </c>
+      <c r="F246" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Indicaciones complementarias para ejecutar la orden. En OT de Levantamiento, descripción del área de trabajo.</t>
+        </is>
       </c>
       <c r="G246" s="33" t="s">
-        <v>246</v>
+        <v>343</v>
       </c>
       <c r="H246" s="33" t="s">
-        <v>1109</v>
+        <v>323</v>
       </c>
       <c r="I246" s="33" t="s">
-        <v>324</v>
-      </c>
-      <c r="L246" s="33" t="s">
-        <v>1110</v>
+        <v>363</v>
+      </c>
+      <c r="K246" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Accion_solicitada o subtipo_accion = Otra / Otra_Intervención, o Accion_solicitada = Levantamiento</t>
+        </is>
+      </c>
+      <c r="L246" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Obligatorio para especificar acciones o subtipos «Otra» y para describir el área de trabajo de una OT de Levantamiento; opcional en los demás casos.</t>
+        </is>
       </c>
     </row>
     <row r="247" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -22648,31 +22821,31 @@
         </is>
       </c>
       <c r="B247" s="41" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C247" s="33" t="s">
-        <v>276</v>
+        <v>318</v>
       </c>
       <c r="D247" s="33" t="s">
-        <v>252</v>
+        <v>319</v>
       </c>
       <c r="E247" s="41" t="s">
-        <v>1111</v>
+        <v>1099</v>
       </c>
       <c r="F247" s="33" t="s">
-        <v>1112</v>
+        <v>1100</v>
       </c>
       <c r="G247" s="33" t="s">
-        <v>357</v>
+        <v>343</v>
       </c>
       <c r="H247" s="33" t="s">
-        <v>1113</v>
+        <v>1101</v>
       </c>
       <c r="I247" s="33" t="s">
         <v>324</v>
       </c>
       <c r="L247" s="33" t="s">
-        <v>1114</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="248" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -22682,7 +22855,7 @@
         </is>
       </c>
       <c r="B248" s="41" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="C248" s="33" t="s">
         <v>276</v>
@@ -22691,111 +22864,100 @@
         <v>252</v>
       </c>
       <c r="E248" s="41" t="s">
-        <v>1115</v>
+        <v>1103</v>
       </c>
       <c r="F248" s="33" t="s">
-        <v>1116</v>
+        <v>1104</v>
       </c>
       <c r="G248" s="33" t="s">
-        <v>357</v>
+        <v>343</v>
       </c>
       <c r="H248" s="33" t="s">
-        <v>358</v>
+        <v>1105</v>
       </c>
       <c r="I248" s="33" t="s">
         <v>324</v>
       </c>
-      <c r="J248" s="33" t="s">
-        <v>1117</v>
-      </c>
       <c r="L248" s="33" t="s">
-        <v>1118</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="249" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A249" s="41" t="s">
-        <v>1150</v>
+      <c r="A249" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USUARIOS</t>
+        </is>
       </c>
       <c r="B249" s="41" t="s">
-        <v>1157</v>
+        <v>246</v>
       </c>
       <c r="C249" s="33" t="s">
-        <v>318</v>
+        <v>276</v>
       </c>
       <c r="D249" s="33" t="s">
-        <v>319</v>
+        <v>252</v>
       </c>
       <c r="E249" s="41" t="s">
-        <v>1159</v>
-      </c>
-      <c r="F249" s="33" t="s">
-        <v>1160</v>
+        <v>1107</v>
+      </c>
+      <c r="F249" s="41" t="s">
+        <v>1108</v>
       </c>
       <c r="G249" s="33" t="s">
-        <v>322</v>
+        <v>246</v>
       </c>
       <c r="H249" s="33" t="s">
-        <v>323</v>
+        <v>1109</v>
       </c>
       <c r="I249" s="33" t="s">
         <v>324</v>
       </c>
-      <c r="J249" s="33" t="s">
-        <v>1161</v>
-      </c>
-      <c r="K249" s="33" t="s">
-        <v>1152</v>
-      </c>
       <c r="L249" s="33" t="s">
-        <v>1162</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="250" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A250" s="41" t="s">
-        <v>1150</v>
+      <c r="A250" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USUARIOS</t>
+        </is>
       </c>
       <c r="B250" s="41" t="s">
-        <v>1</v>
+        <v>247</v>
       </c>
       <c r="C250" s="33" t="s">
-        <v>326</v>
+        <v>276</v>
       </c>
       <c r="D250" s="33" t="s">
-        <v>319</v>
+        <v>252</v>
       </c>
       <c r="E250" s="41" t="s">
-        <v>1163</v>
+        <v>1111</v>
       </c>
       <c r="F250" s="33" t="s">
-        <v>1164</v>
+        <v>1112</v>
       </c>
       <c r="G250" s="33" t="s">
-        <v>322</v>
+        <v>357</v>
       </c>
       <c r="H250" s="33" t="s">
-        <v>323</v>
+        <v>1113</v>
       </c>
       <c r="I250" s="33" t="s">
         <v>324</v>
       </c>
-      <c r="J250" s="33" t="s">
-        <v>1151</v>
-      </c>
-      <c r="K250" s="33" t="s">
-        <v>1152</v>
-      </c>
-      <c r="L250" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Debe referenciar un proyecto existente. El Administrador debe tener autorización para gestionarlo. Un único sector por proyecto.</t>
-        </is>
+      <c r="L250" s="33" t="s">
+        <v>1114</v>
       </c>
     </row>
     <row r="251" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A251" s="41" t="s">
-        <v>1150</v>
+      <c r="A251" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USUARIOS</t>
+        </is>
       </c>
       <c r="B251" s="41" t="s">
-        <v>1158</v>
+        <v>248</v>
       </c>
       <c r="C251" s="33" t="s">
         <v>276</v>
@@ -22804,32 +22966,25 @@
         <v>252</v>
       </c>
       <c r="E251" s="41" t="s">
-        <v>1166</v>
-      </c>
-      <c r="F251" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Nombre visible de la delimitación territorial del proyecto, utilizada para consultar indicadores territoriales.</t>
-        </is>
+        <v>1115</v>
+      </c>
+      <c r="F251" s="33" t="s">
+        <v>1116</v>
       </c>
       <c r="G251" s="33" t="s">
-        <v>343</v>
+        <v>357</v>
       </c>
       <c r="H251" s="33" t="s">
-        <v>323</v>
+        <v>358</v>
       </c>
       <c r="I251" s="33" t="s">
         <v>324</v>
       </c>
       <c r="J251" s="33" t="s">
-        <v>1151</v>
-      </c>
-      <c r="K251" s="33" t="s">
-        <v>1168</v>
-      </c>
-      <c r="L251" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">No vacío. Su modificación no altera id_sector.</t>
-        </is>
+        <v>1117</v>
+      </c>
+      <c r="L251" s="33" t="s">
+        <v>1118</v>
       </c>
     </row>
     <row r="252" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -22837,37 +22992,37 @@
         <v>1150</v>
       </c>
       <c r="B252" s="41" t="s">
-        <v>1153</v>
+        <v>1157</v>
       </c>
       <c r="C252" s="33" t="s">
-        <v>1154</v>
+        <v>318</v>
       </c>
       <c r="D252" s="33" t="s">
-        <v>252</v>
-      </c>
-      <c r="E252" s="60" t="s">
-        <v>1170</v>
+        <v>319</v>
+      </c>
+      <c r="E252" s="41" t="s">
+        <v>1159</v>
       </c>
       <c r="F252" s="33" t="s">
-        <v>1171</v>
+        <v>1160</v>
       </c>
       <c r="G252" s="33" t="s">
-        <v>1155</v>
+        <v>322</v>
       </c>
       <c r="H252" s="33" t="s">
-        <v>1172</v>
+        <v>323</v>
       </c>
       <c r="I252" s="33" t="s">
         <v>324</v>
       </c>
       <c r="J252" s="33" t="s">
-        <v>1173</v>
+        <v>1161</v>
       </c>
       <c r="K252" s="33" t="s">
-        <v>1174</v>
+        <v>1152</v>
       </c>
       <c r="L252" s="33" t="s">
-        <v>1175</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="253" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -22875,410 +23030,344 @@
         <v>1150</v>
       </c>
       <c r="B253" s="41" t="s">
-        <v>1156</v>
+        <v>1</v>
       </c>
       <c r="C253" s="33" t="s">
-        <v>419</v>
+        <v>326</v>
       </c>
       <c r="D253" s="33" t="s">
         <v>319</v>
       </c>
       <c r="E253" s="41" t="s">
-        <v>1176</v>
+        <v>1163</v>
       </c>
       <c r="F253" s="33" t="s">
-        <v>1177</v>
+        <v>1164</v>
       </c>
       <c r="G253" s="33" t="s">
-        <v>347</v>
+        <v>322</v>
       </c>
       <c r="H253" s="33" t="s">
-        <v>567</v>
+        <v>323</v>
       </c>
       <c r="I253" s="33" t="s">
-        <v>1178</v>
+        <v>324</v>
       </c>
       <c r="J253" s="33" t="s">
-        <v>1179</v>
+        <v>1151</v>
       </c>
       <c r="K253" s="33" t="s">
-        <v>1180</v>
-      </c>
-      <c r="L253" s="33" t="s">
-        <v>1181</v>
+        <v>1152</v>
+      </c>
+      <c r="L253" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Debe referenciar un proyecto existente. El Administrador debe tener autorización para gestionarlo. Un único sector por proyecto.</t>
+        </is>
       </c>
     </row>
     <row r="254" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A254" s="41" t="s">
-        <v>1210</v>
+        <v>1150</v>
       </c>
       <c r="B254" s="41" t="s">
-        <v>10</v>
+        <v>1158</v>
       </c>
       <c r="C254" s="33" t="s">
         <v>276</v>
       </c>
       <c r="D254" s="33" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="E254" s="41" t="s">
-        <v>1214</v>
-      </c>
-      <c r="F254" s="33" t="s">
-        <v>1215</v>
+        <v>1166</v>
+      </c>
+      <c r="F254" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nombre visible de la delimitación territorial del proyecto, utilizada para consultar indicadores territoriales.</t>
+        </is>
       </c>
       <c r="G254" s="33" t="s">
         <v>343</v>
       </c>
       <c r="H254" s="33" t="s">
-        <v>1211</v>
+        <v>323</v>
       </c>
       <c r="I254" s="33" t="s">
-        <v>1216</v>
+        <v>324</v>
       </c>
       <c r="J254" s="33" t="s">
         <v>1151</v>
       </c>
       <c r="K254" s="33" t="s">
-        <v>1217</v>
-      </c>
-      <c r="L254" s="33" t="s">
-        <v>1218</v>
+        <v>1168</v>
+      </c>
+      <c r="L254" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No vacío. Su modificación no altera id_sector.</t>
+        </is>
       </c>
     </row>
     <row r="255" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A255" s="41" t="s">
-        <v>1210</v>
+        <v>1150</v>
       </c>
       <c r="B255" s="41" t="s">
-        <v>1208</v>
+        <v>1153</v>
       </c>
       <c r="C255" s="33" t="s">
-        <v>276</v>
+        <v>1154</v>
       </c>
       <c r="D255" s="33" t="s">
-        <v>259</v>
-      </c>
-      <c r="E255" s="41" t="s">
-        <v>1219</v>
+        <v>252</v>
+      </c>
+      <c r="E255" s="60" t="s">
+        <v>1170</v>
       </c>
       <c r="F255" s="33" t="s">
-        <v>1220</v>
+        <v>1171</v>
       </c>
       <c r="G255" s="33" t="s">
-        <v>343</v>
+        <v>1155</v>
       </c>
       <c r="H255" s="33" t="s">
-        <v>1212</v>
+        <v>1172</v>
       </c>
       <c r="I255" s="33" t="s">
-        <v>1221</v>
+        <v>324</v>
       </c>
       <c r="J255" s="33" t="s">
-        <v>1222</v>
+        <v>1173</v>
       </c>
       <c r="K255" s="33" t="s">
-        <v>1223</v>
+        <v>1174</v>
       </c>
       <c r="L255" s="33" t="s">
-        <v>1224</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="256" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A256" s="41" t="s">
+        <v>1150</v>
+      </c>
+      <c r="B256" s="41" t="s">
+        <v>1156</v>
+      </c>
+      <c r="C256" s="33" t="s">
+        <v>419</v>
+      </c>
+      <c r="D256" s="33" t="s">
+        <v>319</v>
+      </c>
+      <c r="E256" s="41" t="s">
+        <v>1176</v>
+      </c>
+      <c r="F256" s="33" t="s">
+        <v>1177</v>
+      </c>
+      <c r="G256" s="33" t="s">
+        <v>347</v>
+      </c>
+      <c r="H256" s="33" t="s">
+        <v>567</v>
+      </c>
+      <c r="I256" s="33" t="s">
+        <v>1178</v>
+      </c>
+      <c r="J256" s="33" t="s">
+        <v>1179</v>
+      </c>
+      <c r="K256" s="33" t="s">
+        <v>1180</v>
+      </c>
+      <c r="L256" s="33" t="s">
+        <v>1181</v>
+      </c>
+    </row>
+    <row r="257" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A257" s="41" t="s">
         <v>1210</v>
       </c>
-      <c r="B256" s="41" t="s">
+      <c r="B257" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="C257" s="33" t="s">
+        <v>276</v>
+      </c>
+      <c r="D257" s="33" t="s">
+        <v>259</v>
+      </c>
+      <c r="E257" s="41" t="s">
+        <v>1214</v>
+      </c>
+      <c r="F257" s="33" t="s">
+        <v>1215</v>
+      </c>
+      <c r="G257" s="33" t="s">
+        <v>343</v>
+      </c>
+      <c r="H257" s="33" t="s">
+        <v>1211</v>
+      </c>
+      <c r="I257" s="33" t="s">
+        <v>1216</v>
+      </c>
+      <c r="J257" s="33" t="s">
+        <v>1151</v>
+      </c>
+      <c r="K257" s="33" t="s">
+        <v>1217</v>
+      </c>
+      <c r="L257" s="33" t="s">
+        <v>1218</v>
+      </c>
+    </row>
+    <row r="258" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A258" s="41" t="s">
+        <v>1210</v>
+      </c>
+      <c r="B258" s="41" t="s">
+        <v>1208</v>
+      </c>
+      <c r="C258" s="33" t="s">
+        <v>276</v>
+      </c>
+      <c r="D258" s="33" t="s">
+        <v>259</v>
+      </c>
+      <c r="E258" s="41" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F258" s="33" t="s">
+        <v>1220</v>
+      </c>
+      <c r="G258" s="33" t="s">
+        <v>343</v>
+      </c>
+      <c r="H258" s="33" t="s">
+        <v>1212</v>
+      </c>
+      <c r="I258" s="33" t="s">
+        <v>1221</v>
+      </c>
+      <c r="J258" s="33" t="s">
+        <v>1222</v>
+      </c>
+      <c r="K258" s="33" t="s">
+        <v>1223</v>
+      </c>
+      <c r="L258" s="33" t="s">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="259" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A259" s="41" t="s">
+        <v>1210</v>
+      </c>
+      <c r="B259" s="41" t="s">
         <v>1209</v>
       </c>
-      <c r="C256" s="33" t="s">
+      <c r="C259" s="33" t="s">
         <v>276</v>
       </c>
-      <c r="D256" s="33" t="s">
+      <c r="D259" s="33" t="s">
         <v>259</v>
       </c>
-      <c r="E256" s="41" t="s">
+      <c r="E259" s="41" t="s">
         <v>1225</v>
       </c>
-      <c r="F256" s="33" t="s">
+      <c r="F259" s="33" t="s">
         <v>1226</v>
       </c>
-      <c r="G256" s="33" t="s">
+      <c r="G259" s="33" t="s">
         <v>343</v>
       </c>
-      <c r="H256" s="33" t="s">
+      <c r="H259" s="33" t="s">
         <v>1213</v>
       </c>
-      <c r="I256" s="33" t="s">
+      <c r="I259" s="33" t="s">
         <v>1221</v>
       </c>
-      <c r="J256" s="33" t="s">
+      <c r="J259" s="33" t="s">
         <v>1227</v>
       </c>
-      <c r="K256" s="33" t="s">
+      <c r="K259" s="33" t="s">
         <v>1223</v>
       </c>
-      <c r="L256" s="33" t="s">
+      <c r="L259" s="33" t="s">
         <v>1228</v>
-      </c>
-    </row>
-    <row r="257" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A257" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CATALOGO_ESPECIES</t>
-        </is>
-      </c>
-      <c r="B257" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">origen_biogeografico</t>
-        </is>
-      </c>
-      <c r="C257" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manual</t>
-        </is>
-      </c>
-      <c r="D257" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Inspector</t>
-        </is>
-      </c>
-      <c r="E257" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Asignación según la distribución natural de la especie respecto de Chile, consultando el Catálogo de las plantas vasculares de Chile (Rodríguez et al., 2018) o su versión en línea vigente.</t>
-        </is>
-      </c>
-      <c r="F257" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Clasificación de la especie según su procedencia biogeográfica respecto del territorio chileno. Endémica: especie nativa cuya distribución natural está restringida a Chile. Nativa: especie nativa de Chile cuya distribución natural no se restringe al país. Introducida: especie exótica presente en Chile fuera de su distribución natural.</t>
-        </is>
-      </c>
-      <c r="G257" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Categoría</t>
-        </is>
-      </c>
-      <c r="H257" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Nativa / Endémica / Introducida</t>
-        </is>
-      </c>
-      <c r="I257" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Obligatorio para completar la clasificación del catálogo</t>
-        </is>
-      </c>
-      <c r="J257" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">La plataforma lo vincula al árbol mediante especie_cientifica.</t>
-        </is>
-      </c>
-      <c r="K257" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Al completar o actualizar la clasificación de la especie.</t>
-        </is>
-      </c>
-      <c r="L257" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Categorías excluyentes: una especie endémica no se registra como Nativa. Considerar la distribución natural de la especie respecto de Chile, no el lugar de plantación ni el origen del ejemplar. Si aún no se conoce, dejar nulo; no inventarlo ni bloquear el registro del árbol. Se muestra en la ficha del árbol mediante especie_cientifica; no se ingresa por ejemplar ni se duplica en ARBOLES. Si el árbol no tiene especie_cientifica vigente, se informa como Origen no determinado.</t>
-        </is>
-      </c>
-    </row>
-    <row r="258" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A258" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CATALOGO_ESPECIES</t>
-        </is>
-      </c>
-      <c r="B258" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">persistencia_follaje</t>
-        </is>
-      </c>
-      <c r="C258" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manual</t>
-        </is>
-      </c>
-      <c r="D258" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Inspector</t>
-        </is>
-      </c>
-      <c r="E258" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Asignación según fuentes botánicas de referencia al incorporar o completar la especie en el catálogo.</t>
-        </is>
-      </c>
-      <c r="F258" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Comportamiento habitual del follaje de la especie a lo largo del año. Perennifolia: conserva follaje funcional durante todo el año, con renovación gradual. Caducifolia: pierde la totalidad del follaje durante la estación desfavorable. Semicaducifolia: pierde parcialmente el follaje, o lo pierde por un período breve, según las condiciones climáticas del año.</t>
-        </is>
-      </c>
-      <c r="G258" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Categoría</t>
-        </is>
-      </c>
-      <c r="H258" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Perennifolia / Caducifolia / Semicaducifolia</t>
-        </is>
-      </c>
-      <c r="I258" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Obligatorio para completar la clasificación del catálogo</t>
-        </is>
-      </c>
-      <c r="J258" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">La plataforma la vincula al árbol mediante especie_cientifica.</t>
-        </is>
-      </c>
-      <c r="K258" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Al completar o actualizar la clasificación de la especie.</t>
-        </is>
-      </c>
-      <c r="L258" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Corresponde al comportamiento habitual de la especie, no a la condición observada en el ejemplar. Si las fuentes describen un comportamiento variable, registrar el habitual en las condiciones climáticas de Valparaíso. Si aún no se conoce, dejar nulo; no inventarla ni bloquear el registro del árbol. No duplicar en ARBOLES. Si el árbol no tiene especie_cientifica vigente, no mostrar valor.</t>
-        </is>
-      </c>
-    </row>
-    <row r="259" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A259" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CATALOGO_ESPECIES</t>
-        </is>
-      </c>
-      <c r="B259" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">tipo_hoja</t>
-        </is>
-      </c>
-      <c r="C259" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manual</t>
-        </is>
-      </c>
-      <c r="D259" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Inspector</t>
-        </is>
-      </c>
-      <c r="E259" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Asignación según fuentes botánicas de referencia al incorporar o completar la especie en el catálogo.</t>
-        </is>
-      </c>
-      <c r="F259" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Morfología predominante de las hojas adultas de la especie. Latifoliada: lámina ancha y plana. Acicular: hoja alargada y angosta, en forma de aguja. Escuamiforme: hoja reducida a escamas adosadas a la ramilla. Palmera: hoja de palmera, palmada o pinnada.</t>
-        </is>
-      </c>
-      <c r="G259" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Categoría</t>
-        </is>
-      </c>
-      <c r="H259" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Latifoliada / Acicular / Escuamiforme / Palmera</t>
-        </is>
-      </c>
-      <c r="I259" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Obligatorio para completar la clasificación del catálogo</t>
-        </is>
-      </c>
-      <c r="J259" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">La plataforma lo vincula al árbol mediante especie_cientifica.</t>
-        </is>
-      </c>
-      <c r="K259" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Al completar o actualizar la clasificación de la especie.</t>
-        </is>
-      </c>
-      <c r="L259" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Seleccionar una única categoría según el follaje adulto; no considerar el follaje juvenil. Si la morfología no coincide exactamente con una categoría, asignar la más cercana: las estructuras planas que cumplen función foliar, como los filodios, se clasifican como Latifoliada; las hojas reducidas a escamas sobre ramillas verdes se clasifican como Escuamiforme. Si aún no se conoce, dejar nulo; no inventarlo ni bloquear el registro del árbol. No duplicar en ARBOLES. Si el árbol no tiene especie_cientifica vigente, no mostrar valor.</t>
-        </is>
       </c>
     </row>
     <row r="260" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A260" s="41" t="inlineStr">
         <is>
-          <t xml:space="preserve">PROYECTOS</t>
+          <t xml:space="preserve">CATALOGO_ESPECIES</t>
         </is>
       </c>
       <c r="B260" s="41" t="inlineStr">
         <is>
-          <t xml:space="preserve">id_proyecto</t>
+          <t xml:space="preserve">origen_biogeografico</t>
         </is>
       </c>
       <c r="C260" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generado por plataforma</t>
+          <t xml:space="preserve">Manual</t>
         </is>
       </c>
       <c r="D260" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sistema</t>
+          <t xml:space="preserve">Inspector</t>
         </is>
       </c>
       <c r="E260" s="41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asignación automática al crear el proyecto.</t>
+          <t xml:space="preserve">Asignación según la distribución natural de la especie respecto de Chile, consultando el Catálogo de las plantas vasculares de Chile (Rodríguez et al., 2018) o su versión en línea vigente.</t>
         </is>
       </c>
       <c r="F260" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Identificador único y estable del proyecto, que separa inventarios, delimitación territorial y acceso de usuarios.</t>
+          <t xml:space="preserve">Clasificación de la especie según su procedencia biogeográfica respecto del territorio chileno. Endémica: especie nativa cuya distribución natural está restringida a Chile. Nativa: especie nativa de Chile cuya distribución natural no se restringe al país. Introducida: especie exótica presente en Chile fuera de su distribución natural.</t>
         </is>
       </c>
       <c r="G260" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Identificador (texto)</t>
+          <t xml:space="preserve">Categoría</t>
         </is>
       </c>
       <c r="H260" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">No aplica</t>
+          <t xml:space="preserve">Nativa / Endémica / Introducida</t>
         </is>
       </c>
       <c r="I260" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Obligatorio</t>
+          <t xml:space="preserve">Obligatorio para completar la clasificación del catálogo</t>
         </is>
       </c>
       <c r="J260" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asignación automática única.</t>
+          <t xml:space="preserve">La plataforma lo vincula al árbol mediante especie_cientifica.</t>
         </is>
       </c>
       <c r="K260" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Al crear el proyecto.</t>
+          <t xml:space="preserve">Al completar o actualizar la clasificación de la especie.</t>
         </is>
       </c>
       <c r="L260" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">No editable. Solo el Administrador puede crear proyectos.</t>
+          <t xml:space="preserve">Categorías excluyentes: una especie endémica no se registra como Nativa. Considerar la distribución natural de la especie respecto de Chile, no el lugar de plantación ni el origen del ejemplar. Si aún no se conoce, dejar nulo; no inventarlo ni bloquear el registro del árbol. Se muestra en la ficha del árbol mediante especie_cientifica; no se ingresa por ejemplar ni se duplica en ARBOLES. Si el árbol no tiene especie_cientifica vigente, se informa como Origen no determinado.</t>
         </is>
       </c>
     </row>
     <row r="261" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A261" s="41" t="inlineStr">
         <is>
-          <t xml:space="preserve">PROYECTOS</t>
+          <t xml:space="preserve">CATALOGO_ESPECIES</t>
         </is>
       </c>
       <c r="B261" s="41" t="inlineStr">
         <is>
-          <t xml:space="preserve">nombre_proyecto</t>
+          <t xml:space="preserve">persistencia_follaje</t>
         </is>
       </c>
       <c r="C261" s="33" t="inlineStr">
@@ -23288,169 +23377,355 @@
       </c>
       <c r="D261" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Administrador</t>
+          <t xml:space="preserve">Inspector</t>
         </is>
       </c>
       <c r="E261" s="41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ingreso del nombre al crear o editar el proyecto.</t>
+          <t xml:space="preserve">Asignación según fuentes botánicas de referencia al incorporar o completar la especie en el catálogo.</t>
         </is>
       </c>
       <c r="F261" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nombre visible del proyecto.</t>
+          <t xml:space="preserve">Comportamiento habitual del follaje de la especie a lo largo del año. Perennifolia: conserva follaje funcional durante todo el año, con renovación gradual. Caducifolia: pierde la totalidad del follaje durante la estación desfavorable. Semicaducifolia: pierde parcialmente el follaje, o lo pierde por un período breve, según las condiciones climáticas del año.</t>
         </is>
       </c>
       <c r="G261" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Texto</t>
+          <t xml:space="preserve">Categoría</t>
         </is>
       </c>
       <c r="H261" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">No aplica</t>
+          <t xml:space="preserve">Perennifolia / Caducifolia / Semicaducifolia</t>
         </is>
       </c>
       <c r="I261" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Obligatorio</t>
+          <t xml:space="preserve">Obligatorio para completar la clasificación del catálogo</t>
         </is>
       </c>
       <c r="J261" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">No aplica.</t>
+          <t xml:space="preserve">La plataforma la vincula al árbol mediante especie_cientifica.</t>
         </is>
       </c>
       <c r="K261" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Al crear o editar el proyecto.</t>
+          <t xml:space="preserve">Al completar o actualizar la clasificación de la especie.</t>
         </is>
       </c>
       <c r="L261" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">No vacío. Su modificación no altera id_proyecto.</t>
+          <t xml:space="preserve">Corresponde al comportamiento habitual de la especie, no a la condición observada en el ejemplar. Si las fuentes describen un comportamiento variable, registrar el habitual en las condiciones climáticas de Valparaíso. Si aún no se conoce, dejar nulo; no inventarla ni bloquear el registro del árbol. No duplicar en ARBOLES. Si el árbol no tiene especie_cientifica vigente, no mostrar valor.</t>
         </is>
       </c>
     </row>
     <row r="262" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A262" s="41" t="inlineStr">
         <is>
-          <t xml:space="preserve">MIEMBROS_PROYECTO</t>
+          <t xml:space="preserve">CATALOGO_ESPECIES</t>
         </is>
       </c>
       <c r="B262" s="41" t="inlineStr">
         <is>
-          <t xml:space="preserve">id_proyecto</t>
+          <t xml:space="preserve">tipo_hoja</t>
         </is>
       </c>
       <c r="C262" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vinculado por plataforma</t>
+          <t xml:space="preserve">Manual</t>
         </is>
       </c>
       <c r="D262" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Administrador</t>
+          <t xml:space="preserve">Inspector</t>
         </is>
       </c>
       <c r="E262" s="41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Selección del proyecto al asignar un miembro.</t>
+          <t xml:space="preserve">Asignación según fuentes botánicas de referencia al incorporar o completar la especie en el catálogo.</t>
         </is>
       </c>
       <c r="F262" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Proyecto al que se asigna el usuario.</t>
+          <t xml:space="preserve">Morfología predominante de las hojas adultas de la especie. Latifoliada: lámina ancha y plana. Acicular: hoja alargada y angosta, en forma de aguja. Escuamiforme: hoja reducida a escamas adosadas a la ramilla. Palmera: hoja de palmera, palmada o pinnada.</t>
         </is>
       </c>
       <c r="G262" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Identificador (texto)</t>
+          <t xml:space="preserve">Categoría</t>
         </is>
       </c>
       <c r="H262" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">No aplica</t>
+          <t xml:space="preserve">Latifoliada / Acicular / Escuamiforme / Palmera</t>
         </is>
       </c>
       <c r="I262" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Obligatorio</t>
+          <t xml:space="preserve">Obligatorio para completar la clasificación del catálogo</t>
         </is>
       </c>
       <c r="J262" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">No aplica.</t>
+          <t xml:space="preserve">La plataforma lo vincula al árbol mediante especie_cientifica.</t>
         </is>
       </c>
       <c r="K262" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Al asignar un usuario a un proyecto.</t>
+          <t xml:space="preserve">Al completar o actualizar la clasificación de la especie.</t>
         </is>
       </c>
       <c r="L262" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Referencia válida a PROYECTOS. Un usuario puede pertenecer a varios proyectos; no repetir la misma combinación id_proyecto e id_usuario.</t>
+          <t xml:space="preserve">Seleccionar una única categoría según el follaje adulto; no considerar el follaje juvenil. Si la morfología no coincide exactamente con una categoría, asignar la más cercana: las estructuras planas que cumplen función foliar, como los filodios, se clasifican como Latifoliada; las hojas reducidas a escamas sobre ramillas verdes se clasifican como Escuamiforme. Si aún no se conoce, dejar nulo; no inventarlo ni bloquear el registro del árbol. No duplicar en ARBOLES. Si el árbol no tiene especie_cientifica vigente, no mostrar valor.</t>
         </is>
       </c>
     </row>
     <row r="263" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A263" s="41" t="inlineStr">
         <is>
+          <t xml:space="preserve">PROYECTOS</t>
+        </is>
+      </c>
+      <c r="B263" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">id_proyecto</t>
+        </is>
+      </c>
+      <c r="C263" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Generado por plataforma</t>
+        </is>
+      </c>
+      <c r="D263" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sistema</t>
+        </is>
+      </c>
+      <c r="E263" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Asignación automática al crear el proyecto.</t>
+        </is>
+      </c>
+      <c r="F263" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Identificador único y estable del proyecto, que separa inventarios, delimitación territorial y acceso de usuarios.</t>
+        </is>
+      </c>
+      <c r="G263" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Identificador (texto)</t>
+        </is>
+      </c>
+      <c r="H263" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No aplica</t>
+        </is>
+      </c>
+      <c r="I263" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Obligatorio</t>
+        </is>
+      </c>
+      <c r="J263" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Asignación automática única.</t>
+        </is>
+      </c>
+      <c r="K263" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Al crear el proyecto.</t>
+        </is>
+      </c>
+      <c r="L263" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No editable. Solo el Administrador puede crear proyectos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="264" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A264" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PROYECTOS</t>
+        </is>
+      </c>
+      <c r="B264" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nombre_proyecto</t>
+        </is>
+      </c>
+      <c r="C264" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="D264" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Administrador</t>
+        </is>
+      </c>
+      <c r="E264" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ingreso del nombre al crear o editar el proyecto.</t>
+        </is>
+      </c>
+      <c r="F264" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nombre visible del proyecto.</t>
+        </is>
+      </c>
+      <c r="G264" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Texto</t>
+        </is>
+      </c>
+      <c r="H264" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No aplica</t>
+        </is>
+      </c>
+      <c r="I264" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Obligatorio</t>
+        </is>
+      </c>
+      <c r="J264" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No aplica.</t>
+        </is>
+      </c>
+      <c r="K264" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Al crear o editar el proyecto.</t>
+        </is>
+      </c>
+      <c r="L264" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No vacío. Su modificación no altera id_proyecto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="265" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A265" s="41" t="inlineStr">
+        <is>
           <t xml:space="preserve">MIEMBROS_PROYECTO</t>
         </is>
       </c>
-      <c r="B263" s="41" t="inlineStr">
+      <c r="B265" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">id_proyecto</t>
+        </is>
+      </c>
+      <c r="C265" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vinculado por plataforma</t>
+        </is>
+      </c>
+      <c r="D265" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Administrador</t>
+        </is>
+      </c>
+      <c r="E265" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Selección del proyecto al asignar un miembro.</t>
+        </is>
+      </c>
+      <c r="F265" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proyecto al que se asigna el usuario.</t>
+        </is>
+      </c>
+      <c r="G265" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Identificador (texto)</t>
+        </is>
+      </c>
+      <c r="H265" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No aplica</t>
+        </is>
+      </c>
+      <c r="I265" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Obligatorio</t>
+        </is>
+      </c>
+      <c r="J265" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No aplica.</t>
+        </is>
+      </c>
+      <c r="K265" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Al asignar un usuario a un proyecto.</t>
+        </is>
+      </c>
+      <c r="L265" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Referencia válida a PROYECTOS. Un usuario puede pertenecer a varios proyectos; no repetir la misma combinación id_proyecto e id_usuario.</t>
+        </is>
+      </c>
+    </row>
+    <row r="266" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A266" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MIEMBROS_PROYECTO</t>
+        </is>
+      </c>
+      <c r="B266" s="41" t="inlineStr">
         <is>
           <t xml:space="preserve">id_usuario</t>
         </is>
       </c>
-      <c r="C263" s="33" t="inlineStr">
+      <c r="C266" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">Vinculado por plataforma</t>
         </is>
       </c>
-      <c r="D263" s="33" t="inlineStr">
+      <c r="D266" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">Administrador</t>
         </is>
       </c>
-      <c r="E263" s="41" t="inlineStr">
+      <c r="E266" s="41" t="inlineStr">
         <is>
           <t xml:space="preserve">Selección del usuario al asignarlo al proyecto.</t>
         </is>
       </c>
-      <c r="F263" s="33" t="inlineStr">
+      <c r="F266" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">Usuario con acceso al proyecto.</t>
         </is>
       </c>
-      <c r="G263" s="33" t="inlineStr">
+      <c r="G266" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">Identificador (texto)</t>
         </is>
       </c>
-      <c r="H263" s="33" t="inlineStr">
+      <c r="H266" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">No aplica</t>
         </is>
       </c>
-      <c r="I263" s="33" t="inlineStr">
+      <c r="I266" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">Obligatorio</t>
         </is>
       </c>
-      <c r="J263" s="33" t="inlineStr">
+      <c r="J266" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">No aplica.</t>
         </is>
       </c>
-      <c r="K263" s="33" t="inlineStr">
+      <c r="K266" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">Al asignar un usuario a un proyecto.</t>
         </is>
       </c>
-      <c r="L263" s="33" t="inlineStr">
+      <c r="L266" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">Referencia válida a USUARIOS con activo = Sí. El rol del usuario se mantiene en USUARIOS.Rol.</t>
         </is>

--- a/docs/excel/Base de Datos Valpo Verde.xlsx
+++ b/docs/excel/Base de Datos Valpo Verde.xlsx
@@ -11367,12 +11367,12 @@
       </c>
       <c r="F97" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leve</t>
+          <t xml:space="preserve">Moderada</t>
         </is>
       </c>
       <c r="G97" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
     </row>

--- a/docs/excel/Base de Datos Valpo Verde.xlsx
+++ b/docs/excel/Base de Datos Valpo Verde.xlsx
@@ -878,10 +878,10 @@
     <t>USR-001</t>
   </si>
   <si>
-    <t>Valentina Jiménez</t>
-  </si>
-  <si>
-    <t>valejimenezvpjc@gmail.com</t>
+    <t/>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t>Administrador</t>
@@ -890,25 +890,25 @@
     <t>USR-002</t>
   </si>
   <si>
-    <t>Mariajosé Baxmann</t>
-  </si>
-  <si>
-    <t>baxmannmariajose@gmail.com</t>
-  </si>
-  <si>
-    <t>baxmannroman12@gmail.com</t>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t>Usuario municipal</t>
   </si>
   <si>
-    <t>valazjc@gmail.com</t>
+    <t/>
   </si>
   <si>
     <t>Inspector</t>
   </si>
   <si>
-    <t>valentina.jimenezc@estudiantes.uv.cl</t>
+    <t/>
   </si>
   <si>
     <t>Encargado de mantención</t>
@@ -11623,7 +11623,12 @@
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">aprobación de publicación pendiente</t>
+          <t xml:space="preserve">publicada</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-20</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
@@ -11631,6 +11636,21 @@
           <t xml:space="preserve">CC-024, CC-026, CC-027, CC-028, CC-029, CC-030, CC-031, CC-032, CC-034, CC-035, CC-036, CC-037, CC-039</t>
         </is>
       </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marybaxmann</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-20</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologia-v2.0.0</t>
+        </is>
+      </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">2.0.0 en preparación (fuente única desde CC-028)</t>
@@ -11638,7 +11658,7 @@
       </c>
       <c r="J5" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Incluye AM-10: textos de CC-031, CC-032, CC-036 y CC-037; rango_edad_estimada_anios opcional (CC-039) y referencia estacional de la defoliación en caducifolias (AM-11). El Excel maestro es la única fuente (CC-028) y los diagramas no forman parte del paquete (CC-030). INDICES sigue en propuesta (DM-09). Todas las reglas de REGLAS_INDICADORES son vigentes en esta versión (PR-011 v3.0). Al publicar, la autora completa fecha_publicacion, aprobado_por, fecha_aprobacion y tag_git, y cambia el estado a publicada.</t>
+          <t xml:space="preserve">Incluye AM-10: textos de CC-031, CC-032, CC-036 y CC-037; rango_edad_estimada_anios opcional (CC-039) y referencia estacional de la defoliación en caducifolias (AM-11). El Excel maestro es la única fuente (CC-028) y los diagramas no forman parte del paquete (CC-030). INDICES sigue en propuesta (DM-09). Todas las reglas de REGLAS_INDICADORES son vigentes en esta versión (PR-011 v3.0). Incluye también IN-RSU-05 = Moderada (CC-030, PR #29). Primera versión publicada, el 2026-10-20 (AM-08).</t>
         </is>
       </c>
     </row>
@@ -12826,11 +12846,15 @@
       <c r="A2" t="s">
         <v>249</v>
       </c>
-      <c r="B2" t="s">
-        <v>250</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>251</v>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Administrador de ejemplo 1</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">admin1@example.org</t>
+        </is>
       </c>
       <c r="D2" t="s">
         <v>252</v>
@@ -12843,11 +12867,15 @@
       <c r="A3" t="s">
         <v>253</v>
       </c>
-      <c r="B3" t="s">
-        <v>254</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>255</v>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Administrador de ejemplo 2</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">admin2@example.org</t>
+        </is>
       </c>
       <c r="D3" t="s">
         <v>252</v>
@@ -12860,11 +12888,15 @@
       <c r="A4" t="s">
         <v>219</v>
       </c>
-      <c r="B4" t="s">
-        <v>254</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>256</v>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Usuario municipal de ejemplo</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">municipal@example.org</t>
+        </is>
       </c>
       <c r="D4" t="s">
         <v>257</v>
@@ -12877,11 +12909,15 @@
       <c r="A5" t="s">
         <v>192</v>
       </c>
-      <c r="B5" t="s">
-        <v>250</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>258</v>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Inspector de ejemplo</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inspector@example.org</t>
+        </is>
       </c>
       <c r="D5" t="s">
         <v>259</v>
@@ -12894,11 +12930,15 @@
       <c r="A6" t="s">
         <v>212</v>
       </c>
-      <c r="B6" t="s">
-        <v>250</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>260</v>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Encargado de mantención de ejemplo</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mantencion@example.org</t>
+        </is>
       </c>
       <c r="D6" t="s">
         <v>261</v>
@@ -12908,13 +12948,6 @@
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" xr:uid="{00000000-0004-0000-0600-000000000000}"/>
-    <hyperlink ref="C3" r:id="rId2" xr:uid="{00000000-0004-0000-0600-000001000000}"/>
-    <hyperlink ref="C4" r:id="rId3" xr:uid="{00000000-0004-0000-0600-000002000000}"/>
-    <hyperlink ref="C5" r:id="rId4" xr:uid="{00000000-0004-0000-0600-000003000000}"/>
-    <hyperlink ref="C6" r:id="rId5" xr:uid="{00000000-0004-0000-0600-000004000000}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/docs/excel/Base de Datos Valpo Verde.xlsx
+++ b/docs/excel/Base de Datos Valpo Verde.xlsx
@@ -7135,7 +7135,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -7716,6 +7716,28 @@
         </is>
       </c>
     </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proyectos</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Un proyecto con estado_proyecto = Cerrado queda en solo consulta: se pueden ver sus árboles, mapa, fichas, indicadores e historial, pero no se registran árboles ni se crean OT, inspecciones, mantenimientos o incidencias, y el formulario QR de sus árboles no recibe incidencias. La delimitación del sector no se modifica; el Administrador puede seguir gestionando los miembros. Solo el Administrador cierra o reabre un proyecto, y no puede cerrarlo mientras alguna OT esté Pendiente, Programada o En ejecución o alguna incidencia esté Ingresada o En revisión.</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estado_proyecto; estado_ot; estado_incidencia</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PROYECTOS; ARBOLES; ORDENES DE TRABAJO; INSPECCION; MANTENIMIENTO; INCIDENCIA; SECTORES; MIEMBROS_PROYECTO</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7723,14 +7745,15 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="40" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:3">
       <c r="A1" t="inlineStr">
         <is>
           <t>id_proyecto</t>
@@ -7739,6 +7762,11 @@
       <c r="B1" t="inlineStr">
         <is>
           <t>nombre_proyecto</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>estado_proyecto</t>
         </is>
       </c>
     </row>
@@ -11457,7 +11485,7 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -11659,6 +11687,38 @@
       <c r="J5" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Incluye AM-10: textos de CC-031, CC-032, CC-036 y CC-037; rango_edad_estimada_anios opcional (CC-039) y referencia estacional de la defoliación en caducifolias (AM-11). El Excel maestro es la única fuente (CC-028) y los diagramas no forman parte del paquete (CC-030). INDICES sigue en propuesta (DM-09). Todas las reglas de REGLAS_INDICADORES son vigentes en esta versión (PR-011 v3.0). Incluye también IN-RSU-05 = Moderada (CC-030, PR #29). Primera versión publicada, el 2026-10-20 (AM-08).</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.0.1</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.0</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">en preparación</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CC-042</t>
+        </is>
+      </c>
+      <c r="I6" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.0.0</t>
+        </is>
+      </c>
+      <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PATCH: agrega PROYECTOS.estado_proyecto (Activo / Cerrado) y su regla en REGLAS_GENERALES (Proyectos). El campo no participa en ninguna regla de cálculo: no cambia resultados y rule_version sigue siendo 2.0. NO publicada.</t>
         </is>
       </c>
     </row>
@@ -13155,7 +13215,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M266"/>
+  <dimension ref="A1:M267"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="24" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7" style="41" customWidth="1"/>
@@ -23640,45 +23700,45 @@
         </is>
       </c>
     </row>
-    <row r="265" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A265" s="41" t="inlineStr">
         <is>
-          <t xml:space="preserve">MIEMBROS_PROYECTO</t>
+          <t xml:space="preserve">PROYECTOS</t>
         </is>
       </c>
       <c r="B265" s="41" t="inlineStr">
         <is>
-          <t xml:space="preserve">id_proyecto</t>
+          <t xml:space="preserve">estado_proyecto</t>
         </is>
       </c>
       <c r="C265" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vinculado por plataforma</t>
+          <t xml:space="preserve">Manual</t>
         </is>
       </c>
       <c r="D265" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Administrador</t>
+          <t xml:space="preserve">Administrador / Sistema</t>
         </is>
       </c>
       <c r="E265" s="41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Selección del proyecto al asignar un miembro.</t>
+          <t xml:space="preserve">Valor inicial asignado por la plataforma al crear el proyecto; el Administrador lo cambia al cerrar o reabrir el proyecto.</t>
         </is>
       </c>
       <c r="F265" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Proyecto al que se asigna el usuario.</t>
+          <t xml:space="preserve">Situación del proyecto. Activo: permite registrar y gestionar árboles, OT, inspecciones, mantenimientos e incidencias. Cerrado: el proyecto queda en solo consulta.</t>
         </is>
       </c>
       <c r="G265" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Identificador (texto)</t>
+          <t xml:space="preserve">Categoría</t>
         </is>
       </c>
       <c r="H265" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">No aplica</t>
+          <t xml:space="preserve">Activo / Cerrado</t>
         </is>
       </c>
       <c r="I265" s="33" t="inlineStr">
@@ -23693,12 +23753,12 @@
       </c>
       <c r="K265" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Al asignar un usuario a un proyecto.</t>
+          <t xml:space="preserve">Al crear el proyecto y al cerrarlo o reabrirlo.</t>
         </is>
       </c>
       <c r="L265" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Referencia válida a PROYECTOS. Un usuario puede pertenecer a varios proyectos; no repetir la misma combinación id_proyecto e id_usuario.</t>
+          <t xml:space="preserve">Valor inicial: Activo. Solo el Administrador cierra o reabre el proyecto. No permitir Cerrado mientras alguna OT del proyecto tenga estado_ot = Pendiente, Programada o En ejecución, o alguna incidencia de sus árboles tenga estado_incidencia = Ingresada o En revisión. Un proyecto Cerrado puede reabrirse (Activo). El cambio de estado no altera id_proyecto ni el historial.</t>
         </is>
       </c>
     </row>
@@ -23710,55 +23770,117 @@
       </c>
       <c r="B266" s="41" t="inlineStr">
         <is>
+          <t xml:space="preserve">id_proyecto</t>
+        </is>
+      </c>
+      <c r="C266" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vinculado por plataforma</t>
+        </is>
+      </c>
+      <c r="D266" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Administrador</t>
+        </is>
+      </c>
+      <c r="E266" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Selección del proyecto al asignar un miembro.</t>
+        </is>
+      </c>
+      <c r="F266" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proyecto al que se asigna el usuario.</t>
+        </is>
+      </c>
+      <c r="G266" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Identificador (texto)</t>
+        </is>
+      </c>
+      <c r="H266" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No aplica</t>
+        </is>
+      </c>
+      <c r="I266" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Obligatorio</t>
+        </is>
+      </c>
+      <c r="J266" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No aplica.</t>
+        </is>
+      </c>
+      <c r="K266" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Al asignar un usuario a un proyecto.</t>
+        </is>
+      </c>
+      <c r="L266" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Referencia válida a PROYECTOS. Un usuario puede pertenecer a varios proyectos; no repetir la misma combinación id_proyecto e id_usuario.</t>
+        </is>
+      </c>
+    </row>
+    <row r="267" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A267" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MIEMBROS_PROYECTO</t>
+        </is>
+      </c>
+      <c r="B267" s="41" t="inlineStr">
+        <is>
           <t xml:space="preserve">id_usuario</t>
         </is>
       </c>
-      <c r="C266" s="33" t="inlineStr">
+      <c r="C267" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">Vinculado por plataforma</t>
         </is>
       </c>
-      <c r="D266" s="33" t="inlineStr">
+      <c r="D267" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">Administrador</t>
         </is>
       </c>
-      <c r="E266" s="41" t="inlineStr">
+      <c r="E267" s="41" t="inlineStr">
         <is>
           <t xml:space="preserve">Selección del usuario al asignarlo al proyecto.</t>
         </is>
       </c>
-      <c r="F266" s="33" t="inlineStr">
+      <c r="F267" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">Usuario con acceso al proyecto.</t>
         </is>
       </c>
-      <c r="G266" s="33" t="inlineStr">
+      <c r="G267" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">Identificador (texto)</t>
         </is>
       </c>
-      <c r="H266" s="33" t="inlineStr">
+      <c r="H267" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">No aplica</t>
         </is>
       </c>
-      <c r="I266" s="33" t="inlineStr">
+      <c r="I267" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">Obligatorio</t>
         </is>
       </c>
-      <c r="J266" s="33" t="inlineStr">
+      <c r="J267" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">No aplica.</t>
         </is>
       </c>
-      <c r="K266" s="33" t="inlineStr">
+      <c r="K267" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">Al asignar un usuario a un proyecto.</t>
         </is>
       </c>
-      <c r="L266" s="33" t="inlineStr">
+      <c r="L267" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">Referencia válida a USUARIOS con activo = Sí. El rol del usuario se mantiene en USUARIOS.Rol.</t>
         </is>

--- a/docs/excel/Base de Datos Valpo Verde.xlsx
+++ b/docs/excel/Base de Datos Valpo Verde.xlsx
@@ -7724,7 +7724,7 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Un proyecto con estado_proyecto = Cerrado queda en solo consulta: se pueden ver sus árboles, mapa, fichas, indicadores e historial, pero no se registran árboles ni se crean OT, inspecciones, mantenimientos o incidencias, y el formulario QR de sus árboles no recibe incidencias. La delimitación del sector no se modifica; el Administrador puede seguir gestionando los miembros. Solo el Administrador cierra o reabre un proyecto, y no puede cerrarlo mientras alguna OT esté Pendiente, Programada o En ejecución o alguna incidencia esté Ingresada o En revisión.</t>
+          <t xml:space="preserve">Un proyecto con estado_proyecto = Cerrado queda en solo consulta: se pueden ver sus árboles, mapa, fichas, indicadores e historial, pero no se registran árboles ni se crean OT, inspecciones, mantenimientos o incidencias, y el formulario QR de sus árboles no recibe incidencias. La delimitación del sector no se modifica; el Administrador puede seguir gestionando los miembros. Solo el Administrador cierra o reabre un proyecto. Puede cerrarse aunque existan OT o incidencias abiertas: mientras el proyecto está Cerrado, esas OT e incidencias se conservan en su estado y no avanzan hasta que el proyecto se reabra.</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
@@ -23758,7 +23758,7 @@
       </c>
       <c r="L265" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valor inicial: Activo. Solo el Administrador cierra o reabre el proyecto. No permitir Cerrado mientras alguna OT del proyecto tenga estado_ot = Pendiente, Programada o En ejecución, o alguna incidencia de sus árboles tenga estado_incidencia = Ingresada o En revisión. Un proyecto Cerrado puede reabrirse (Activo). El cambio de estado no altera id_proyecto ni el historial.</t>
+          <t xml:space="preserve">Valor inicial: Activo. Solo el Administrador cierra o reabre el proyecto. Puede cerrarse aunque existan OT o incidencias abiertas: mientras el proyecto está Cerrado, esas OT e incidencias se conservan en su estado y no avanzan hasta que el proyecto se reabra. Un proyecto Cerrado puede reabrirse (Activo). El cambio de estado no altera id_proyecto ni el historial.</t>
         </is>
       </c>
     </row>

--- a/docs/excel/Base de Datos Valpo Verde.xlsx
+++ b/docs/excel/Base de Datos Valpo Verde.xlsx
@@ -7135,7 +7135,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -7735,6 +7735,28 @@
       <c r="D27" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">PROYECTOS; ARBOLES; ORDENES DE TRABAJO; INSPECCION; MANTENIMIENTO; INCIDENCIA; SECTORES; MIEMBROS_PROYECTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preguardado y finalización</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">La evaluación que se exige para finalizar depende de tipo_inspeccion_realizada. Evaluación inicial, Reevaluación y Levantamiento: evaluación completa (todos los campos Obligatorios y los Condicionales activados de ARBOLES y REGISTRO_EVALUACION). Evaluación instrumental: solo los campos de cavidad basal y de tronco; resuelve el No determinado de Requiere evaluación instrumental. Monitoreo: solo los campos de su subtipo (Fitosanitario, Estructural o Vitalidad). En una inspección parcial, los campos registrados reemplazan el valor vigente del árbol al completar la OT; los demás conservan su valor vigente anterior. El historial no se sobrescribe: cada valor queda vinculado a la inspección que lo registró. Las clasificaciones se calculan con los valores vigentes resultantes: para cada campo, el último valor entre las inspecciones no anuladas de OT completadas. Las cuatro vistas fotográficas del árbol se exigen solo en Evaluación inicial, Reevaluación y Levantamiento; la Evaluación instrumental no considera fotografías y en el Monitoreo no son obligatorias. Campos por subtipo de Monitoreo: Fitosanitario = defoliacion_estimada_pct, clorosis_pct, necrosis_pct, muerte_regresiva_copa_pct y presenta_exudaciones; Estructural = las entradas de R01, R02 y R03; Vitalidad = clasificacion_vitalidad. En la Evaluación instrumental, cavidad_basal_interna y cavidad_interna_tronco solo admiten Sí o No. Si falta un valor vigente que una clasificación necesita, esa clasificación queda No determinado. Si al recalcular la evaluación vigente el valor calculado cambia, el ajuste del Inspector se descarta y queda marcado para su revisión.</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tipo_inspeccion_realizada; subtipo_inspeccion; estado_registro; fotografias_arbol; campos de cavidad; campos de cada subtipo de Monitoreo</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">INSPECCION; REGISTRO_EVALUACION; ARBOLES</t>
         </is>
       </c>
     </row>
@@ -11693,12 +11715,12 @@
     <row r="6" spans="1:10">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.0.1</t>
+          <t xml:space="preserve">2.1.0</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.0</t>
+          <t xml:space="preserve">2.1</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
@@ -11708,7 +11730,7 @@
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">CC-042</t>
+          <t xml:space="preserve">CC-040, CC-042</t>
         </is>
       </c>
       <c r="I6" s="7" t="inlineStr">
@@ -11718,7 +11740,7 @@
       </c>
       <c r="J6" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">PATCH: agrega PROYECTOS.estado_proyecto (Activo / Cerrado) y su regla en REGLAS_GENERALES (Proyectos). El campo no participa en ninguna regla de cálculo: no cambia resultados y rule_version sigue siendo 2.0. NO publicada.</t>
+          <t xml:space="preserve">MINOR: CC-040 cambia los valores con que se calculan las clasificaciones (alcance de la evaluación según el tipo de inspección, evaluación vigente compuesta campo por campo, campos por subtipo de Monitoreo, cavidades internas Sí/No en la instrumental y ajustes del Inspector en el recálculo; REGLAS_GENERALES fila 28, D-209 y D-27; AM-12). Incluye CC-042: PROYECTOS.estado_proyecto (Activo / Cerrado) y REGLAS_GENERALES fila 27. NO publicada.</t>
         </is>
       </c>
     </row>
@@ -14257,14 +14279,18 @@
       <c r="H27" s="50" t="s">
         <v>1438</v>
       </c>
-      <c r="I27" s="50" t="s">
-        <v>1439</v>
+      <c r="I27" s="50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Obligatorio para finalizar la Evaluación inicial, la Reevaluación y el Levantamiento</t>
+        </is>
       </c>
       <c r="J27" s="50" t="s">
         <v>1440</v>
       </c>
-      <c r="K27" s="50" t="s">
-        <v>1441</v>
+      <c r="K27" s="50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">En la inspección de Evaluación inicial, Reevaluación o Levantamiento mediante OT. No aplica en la Evaluación instrumental; en el Monitoreo no es obligatoria.</t>
+        </is>
       </c>
       <c r="L27" s="50" t="s">
         <v>1442</v>
@@ -21388,7 +21414,7 @@
       </c>
       <c r="J209" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Finalizado cuando están completos todos los campos obligatorios y los condicionales activados de la inspección, de su REGISTRO_EVALUACION y de los datos técnicos del árbol registrados en ella; en otro caso, Preguardado. Anulado solo desde Finalizado, cuando el Inspector registra motivo_anulacion.</t>
+          <t xml:space="preserve">Finalizado cuando están completos todos los campos obligatorios y los condicionales activados que exige el tipo de inspección (REGLAS_GENERALES, Preguardado y finalización): evaluación completa en Evaluación inicial, Reevaluación y Levantamiento; campos de cavidad en Evaluación instrumental; campos de su subtipo en Monitoreo. En otro caso, Preguardado. Anulado solo desde Finalizado, cuando el Inspector registra motivo_anulacion.</t>
         </is>
       </c>
       <c r="K209" s="8" t="inlineStr">
@@ -21398,7 +21424,7 @@
       </c>
       <c r="L209" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">No editable manualmente, salvo la anulación por el Inspector. Valor inicial: Preguardado. Una inspección Preguardado o Anulado no modifica la evaluación vigente del árbol. Mientras alguna inspección vinculada esté Preguardado, la OT no puede pasar a estado_ot = Completada. Una medición pendiente no equivale a cero ni a No presenta.</t>
+          <t xml:space="preserve">No editable manualmente, salvo la anulación por el Inspector. Valor inicial: Preguardado. Una inspección Preguardado o Anulado no modifica la evaluación vigente del árbol. Una inspección parcial solo reemplaza los valores vigentes de los campos que registra. Mientras alguna inspección vinculada esté Preguardado, la OT no puede pasar a estado_ot = Completada. Una medición pendiente no equivale a cero ni a No presenta.</t>
         </is>
       </c>
     </row>

--- a/docs/excel/Base de Datos Valpo Verde.xlsx
+++ b/docs/excel/Base de Datos Valpo Verde.xlsx
@@ -11725,7 +11725,12 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">en preparación</t>
+          <t xml:space="preserve">publicada</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-21</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
@@ -11733,6 +11738,21 @@
           <t xml:space="preserve">CC-040, CC-042</t>
         </is>
       </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marybaxmann</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-21</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodologia-v2.1.0</t>
+        </is>
+      </c>
       <c r="I6" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">2.0.0</t>
@@ -11740,7 +11760,7 @@
       </c>
       <c r="J6" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">MINOR: CC-040 cambia los valores con que se calculan las clasificaciones (alcance de la evaluación según el tipo de inspección, evaluación vigente compuesta campo por campo, campos por subtipo de Monitoreo, cavidades internas Sí/No en la instrumental y ajustes del Inspector en el recálculo; REGLAS_GENERALES fila 28, D-209 y D-27; AM-12). Incluye CC-042: PROYECTOS.estado_proyecto (Activo / Cerrado) y REGLAS_GENERALES fila 27. NO publicada.</t>
+          <t xml:space="preserve">MINOR: CC-040 cambia los valores con que se calculan las clasificaciones (alcance de la evaluación según el tipo de inspección, evaluación vigente compuesta campo por campo, campos por subtipo de Monitoreo, cavidades internas Sí/No en la instrumental y ajustes del Inspector en el recálculo; REGLAS_GENERALES fila 28, D-209 y D-27; AM-12). Incluye CC-042: PROYECTOS.estado_proyecto (Activo / Cerrado) y REGLAS_GENERALES fila 27. Publicada el 2026-10-21 (AM-13), antes de la Fase 4.</t>
         </is>
       </c>
     </row>
